--- a/rtss-pre1917/src/main/resources/emigration.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC70D0B-B93A-4232-AF5A-2E2458F18549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F304E72-19C3-49F0-A80D-B22B69647ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="5" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="214">
   <si>
     <t>Источник: ЦСК, "Ежегодник России" ("Статистический Ежегодник России")</t>
   </si>
@@ -686,6 +686,18 @@
   <si>
     <t>% объёма в календарный год сравнительно со среднегодовым за 1896-1900</t>
   </si>
+  <si>
+    <t>среднее за 1896-1900  для расчёта 1881-1895, финская эмиграция из Выборгской губернии в этот период исчезает</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>v-diff</t>
+  </si>
+  <si>
+    <t>###!!!без финляндии</t>
+  </si>
 </sst>
 </file>
 
@@ -874,7 +886,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1190,11 +1204,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E018E8-FFD2-476D-8A98-BDF34A70858D}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.578125" customWidth="1"/>
-    <col min="3" max="3" width="20.83984375" customWidth="1"/>
-    <col min="4" max="4" width="24.578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1207,7 +1221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8">
+    <row r="5" spans="1:5" ht="30">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1766,14 +1780,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7496F63D-12C4-4F78-B39E-C61E39C373AD}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="10.41796875" customWidth="1"/>
-    <col min="5" max="5" width="12.41796875" customWidth="1"/>
-    <col min="6" max="6" width="27.15625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="43.2">
+    <row r="1" spans="1:20" ht="45">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -2410,35 +2424,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54424CF4-C226-4A4F-8C1B-D8A2CB8D4757}">
   <dimension ref="A1:AI310"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.578125" customWidth="1"/>
-    <col min="2" max="2" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.15625" customWidth="1"/>
-    <col min="4" max="4" width="7.578125" customWidth="1"/>
-    <col min="5" max="5" width="5.68359375" customWidth="1"/>
-    <col min="6" max="6" width="9.578125" customWidth="1"/>
-    <col min="7" max="7" width="8.15625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.68359375" customWidth="1"/>
-    <col min="9" max="9" width="7.578125" customWidth="1"/>
-    <col min="10" max="10" width="7.15625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.15625" customWidth="1"/>
-    <col min="13" max="13" width="6.83984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.41796875" customWidth="1"/>
-    <col min="17" max="17" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -17271,13 +17285,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
   <dimension ref="A1:P212"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.41796875" customWidth="1"/>
-    <col min="2" max="2" width="17.41796875" customWidth="1"/>
-    <col min="3" max="3" width="10.68359375" customWidth="1"/>
-    <col min="4" max="4" width="14.26171875" customWidth="1"/>
-    <col min="9" max="9" width="12.26171875" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -17290,7 +17304,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="57.6">
+    <row r="4" spans="1:13" ht="60">
       <c r="A4" s="2" t="s">
         <v>117</v>
       </c>
@@ -18398,7 +18412,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="43.2">
+    <row r="42" spans="1:16" ht="45">
       <c r="A42" s="2" t="s">
         <v>117</v>
       </c>
@@ -20033,7 +20047,7 @@
         <v>302694</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="28.8">
+    <row r="196" spans="1:5" ht="30">
       <c r="A196" s="45" t="s">
         <v>204</v>
       </c>
@@ -20209,14 +20223,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D506FF2-5C72-4314-9474-BB1C48673607}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.68359375" customWidth="1"/>
-    <col min="3" max="3" width="18.83984375" customWidth="1"/>
-    <col min="4" max="4" width="13.83984375" customWidth="1"/>
-    <col min="5" max="5" width="16.83984375" customWidth="1"/>
-    <col min="7" max="7" width="13.26171875" customWidth="1"/>
-    <col min="8" max="8" width="16.41796875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -21012,12 +21026,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
-  <dimension ref="A1:R27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:R37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="13.578125" customWidth="1"/>
-    <col min="15" max="15" width="26.68359375" customWidth="1"/>
-    <col min="16" max="16" width="19.83984375" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -22051,6 +22066,144 @@
       <c r="A27" t="s">
         <v>207</v>
       </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="4">
+        <f>AVERAGE(B2:B6)</f>
+        <v>0.29029344824026204</v>
+      </c>
+      <c r="C31" s="4">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4">
+        <f t="shared" ref="C31:M31" si="0">AVERAGE(D2:D6)</f>
+        <v>4231.1951632577848</v>
+      </c>
+      <c r="E31" s="4">
+        <f t="shared" si="0"/>
+        <v>0.76053690733800128</v>
+      </c>
+      <c r="F31" s="4">
+        <f t="shared" si="0"/>
+        <v>25753.922387578099</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" si="0"/>
+        <v>5811.2768055236984</v>
+      </c>
+      <c r="H31" s="4">
+        <f t="shared" si="0"/>
+        <v>11833.25487288596</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="0"/>
+        <v>665.11834373800025</v>
+      </c>
+      <c r="J31" s="4">
+        <f t="shared" si="0"/>
+        <v>10.241153407602926</v>
+      </c>
+      <c r="K31" s="4">
+        <f t="shared" si="0"/>
+        <v>1011.3841073369298</v>
+      </c>
+      <c r="L31" s="4">
+        <f t="shared" si="0"/>
+        <v>55228.256248743775</v>
+      </c>
+      <c r="M31" s="4">
+        <f t="shared" si="0"/>
+        <v>49.260590808123176</v>
+      </c>
+      <c r="O31" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" t="s">
+        <v>213</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="O37" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22059,149 +22212,1115 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FEA9BB-FB24-45B6-A20A-F26B22290AE7}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:V25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:22">
       <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="36" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T1" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1">
         <v>1881</v>
       </c>
       <c r="B2" s="26">
         <v>16.564583374629162</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="4">
+        <f>C$25*$B2/100</f>
+        <v>4.8085900264844161E-2</v>
+      </c>
+      <c r="D2" s="4">
+        <f t="shared" ref="D2:N16" si="0">D$25*$B2/100</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <f t="shared" si="0"/>
+        <v>700.87985056111222</v>
+      </c>
+      <c r="F2" s="4">
+        <f t="shared" si="0"/>
+        <v>0.12597977011082936</v>
+      </c>
+      <c r="G2" s="4">
+        <f t="shared" si="0"/>
+        <v>4266.02994612766</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" si="0"/>
+        <v>962.61379158145928</v>
+      </c>
+      <c r="I2" s="4">
+        <f t="shared" si="0"/>
+        <v>1960.1293693515629</v>
+      </c>
+      <c r="J2" s="4">
+        <f t="shared" si="0"/>
+        <v>110.17408258843363</v>
+      </c>
+      <c r="K2" s="4">
+        <f t="shared" si="0"/>
+        <v>1.6964043947260623</v>
+      </c>
+      <c r="L2" s="4">
+        <f t="shared" si="0"/>
+        <v>167.53156369757463</v>
+      </c>
+      <c r="M2" s="4">
+        <f t="shared" si="0"/>
+        <v>9148.3305526770018</v>
+      </c>
+      <c r="N2" s="4">
+        <f t="shared" si="0"/>
+        <v>8.1598116352464736</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>10028</v>
+      </c>
+      <c r="V2" s="4">
+        <f>T2-M2</f>
+        <v>879.66944732299817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" s="1">
         <v>1882</v>
       </c>
       <c r="B3" s="26">
         <v>19.924412112562521</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" s="4">
+        <f t="shared" ref="C3:C16" si="1">C$25*$B3/100</f>
+        <v>5.7839262963158181E-2</v>
+      </c>
+      <c r="D3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <f t="shared" si="0"/>
+        <v>843.04076161429361</v>
+      </c>
+      <c r="F3" s="4">
+        <f t="shared" si="0"/>
+        <v>0.15153250768616114</v>
+      </c>
+      <c r="G3" s="4">
+        <f t="shared" si="0"/>
+        <v>5131.3176316505615</v>
+      </c>
+      <c r="H3" s="4">
+        <f t="shared" si="0"/>
+        <v>1157.8627397343</v>
+      </c>
+      <c r="I3" s="4">
+        <f t="shared" si="0"/>
+        <v>2357.706467203685</v>
+      </c>
+      <c r="J3" s="4">
+        <f t="shared" si="0"/>
+        <v>132.52091984260935</v>
+      </c>
+      <c r="K3" s="4">
+        <f t="shared" si="0"/>
+        <v>2.040489610010547</v>
+      </c>
+      <c r="L3" s="4">
+        <f t="shared" si="0"/>
+        <v>201.51233758677157</v>
+      </c>
+      <c r="M3" s="4">
+        <f t="shared" si="0"/>
+        <v>11003.905377581772</v>
+      </c>
+      <c r="N3" s="4">
+        <f t="shared" si="0"/>
+        <v>9.814883121693553</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>12062</v>
+      </c>
+      <c r="V3" s="4">
+        <f t="shared" ref="V3:V16" si="2">T3-M3</f>
+        <v>1058.094622418228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" s="1">
         <v>1883</v>
       </c>
       <c r="B4" s="26">
         <v>24.424831678196462</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" s="4">
+        <f t="shared" si="1"/>
+        <v>7.0903686105516381E-2</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="0"/>
+        <v>1033.4622966017039</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.1857598594678678</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>6290.3521936993056</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>1419.3945781032357</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
+        <v>2890.2525847543766</v>
+      </c>
+      <c r="J4" s="4">
+        <f t="shared" si="0"/>
+        <v>162.45403591881472</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" si="0"/>
+        <v>2.5013844817128956</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" si="0"/>
+        <v>247.02886583707493</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" si="0"/>
+        <v>13489.408627558685</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" si="0"/>
+        <v>12.031816388569204</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>14786.5</v>
+      </c>
+      <c r="V4" s="4">
+        <f t="shared" si="2"/>
+        <v>1297.0913724413149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="1">
         <v>1884</v>
       </c>
       <c r="B5" s="26">
         <v>30.304531969579841</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5" s="4">
+        <f t="shared" si="1"/>
+        <v>8.7972070827565918E-2</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="0"/>
+        <v>1282.2438909447715</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.23047715022469842</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>7804.6056433643853</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="0"/>
+        <v>1761.0802373707074</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
+        <v>3586.0125059955903</v>
+      </c>
+      <c r="J5" s="4">
+        <f t="shared" si="0"/>
+        <v>201.56100111362221</v>
+      </c>
+      <c r="K5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.1035336084607441</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" si="0"/>
+        <v>306.49522014316955</v>
+      </c>
+      <c r="M5" s="4">
+        <f t="shared" si="0"/>
+        <v>16736.664571142035</v>
+      </c>
+      <c r="N5" s="4">
+        <f t="shared" si="0"/>
+        <v>14.928191489851597</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <v>18346</v>
+      </c>
+      <c r="V5" s="4">
+        <f t="shared" si="2"/>
+        <v>1609.3354288579649</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1">
         <v>1885</v>
       </c>
       <c r="B6" s="26">
         <v>38.098706944967525</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6" s="4">
+        <f t="shared" si="1"/>
+        <v>0.11059805012549843</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="0"/>
+        <v>1612.0306455192238</v>
+      </c>
+      <c r="F6" s="4">
+        <f t="shared" si="0"/>
+        <v>0.28975472753502435</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>9811.9114172777645</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="0"/>
+        <v>2214.0213198973443</v>
+      </c>
+      <c r="I6" s="4">
+        <f t="shared" si="0"/>
+        <v>4508.3170960719117</v>
+      </c>
+      <c r="J6" s="4">
+        <f t="shared" si="0"/>
+        <v>253.40148861796246</v>
+      </c>
+      <c r="K6" s="4">
+        <f t="shared" si="0"/>
+        <v>3.9017470245471939</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="0"/>
+        <v>385.32426714227267</v>
+      </c>
+      <c r="M6" s="4">
+        <f t="shared" si="0"/>
+        <v>21041.251499024605</v>
+      </c>
+      <c r="N6" s="4">
+        <f t="shared" si="0"/>
+        <v>18.767648131346458</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>23064.5</v>
+      </c>
+      <c r="V6" s="4">
+        <f t="shared" si="2"/>
+        <v>2023.2485009753946</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1">
         <v>1886</v>
       </c>
       <c r="B7" s="26">
         <v>47.195352402095843</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7" s="4">
+        <f t="shared" si="1"/>
+        <v>0.13700501589718736</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" si="0"/>
+        <v>1996.9274681199461</v>
+      </c>
+      <c r="F7" s="4">
+        <f t="shared" si="0"/>
+        <v>0.3589380735661708</v>
+      </c>
+      <c r="G7" s="4">
+        <f t="shared" si="0"/>
+        <v>12154.65442817974</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" si="0"/>
+        <v>2742.652567428167</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" si="0"/>
+        <v>5584.7463378967077</v>
+      </c>
+      <c r="J7" s="4">
+        <f t="shared" si="0"/>
+        <v>313.90494621813241</v>
+      </c>
+      <c r="K7" s="4">
+        <f t="shared" si="0"/>
+        <v>4.8333484407574483</v>
+      </c>
+      <c r="L7" s="4">
+        <f t="shared" si="0"/>
+        <v>477.32629359645529</v>
+      </c>
+      <c r="M7" s="4">
+        <f t="shared" si="0"/>
+        <v>26065.170162127142</v>
+      </c>
+      <c r="N7" s="4">
+        <f t="shared" si="0"/>
+        <v>23.248709427248162</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>28571.5</v>
+      </c>
+      <c r="V7" s="4">
+        <f t="shared" si="2"/>
+        <v>2506.3298378728578</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1">
         <v>1887</v>
       </c>
       <c r="B8" s="26">
         <v>56.825539984274542</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8" s="4">
+        <f t="shared" si="1"/>
+        <v>0.16496081950149943</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>2404.3994993097426</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="0"/>
+        <v>0.43217920437452095</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="0"/>
+        <v>14634.805463872226</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="0"/>
+        <v>3302.2894247197419</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>6724.3109792329269</v>
+      </c>
+      <c r="J8" s="4">
+        <f t="shared" si="0"/>
+        <v>377.95709036358198</v>
+      </c>
+      <c r="K8" s="4">
+        <f t="shared" si="0"/>
+        <v>5.8195907244882958</v>
+      </c>
+      <c r="L8" s="4">
+        <f t="shared" si="0"/>
+        <v>574.72448030934515</v>
+      </c>
+      <c r="M8" s="4">
+        <f t="shared" si="0"/>
+        <v>31383.754837247496</v>
+      </c>
+      <c r="N8" s="4">
+        <f t="shared" si="0"/>
+        <v>27.992596726159903</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>34401.5</v>
+      </c>
+      <c r="V8" s="4">
+        <f t="shared" si="2"/>
+        <v>3017.7451627525043</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1">
         <v>1888</v>
       </c>
       <c r="B9" s="26">
         <v>67.303943916959042</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9" s="4">
+        <f t="shared" si="1"/>
+        <v>0.19537893959823249</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="0"/>
+        <v>2847.7612196961027</v>
+      </c>
+      <c r="F9" s="4">
+        <f t="shared" si="0"/>
+        <v>0.51187133358254311</v>
+      </c>
+      <c r="G9" s="4">
+        <f t="shared" si="0"/>
+        <v>17333.405480152724</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="0"/>
+        <v>3911.2184820489188</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" si="0"/>
+        <v>7964.24722319799</v>
+      </c>
+      <c r="J9" s="4">
+        <f t="shared" si="0"/>
+        <v>447.65087705083056</v>
+      </c>
+      <c r="K9" s="4">
+        <f t="shared" si="0"/>
+        <v>6.892700145902813</v>
+      </c>
+      <c r="L9" s="4">
+        <f t="shared" si="0"/>
+        <v>680.70139238708407</v>
+      </c>
+      <c r="M9" s="4">
+        <f t="shared" si="0"/>
+        <v>37170.794611968937</v>
+      </c>
+      <c r="N9" s="4">
+        <f t="shared" si="0"/>
+        <v>33.154320410661903</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <v>40745</v>
+      </c>
+      <c r="V9" s="4">
+        <f t="shared" si="2"/>
+        <v>3574.2053880310632</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="1">
         <v>1889</v>
       </c>
       <c r="B10" s="26">
         <v>78.685900612499751</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10" s="4">
+        <f t="shared" si="1"/>
+        <v>0.228420014166931</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
+        <v>3329.3540208819172</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="0"/>
+        <v>0.59843531502935898</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="0"/>
+        <v>20264.705773710026</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="0"/>
+        <v>4572.6554915116276</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="0"/>
+        <v>9311.1031685028302</v>
+      </c>
+      <c r="J10" s="4">
+        <f t="shared" si="0"/>
+        <v>523.35435890918734</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" si="0"/>
+        <v>8.0583437918800698</v>
+      </c>
+      <c r="L10" s="4">
+        <f t="shared" si="0"/>
+        <v>795.81669350975437</v>
+      </c>
+      <c r="M10" s="4">
+        <f t="shared" si="0"/>
+        <v>43456.850821903208</v>
+      </c>
+      <c r="N10" s="4">
+        <f t="shared" si="0"/>
+        <v>38.761139524409991</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <v>47635.5</v>
+      </c>
+      <c r="V10" s="4">
+        <f t="shared" si="2"/>
+        <v>4178.6491780967917</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1">
         <v>1890</v>
       </c>
       <c r="B11" s="26">
         <v>91.885699749582088</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="C11" s="4">
+        <f t="shared" si="1"/>
+        <v>0.26673816624275565</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="0"/>
+        <v>3887.8632835298877</v>
+      </c>
+      <c r="F11" s="4">
+        <f t="shared" si="0"/>
+        <v>0.69882465916135317</v>
+      </c>
+      <c r="G11" s="4">
+        <f t="shared" si="0"/>
+        <v>23664.171798790412</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" si="0"/>
+        <v>5339.7323571406105</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="0"/>
+        <v>10873.069043102785</v>
+      </c>
+      <c r="J11" s="4">
+        <f t="shared" si="0"/>
+        <v>611.1486443064922</v>
+      </c>
+      <c r="K11" s="4">
+        <f t="shared" si="0"/>
+        <v>9.4101554710041189</v>
+      </c>
+      <c r="L11" s="4">
+        <f t="shared" si="0"/>
+        <v>929.31736418260232</v>
+      </c>
+      <c r="M11" s="4">
+        <f t="shared" si="0"/>
+        <v>50746.869713650514</v>
+      </c>
+      <c r="N11" s="4">
+        <f t="shared" si="0"/>
+        <v>45.263438564822287</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4">
+        <v>55626.5</v>
+      </c>
+      <c r="V11" s="4">
+        <f t="shared" si="2"/>
+        <v>4879.6302863494857</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1">
         <v>1891</v>
       </c>
       <c r="B12" s="26">
         <v>103.17019828605787</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12" s="4">
+        <f t="shared" si="1"/>
+        <v>0.2994963261609131</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="0"/>
+        <v>4365.3324398031464</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="0"/>
+        <v>0.78464743533926806</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="0"/>
+        <v>26570.372793701776</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="0"/>
+        <v>5995.5058032104889</v>
+      </c>
+      <c r="I12" s="4">
+        <f t="shared" si="0"/>
+        <v>12208.392516051048</v>
+      </c>
+      <c r="J12" s="4">
+        <f t="shared" si="0"/>
+        <v>686.20391407143882</v>
+      </c>
+      <c r="K12" s="4">
+        <f t="shared" si="0"/>
+        <v>10.565818277403311</v>
+      </c>
+      <c r="L12" s="4">
+        <f t="shared" si="0"/>
+        <v>1043.4469889731868</v>
+      </c>
+      <c r="M12" s="4">
+        <f t="shared" si="0"/>
+        <v>56979.101481761092</v>
+      </c>
+      <c r="N12" s="4">
+        <f t="shared" si="0"/>
+        <v>50.822249213624275</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4">
+        <v>62458</v>
+      </c>
+      <c r="V12" s="4">
+        <f t="shared" si="2"/>
+        <v>5478.8985182389079</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1">
         <v>1892</v>
       </c>
       <c r="B13" s="26">
         <v>108.41724646012143</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13" s="4">
+        <f t="shared" si="1"/>
+        <v>0.31472816323622993</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="0"/>
+        <v>4587.3452883579293</v>
+      </c>
+      <c r="F13" s="4">
+        <f t="shared" si="0"/>
+        <v>0.82455317324882627</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="0"/>
+        <v>27921.693508088938</v>
+      </c>
+      <c r="H13" s="4">
+        <f t="shared" si="0"/>
+        <v>6300.4262967245004</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="0"/>
+        <v>12829.289099791102</v>
+      </c>
+      <c r="J13" s="4">
+        <f t="shared" si="0"/>
+        <v>721.10299398190534</v>
+      </c>
+      <c r="K13" s="4">
+        <f t="shared" si="0"/>
+        <v>11.103176530279988</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" si="0"/>
+        <v>1096.5148003099782</v>
+      </c>
+      <c r="M13" s="4">
+        <f t="shared" si="0"/>
+        <v>59876.95469282796</v>
+      </c>
+      <c r="N13" s="4">
+        <f t="shared" si="0"/>
+        <v>53.406976144154832</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4">
+        <v>65634.5</v>
+      </c>
+      <c r="V13" s="4">
+        <f t="shared" si="2"/>
+        <v>5757.5453071720403</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="1">
         <v>1893</v>
       </c>
       <c r="B14" s="26">
         <v>108.00098449258988</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="C14" s="4">
+        <f t="shared" si="1"/>
+        <v>0.31351978201696984</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="0"/>
+        <v>4569.7324321212536</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.82138734735453733</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="0"/>
+        <v>27814.489724041858</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="0"/>
+        <v>6276.2361615551217</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>12780.031760234202</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="0"/>
+        <v>718.33435927784831</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="0"/>
+        <v>11.060546503607577</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="0"/>
+        <v>1092.304792925476</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="0"/>
+        <v>59647.060466733565</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="0"/>
+        <v>53.201923039639269</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <v>65382.5</v>
+      </c>
+      <c r="V14" s="4">
+        <f t="shared" si="2"/>
+        <v>5735.4395332664353</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1">
         <v>1894</v>
       </c>
       <c r="B15" s="26">
         <v>102.04777762360668</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="C15" s="4">
+        <f t="shared" si="1"/>
+        <v>0.29623801251612236</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="0"/>
+        <v>4317.8406310221062</v>
+      </c>
+      <c r="F15" s="4">
+        <f t="shared" si="0"/>
+        <v>0.77611101194573906</v>
+      </c>
+      <c r="G15" s="4">
+        <f t="shared" si="0"/>
+        <v>26281.305447431951</v>
+      </c>
+      <c r="H15" s="4">
+        <f t="shared" si="0"/>
+        <v>5930.2788315930575</v>
+      </c>
+      <c r="I15" s="4">
+        <f t="shared" si="0"/>
+        <v>12075.573618317265</v>
+      </c>
+      <c r="J15" s="4">
+        <f t="shared" si="0"/>
+        <v>678.73848835157037</v>
+      </c>
+      <c r="K15" s="4">
+        <f t="shared" si="0"/>
+        <v>10.450869455483053</v>
+      </c>
+      <c r="L15" s="4">
+        <f t="shared" si="0"/>
+        <v>1032.0950047756896</v>
+      </c>
+      <c r="M15" s="4">
+        <f t="shared" si="0"/>
+        <v>56359.208122113712</v>
+      </c>
+      <c r="N15" s="4">
+        <f t="shared" si="0"/>
+        <v>50.269338163948369</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>61778.5</v>
+      </c>
+      <c r="V15" s="4">
+        <f t="shared" si="2"/>
+        <v>5419.2918778862877</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1">
         <v>1895</v>
       </c>
       <c r="B16" s="26">
         <v>89.260110871044688</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="C16" s="4">
+        <f t="shared" si="1"/>
+        <v>0.25911625375063663</v>
+      </c>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="0"/>
+        <v>3776.769493894179</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="0"/>
+        <v>0.67885608670511433</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="0"/>
+        <v>22987.97967679501</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="0"/>
+        <v>5187.1521196337571</v>
+      </c>
+      <c r="I16" s="4">
+        <f t="shared" si="0"/>
+        <v>10562.376419191307</v>
+      </c>
+      <c r="J16" s="4">
+        <f t="shared" si="0"/>
+        <v>593.68537104419511</v>
+      </c>
+      <c r="K16" s="4">
+        <f t="shared" si="0"/>
+        <v>9.141264886100144</v>
+      </c>
+      <c r="L16" s="4">
+        <f t="shared" si="0"/>
+        <v>902.76257554106905</v>
+      </c>
+      <c r="M16" s="4">
+        <f t="shared" si="0"/>
+        <v>49296.80275977336</v>
+      </c>
+      <c r="N16" s="4">
+        <f t="shared" si="0"/>
+        <v>43.970057971062396</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>54037</v>
+      </c>
+      <c r="V16" s="4">
+        <f t="shared" si="2"/>
+        <v>4740.1972402266401</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="47" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="49" t="s">
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0.29029344824026204</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>4231.1951632577848</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0.76053690733800128</v>
+      </c>
+      <c r="G25" s="4">
+        <v>25753.922387578099</v>
+      </c>
+      <c r="H25" s="4">
+        <v>5811.2768055236984</v>
+      </c>
+      <c r="I25" s="4">
+        <v>11833.25487288596</v>
+      </c>
+      <c r="J25" s="4">
+        <v>665.11834373800025</v>
+      </c>
+      <c r="K25" s="4">
+        <v>10.241153407602926</v>
+      </c>
+      <c r="L25" s="4">
+        <v>1011.3841073369298</v>
+      </c>
+      <c r="M25" s="4">
+        <v>55228.256248743775</v>
+      </c>
+      <c r="N25" s="4">
+        <v>49.260590808123176</v>
+      </c>
+      <c r="P25" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/rtss-pre1917/src/main/resources/emigration.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F304E72-19C3-49F0-A80D-B22B69647ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42B11D4-9F4F-4163-91FB-3732AA17827C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="5" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="data-1896-1916" sheetId="4" r:id="rId6"/>
     <sheet name="data-1881-1895" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,12 +29,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="216">
   <si>
     <t>Источник: ЦСК, "Ежегодник России" ("Статистический Ежегодник России")</t>
   </si>
@@ -645,17 +640,6 @@
     <t>Эмиграция из России в различные страны (для США - по финансовым годам)</t>
   </si>
   <si>
-    <t>Эмиграция из России в различные страны (для США - по финансовым годам) с поправкой на более учёт эмиграции</t>
-  </si>
-  <si>
-    <t>из русской Польши (см. приложение № 2 к pre1917.docx/pdf)</t>
-  </si>
-  <si>
-    <t>уточнение
-рус. Польша
-в США</t>
-  </si>
-  <si>
     <t>объём, чел.</t>
   </si>
   <si>
@@ -698,6 +682,29 @@
   <si>
     <t>###!!!без финляндии</t>
   </si>
+  <si>
+    <t>Эмиграция из России в различные страны (для США - по финансовым годам) с поправкой на более точный учёт эмиграции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">из русской Польши (см. приложение № 2 к pre1917.docx/pdf) и на вычет эмиграции из Финляндии (см. приложение № 4 к pre1917.docx/pdf) </t>
+  </si>
+  <si>
+    <t>минус
+Финляндия в США</t>
+  </si>
+  <si>
+    <t>плюс
+уточнение
+рус. Польша
+в США</t>
+  </si>
+  <si>
+    <t>Россия без
+Финляндии
+с русской
+Польшей
+в США</t>
+  </si>
 </sst>
 </file>
 
@@ -708,7 +715,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -782,7 +789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -883,12 +890,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -907,9 +915,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -947,7 +955,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1053,7 +1061,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1195,7 +1203,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1204,24 +1212,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E018E8-FFD2-476D-8A98-BDF34A70858D}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1233,7 +1241,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>1904</v>
       </c>
@@ -1244,7 +1252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>1906</v>
       </c>
@@ -1255,7 +1263,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>1909</v>
       </c>
@@ -1266,7 +1274,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>1910</v>
       </c>
@@ -1277,7 +1285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>1911</v>
       </c>
@@ -1288,7 +1296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>1912</v>
       </c>
@@ -1299,7 +1307,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>1913</v>
       </c>
@@ -1310,162 +1318,162 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>53</v>
       </c>
@@ -1473,7 +1481,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B60" s="1">
         <v>1896</v>
       </c>
@@ -1481,7 +1489,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B61" s="1">
         <f>B60+1</f>
         <v>1897</v>
@@ -1490,7 +1498,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B62" s="1">
         <f t="shared" ref="B62:B80" si="0">B61+1</f>
         <v>1898</v>
@@ -1499,7 +1507,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B63" s="1">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -1508,7 +1516,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B64" s="1">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -1517,7 +1525,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="2:3">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -1526,7 +1534,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="2:3">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -1535,7 +1543,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="2:3">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="1">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -1544,7 +1552,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="2:3">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="1">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -1553,7 +1561,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="2:3">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="1">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -1562,7 +1570,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="2:3">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="1">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -1571,7 +1579,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="2:3">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="1">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -1580,7 +1588,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="2:3">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="1">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -1589,7 +1597,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="2:3">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="1">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -1598,7 +1606,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="2:3">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="1">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -1607,7 +1615,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="2:3">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="1">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -1616,7 +1624,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="2:3">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="1">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -1625,7 +1633,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="2:3">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="1">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -1634,7 +1642,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="78" spans="2:3">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="1">
         <f t="shared" si="0"/>
         <v>1914</v>
@@ -1643,7 +1651,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="79" spans="2:3">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="1">
         <f t="shared" si="0"/>
         <v>1915</v>
@@ -1652,7 +1660,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="2:3">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="1">
         <f t="shared" si="0"/>
         <v>1916</v>
@@ -1661,7 +1669,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B81" s="1">
         <v>1917</v>
       </c>
@@ -1669,22 +1677,22 @@
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B88" s="1">
         <v>1908</v>
       </c>
@@ -1692,7 +1700,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B89" s="1">
         <f t="shared" ref="B89:B96" si="1">B88+1</f>
         <v>1909</v>
@@ -1701,7 +1709,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B90" s="1">
         <f t="shared" si="1"/>
         <v>1910</v>
@@ -1710,7 +1718,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B91" s="1">
         <f t="shared" si="1"/>
         <v>1911</v>
@@ -1719,7 +1727,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B92" s="1">
         <f t="shared" si="1"/>
         <v>1912</v>
@@ -1728,7 +1736,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B93" s="1">
         <f t="shared" si="1"/>
         <v>1913</v>
@@ -1737,7 +1745,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B94" s="1">
         <f t="shared" si="1"/>
         <v>1914</v>
@@ -1746,7 +1754,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B95" s="1">
         <f t="shared" si="1"/>
         <v>1915</v>
@@ -1755,7 +1763,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B96" s="1">
         <f t="shared" si="1"/>
         <v>1916</v>
@@ -1764,7 +1772,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="97" spans="2:3">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="1">
         <v>1917</v>
       </c>
@@ -1780,14 +1788,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7496F63D-12C4-4F78-B39E-C61E39C373AD}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" customWidth="1"/>
     <col min="6" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45">
+    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -1828,7 +1836,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1896</v>
       </c>
@@ -1871,7 +1879,7 @@
         <v>52136</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>1897</v>
@@ -1913,7 +1921,7 @@
         <v>29981</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A22" si="3">A3+1</f>
         <v>1898</v>
@@ -1955,7 +1963,7 @@
         <v>34554</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -1979,7 +1987,7 @@
         <v>57773.68421052632</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -2003,7 +2011,7 @@
         <v>82289.473684210534</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -2027,7 +2035,7 @@
         <v>79218.947368421053</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -2051,7 +2059,7 @@
         <v>98398.947368421053</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -2075,7 +2083,7 @@
         <v>123398.94736842105</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -2099,7 +2107,7 @@
         <v>142088.42105263157</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -2123,7 +2131,7 @@
         <v>176721.05263157896</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -2147,7 +2155,7 @@
         <v>212135.78947368421</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -2171,7 +2179,7 @@
         <v>256929.47368421053</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -2195,7 +2203,7 @@
         <v>157857.89473684211</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -2219,7 +2227,7 @@
         <v>114497.89473684211</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -2243,7 +2251,7 @@
         <v>180058.94736842107</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -2267,7 +2275,7 @@
         <v>156781.05263157896</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -2291,7 +2299,7 @@
         <v>163951.57894736843</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -2315,7 +2323,7 @@
         <v>292930.5263157895</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -2339,7 +2347,7 @@
         <v>255636.84210526317</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -2363,7 +2371,7 @@
         <v>23910.526315789473</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -2387,7 +2395,7 @@
         <v>2308.4210526315792</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2412,7 +2420,7 @@
         <v>2687088.4210526319</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
@@ -2424,7 +2432,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54424CF4-C226-4A4F-8C1B-D8A2CB8D4757}">
   <dimension ref="A1:AI310"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -2455,27 +2463,27 @@
     <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -2483,7 +2491,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="P9" s="14" t="s">
         <v>71</v>
       </c>
@@ -2516,7 +2524,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>84</v>
       </c>
@@ -2599,7 +2607,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1896</v>
       </c>
@@ -2653,7 +2661,7 @@
       </c>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f>A11+1</f>
         <v>1897</v>
@@ -2708,7 +2716,7 @@
       </c>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" ref="A13:A31" si="2">A12+1</f>
         <v>1898</v>
@@ -2763,7 +2771,7 @@
       </c>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>1899</v>
@@ -2861,7 +2869,7 @@
         <v>4.3528753924899997</v>
       </c>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>1900</v>
@@ -2959,7 +2967,7 @@
         <v>5.6415392085457636</v>
       </c>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>1901</v>
@@ -3057,7 +3065,7 @@
         <v>2.5448767286540708</v>
       </c>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1902</v>
@@ -3155,7 +3163,7 @@
         <v>3.0960917891717461</v>
       </c>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1903</v>
@@ -3253,7 +3261,7 @@
         <v>1.9799110237312059</v>
       </c>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1904</v>
@@ -3351,7 +3359,7 @@
         <v>1.427190352127677</v>
       </c>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>1905</v>
@@ -3449,7 +3457,7 @@
         <v>1.1078286558345642</v>
       </c>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>1906</v>
@@ -3547,7 +3555,7 @@
         <v>1.61159938769543</v>
       </c>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>1907</v>
@@ -3645,7 +3653,7 @@
         <v>2.650444548432382</v>
       </c>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>1908</v>
@@ -3743,7 +3751,7 @@
         <v>1.6072463326115465</v>
       </c>
     </row>
-    <row r="24" spans="1:35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>1909</v>
@@ -3841,7 +3849,7 @@
         <v>1.6887644302205966</v>
       </c>
     </row>
-    <row r="25" spans="1:35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>1910</v>
@@ -3939,7 +3947,7 @@
         <v>2.6865499548398257</v>
       </c>
     </row>
-    <row r="26" spans="1:35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>1911</v>
@@ -4037,7 +4045,7 @@
         <v>1.5918358446542664</v>
       </c>
     </row>
-    <row r="27" spans="1:35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>1912</v>
@@ -4135,7 +4143,7 @@
         <v>1.3100851238884845</v>
       </c>
     </row>
-    <row r="28" spans="1:35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>1913</v>
@@ -4233,7 +4241,7 @@
         <v>2.3027080052662829</v>
       </c>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>1914</v>
@@ -4331,7 +4339,7 @@
         <v>2.0608548525781489</v>
       </c>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>1915</v>
@@ -4429,7 +4437,7 @@
         <v>0.49870172690928577</v>
       </c>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>1916</v>
@@ -4527,7 +4535,7 @@
         <v>1.3926559566033798</v>
       </c>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>1917</v>
       </c>
@@ -4624,7 +4632,7 @@
         <v>5.8184812868690303E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="P33" s="17">
         <f>SUM(P14:P31)-P32</f>
         <v>0</v>
@@ -4667,7 +4675,7 @@
       </c>
       <c r="AI33" s="4"/>
     </row>
-    <row r="34" spans="1:35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4720,7 +4728,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -4773,12 +4781,12 @@
         <v>0.1375376540970189</v>
       </c>
     </row>
-    <row r="38" spans="1:35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>87</v>
       </c>
@@ -4822,7 +4830,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>1896</v>
       </c>
@@ -4879,7 +4887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <f>A41+1</f>
         <v>1897</v>
@@ -4937,7 +4945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <f t="shared" ref="A43:A60" si="17">A42+1</f>
         <v>1898</v>
@@ -4995,7 +5003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <f t="shared" si="17"/>
         <v>1899</v>
@@ -5053,7 +5061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <f t="shared" si="17"/>
         <v>1900</v>
@@ -5111,7 +5119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="17"/>
         <v>1901</v>
@@ -5169,7 +5177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="17"/>
         <v>1902</v>
@@ -5227,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <f t="shared" si="17"/>
         <v>1903</v>
@@ -5285,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <f t="shared" si="17"/>
         <v>1904</v>
@@ -5343,7 +5351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <f t="shared" si="17"/>
         <v>1905</v>
@@ -5401,7 +5409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <f t="shared" si="17"/>
         <v>1906</v>
@@ -5459,7 +5467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <f t="shared" si="17"/>
         <v>1907</v>
@@ -5517,7 +5525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <f t="shared" si="17"/>
         <v>1908</v>
@@ -5575,7 +5583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <f t="shared" si="17"/>
         <v>1909</v>
@@ -5633,7 +5641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <f t="shared" si="17"/>
         <v>1910</v>
@@ -5691,7 +5699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <f t="shared" si="17"/>
         <v>1911</v>
@@ -5749,7 +5757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <f t="shared" si="17"/>
         <v>1912</v>
@@ -5807,7 +5815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <f t="shared" si="17"/>
         <v>1913</v>
@@ -5865,7 +5873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <f t="shared" si="17"/>
         <v>1914</v>
@@ -5923,7 +5931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <f t="shared" si="17"/>
         <v>1915</v>
@@ -5981,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>1916</v>
       </c>
@@ -6038,7 +6046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>49</v>
       </c>
@@ -6095,7 +6103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>88</v>
       </c>
@@ -6148,12 +6156,12 @@
         <v>0.12899442300236147</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>84</v>
       </c>
@@ -6194,7 +6202,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>1908</v>
       </c>
@@ -6236,7 +6244,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <f t="shared" ref="A70:A76" si="39">A69+1</f>
         <v>1909</v>
@@ -6279,7 +6287,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <f t="shared" si="39"/>
         <v>1910</v>
@@ -6322,7 +6330,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <f t="shared" si="39"/>
         <v>1911</v>
@@ -6348,7 +6356,7 @@
       </c>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <f t="shared" si="39"/>
         <v>1912</v>
@@ -6391,7 +6399,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <f t="shared" si="39"/>
         <v>1913</v>
@@ -6417,7 +6425,7 @@
       </c>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <f t="shared" si="39"/>
         <v>1914</v>
@@ -6460,7 +6468,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <f t="shared" si="39"/>
         <v>1915</v>
@@ -6512,7 +6520,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>1916</v>
       </c>
@@ -6562,7 +6570,7 @@
         <v>1.1658168920416758</v>
       </c>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>1917</v>
       </c>
@@ -6592,12 +6600,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>84</v>
       </c>
@@ -6638,7 +6646,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>1908</v>
       </c>
@@ -6680,7 +6688,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <f t="shared" ref="A84:A90" si="41">A83+1</f>
         <v>1909</v>
@@ -6723,7 +6731,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <f t="shared" si="41"/>
         <v>1910</v>
@@ -6766,7 +6774,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <f t="shared" si="41"/>
         <v>1911</v>
@@ -6792,7 +6800,7 @@
       </c>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <f t="shared" si="41"/>
         <v>1912</v>
@@ -6835,7 +6843,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <f t="shared" si="41"/>
         <v>1913</v>
@@ -6861,7 +6869,7 @@
       </c>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <f t="shared" si="41"/>
         <v>1914</v>
@@ -6904,7 +6912,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <f t="shared" si="41"/>
         <v>1915</v>
@@ -6947,7 +6955,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>1916</v>
       </c>
@@ -6989,7 +6997,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>1917</v>
       </c>
@@ -7014,12 +7022,12 @@
       </c>
       <c r="M92" s="4"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
@@ -7057,7 +7065,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>143</v>
       </c>
@@ -7110,7 +7118,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>144</v>
       </c>
@@ -7163,7 +7171,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>145</v>
       </c>
@@ -7216,7 +7224,7 @@
         <v>54.280155642023345</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B100" s="26"/>
       <c r="C100" s="26"/>
       <c r="D100" s="26"/>
@@ -7230,7 +7238,7 @@
       <c r="L100" s="26"/>
       <c r="M100" s="26"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>152</v>
       </c>
@@ -7247,7 +7255,7 @@
       <c r="L101" s="26"/>
       <c r="M101" s="26"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B102" s="26"/>
       <c r="C102" s="26"/>
       <c r="D102" s="26"/>
@@ -7261,7 +7269,7 @@
       <c r="L102" s="26"/>
       <c r="M102" s="26"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B103" s="10" t="s">
         <v>70</v>
       </c>
@@ -7299,7 +7307,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>143</v>
       </c>
@@ -7352,7 +7360,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>144</v>
       </c>
@@ -7405,7 +7413,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>145</v>
       </c>
@@ -7458,7 +7466,7 @@
         <v>47.149894440534837</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B107" s="26"/>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
@@ -7472,7 +7480,7 @@
       <c r="L107" s="26"/>
       <c r="M107" s="26"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>153</v>
       </c>
@@ -7489,7 +7497,7 @@
       <c r="L108" s="26"/>
       <c r="M108" s="26"/>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>154</v>
       </c>
@@ -7506,7 +7514,7 @@
       <c r="L109" s="26"/>
       <c r="M109" s="26"/>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B110" s="26"/>
       <c r="C110" s="26"/>
       <c r="D110" s="26"/>
@@ -7520,7 +7528,7 @@
       <c r="L110" s="26"/>
       <c r="M110" s="26"/>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
@@ -7558,7 +7566,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B112" s="26">
         <f>B106</f>
         <v>6.9984447900466566</v>
@@ -7608,12 +7616,12 @@
         <v>50.715025041279091</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>84</v>
       </c>
@@ -7660,7 +7668,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>1896</v>
       </c>
@@ -7717,7 +7725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <f>A117+1</f>
         <v>1897</v>
@@ -7775,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <f t="shared" ref="A119:A137" si="54">A118+1</f>
         <v>1898</v>
@@ -7833,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <f t="shared" si="54"/>
         <v>1899</v>
@@ -7891,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <f t="shared" si="54"/>
         <v>1900</v>
@@ -7949,7 +7957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <f t="shared" si="54"/>
         <v>1901</v>
@@ -8007,7 +8015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <f t="shared" si="54"/>
         <v>1902</v>
@@ -8065,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <f t="shared" si="54"/>
         <v>1903</v>
@@ -8123,7 +8131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <f t="shared" si="54"/>
         <v>1904</v>
@@ -8181,7 +8189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <f t="shared" si="54"/>
         <v>1905</v>
@@ -8239,7 +8247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <f t="shared" si="54"/>
         <v>1906</v>
@@ -8297,7 +8305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <f t="shared" si="54"/>
         <v>1907</v>
@@ -8355,7 +8363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <f t="shared" si="54"/>
         <v>1908</v>
@@ -8402,7 +8410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <f t="shared" si="54"/>
         <v>1909</v>
@@ -8449,7 +8457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <f t="shared" si="54"/>
         <v>1910</v>
@@ -8496,7 +8504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <f t="shared" si="54"/>
         <v>1911</v>
@@ -8554,7 +8562,7 @@
         <v>15723.438359773389</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <f t="shared" si="54"/>
         <v>1912</v>
@@ -8601,7 +8609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <f t="shared" si="54"/>
         <v>1913</v>
@@ -8659,7 +8667,7 @@
         <v>36173.276557684701</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <f t="shared" si="54"/>
         <v>1914</v>
@@ -8706,7 +8714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <f t="shared" si="54"/>
         <v>1915</v>
@@ -8753,7 +8761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <f t="shared" si="54"/>
         <v>1916</v>
@@ -8800,7 +8808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>1917</v>
       </c>
@@ -8857,7 +8865,7 @@
         <v>639.69124188047317</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -8872,7 +8880,7 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="30" t="s">
         <v>174</v>
       </c>
@@ -8889,7 +8897,7 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -8904,7 +8912,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>1911</v>
       </c>
@@ -8945,7 +8953,7 @@
         <v>-11.876056132993654</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <f>A142+1</f>
         <v>1912</v>
@@ -8963,7 +8971,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <f t="shared" ref="A144:A148" si="74">A143+1</f>
         <v>1913</v>
@@ -9005,7 +9013,7 @@
         <v>116.94950349421394</v>
       </c>
     </row>
-    <row r="145" spans="1:15">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <f t="shared" si="74"/>
         <v>1914</v>
@@ -9023,7 +9031,7 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
     </row>
-    <row r="146" spans="1:15">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <f t="shared" si="74"/>
         <v>1915</v>
@@ -9041,7 +9049,7 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
     </row>
-    <row r="147" spans="1:15">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <f t="shared" si="74"/>
         <v>1916</v>
@@ -9059,7 +9067,7 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
     </row>
-    <row r="148" spans="1:15">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <f t="shared" si="74"/>
         <v>1917</v>
@@ -9101,7 +9109,7 @@
         <v>218.84913831012869</v>
       </c>
     </row>
-    <row r="149" spans="1:15">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -9116,7 +9124,7 @@
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
     </row>
-    <row r="150" spans="1:15">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="30" t="s">
         <v>172</v>
       </c>
@@ -9133,7 +9141,7 @@
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
     </row>
-    <row r="151" spans="1:15">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -9148,7 +9156,7 @@
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
     </row>
-    <row r="152" spans="1:15">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="str">
         <f t="shared" ref="A152:M152" si="76">A116</f>
         <v>фин. год</v>
@@ -9207,7 +9215,7 @@
         <v>разница</v>
       </c>
     </row>
-    <row r="153" spans="1:15">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <f t="shared" ref="A153:M153" si="77">A117</f>
         <v>1896</v>
@@ -9266,7 +9274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:15">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <f t="shared" ref="A154:M154" si="79">A118</f>
         <v>1897</v>
@@ -9325,7 +9333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <f t="shared" ref="A155:M155" si="80">A119</f>
         <v>1898</v>
@@ -9384,7 +9392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <f t="shared" ref="A156:M156" si="81">A120</f>
         <v>1899</v>
@@ -9443,7 +9451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <f t="shared" ref="A157:M157" si="82">A121</f>
         <v>1900</v>
@@ -9502,7 +9510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <f t="shared" ref="A158:M158" si="83">A122</f>
         <v>1901</v>
@@ -9561,7 +9569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:15">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <f t="shared" ref="A159:M159" si="84">A123</f>
         <v>1902</v>
@@ -9620,7 +9628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <f t="shared" ref="A160:M160" si="85">A124</f>
         <v>1903</v>
@@ -9679,7 +9687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <f t="shared" ref="A161:M161" si="86">A125</f>
         <v>1904</v>
@@ -9738,7 +9746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <f t="shared" ref="A162:M162" si="87">A126</f>
         <v>1905</v>
@@ -9797,7 +9805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <f t="shared" ref="A163:M163" si="88">A127</f>
         <v>1906</v>
@@ -9856,7 +9864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <f t="shared" ref="A164:M164" si="89">A128</f>
         <v>1907</v>
@@ -9915,7 +9923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <f t="shared" ref="A165:M165" si="90">A129</f>
         <v>1908</v>
@@ -9974,7 +9982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <f t="shared" ref="A166:M166" si="91">A130</f>
         <v>1909</v>
@@ -10033,7 +10041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <f t="shared" ref="A167:M167" si="92">A131</f>
         <v>1910</v>
@@ -10092,7 +10100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:15">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <f t="shared" ref="A168:A174" si="93">A132</f>
         <v>1911</v>
@@ -10151,7 +10159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:15">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <f t="shared" si="93"/>
         <v>1912</v>
@@ -10210,7 +10218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <f t="shared" si="93"/>
         <v>1913</v>
@@ -10269,7 +10277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <f t="shared" si="93"/>
         <v>1914</v>
@@ -10328,7 +10336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <f t="shared" si="93"/>
         <v>1915</v>
@@ -10387,7 +10395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <f t="shared" si="93"/>
         <v>1916</v>
@@ -10446,7 +10454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <f t="shared" si="93"/>
         <v>1917</v>
@@ -10505,12 +10513,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
         <v>84</v>
       </c>
@@ -10554,7 +10562,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>1896</v>
       </c>
@@ -10612,7 +10620,7 @@
       </c>
       <c r="P179" s="4"/>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <f>A179+1</f>
         <v>1897</v>
@@ -10671,7 +10679,7 @@
       </c>
       <c r="P180" s="4"/>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <f t="shared" ref="A181:A199" si="104">A180+1</f>
         <v>1898</v>
@@ -10730,7 +10738,7 @@
       </c>
       <c r="P181" s="4"/>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <f t="shared" si="104"/>
         <v>1899</v>
@@ -10789,7 +10797,7 @@
       </c>
       <c r="P182" s="4"/>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <f t="shared" si="104"/>
         <v>1900</v>
@@ -10848,7 +10856,7 @@
       </c>
       <c r="P183" s="4"/>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <f t="shared" si="104"/>
         <v>1901</v>
@@ -10907,7 +10915,7 @@
       </c>
       <c r="P184" s="4"/>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <f t="shared" si="104"/>
         <v>1902</v>
@@ -10966,7 +10974,7 @@
       </c>
       <c r="P185" s="4"/>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <f t="shared" si="104"/>
         <v>1903</v>
@@ -11025,7 +11033,7 @@
       </c>
       <c r="P186" s="4"/>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <f t="shared" si="104"/>
         <v>1904</v>
@@ -11084,7 +11092,7 @@
       </c>
       <c r="P187" s="4"/>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <f t="shared" si="104"/>
         <v>1905</v>
@@ -11143,7 +11151,7 @@
       </c>
       <c r="P188" s="4"/>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <f t="shared" si="104"/>
         <v>1906</v>
@@ -11202,7 +11210,7 @@
       </c>
       <c r="P189" s="4"/>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <f t="shared" si="104"/>
         <v>1907</v>
@@ -11261,7 +11269,7 @@
       </c>
       <c r="P190" s="4"/>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <f t="shared" si="104"/>
         <v>1908</v>
@@ -11319,7 +11327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <f t="shared" si="104"/>
         <v>1909</v>
@@ -11377,7 +11385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <f t="shared" si="104"/>
         <v>1910</v>
@@ -11435,7 +11443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <f t="shared" si="104"/>
         <v>1911</v>
@@ -11493,7 +11501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <f t="shared" si="104"/>
         <v>1912</v>
@@ -11551,7 +11559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:15">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <f t="shared" si="104"/>
         <v>1913</v>
@@ -11609,7 +11617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:15">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <f t="shared" si="104"/>
         <v>1914</v>
@@ -11667,7 +11675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <f t="shared" si="104"/>
         <v>1915</v>
@@ -11725,7 +11733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <f t="shared" si="104"/>
         <v>1916</v>
@@ -11783,7 +11791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:15">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>1917</v>
       </c>
@@ -11840,12 +11848,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="204" spans="1:15">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
         <v>87</v>
       </c>
@@ -11889,7 +11897,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="205" spans="1:15">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>1896</v>
       </c>
@@ -11946,7 +11954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:15">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <f>A205+1</f>
         <v>1897</v>
@@ -12004,7 +12012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:15">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <f t="shared" ref="A207:A224" si="128">A206+1</f>
         <v>1898</v>
@@ -12062,7 +12070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <f t="shared" si="128"/>
         <v>1899</v>
@@ -12120,7 +12128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <f t="shared" si="128"/>
         <v>1900</v>
@@ -12178,7 +12186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:15">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <f t="shared" si="128"/>
         <v>1901</v>
@@ -12236,7 +12244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:15">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <f t="shared" si="128"/>
         <v>1902</v>
@@ -12294,7 +12302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <f t="shared" si="128"/>
         <v>1903</v>
@@ -12352,7 +12360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:15">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <f t="shared" si="128"/>
         <v>1904</v>
@@ -12410,7 +12418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <f t="shared" si="128"/>
         <v>1905</v>
@@ -12468,7 +12476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:15">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <f t="shared" si="128"/>
         <v>1906</v>
@@ -12526,7 +12534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <f t="shared" si="128"/>
         <v>1907</v>
@@ -12584,7 +12592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <f t="shared" si="128"/>
         <v>1908</v>
@@ -12642,7 +12650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <f t="shared" si="128"/>
         <v>1909</v>
@@ -12700,7 +12708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:15">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <f t="shared" si="128"/>
         <v>1910</v>
@@ -12758,7 +12766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:15">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <f t="shared" si="128"/>
         <v>1911</v>
@@ -12816,7 +12824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <f t="shared" si="128"/>
         <v>1912</v>
@@ -12874,7 +12882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <f t="shared" si="128"/>
         <v>1913</v>
@@ -12932,7 +12940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <f t="shared" si="128"/>
         <v>1914</v>
@@ -12990,7 +12998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <f t="shared" si="128"/>
         <v>1915</v>
@@ -13048,7 +13056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>1916</v>
       </c>
@@ -13105,7 +13113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:15">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>49</v>
       </c>
@@ -13162,7 +13170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:15">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>88</v>
       </c>
@@ -13215,15 +13223,15 @@
         <v>8.2845503895924058E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:15">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="230" spans="1:15">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L230" s="4"/>
     </row>
-    <row r="231" spans="1:15">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>181</v>
       </c>
@@ -13232,10 +13240,10 @@
       </c>
       <c r="L231" s="4"/>
     </row>
-    <row r="232" spans="1:15">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L232" s="4"/>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
         <v>87</v>
       </c>
@@ -13279,7 +13287,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="234" spans="1:15">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>1896</v>
       </c>
@@ -13336,7 +13344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <f>A234+1</f>
         <v>1897</v>
@@ -13394,7 +13402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <f t="shared" ref="A236:A253" si="153">A235+1</f>
         <v>1898</v>
@@ -13452,7 +13460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:15">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <f t="shared" si="153"/>
         <v>1899</v>
@@ -13510,7 +13518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:15">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <f t="shared" si="153"/>
         <v>1900</v>
@@ -13568,7 +13576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <f t="shared" si="153"/>
         <v>1901</v>
@@ -13626,7 +13634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:15">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <f t="shared" si="153"/>
         <v>1902</v>
@@ -13684,7 +13692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <f t="shared" si="153"/>
         <v>1903</v>
@@ -13742,7 +13750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <f t="shared" si="153"/>
         <v>1904</v>
@@ -13800,7 +13808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <f t="shared" si="153"/>
         <v>1905</v>
@@ -13858,7 +13866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:15">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <f t="shared" si="153"/>
         <v>1906</v>
@@ -13916,7 +13924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:15">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <f t="shared" si="153"/>
         <v>1907</v>
@@ -13974,7 +13982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:15">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <f t="shared" si="153"/>
         <v>1908</v>
@@ -14032,7 +14040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <f t="shared" si="153"/>
         <v>1909</v>
@@ -14090,7 +14098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:15">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <f t="shared" si="153"/>
         <v>1910</v>
@@ -14148,7 +14156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <f t="shared" si="153"/>
         <v>1911</v>
@@ -14206,7 +14214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <f t="shared" si="153"/>
         <v>1912</v>
@@ -14264,7 +14272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:15">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <f t="shared" si="153"/>
         <v>1913</v>
@@ -14322,7 +14330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <f t="shared" si="153"/>
         <v>1914</v>
@@ -14380,7 +14388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <f t="shared" si="153"/>
         <v>1915</v>
@@ -14438,7 +14446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>1916</v>
       </c>
@@ -14495,7 +14503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>49</v>
       </c>
@@ -14552,12 +14560,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:17">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="259" spans="1:17">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A259" s="14" t="s">
         <v>182</v>
       </c>
@@ -14598,7 +14606,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="260" spans="1:17">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B260">
         <v>0.55000000000000004</v>
       </c>
@@ -14633,7 +14641,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="262" spans="1:17">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
         <v>87</v>
       </c>
@@ -14677,7 +14685,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="263" spans="1:17">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>1896</v>
       </c>
@@ -14734,7 +14742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <f>A263+1</f>
         <v>1897</v>
@@ -14792,7 +14800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:17">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <f t="shared" ref="A265:A282" si="179">A264+1</f>
         <v>1898</v>
@@ -14850,7 +14858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <f t="shared" si="179"/>
         <v>1899</v>
@@ -14908,7 +14916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:17">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <f t="shared" si="179"/>
         <v>1900</v>
@@ -14966,7 +14974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <f t="shared" si="179"/>
         <v>1901</v>
@@ -15025,7 +15033,7 @@
       </c>
       <c r="Q268" s="4"/>
     </row>
-    <row r="269" spans="1:17">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <f t="shared" si="179"/>
         <v>1902</v>
@@ -15083,7 +15091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:17">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <f t="shared" si="179"/>
         <v>1903</v>
@@ -15141,7 +15149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:17">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <f t="shared" si="179"/>
         <v>1904</v>
@@ -15199,7 +15207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:17">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <f t="shared" si="179"/>
         <v>1905</v>
@@ -15257,7 +15265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:15">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <f t="shared" si="179"/>
         <v>1906</v>
@@ -15315,7 +15323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:15">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <f t="shared" si="179"/>
         <v>1907</v>
@@ -15373,7 +15381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:15">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <f t="shared" si="179"/>
         <v>1908</v>
@@ -15431,7 +15439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <f t="shared" si="179"/>
         <v>1909</v>
@@ -15489,7 +15497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:15">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <f t="shared" si="179"/>
         <v>1910</v>
@@ -15547,7 +15555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:15">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <f t="shared" si="179"/>
         <v>1911</v>
@@ -15605,7 +15613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <f t="shared" si="179"/>
         <v>1912</v>
@@ -15663,7 +15671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <f t="shared" si="179"/>
         <v>1913</v>
@@ -15721,7 +15729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <f t="shared" si="179"/>
         <v>1914</v>
@@ -15779,7 +15787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <f t="shared" si="179"/>
         <v>1915</v>
@@ -15837,7 +15845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>1916</v>
       </c>
@@ -15894,7 +15902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:15">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
         <v>49</v>
       </c>
@@ -15951,12 +15959,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:15">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="288" spans="1:15">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
         <v>87</v>
       </c>
@@ -16000,7 +16008,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="289" spans="1:15">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>1896</v>
       </c>
@@ -16057,7 +16065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:15">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <f>A289+1</f>
         <v>1897</v>
@@ -16115,7 +16123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:15">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <f t="shared" ref="A291:A308" si="203">A290+1</f>
         <v>1898</v>
@@ -16173,7 +16181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:15">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <f t="shared" si="203"/>
         <v>1899</v>
@@ -16231,7 +16239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:15">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <f t="shared" si="203"/>
         <v>1900</v>
@@ -16289,7 +16297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <f t="shared" si="203"/>
         <v>1901</v>
@@ -16347,7 +16355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:15">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <f t="shared" si="203"/>
         <v>1902</v>
@@ -16405,7 +16413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:15">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <f t="shared" si="203"/>
         <v>1903</v>
@@ -16463,7 +16471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:15">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <f t="shared" si="203"/>
         <v>1904</v>
@@ -16521,7 +16529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:15">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <f t="shared" si="203"/>
         <v>1905</v>
@@ -16579,7 +16587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:15">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <f t="shared" si="203"/>
         <v>1906</v>
@@ -16637,7 +16645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <f t="shared" si="203"/>
         <v>1907</v>
@@ -16695,7 +16703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <f t="shared" si="203"/>
         <v>1908</v>
@@ -16753,7 +16761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:15">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <f t="shared" si="203"/>
         <v>1909</v>
@@ -16811,7 +16819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:15">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <f t="shared" si="203"/>
         <v>1910</v>
@@ -16869,7 +16877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:15">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <f t="shared" si="203"/>
         <v>1911</v>
@@ -16927,7 +16935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <f t="shared" si="203"/>
         <v>1912</v>
@@ -16985,7 +16993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:15">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <f t="shared" si="203"/>
         <v>1913</v>
@@ -17043,7 +17051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:15">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <f t="shared" si="203"/>
         <v>1914</v>
@@ -17101,7 +17109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <f t="shared" si="203"/>
         <v>1915</v>
@@ -17159,7 +17167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>1916</v>
       </c>
@@ -17216,7 +17224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
         <v>49</v>
       </c>
@@ -17284,27 +17292,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
-  <dimension ref="A1:P212"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:N213"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" customWidth="1"/>
     <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="60">
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>117</v>
       </c>
@@ -17339,7 +17351,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -17373,10 +17385,8 @@
       <c r="K5" s="4">
         <v>30398</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -17410,10 +17420,8 @@
       <c r="K6" s="4">
         <v>27525</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -17447,10 +17455,8 @@
       <c r="K7" s="4">
         <v>64393</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>121</v>
       </c>
@@ -17484,10 +17490,8 @@
       <c r="K8" s="4">
         <v>223248</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:13">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
@@ -17521,10 +17525,8 @@
       <c r="K9" s="4">
         <v>279258</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -17558,10 +17560,8 @@
       <c r="K10" s="4">
         <v>173914</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -17595,10 +17595,8 @@
       <c r="K11" s="4">
         <v>340174</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" spans="1:13">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -17632,10 +17630,8 @@
       <c r="K12" s="4">
         <v>471971</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -17669,10 +17665,8 @@
       <c r="K13" s="4">
         <v>409911</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" spans="1:13">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>129</v>
       </c>
@@ -17716,10 +17710,8 @@
         <f t="shared" si="0"/>
         <v>2020792</v>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" spans="1:13">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>130</v>
       </c>
@@ -17763,9 +17755,8 @@
         <f t="shared" ref="K15" si="10">100*K14/$K14</f>
         <v>100</v>
       </c>
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" spans="1:13">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>127</v>
       </c>
@@ -17810,7 +17801,7 @@
         <v>1395970</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>128</v>
       </c>
@@ -17855,7 +17846,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>185</v>
       </c>
@@ -17900,7 +17891,7 @@
         <v>566899</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
         <v>186</v>
       </c>
@@ -17945,7 +17936,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>196</v>
       </c>
@@ -17960,7 +17951,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>194</v>
       </c>
@@ -17975,7 +17966,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -17987,7 +17978,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
         <v>117</v>
       </c>
@@ -18018,7 +18009,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -18042,7 +18033,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>120</v>
       </c>
@@ -18068,7 +18059,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -18094,7 +18085,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>122</v>
       </c>
@@ -18120,7 +18111,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
         <v>123</v>
       </c>
@@ -18148,10 +18139,8 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-    </row>
-    <row r="31" spans="1:16">
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -18183,10 +18172,8 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-    </row>
-    <row r="32" spans="1:16">
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -18216,10 +18203,8 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-    </row>
-    <row r="33" spans="1:16">
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -18251,10 +18236,8 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-    </row>
-    <row r="34" spans="1:16">
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
         <v>127</v>
       </c>
@@ -18295,10 +18278,8 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-    </row>
-    <row r="35" spans="1:16">
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
         <v>88</v>
       </c>
@@ -18339,10 +18320,8 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-    </row>
-    <row r="36" spans="1:16">
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
         <v>185</v>
       </c>
@@ -18374,10 +18353,8 @@
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-    </row>
-    <row r="37" spans="1:16">
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="33" t="s">
         <v>88</v>
       </c>
@@ -18402,17 +18379,17 @@
         <v>99.993052867676965</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="45">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>117</v>
       </c>
@@ -18422,29 +18399,35 @@
       <c r="C42" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="F42" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="G42" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="E42" s="39" t="s">
+      <c r="H42" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="F42" s="39" t="s">
+      <c r="I42" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="G42" s="39" t="s">
+      <c r="J42" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="H42" s="39" t="s">
+      <c r="K42" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="I42" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="J42" s="39" t="s">
+      <c r="L42" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -18453,23 +18436,31 @@
         <v>23669</v>
       </c>
       <c r="D43" s="4">
+        <v>2336</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4">
+        <f>C43+D43-E43</f>
+        <v>26005</v>
+      </c>
+      <c r="G43" s="4">
         <v>190</v>
       </c>
-      <c r="E43" s="4">
+      <c r="H43" s="4">
         <v>7463</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4">
-        <v>2336</v>
-      </c>
-      <c r="J43" s="4">
-        <f>SUM(B43:I43)</f>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4">
+        <f>SUM(B43) + SUM(F43:K43)</f>
         <v>33658</v>
       </c>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>120</v>
       </c>
@@ -18478,25 +18469,33 @@
         <v>58829</v>
       </c>
       <c r="D44" s="4">
+        <v>9959</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" ref="F44:F50" si="17">C44+D44-E44</f>
+        <v>68788</v>
+      </c>
+      <c r="G44" s="4">
         <v>120</v>
       </c>
-      <c r="E44" s="4">
+      <c r="H44" s="4">
         <v>1066</v>
       </c>
-      <c r="F44" s="4">
+      <c r="I44" s="4">
         <v>8</v>
       </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4">
-        <v>9959</v>
-      </c>
-      <c r="J44" s="4">
-        <f t="shared" ref="J44:J51" si="17">SUM(B44:I44)</f>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4">
+        <f t="shared" ref="L44:L54" si="18">SUM(B44) + SUM(F44:K44)</f>
         <v>69982</v>
       </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>121</v>
       </c>
@@ -18505,25 +18504,33 @@
         <v>142545</v>
       </c>
       <c r="D45" s="4">
+        <v>15994</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4">
+        <f t="shared" si="17"/>
+        <v>158539</v>
+      </c>
+      <c r="G45" s="4">
         <v>4035</v>
       </c>
-      <c r="E45" s="4">
+      <c r="H45" s="4">
         <v>27271</v>
       </c>
-      <c r="F45" s="4">
+      <c r="I45" s="4">
         <v>5</v>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4">
-        <v>15994</v>
-      </c>
-      <c r="J45" s="4">
-        <f t="shared" si="17"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4">
+        <f t="shared" si="18"/>
         <v>189850</v>
       </c>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>122</v>
       </c>
@@ -18532,25 +18539,33 @@
         <v>246432</v>
       </c>
       <c r="D46" s="4">
+        <v>44935</v>
+      </c>
+      <c r="E46" s="4">
+        <v>22287</v>
+      </c>
+      <c r="F46" s="4">
+        <f t="shared" si="17"/>
+        <v>269080</v>
+      </c>
+      <c r="G46" s="4">
         <v>11010</v>
       </c>
-      <c r="E46" s="4">
+      <c r="H46" s="4">
         <v>12462</v>
       </c>
-      <c r="F46" s="4">
+      <c r="I46" s="4">
         <v>22</v>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4">
-        <v>44935</v>
-      </c>
-      <c r="J46" s="4">
-        <f t="shared" si="17"/>
-        <v>314861</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4">
+        <f t="shared" si="18"/>
+        <v>292574</v>
+      </c>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>123</v>
       </c>
@@ -18559,25 +18574,33 @@
         <v>258858</v>
       </c>
       <c r="D47" s="4">
+        <v>9582</v>
+      </c>
+      <c r="E47" s="4">
+        <v>30544</v>
+      </c>
+      <c r="F47" s="4">
+        <f t="shared" si="17"/>
+        <v>237896</v>
+      </c>
+      <c r="G47" s="4">
         <v>6456</v>
       </c>
-      <c r="E47" s="4">
+      <c r="H47" s="4">
         <v>1978</v>
       </c>
-      <c r="F47" s="4">
+      <c r="I47" s="4">
         <v>9</v>
       </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4">
-        <v>9582</v>
-      </c>
-      <c r="J47" s="4">
-        <f t="shared" si="17"/>
-        <v>276883</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4">
+        <f t="shared" si="18"/>
+        <v>246339</v>
+      </c>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>124</v>
       </c>
@@ -18587,26 +18610,34 @@
       <c r="C48" s="4">
         <v>678735</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="4"/>
+      <c r="E48" s="4">
+        <v>69344</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="17"/>
+        <v>609391</v>
+      </c>
+      <c r="G48" s="4">
         <v>19739</v>
       </c>
-      <c r="E48" s="4">
+      <c r="H48" s="4">
         <v>1861</v>
       </c>
-      <c r="F48" s="4">
+      <c r="I48" s="4">
         <v>18</v>
       </c>
-      <c r="G48" s="4">
+      <c r="J48" s="4">
         <v>527</v>
       </c>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4">
-        <f t="shared" si="17"/>
-        <v>713875</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+      <c r="K48" s="4"/>
+      <c r="L48" s="4">
+        <f t="shared" si="18"/>
+        <v>644531</v>
+      </c>
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -18616,24 +18647,32 @@
       <c r="C49" s="4">
         <v>938571</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="4"/>
+      <c r="E49" s="4">
+        <v>60276</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="17"/>
+        <v>878295</v>
+      </c>
+      <c r="G49" s="4">
         <v>64754</v>
       </c>
-      <c r="E49" s="4">
+      <c r="H49" s="4">
         <v>15360</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4">
-        <v>2231</v>
-      </c>
-      <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4">
-        <f t="shared" si="17"/>
-        <v>1047253</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>2231</v>
+      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4">
+        <f t="shared" si="18"/>
+        <v>986977</v>
+      </c>
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -18643,26 +18682,34 @@
       <c r="C50" s="4">
         <v>894003</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="4"/>
+      <c r="E50" s="4">
+        <v>38424</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" si="17"/>
+        <v>855579</v>
+      </c>
+      <c r="G50" s="4">
         <v>55308</v>
       </c>
-      <c r="E50" s="4">
+      <c r="H50" s="4">
         <v>35055</v>
-      </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4">
-        <v>5649</v>
-      </c>
-      <c r="H50" s="4">
-        <v>404</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4">
-        <f t="shared" si="17"/>
-        <v>1048709</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>5649</v>
+      </c>
+      <c r="K50" s="4">
+        <v>404</v>
+      </c>
+      <c r="L50" s="4">
+        <f t="shared" si="18"/>
+        <v>1010285</v>
+      </c>
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
         <v>127</v>
       </c>
@@ -18671,161 +18718,181 @@
         <v>97622</v>
       </c>
       <c r="C51" s="12">
-        <f t="shared" ref="C51:I51" si="18">SUM(C47:C50)</f>
+        <f t="shared" ref="C51:K51" si="19">SUM(C47:C50)</f>
         <v>2770167</v>
       </c>
       <c r="D51" s="12">
+        <f t="shared" si="19"/>
+        <v>9582</v>
+      </c>
+      <c r="E51" s="12">
+        <f t="shared" si="19"/>
+        <v>198588</v>
+      </c>
+      <c r="F51" s="12">
+        <f t="shared" si="19"/>
+        <v>2581161</v>
+      </c>
+      <c r="G51" s="12">
+        <f t="shared" si="19"/>
+        <v>146257</v>
+      </c>
+      <c r="H51" s="12">
+        <f t="shared" si="19"/>
+        <v>54254</v>
+      </c>
+      <c r="I51" s="12">
+        <f t="shared" si="19"/>
+        <v>27</v>
+      </c>
+      <c r="J51" s="12">
+        <f t="shared" si="19"/>
+        <v>8407</v>
+      </c>
+      <c r="K51" s="12">
+        <f t="shared" si="19"/>
+        <v>404</v>
+      </c>
+      <c r="L51" s="12">
         <f t="shared" si="18"/>
-        <v>146257</v>
-      </c>
-      <c r="E51" s="12">
-        <f t="shared" si="18"/>
-        <v>54254</v>
-      </c>
-      <c r="F51" s="12">
-        <f t="shared" si="18"/>
-        <v>27</v>
-      </c>
-      <c r="G51" s="12">
-        <f t="shared" si="18"/>
-        <v>8407</v>
-      </c>
-      <c r="H51" s="12">
-        <f t="shared" si="18"/>
-        <v>404</v>
-      </c>
-      <c r="I51" s="12">
-        <f t="shared" si="18"/>
-        <v>9582</v>
-      </c>
-      <c r="J51" s="12">
-        <f t="shared" si="17"/>
-        <v>3086720</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>2888132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
         <v>88</v>
       </c>
       <c r="B52" s="23">
-        <f t="shared" ref="B52:J52" si="19">100*B51/$J51</f>
-        <v>3.162645137880987</v>
-      </c>
-      <c r="C52" s="23">
-        <f t="shared" si="19"/>
-        <v>89.744680437487048</v>
-      </c>
-      <c r="D52" s="23">
-        <f t="shared" si="19"/>
-        <v>4.7382658614969939</v>
-      </c>
-      <c r="E52" s="23">
-        <f t="shared" si="19"/>
-        <v>1.7576586149699358</v>
-      </c>
+        <f>B51/$L51*100</f>
+        <v>3.38010866539341</v>
+      </c>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
       <c r="F52" s="23">
-        <f t="shared" si="19"/>
-        <v>8.7471490773377569E-4</v>
+        <f>F51/$L51*100</f>
+        <v>89.371296048795557</v>
       </c>
       <c r="G52" s="23">
-        <f t="shared" si="19"/>
-        <v>0.27236030478955009</v>
+        <f>G51/$L51*100</f>
+        <v>5.064069093794882</v>
       </c>
       <c r="H52" s="23">
-        <f t="shared" si="19"/>
-        <v>1.308832676757205E-2</v>
+        <f>H51/$L51*100</f>
+        <v>1.8785152479180314</v>
       </c>
       <c r="I52" s="23">
-        <f t="shared" si="19"/>
-        <v>0.3104266017001866</v>
+        <f>I51/$L51*100</f>
+        <v>9.3486031801870548E-4</v>
       </c>
       <c r="J52" s="23">
-        <f t="shared" si="19"/>
+        <f>J51/$L51*100</f>
+        <v>0.29108780346604657</v>
+      </c>
+      <c r="K52" s="23">
+        <f>K51/$L51*100</f>
+        <v>1.3988280314057668E-2</v>
+      </c>
+      <c r="L52" s="23">
+        <f t="shared" si="18"/>
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="B53" s="34"/>
+      <c r="B53" s="34">
+        <f t="shared" ref="B53:K53" si="20">SUM(B44:B46)</f>
+        <v>0</v>
+      </c>
       <c r="C53" s="34">
-        <f t="shared" ref="C53:I53" si="20">SUM(C44:C46)</f>
+        <f t="shared" si="20"/>
         <v>447806</v>
       </c>
       <c r="D53" s="34">
         <f t="shared" si="20"/>
-        <v>15165</v>
+        <v>70888</v>
       </c>
       <c r="E53" s="34">
         <f t="shared" si="20"/>
-        <v>40799</v>
+        <v>22287</v>
       </c>
       <c r="F53" s="34">
         <f t="shared" si="20"/>
-        <v>35</v>
+        <v>496407</v>
       </c>
       <c r="G53" s="34">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>15165</v>
       </c>
       <c r="H53" s="34">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>40799</v>
       </c>
       <c r="I53" s="34">
         <f t="shared" si="20"/>
-        <v>70888</v>
+        <v>35</v>
       </c>
       <c r="J53" s="34">
-        <f>SUM(B53:I53)</f>
-        <v>574693</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="34">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="34">
+        <f t="shared" si="18"/>
+        <v>552406</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35">
-        <f t="shared" ref="C54:I54" si="21">C53/$J53*100</f>
-        <v>77.920907336612771</v>
-      </c>
-      <c r="D54" s="35">
-        <f t="shared" si="21"/>
-        <v>2.6388001941906372</v>
-      </c>
-      <c r="E54" s="35">
-        <f t="shared" si="21"/>
-        <v>7.099268653002559</v>
-      </c>
+      <c r="B54" s="35">
+        <f>B53/$L53*100</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
       <c r="F54" s="35">
-        <f t="shared" si="21"/>
-        <v>6.0902081633150218E-3</v>
+        <f>F53/$L53*100</f>
+        <v>89.862709673682033</v>
       </c>
       <c r="G54" s="35">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>G53/$L53*100</f>
+        <v>2.7452634475367756</v>
       </c>
       <c r="H54" s="35">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>H53/$L53*100</f>
+        <v>7.3856909591858155</v>
       </c>
       <c r="I54" s="35">
-        <f t="shared" si="21"/>
-        <v>12.334933608030722</v>
+        <f>I53/$L53*100</f>
+        <v>6.3359195953700724E-3</v>
       </c>
       <c r="J54" s="35">
-        <f>SUM(B54:H54)</f>
-        <v>87.665066391969276</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <f>J53/$L53*100</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="35">
+        <f>K53/$L53*100</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="35">
+        <f t="shared" si="18"/>
+        <v>99.999999999999986</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="36" t="s">
         <v>19</v>
       </c>
@@ -18833,7 +18900,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>1896</v>
       </c>
@@ -18841,7 +18908,7 @@
         <v>35639</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>1897</v>
       </c>
@@ -18849,7 +18916,7 @@
         <v>28021</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>1898</v>
       </c>
@@ -18857,7 +18924,7 @@
         <v>41907</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>1899</v>
       </c>
@@ -18865,7 +18932,7 @@
         <v>65559</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>1900</v>
       </c>
@@ -18873,7 +18940,7 @@
         <v>76085</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>1901</v>
       </c>
@@ -18881,7 +18948,7 @@
         <v>83166</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>1902</v>
       </c>
@@ -18889,7 +18956,7 @@
         <v>103114</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>1903</v>
       </c>
@@ -18897,7 +18964,7 @@
         <v>125022</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>1904</v>
       </c>
@@ -18905,7 +18972,7 @@
         <v>151739</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>1905</v>
       </c>
@@ -18913,7 +18980,7 @@
         <v>186157</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>1906</v>
       </c>
@@ -18921,7 +18988,7 @@
         <v>221400</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>1907</v>
       </c>
@@ -18929,7 +18996,7 @@
         <v>186071</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>1908</v>
       </c>
@@ -18937,7 +19004,7 @@
         <v>119541</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>1909</v>
       </c>
@@ -18945,7 +19012,7 @@
         <v>141698</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>1910</v>
       </c>
@@ -18953,7 +19020,7 @@
         <v>162676</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>1911</v>
       </c>
@@ -18961,7 +19028,7 @@
         <v>144660</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>1912</v>
       </c>
@@ -18969,7 +19036,7 @@
         <v>217990</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>1913</v>
       </c>
@@ -18977,7 +19044,7 @@
         <v>261265</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>1914</v>
       </c>
@@ -18985,7 +19052,7 @@
         <v>119358</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>1915</v>
       </c>
@@ -18993,7 +19060,7 @@
         <v>3880</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>1916</v>
       </c>
@@ -19001,7 +19068,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>49</v>
       </c>
@@ -19010,7 +19077,7 @@
         <v>2477253</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>123</v>
       </c>
@@ -19019,7 +19086,7 @@
         <v>247211</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>124</v>
       </c>
@@ -19028,7 +19095,7 @@
         <v>649198</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>125</v>
       </c>
@@ -19037,7 +19104,7 @@
         <v>831386</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>126</v>
       </c>
@@ -19046,7 +19113,7 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="36" t="s">
         <v>117</v>
       </c>
@@ -19064,16 +19131,16 @@
       </c>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B90" s="4">
-        <f t="shared" ref="B90:B97" si="22">K6</f>
+        <f t="shared" ref="B90:B97" si="21">K6</f>
         <v>27525</v>
       </c>
       <c r="C90" s="4">
-        <f>J43</f>
+        <f>L43</f>
         <v>33658</v>
       </c>
       <c r="D90" s="26">
@@ -19082,16 +19149,16 @@
       </c>
       <c r="E90" s="14"/>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B91" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>64393</v>
       </c>
       <c r="C91" s="4">
-        <f t="shared" ref="C91:C97" si="23">J44</f>
+        <f>L44</f>
         <v>69982</v>
       </c>
       <c r="D91" s="26">
@@ -19099,1119 +19166,1173 @@
         <v>92.01366065559715</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B92" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>223248</v>
       </c>
       <c r="C92" s="4">
-        <f t="shared" si="23"/>
+        <f>L45</f>
         <v>189850</v>
       </c>
       <c r="D92" s="26">
-        <f t="shared" ref="D92:D97" si="24">B92/C92*100</f>
+        <f t="shared" ref="D92:D97" si="22">B92/C92*100</f>
         <v>117.59178298656833</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B93" s="4">
+        <f t="shared" si="21"/>
+        <v>279258</v>
+      </c>
+      <c r="C93" s="4">
+        <f>L46</f>
+        <v>292574</v>
+      </c>
+      <c r="D93" s="26">
         <f t="shared" si="22"/>
-        <v>279258</v>
-      </c>
-      <c r="C93" s="4">
-        <f t="shared" si="23"/>
-        <v>314861</v>
-      </c>
-      <c r="D93" s="26">
-        <f t="shared" si="24"/>
-        <v>88.692470645777021</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+        <v>95.448672814399089</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="43" t="s">
         <v>123</v>
       </c>
       <c r="B94" s="4">
+        <f t="shared" si="21"/>
+        <v>173914</v>
+      </c>
+      <c r="C94" s="4">
+        <f>L47</f>
+        <v>246339</v>
+      </c>
+      <c r="D94" s="26">
         <f t="shared" si="22"/>
-        <v>173914</v>
-      </c>
-      <c r="C94" s="4">
-        <f t="shared" si="23"/>
-        <v>276883</v>
-      </c>
-      <c r="D94" s="26">
-        <f t="shared" si="24"/>
-        <v>62.811367978532452</v>
+        <v>70.599458469832229</v>
       </c>
       <c r="E94" s="4">
         <f>B82</f>
         <v>247211</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B95" s="4">
+        <f t="shared" si="21"/>
+        <v>340174</v>
+      </c>
+      <c r="C95" s="4">
+        <f>L48</f>
+        <v>644531</v>
+      </c>
+      <c r="D95" s="26">
         <f t="shared" si="22"/>
-        <v>340174</v>
-      </c>
-      <c r="C95" s="4">
-        <f t="shared" si="23"/>
-        <v>713875</v>
-      </c>
-      <c r="D95" s="26">
-        <f t="shared" si="24"/>
-        <v>47.651759761863069</v>
+        <v>52.778531986824525</v>
       </c>
       <c r="E95" s="4">
         <f>B83</f>
         <v>649198</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B96" s="4">
+        <f t="shared" si="21"/>
+        <v>471971</v>
+      </c>
+      <c r="C96" s="4">
+        <f>L49</f>
+        <v>986977</v>
+      </c>
+      <c r="D96" s="26">
         <f t="shared" si="22"/>
-        <v>471971</v>
-      </c>
-      <c r="C96" s="4">
-        <f t="shared" si="23"/>
-        <v>1047253</v>
-      </c>
-      <c r="D96" s="26">
-        <f t="shared" si="24"/>
-        <v>45.067524275413867</v>
+        <v>47.819858010875635</v>
       </c>
       <c r="E96" s="4">
         <f>B84</f>
         <v>831386</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B97" s="4">
+        <f t="shared" si="21"/>
+        <v>409911</v>
+      </c>
+      <c r="C97" s="4">
+        <f>L50</f>
+        <v>1010285</v>
+      </c>
+      <c r="D97" s="26">
         <f t="shared" si="22"/>
-        <v>409911</v>
-      </c>
-      <c r="C97" s="4">
-        <f t="shared" si="23"/>
-        <v>1048709</v>
-      </c>
-      <c r="D97" s="26">
-        <f t="shared" si="24"/>
-        <v>39.087201502037267</v>
+        <v>40.573798482606392</v>
       </c>
       <c r="E97" s="4">
         <f>B85</f>
         <v>747153</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B98" s="4"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B99" s="4"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="36" t="s">
         <v>117</v>
       </c>
       <c r="B101" s="36" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="str">
         <f>A43</f>
         <v>1876-1880</v>
       </c>
       <c r="B102" s="4">
-        <f>J43</f>
+        <f>L43</f>
         <v>33658</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="str">
-        <f t="shared" ref="A103:A110" si="25">A44</f>
+        <f t="shared" ref="A103:A110" si="23">A44</f>
         <v>1881-1885</v>
       </c>
       <c r="B103" s="4">
-        <f t="shared" ref="B103:B110" si="26">J44</f>
+        <f>L44</f>
         <v>69982</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1886-1890</v>
       </c>
       <c r="B104" s="4">
-        <f t="shared" si="26"/>
+        <f>L45</f>
         <v>189850</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1891-1895</v>
       </c>
       <c r="B105" s="4">
-        <f t="shared" si="26"/>
-        <v>314861</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <f>L46</f>
+        <v>292574</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1896-1900</v>
       </c>
       <c r="B106" s="4">
-        <f t="shared" si="26"/>
-        <v>276883</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <f>L47</f>
+        <v>246339</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1901-1905</v>
       </c>
       <c r="B107" s="4">
-        <f t="shared" si="26"/>
-        <v>713875</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <f>L48</f>
+        <v>644531</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1906-1910</v>
       </c>
       <c r="B108" s="4">
-        <f t="shared" si="26"/>
-        <v>1047253</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <f>L49</f>
+        <v>986977</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1911-1915</v>
       </c>
       <c r="B109" s="4">
-        <f t="shared" si="26"/>
-        <v>1048709</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <f>L50</f>
+        <v>1010285</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1896-1915</v>
       </c>
       <c r="B110" s="42">
-        <f t="shared" si="26"/>
-        <v>3086720</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <f>L51</f>
+        <v>2888132</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>129</v>
       </c>
       <c r="B111" s="42">
         <f>SUM(B102:B109)</f>
-        <v>3695071</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
+        <v>3474196</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="36" t="s">
         <v>117</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>1876</v>
       </c>
-      <c r="B115" s="4">
-        <v>5936</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
+      <c r="B115" s="50">
+        <v>5958.6872560000002</v>
+      </c>
+      <c r="F115" s="50"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>1877</v>
       </c>
-      <c r="B116" s="4">
-        <v>6116</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
+      <c r="B116" s="50">
+        <v>6133.5817779999998</v>
+      </c>
+      <c r="F116" s="50"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>1878</v>
       </c>
-      <c r="B117" s="4">
-        <v>6491</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
+      <c r="B117" s="50">
+        <v>6497.8953369999999</v>
+      </c>
+      <c r="F117" s="50"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>1879</v>
       </c>
-      <c r="B118" s="4">
-        <v>7110</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
+      <c r="B118" s="50">
+        <v>7099.2952009999999</v>
+      </c>
+      <c r="F118" s="50"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>1880</v>
       </c>
-      <c r="B119" s="4">
-        <v>8006</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
+      <c r="B119" s="50">
+        <v>7968.5404280000002</v>
+      </c>
+      <c r="F119" s="50"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>1881</v>
       </c>
-      <c r="B120" s="4">
-        <v>9166</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
+      <c r="B120" s="50">
+        <v>9081.0078830000002</v>
+      </c>
+      <c r="F120" s="50"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>1882</v>
       </c>
-      <c r="B121" s="4">
-        <v>10890</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
+      <c r="B121" s="50">
+        <v>10799.985825</v>
+      </c>
+      <c r="F121" s="50"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>1883</v>
       </c>
-      <c r="B122" s="4">
-        <v>13234</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
+      <c r="B122" s="50">
+        <v>13180.685009000001</v>
+      </c>
+      <c r="F122" s="50"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>1884</v>
       </c>
-      <c r="B123" s="4">
-        <v>16339</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
+      <c r="B123" s="50">
+        <v>16376.145667999999</v>
+      </c>
+      <c r="F123" s="50"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>1885</v>
       </c>
-      <c r="B124" s="4">
-        <v>20353</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
+      <c r="B124" s="50">
+        <v>20544.175615</v>
+      </c>
+      <c r="F124" s="50"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>1886</v>
       </c>
-      <c r="B125" s="4">
-        <v>25776</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
+      <c r="B125" s="50">
+        <v>26303.239323000002</v>
+      </c>
+      <c r="F125" s="50"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>1887</v>
       </c>
-      <c r="B126" s="4">
-        <v>31367</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
+      <c r="B126" s="50">
+        <v>31933.797870999999</v>
+      </c>
+      <c r="F126" s="50"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>1888</v>
       </c>
-      <c r="B127" s="4">
-        <v>37436</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
+      <c r="B127" s="50">
+        <v>37768.818612000003</v>
+      </c>
+      <c r="F127" s="50"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>1889</v>
       </c>
-      <c r="B128" s="4">
-        <v>44054</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
+      <c r="B128" s="50">
+        <v>43815.890546000002</v>
+      </c>
+      <c r="F128" s="50"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>1890</v>
       </c>
-      <c r="B129" s="4">
-        <v>51217</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
+      <c r="B129" s="50">
+        <v>50028.253647999998</v>
+      </c>
+      <c r="F129" s="50"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>1891</v>
       </c>
-      <c r="B130" s="4">
-        <v>60036</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
+      <c r="B130" s="50">
+        <v>57244.128299000004</v>
+      </c>
+      <c r="F130" s="50"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>1892</v>
       </c>
-      <c r="B131" s="4">
-        <v>64880</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
+      <c r="B131" s="50">
+        <v>60906.481652000002</v>
+      </c>
+      <c r="F131" s="50"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>1893</v>
       </c>
-      <c r="B132" s="4">
-        <v>66389</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
+      <c r="B132" s="50">
+        <v>61556.958893000003</v>
+      </c>
+      <c r="F132" s="50"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>1894</v>
       </c>
-      <c r="B133" s="4">
-        <v>64376</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
+      <c r="B133" s="50">
+        <v>59073.614796000002</v>
+      </c>
+      <c r="F133" s="50"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>1895</v>
       </c>
-      <c r="B134" s="4">
-        <v>59181</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
+      <c r="B134" s="50">
+        <v>53792.816358999997</v>
+      </c>
+      <c r="F134" s="50"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>1896</v>
       </c>
-      <c r="B135" s="4">
-        <v>48893</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
+      <c r="B135" s="50">
+        <v>44001.050108000003</v>
+      </c>
+      <c r="F135" s="50"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>1897</v>
       </c>
-      <c r="B136" s="4">
-        <v>46578</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
+      <c r="B136" s="50">
+        <v>41555.827486000002</v>
+      </c>
+      <c r="F136" s="50"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>1898</v>
       </c>
-      <c r="B137" s="4">
-        <v>49507</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
+      <c r="B137" s="50">
+        <v>43914.876993999998</v>
+      </c>
+      <c r="F137" s="50"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>1899</v>
       </c>
-      <c r="B138" s="4">
-        <v>58290</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
+      <c r="B138" s="50">
+        <v>51608.617109999999</v>
+      </c>
+      <c r="F138" s="50"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>1900</v>
       </c>
-      <c r="B139" s="4">
-        <v>73615</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
+      <c r="B139" s="50">
+        <v>65258.628300999997</v>
+      </c>
+      <c r="F139" s="50"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>1901</v>
       </c>
-      <c r="B140" s="4">
-        <v>100515</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
+      <c r="B140" s="50">
+        <v>89374.285107000003</v>
+      </c>
+      <c r="F140" s="50"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>1902</v>
       </c>
-      <c r="B141" s="4">
-        <v>123543</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
+      <c r="B141" s="50">
+        <v>110396.48513099999</v>
+      </c>
+      <c r="F141" s="50"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>1903</v>
       </c>
-      <c r="B142" s="4">
-        <v>144936</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
+      <c r="B142" s="50">
+        <v>130369.29534500001</v>
+      </c>
+      <c r="F142" s="50"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>1904</v>
       </c>
-      <c r="B143" s="4">
-        <v>164107</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
+      <c r="B143" s="50">
+        <v>148831.43620900001</v>
+      </c>
+      <c r="F143" s="50"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>1905</v>
       </c>
-      <c r="B144" s="4">
-        <v>180774</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
+      <c r="B144" s="50">
+        <v>165559.498208</v>
+      </c>
+      <c r="F144" s="50"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>1906</v>
       </c>
-      <c r="B145" s="4">
-        <v>194743</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
+      <c r="B145" s="50">
+        <v>180624.48191</v>
+      </c>
+      <c r="F145" s="50"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>1907</v>
       </c>
-      <c r="B146" s="4">
-        <v>205493</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
+      <c r="B146" s="50">
+        <v>192365.54383800001</v>
+      </c>
+      <c r="F146" s="50"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>1908</v>
       </c>
-      <c r="B147" s="4">
-        <v>212897</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
+      <c r="B147" s="50">
+        <v>200821.20595</v>
+      </c>
+      <c r="F147" s="50"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>1909</v>
       </c>
-      <c r="B148" s="4">
-        <v>216819</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
+      <c r="B148" s="50">
+        <v>205811.42198099999</v>
+      </c>
+      <c r="F148" s="50"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>1910</v>
       </c>
-      <c r="B149" s="4">
-        <v>217301</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
+      <c r="B149" s="50">
+        <v>207354.34632099999</v>
+      </c>
+      <c r="F149" s="50"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>1911</v>
       </c>
-      <c r="B150" s="4">
-        <v>213270</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
+      <c r="B150" s="50">
+        <v>204407.818902</v>
+      </c>
+      <c r="F150" s="50"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>1912</v>
       </c>
-      <c r="B151" s="4">
-        <v>210897</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
+      <c r="B151" s="50">
+        <v>202841.37030400001</v>
+      </c>
+      <c r="F151" s="50"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>1913</v>
       </c>
-      <c r="B152" s="4">
-        <v>209103</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
+      <c r="B152" s="50">
+        <v>201633.03541400001</v>
+      </c>
+      <c r="F152" s="50"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>1914</v>
       </c>
-      <c r="B153" s="4">
-        <v>207991</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
+      <c r="B153" s="50">
+        <v>200884.29531700001</v>
+      </c>
+      <c r="F153" s="50"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>1915</v>
       </c>
-      <c r="B154" s="4">
-        <v>207448</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
+      <c r="B154" s="50">
+        <v>200518.480064</v>
+      </c>
+      <c r="F154" s="50"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B155" s="4">
         <f>SUM(B135:B154)</f>
-        <v>3086720</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
+        <v>2888132</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
         <v>129</v>
       </c>
       <c r="B156" s="4">
         <f>SUM(B115:B154)</f>
-        <v>3695073</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="14" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="36" t="s">
+        <v>3474195.9999989998</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B157" s="4">
+        <f>SUM(B120:B134)</f>
+        <v>552405.99999899999</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="10"/>
+      <c r="B158" s="4"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="14" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B160" s="36" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="1">
+      <c r="B161" s="36" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
         <v>1881</v>
       </c>
-      <c r="B161" s="4">
-        <f t="shared" ref="B161:B194" si="27">(B120+B121) / 2</f>
-        <v>10028</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="1">
-        <f>A161+1</f>
+      <c r="B162" s="4">
+        <f>(B120+B121) / 2</f>
+        <v>9940.4968540000009</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <f>A162+1</f>
         <v>1882</v>
       </c>
-      <c r="B162" s="4">
-        <f t="shared" si="27"/>
-        <v>12062</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="1">
-        <f t="shared" ref="A163:A194" si="28">A162+1</f>
+      <c r="B163" s="4">
+        <f>(B121+B122) / 2</f>
+        <v>11990.335417</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <f t="shared" ref="A164:A195" si="24">A163+1</f>
         <v>1883</v>
       </c>
-      <c r="B163" s="4">
-        <f t="shared" si="27"/>
-        <v>14786.5</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="1">
-        <f t="shared" si="28"/>
+      <c r="B164" s="4">
+        <f>(B122+B123) / 2</f>
+        <v>14778.415338499999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <f t="shared" si="24"/>
         <v>1884</v>
       </c>
-      <c r="B164" s="4">
-        <f t="shared" si="27"/>
-        <v>18346</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="1">
-        <f t="shared" si="28"/>
+      <c r="B165" s="4">
+        <f>(B123+B124) / 2</f>
+        <v>18460.160641499999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <f t="shared" si="24"/>
         <v>1885</v>
       </c>
-      <c r="B165" s="4">
-        <f t="shared" si="27"/>
-        <v>23064.5</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="1">
-        <f t="shared" si="28"/>
+      <c r="B166" s="4">
+        <f>(B124+B125) / 2</f>
+        <v>23423.707469000001</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <f t="shared" si="24"/>
         <v>1886</v>
       </c>
-      <c r="B166" s="4">
-        <f t="shared" si="27"/>
-        <v>28571.5</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="1">
-        <f t="shared" si="28"/>
+      <c r="B167" s="4">
+        <f>(B125+B126) / 2</f>
+        <v>29118.518597000002</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <f t="shared" si="24"/>
         <v>1887</v>
       </c>
-      <c r="B167" s="4">
-        <f t="shared" si="27"/>
-        <v>34401.5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="1">
-        <f t="shared" si="28"/>
+      <c r="B168" s="4">
+        <f>(B126+B127) / 2</f>
+        <v>34851.308241500003</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <f t="shared" si="24"/>
         <v>1888</v>
       </c>
-      <c r="B168" s="4">
-        <f t="shared" si="27"/>
-        <v>40745</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="1">
-        <f t="shared" si="28"/>
+      <c r="B169" s="4">
+        <f>(B127+B128) / 2</f>
+        <v>40792.354579000006</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <f t="shared" si="24"/>
         <v>1889</v>
       </c>
-      <c r="B169" s="4">
-        <f t="shared" si="27"/>
-        <v>47635.5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="1">
-        <f t="shared" si="28"/>
+      <c r="B170" s="4">
+        <f>(B128+B129) / 2</f>
+        <v>46922.072096999997</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <f t="shared" si="24"/>
         <v>1890</v>
       </c>
-      <c r="B170" s="4">
-        <f t="shared" si="27"/>
-        <v>55626.5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="1">
-        <f t="shared" si="28"/>
+      <c r="B171" s="4">
+        <f>(B129+B130) / 2</f>
+        <v>53636.190973500001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <f t="shared" si="24"/>
         <v>1891</v>
       </c>
-      <c r="B171" s="4">
-        <f t="shared" si="27"/>
-        <v>62458</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="1">
-        <f t="shared" si="28"/>
+      <c r="B172" s="4">
+        <f>(B130+B131) / 2</f>
+        <v>59075.304975500003</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <f t="shared" si="24"/>
         <v>1892</v>
       </c>
-      <c r="B172" s="4">
-        <f t="shared" si="27"/>
-        <v>65634.5</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="1">
-        <f t="shared" si="28"/>
+      <c r="B173" s="4">
+        <f>(B131+B132) / 2</f>
+        <v>61231.720272500002</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <f t="shared" si="24"/>
         <v>1893</v>
       </c>
-      <c r="B173" s="4">
-        <f t="shared" si="27"/>
-        <v>65382.5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="1">
-        <f t="shared" si="28"/>
+      <c r="B174" s="4">
+        <f>(B132+B133) / 2</f>
+        <v>60315.286844500006</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <f t="shared" si="24"/>
         <v>1894</v>
       </c>
-      <c r="B174" s="4">
-        <f t="shared" si="27"/>
-        <v>61778.5</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="1">
-        <f t="shared" si="28"/>
+      <c r="B175" s="4">
+        <f>(B133+B134) / 2</f>
+        <v>56433.215577499999</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <f t="shared" si="24"/>
         <v>1895</v>
       </c>
-      <c r="B175" s="4">
-        <f t="shared" si="27"/>
-        <v>54037</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="1">
-        <f t="shared" si="28"/>
+      <c r="B176" s="4">
+        <f>(B134+B135) / 2</f>
+        <v>48896.9332335</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <f t="shared" si="24"/>
         <v>1896</v>
       </c>
-      <c r="B176" s="4">
-        <f t="shared" si="27"/>
-        <v>47735.5</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="1">
-        <f t="shared" si="28"/>
+      <c r="B177" s="4">
+        <f>(B135+B136) / 2</f>
+        <v>42778.438797000003</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <f t="shared" si="24"/>
         <v>1897</v>
       </c>
-      <c r="B177" s="4">
-        <f t="shared" si="27"/>
-        <v>48042.5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="1">
-        <f t="shared" si="28"/>
+      <c r="B178" s="4">
+        <f>(B136+B137) / 2</f>
+        <v>42735.35224</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <f t="shared" si="24"/>
         <v>1898</v>
       </c>
-      <c r="B178" s="4">
-        <f t="shared" si="27"/>
-        <v>53898.5</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="1">
-        <f t="shared" si="28"/>
+      <c r="B179" s="4">
+        <f>(B137+B138) / 2</f>
+        <v>47761.747051999999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <f t="shared" si="24"/>
         <v>1899</v>
       </c>
-      <c r="B179" s="4">
-        <f t="shared" si="27"/>
-        <v>65952.5</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="1">
-        <f t="shared" si="28"/>
+      <c r="B180" s="4">
+        <f>(B138+B139) / 2</f>
+        <v>58433.622705499998</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <f t="shared" si="24"/>
         <v>1900</v>
       </c>
-      <c r="B180" s="4">
-        <f t="shared" si="27"/>
-        <v>87065</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="1">
-        <f t="shared" si="28"/>
+      <c r="B181" s="4">
+        <f>(B139+B140) / 2</f>
+        <v>77316.456703999997</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <f t="shared" si="24"/>
         <v>1901</v>
       </c>
-      <c r="B181" s="4">
-        <f t="shared" si="27"/>
-        <v>112029</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="1">
-        <f t="shared" si="28"/>
+      <c r="B182" s="4">
+        <f>(B140+B141) / 2</f>
+        <v>99885.385118999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <f t="shared" si="24"/>
         <v>1902</v>
       </c>
-      <c r="B182" s="4">
-        <f t="shared" si="27"/>
-        <v>134239.5</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="1">
-        <f t="shared" si="28"/>
+      <c r="B183" s="4">
+        <f>(B141+B142) / 2</f>
+        <v>120382.89023799999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <f t="shared" si="24"/>
         <v>1903</v>
       </c>
-      <c r="B183" s="4">
-        <f t="shared" si="27"/>
-        <v>154521.5</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="1">
-        <f t="shared" si="28"/>
+      <c r="B184" s="4">
+        <f>(B142+B143) / 2</f>
+        <v>139600.365777</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <f t="shared" si="24"/>
         <v>1904</v>
       </c>
-      <c r="B184" s="4">
-        <f t="shared" si="27"/>
-        <v>172440.5</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="1">
-        <f t="shared" si="28"/>
+      <c r="B185" s="4">
+        <f>(B143+B144) / 2</f>
+        <v>157195.46720850002</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <f t="shared" si="24"/>
         <v>1905</v>
       </c>
-      <c r="B185" s="4">
-        <f t="shared" si="27"/>
-        <v>187758.5</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="1">
-        <f t="shared" si="28"/>
+      <c r="B186" s="4">
+        <f>(B144+B145) / 2</f>
+        <v>173091.990059</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <f t="shared" si="24"/>
         <v>1906</v>
       </c>
-      <c r="B186" s="4">
-        <f t="shared" si="27"/>
-        <v>200118</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="1">
-        <f t="shared" si="28"/>
+      <c r="B187" s="4">
+        <f>(B145+B146) / 2</f>
+        <v>186495.01287400001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <f t="shared" si="24"/>
         <v>1907</v>
       </c>
-      <c r="B187" s="4">
-        <f t="shared" si="27"/>
-        <v>209195</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="1">
-        <f t="shared" si="28"/>
+      <c r="B188" s="4">
+        <f>(B146+B147) / 2</f>
+        <v>196593.37489400001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <f t="shared" si="24"/>
         <v>1908</v>
       </c>
-      <c r="B188" s="4">
-        <f t="shared" si="27"/>
-        <v>214858</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="1">
-        <f t="shared" si="28"/>
+      <c r="B189" s="4">
+        <f>(B147+B148) / 2</f>
+        <v>203316.31396549998</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <f t="shared" si="24"/>
         <v>1909</v>
       </c>
-      <c r="B189" s="4">
-        <f t="shared" si="27"/>
-        <v>217060</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="1">
-        <f t="shared" si="28"/>
+      <c r="B190" s="4">
+        <f>(B148+B149) / 2</f>
+        <v>206582.88415100001</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <f t="shared" si="24"/>
         <v>1910</v>
       </c>
-      <c r="B190" s="4">
-        <f t="shared" si="27"/>
-        <v>215285.5</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="1">
-        <f t="shared" si="28"/>
+      <c r="B191" s="4">
+        <f>(B149+B150) / 2</f>
+        <v>205881.08261149999</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <f t="shared" si="24"/>
         <v>1911</v>
       </c>
-      <c r="B191" s="4">
-        <f t="shared" si="27"/>
-        <v>212083.5</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="1">
-        <f t="shared" si="28"/>
+      <c r="B192" s="4">
+        <f>(B150+B151) / 2</f>
+        <v>203624.59460300001</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <f t="shared" si="24"/>
         <v>1912</v>
       </c>
-      <c r="B192" s="4">
-        <f t="shared" si="27"/>
-        <v>210000</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193" s="1">
-        <f t="shared" si="28"/>
+      <c r="B193" s="4">
+        <f>(B151+B152) / 2</f>
+        <v>202237.20285900001</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <f t="shared" si="24"/>
         <v>1913</v>
       </c>
-      <c r="B193" s="4">
-        <f t="shared" si="27"/>
-        <v>208547</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
-      <c r="A194" s="1">
-        <f t="shared" si="28"/>
+      <c r="B194" s="4">
+        <f>(B152+B153) / 2</f>
+        <v>201258.66536550003</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <f t="shared" si="24"/>
         <v>1914</v>
       </c>
-      <c r="B194" s="4">
-        <f t="shared" si="27"/>
-        <v>207719.5</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
-      <c r="A195" s="10" t="s">
+      <c r="B195" s="4">
+        <f>(B153+B154) / 2</f>
+        <v>200701.38769050001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B195" s="42">
-        <f>SUM(B176:B180)</f>
-        <v>302694</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" ht="30">
-      <c r="A196" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="B196" s="46">
-        <f>B195/5</f>
-        <v>60538.8</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
-      <c r="A197" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="B197" s="44"/>
-      <c r="C197" s="41"/>
-      <c r="D197" s="38"/>
-      <c r="E197" s="38"/>
-    </row>
-    <row r="198" spans="1:5">
-      <c r="A198" s="1">
+      <c r="B196" s="42">
+        <f>SUM(B177:B181)</f>
+        <v>269025.61749849998</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A197" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="B197" s="46">
+        <f>B196/5</f>
+        <v>53805.123499699999</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="B198" s="44"/>
+      <c r="C198" s="41"/>
+      <c r="D198" s="38"/>
+      <c r="E198" s="38"/>
+      <c r="F198" s="38"/>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
         <v>1881</v>
       </c>
-      <c r="B198" s="26">
-        <f>B161/B$196*100</f>
-        <v>16.564583374629162</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
-      <c r="A199" s="1">
-        <f>A198+1</f>
+      <c r="B199" s="26">
+        <f>B162/B$197*100</f>
+        <v>18.475000534206423</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <f>A199+1</f>
         <v>1882</v>
       </c>
-      <c r="B199" s="26">
-        <f t="shared" ref="B199:B212" si="29">B162/B$196*100</f>
-        <v>19.924412112562521</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
-      <c r="A200" s="1">
-        <f t="shared" ref="A200:A212" si="30">A199+1</f>
+      <c r="B200" s="26">
+        <f t="shared" ref="B200:B213" si="25">B163/B$197*100</f>
+        <v>22.28474657634947</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <f t="shared" ref="A201:A213" si="26">A200+1</f>
         <v>1883</v>
       </c>
-      <c r="B200" s="26">
-        <f t="shared" si="29"/>
-        <v>24.424831678196462</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
-      <c r="A201" s="1">
-        <f t="shared" si="30"/>
+      <c r="B201" s="26">
+        <f t="shared" si="25"/>
+        <v>27.466557787163893</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <f t="shared" si="26"/>
         <v>1884</v>
       </c>
-      <c r="B201" s="26">
-        <f t="shared" si="29"/>
-        <v>30.304531969579841</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
-      <c r="A202" s="1">
-        <f t="shared" si="30"/>
+      <c r="B202" s="26">
+        <f t="shared" si="25"/>
+        <v>34.309298893446325</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <f t="shared" si="26"/>
         <v>1885</v>
       </c>
-      <c r="B202" s="26">
-        <f t="shared" si="29"/>
-        <v>38.098706944967525</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
-      <c r="A203" s="1">
-        <f t="shared" si="30"/>
+      <c r="B203" s="26">
+        <f t="shared" si="25"/>
+        <v>43.534343842051776</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <f t="shared" si="26"/>
         <v>1886</v>
       </c>
-      <c r="B203" s="26">
-        <f t="shared" si="29"/>
-        <v>47.195352402095843</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
-      <c r="A204" s="1">
-        <f t="shared" si="30"/>
+      <c r="B204" s="26">
+        <f t="shared" si="25"/>
+        <v>54.118486684938759</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <f t="shared" si="26"/>
         <v>1887</v>
       </c>
-      <c r="B204" s="26">
-        <f t="shared" si="29"/>
-        <v>56.825539984274542</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
-      <c r="A205" s="1">
-        <f t="shared" si="30"/>
+      <c r="B205" s="26">
+        <f t="shared" si="25"/>
+        <v>64.77321484392526</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <f t="shared" si="26"/>
         <v>1888</v>
       </c>
-      <c r="B205" s="26">
-        <f t="shared" si="29"/>
-        <v>67.303943916959042</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
-      <c r="A206" s="1">
-        <f t="shared" si="30"/>
+      <c r="B206" s="26">
+        <f t="shared" si="25"/>
+        <v>75.815000367441684</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <f t="shared" si="26"/>
         <v>1889</v>
       </c>
-      <c r="B206" s="26">
-        <f t="shared" si="29"/>
-        <v>78.685900612499751</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
-      <c r="A207" s="1">
-        <f t="shared" si="30"/>
+      <c r="B207" s="26">
+        <f t="shared" si="25"/>
+        <v>87.207442423697103</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <f t="shared" si="26"/>
         <v>1890</v>
       </c>
-      <c r="B207" s="26">
-        <f t="shared" si="29"/>
-        <v>91.885699749582088</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
-      <c r="A208" s="1">
-        <f t="shared" si="30"/>
+      <c r="B208" s="26">
+        <f t="shared" si="25"/>
+        <v>99.686028922132408</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <f t="shared" si="26"/>
         <v>1891</v>
       </c>
-      <c r="B208" s="26">
-        <f t="shared" si="29"/>
-        <v>103.17019828605787</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2">
-      <c r="A209" s="1">
-        <f t="shared" si="30"/>
+      <c r="B209" s="26">
+        <f t="shared" si="25"/>
+        <v>109.79494355371079</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <f t="shared" si="26"/>
         <v>1892</v>
       </c>
-      <c r="B209" s="26">
-        <f t="shared" si="29"/>
-        <v>108.41724646012143</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2">
-      <c r="A210" s="1">
-        <f t="shared" si="30"/>
+      <c r="B210" s="26">
+        <f t="shared" si="25"/>
+        <v>113.80276875090047</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <f t="shared" si="26"/>
         <v>1893</v>
       </c>
-      <c r="B210" s="26">
-        <f t="shared" si="29"/>
-        <v>108.00098449258988</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="1">
-        <f t="shared" si="30"/>
+      <c r="B211" s="26">
+        <f t="shared" si="25"/>
+        <v>112.09952309622764</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <f t="shared" si="26"/>
         <v>1894</v>
       </c>
-      <c r="B211" s="26">
-        <f t="shared" si="29"/>
-        <v>102.04777762360668</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
-      <c r="A212" s="1">
-        <f t="shared" si="30"/>
+      <c r="B212" s="26">
+        <f t="shared" si="25"/>
+        <v>104.88446435368679</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <f t="shared" si="26"/>
         <v>1895</v>
       </c>
-      <c r="B212" s="26">
-        <f t="shared" si="29"/>
-        <v>89.260110871044688</v>
+      <c r="B213" s="26">
+        <f t="shared" si="25"/>
+        <v>90.877838490181389</v>
       </c>
     </row>
   </sheetData>
@@ -20223,7 +20344,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D506FF2-5C72-4314-9474-BB1C48673607}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
@@ -20233,32 +20354,32 @@
     <col min="8" max="8" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>1</v>
       </c>
@@ -20266,7 +20387,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>1908</v>
       </c>
@@ -20274,7 +20395,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>1917</v>
       </c>
@@ -20282,7 +20403,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>1918</v>
       </c>
@@ -20290,21 +20411,21 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="48" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48" t="s">
+      <c r="C14" s="49"/>
+      <c r="D14" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="48"/>
-      <c r="G14" s="48" t="s">
+      <c r="E14" s="49"/>
+      <c r="G14" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="H14" s="48"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="H14" s="49"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>19</v>
       </c>
@@ -20330,7 +20451,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1896</v>
       </c>
@@ -20360,7 +20481,7 @@
         <v>0.76905150314611981</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f>A16+1</f>
         <v>1897</v>
@@ -20391,7 +20512,7 @@
         <v>1.1447260834014719</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" ref="A18:A36" si="3">A17+1</f>
         <v>1898</v>
@@ -20422,7 +20543,7 @@
         <v>3.4542314335060449E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -20453,7 +20574,7 @@
         <v>1.0711553175210407</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -20484,7 +20605,7 @@
         <v>2.3305537737866153</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -20515,7 +20636,7 @@
         <v>5.4061158328222199</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -20546,7 +20667,7 @@
         <v>7.1772055188530857</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -20577,7 +20698,7 @@
         <v>5.5701523909616393</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -20608,7 +20729,7 @@
         <v>7.0417936438833264</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -20639,7 +20760,7 @@
         <v>5.8077684314695697</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -20670,7 +20791,7 @@
         <v>5.8372604461200126</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -20701,7 +20822,7 @@
         <v>8.159514105330457</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -20732,7 +20853,7 @@
         <v>13.693419551160137</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -20763,7 +20884,7 @@
         <v>9.1432480191529386</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -20794,7 +20915,7 @@
         <v>11.441897961534032</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -20825,7 +20946,7 @@
         <v>13.023456612462224</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -20856,7 +20977,7 @@
         <v>13.15820198482195</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -20887,7 +21008,7 @@
         <v>9.6225471121240762</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -20918,7 +21039,7 @@
         <v>12.839879154078551</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -20949,7 +21070,7 @@
         <v>5.8097109177659272</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -20980,7 +21101,7 @@
         <v>5.6818181818181817</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>80</v>
       </c>
@@ -21027,7 +21148,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" customWidth="1"/>
@@ -21035,7 +21156,7 @@
     <col min="16" max="16" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
@@ -21080,7 +21201,7 @@
       </c>
       <c r="P1" s="10"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1896</v>
       </c>
@@ -21126,7 +21247,7 @@
       <c r="P2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1897</v>
       </c>
@@ -21172,7 +21293,7 @@
       <c r="P3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1898</v>
       </c>
@@ -21218,7 +21339,7 @@
       <c r="P4" s="4"/>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1899</v>
       </c>
@@ -21264,7 +21385,7 @@
       <c r="P5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -21310,7 +21431,7 @@
       <c r="P6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1901</v>
       </c>
@@ -21356,7 +21477,7 @@
       <c r="P7" s="4"/>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1902</v>
       </c>
@@ -21402,7 +21523,7 @@
       <c r="P8" s="4"/>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1903</v>
       </c>
@@ -21448,7 +21569,7 @@
       <c r="P9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1904</v>
       </c>
@@ -21494,7 +21615,7 @@
       <c r="P10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1905</v>
       </c>
@@ -21540,7 +21661,7 @@
       <c r="P11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1906</v>
       </c>
@@ -21586,7 +21707,7 @@
       <c r="P12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1907</v>
       </c>
@@ -21632,7 +21753,7 @@
       <c r="P13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1908</v>
       </c>
@@ -21678,7 +21799,7 @@
       <c r="P14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1909</v>
       </c>
@@ -21724,7 +21845,7 @@
       <c r="P15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1910</v>
       </c>
@@ -21770,7 +21891,7 @@
       <c r="P16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1911</v>
       </c>
@@ -21816,7 +21937,7 @@
       <c r="P17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1912</v>
       </c>
@@ -21862,7 +21983,7 @@
       <c r="P18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1913</v>
       </c>
@@ -21908,7 +22029,7 @@
       <c r="P19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1914</v>
       </c>
@@ -21954,7 +22075,7 @@
       <c r="P20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1915</v>
       </c>
@@ -22000,7 +22121,7 @@
       <c r="P21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1916</v>
       </c>
@@ -22046,33 +22167,33 @@
       <c r="P22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="R24" s="4"/>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="47" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
-      <c r="A29" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -22084,7 +22205,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" ref="C31:M31" si="0">AVERAGE(D2:D6)</f>
+        <f t="shared" ref="D31:M31" si="0">AVERAGE(D2:D6)</f>
         <v>4231.1951632577848</v>
       </c>
       <c r="E31" s="4">
@@ -22127,7 +22248,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -22142,9 +22263,9 @@
       <c r="M32" s="4"/>
       <c r="O32" s="4"/>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -22160,7 +22281,7 @@
       <c r="M33" s="4"/>
       <c r="O33" s="4"/>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -22175,7 +22296,7 @@
       <c r="M34" s="4"/>
       <c r="O34" s="4"/>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -22190,7 +22311,7 @@
       <c r="M35" s="4"/>
       <c r="O35" s="4"/>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -22213,9 +22334,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FEA9BB-FB24-45B6-A20A-F26B22290AE7}">
   <dimension ref="A1:V25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
@@ -22261,15 +22382,15 @@
       <c r="P1" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="T1" s="49" t="s">
-        <v>211</v>
-      </c>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="T1" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1881</v>
       </c>
@@ -22335,7 +22456,7 @@
         <v>879.66944732299817</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1882</v>
       </c>
@@ -22401,7 +22522,7 @@
         <v>1058.094622418228</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1883</v>
       </c>
@@ -22467,7 +22588,7 @@
         <v>1297.0913724413149</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1884</v>
       </c>
@@ -22533,7 +22654,7 @@
         <v>1609.3354288579649</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1885</v>
       </c>
@@ -22599,7 +22720,7 @@
         <v>2023.2485009753946</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1886</v>
       </c>
@@ -22665,7 +22786,7 @@
         <v>2506.3298378728578</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1887</v>
       </c>
@@ -22731,7 +22852,7 @@
         <v>3017.7451627525043</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1888</v>
       </c>
@@ -22797,7 +22918,7 @@
         <v>3574.2053880310632</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1889</v>
       </c>
@@ -22863,7 +22984,7 @@
         <v>4178.6491780967917</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1890</v>
       </c>
@@ -22929,7 +23050,7 @@
         <v>4879.6302863494857</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1891</v>
       </c>
@@ -22995,7 +23116,7 @@
         <v>5478.8985182389079</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>1892</v>
       </c>
@@ -23061,7 +23182,7 @@
         <v>5757.5453071720403</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>1893</v>
       </c>
@@ -23127,7 +23248,7 @@
         <v>5735.4395332664353</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>1894</v>
       </c>
@@ -23193,7 +23314,7 @@
         <v>5419.2918778862877</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1895</v>
       </c>
@@ -23259,22 +23380,22 @@
         <v>4740.1972402266401</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="47" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
-      <c r="A21" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>123</v>
       </c>

--- a/rtss-pre1917/src/main/resources/emigration.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42B11D4-9F4F-4163-91FB-3732AA17827C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21740C73-4730-4EB9-9F14-C3677748D918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="data-1896-1916" sheetId="4" r:id="rId6"/>
     <sheet name="data-1881-1895" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +29,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="217">
   <si>
     <t>Источник: ЦСК, "Ежегодник России" ("Статистический Ежегодник России")</t>
   </si>
@@ -665,22 +670,10 @@
     <t>по календарным годам и по этническим группам</t>
   </si>
   <si>
-    <t>% объёма эмиграции в календарный год сравнительно со среднегодовым за 1896-1900</t>
-  </si>
-  <si>
     <t>% объёма в календарный год сравнительно со среднегодовым за 1896-1900</t>
   </si>
   <si>
-    <t>среднее за 1896-1900  для расчёта 1881-1895, финская эмиграция из Выборгской губернии в этот период исчезает</t>
-  </si>
-  <si>
     <t>v</t>
-  </si>
-  <si>
-    <t>v-diff</t>
-  </si>
-  <si>
-    <t>###!!!без финляндии</t>
   </si>
   <si>
     <t>Эмиграция из России в различные страны (для США - по финансовым годам) с поправкой на более точный учёт эмиграции</t>
@@ -705,6 +698,21 @@
 Польшей
 в США</t>
   </si>
+  <si>
+    <t>среднее за 1896-1900  для расчёта 1881-1895</t>
+  </si>
+  <si>
+    <t>средний состав эмиграции  за 1896-1900  для расчёта 1881-1895, финская эмиграция из Выборгской губернии в этот период исчезает</t>
+  </si>
+  <si>
+    <t>То же без Финляндии, т.к. , финская эмиграция из Выборгской губернии в период до 1895 практически исчезает (становится единичной)</t>
+  </si>
+  <si>
+    <t>% для Выборгской губернии фиктивен (умножается на 0) и используется общим кодом загрузки</t>
+  </si>
+  <si>
+    <t>v%</t>
+  </si>
 </sst>
 </file>
 
@@ -715,7 +723,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -789,7 +797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -890,13 +898,17 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,9 +927,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -955,7 +967,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1061,7 +1073,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1203,7 +1215,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1212,24 +1224,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E018E8-FFD2-476D-8A98-BDF34A70858D}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.578125" customWidth="1"/>
+    <col min="3" max="3" width="20.83984375" customWidth="1"/>
+    <col min="4" max="4" width="24.578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="28.8">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1241,7 +1253,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="B6" s="1">
         <v>1904</v>
       </c>
@@ -1252,7 +1264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="B7" s="1">
         <v>1906</v>
       </c>
@@ -1263,7 +1275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="B8" s="1">
         <v>1909</v>
       </c>
@@ -1274,7 +1286,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="B9" s="1">
         <v>1910</v>
       </c>
@@ -1285,7 +1297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="B10" s="1">
         <v>1911</v>
       </c>
@@ -1296,7 +1308,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="B11" s="1">
         <v>1912</v>
       </c>
@@ -1307,7 +1319,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="B12" s="1">
         <v>1913</v>
       </c>
@@ -1318,162 +1330,162 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2">
       <c r="B18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2">
       <c r="B22" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2">
       <c r="B23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2">
       <c r="B24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2">
       <c r="B25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2">
       <c r="B27" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2">
       <c r="B28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2">
       <c r="B30" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2">
       <c r="B31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2">
       <c r="B32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="B34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="B35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="B37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="B38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="B40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="B41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="B42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="B59" s="1" t="s">
         <v>53</v>
       </c>
@@ -1481,7 +1493,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="B60" s="1">
         <v>1896</v>
       </c>
@@ -1489,7 +1501,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="B61" s="1">
         <f>B60+1</f>
         <v>1897</v>
@@ -1498,7 +1510,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="B62" s="1">
         <f t="shared" ref="B62:B80" si="0">B61+1</f>
         <v>1898</v>
@@ -1507,7 +1519,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="B63" s="1">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -1516,7 +1528,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="B64" s="1">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -1525,7 +1537,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3">
       <c r="B65" s="1">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -1534,7 +1546,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3">
       <c r="B66" s="1">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -1543,7 +1555,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3">
       <c r="B67" s="1">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -1552,7 +1564,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3">
       <c r="B68" s="1">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -1561,7 +1573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3">
       <c r="B69" s="1">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -1570,7 +1582,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3">
       <c r="B70" s="1">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -1579,7 +1591,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3">
       <c r="B71" s="1">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -1588,7 +1600,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:3">
       <c r="B72" s="1">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -1597,7 +1609,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3">
       <c r="B73" s="1">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -1606,7 +1618,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3">
       <c r="B74" s="1">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -1615,7 +1627,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3">
       <c r="B75" s="1">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -1624,7 +1636,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3">
       <c r="B76" s="1">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -1633,7 +1645,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3">
       <c r="B77" s="1">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -1642,7 +1654,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3">
       <c r="B78" s="1">
         <f t="shared" si="0"/>
         <v>1914</v>
@@ -1651,7 +1663,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3">
       <c r="B79" s="1">
         <f t="shared" si="0"/>
         <v>1915</v>
@@ -1660,7 +1672,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3">
       <c r="B80" s="1">
         <f t="shared" si="0"/>
         <v>1916</v>
@@ -1669,7 +1681,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="B81" s="1">
         <v>1917</v>
       </c>
@@ -1677,22 +1689,22 @@
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="B88" s="1">
         <v>1908</v>
       </c>
@@ -1700,7 +1712,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="B89" s="1">
         <f t="shared" ref="B89:B96" si="1">B88+1</f>
         <v>1909</v>
@@ -1709,7 +1721,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="B90" s="1">
         <f t="shared" si="1"/>
         <v>1910</v>
@@ -1718,7 +1730,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3">
       <c r="B91" s="1">
         <f t="shared" si="1"/>
         <v>1911</v>
@@ -1727,7 +1739,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="B92" s="1">
         <f t="shared" si="1"/>
         <v>1912</v>
@@ -1736,7 +1748,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="B93" s="1">
         <f t="shared" si="1"/>
         <v>1913</v>
@@ -1745,7 +1757,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="B94" s="1">
         <f t="shared" si="1"/>
         <v>1914</v>
@@ -1754,7 +1766,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="B95" s="1">
         <f t="shared" si="1"/>
         <v>1915</v>
@@ -1763,7 +1775,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3">
       <c r="B96" s="1">
         <f t="shared" si="1"/>
         <v>1916</v>
@@ -1772,7 +1784,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:3">
       <c r="B97" s="1">
         <v>1917</v>
       </c>
@@ -1788,14 +1800,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7496F63D-12C4-4F78-B39E-C61E39C373AD}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.41796875" customWidth="1"/>
+    <col min="5" max="5" width="12.41796875" customWidth="1"/>
+    <col min="6" max="6" width="27.15625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="43.2">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -1836,7 +1848,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20">
       <c r="A2" s="1">
         <v>1896</v>
       </c>
@@ -1879,7 +1891,7 @@
         <v>52136</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>1897</v>
@@ -1921,7 +1933,7 @@
         <v>29981</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A22" si="3">A3+1</f>
         <v>1898</v>
@@ -1963,7 +1975,7 @@
         <v>34554</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20">
       <c r="A5" s="1">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -1987,7 +1999,7 @@
         <v>57773.68421052632</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20">
       <c r="A6" s="1">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -2011,7 +2023,7 @@
         <v>82289.473684210534</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20">
       <c r="A7" s="1">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -2035,7 +2047,7 @@
         <v>79218.947368421053</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20">
       <c r="A8" s="1">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -2059,7 +2071,7 @@
         <v>98398.947368421053</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20">
       <c r="A9" s="1">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -2083,7 +2095,7 @@
         <v>123398.94736842105</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20">
       <c r="A10" s="1">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -2107,7 +2119,7 @@
         <v>142088.42105263157</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20">
       <c r="A11" s="1">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -2131,7 +2143,7 @@
         <v>176721.05263157896</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20">
       <c r="A12" s="1">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -2155,7 +2167,7 @@
         <v>212135.78947368421</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20">
       <c r="A13" s="1">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -2179,7 +2191,7 @@
         <v>256929.47368421053</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20">
       <c r="A14" s="1">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -2203,7 +2215,7 @@
         <v>157857.89473684211</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20">
       <c r="A15" s="1">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -2227,7 +2239,7 @@
         <v>114497.89473684211</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20">
       <c r="A16" s="1">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -2251,7 +2263,7 @@
         <v>180058.94736842107</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -2275,7 +2287,7 @@
         <v>156781.05263157896</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -2299,7 +2311,7 @@
         <v>163951.57894736843</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -2323,7 +2335,7 @@
         <v>292930.5263157895</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -2347,7 +2359,7 @@
         <v>255636.84210526317</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -2371,7 +2383,7 @@
         <v>23910.526315789473</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -2395,7 +2407,7 @@
         <v>2308.4210526315792</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2420,7 +2432,7 @@
         <v>2687088.4210526319</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
@@ -2432,58 +2444,58 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54424CF4-C226-4A4F-8C1B-D8A2CB8D4757}">
   <dimension ref="A1:AI310"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.578125" customWidth="1"/>
+    <col min="2" max="2" width="7.26171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.15625" customWidth="1"/>
+    <col min="4" max="4" width="7.578125" customWidth="1"/>
+    <col min="5" max="5" width="5.68359375" customWidth="1"/>
+    <col min="6" max="6" width="9.578125" customWidth="1"/>
+    <col min="7" max="7" width="8.15625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.68359375" customWidth="1"/>
+    <col min="9" max="9" width="7.578125" customWidth="1"/>
+    <col min="10" max="10" width="7.15625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.42578125" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.15625" customWidth="1"/>
+    <col min="13" max="13" width="6.83984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.41796875" customWidth="1"/>
+    <col min="17" max="17" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35">
       <c r="A3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35">
       <c r="A5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35">
       <c r="A6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -2491,7 +2503,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35">
       <c r="P9" s="14" t="s">
         <v>71</v>
       </c>
@@ -2524,7 +2536,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35">
       <c r="A10" s="10" t="s">
         <v>84</v>
       </c>
@@ -2607,7 +2619,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35">
       <c r="A11" s="1">
         <v>1896</v>
       </c>
@@ -2661,7 +2673,7 @@
       </c>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35">
       <c r="A12" s="1">
         <f>A11+1</f>
         <v>1897</v>
@@ -2716,7 +2728,7 @@
       </c>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35">
       <c r="A13" s="1">
         <f t="shared" ref="A13:A31" si="2">A12+1</f>
         <v>1898</v>
@@ -2771,7 +2783,7 @@
       </c>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>1899</v>
@@ -2869,7 +2881,7 @@
         <v>4.3528753924899997</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>1900</v>
@@ -2967,7 +2979,7 @@
         <v>5.6415392085457636</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>1901</v>
@@ -3065,7 +3077,7 @@
         <v>2.5448767286540708</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1902</v>
@@ -3163,7 +3175,7 @@
         <v>3.0960917891717461</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1903</v>
@@ -3261,7 +3273,7 @@
         <v>1.9799110237312059</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1904</v>
@@ -3359,7 +3371,7 @@
         <v>1.427190352127677</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>1905</v>
@@ -3457,7 +3469,7 @@
         <v>1.1078286558345642</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>1906</v>
@@ -3555,7 +3567,7 @@
         <v>1.61159938769543</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>1907</v>
@@ -3653,7 +3665,7 @@
         <v>2.650444548432382</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>1908</v>
@@ -3751,7 +3763,7 @@
         <v>1.6072463326115465</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>1909</v>
@@ -3849,7 +3861,7 @@
         <v>1.6887644302205966</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>1910</v>
@@ -3947,7 +3959,7 @@
         <v>2.6865499548398257</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>1911</v>
@@ -4045,7 +4057,7 @@
         <v>1.5918358446542664</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>1912</v>
@@ -4143,7 +4155,7 @@
         <v>1.3100851238884845</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>1913</v>
@@ -4241,7 +4253,7 @@
         <v>2.3027080052662829</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>1914</v>
@@ -4339,7 +4351,7 @@
         <v>2.0608548525781489</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>1915</v>
@@ -4437,7 +4449,7 @@
         <v>0.49870172690928577</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>1916</v>
@@ -4535,7 +4547,7 @@
         <v>1.3926559566033798</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35">
       <c r="A32" s="1">
         <v>1917</v>
       </c>
@@ -4632,7 +4644,7 @@
         <v>5.8184812868690303E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35">
       <c r="P33" s="17">
         <f>SUM(P14:P31)-P32</f>
         <v>0</v>
@@ -4675,7 +4687,7 @@
       </c>
       <c r="AI33" s="4"/>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4728,7 +4740,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -4781,12 +4793,12 @@
         <v>0.1375376540970189</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35">
       <c r="A38" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35">
       <c r="A40" s="10" t="s">
         <v>87</v>
       </c>
@@ -4830,7 +4842,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35">
       <c r="A41" s="1">
         <v>1896</v>
       </c>
@@ -4887,7 +4899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35">
       <c r="A42" s="1">
         <f>A41+1</f>
         <v>1897</v>
@@ -4945,7 +4957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35">
       <c r="A43" s="1">
         <f t="shared" ref="A43:A60" si="17">A42+1</f>
         <v>1898</v>
@@ -5003,7 +5015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35">
       <c r="A44" s="1">
         <f t="shared" si="17"/>
         <v>1899</v>
@@ -5061,7 +5073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35">
       <c r="A45" s="1">
         <f t="shared" si="17"/>
         <v>1900</v>
@@ -5119,7 +5131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35">
       <c r="A46" s="1">
         <f t="shared" si="17"/>
         <v>1901</v>
@@ -5177,7 +5189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35">
       <c r="A47" s="1">
         <f t="shared" si="17"/>
         <v>1902</v>
@@ -5235,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35">
       <c r="A48" s="1">
         <f t="shared" si="17"/>
         <v>1903</v>
@@ -5293,7 +5305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15">
       <c r="A49" s="1">
         <f t="shared" si="17"/>
         <v>1904</v>
@@ -5351,7 +5363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15">
       <c r="A50" s="1">
         <f t="shared" si="17"/>
         <v>1905</v>
@@ -5409,7 +5421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15">
       <c r="A51" s="1">
         <f t="shared" si="17"/>
         <v>1906</v>
@@ -5467,7 +5479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15">
       <c r="A52" s="1">
         <f t="shared" si="17"/>
         <v>1907</v>
@@ -5525,7 +5537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15">
       <c r="A53" s="1">
         <f t="shared" si="17"/>
         <v>1908</v>
@@ -5583,7 +5595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15">
       <c r="A54" s="1">
         <f t="shared" si="17"/>
         <v>1909</v>
@@ -5641,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15">
       <c r="A55" s="1">
         <f t="shared" si="17"/>
         <v>1910</v>
@@ -5699,7 +5711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15">
       <c r="A56" s="1">
         <f t="shared" si="17"/>
         <v>1911</v>
@@ -5757,7 +5769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15">
       <c r="A57" s="1">
         <f t="shared" si="17"/>
         <v>1912</v>
@@ -5815,7 +5827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15">
       <c r="A58" s="1">
         <f t="shared" si="17"/>
         <v>1913</v>
@@ -5873,7 +5885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15">
       <c r="A59" s="1">
         <f t="shared" si="17"/>
         <v>1914</v>
@@ -5931,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15">
       <c r="A60" s="1">
         <f t="shared" si="17"/>
         <v>1915</v>
@@ -5989,7 +6001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15">
       <c r="A61" s="1">
         <v>1916</v>
       </c>
@@ -6046,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15">
       <c r="A62" s="11" t="s">
         <v>49</v>
       </c>
@@ -6103,7 +6115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15">
       <c r="A63" s="11" t="s">
         <v>88</v>
       </c>
@@ -6156,12 +6168,12 @@
         <v>0.12899442300236147</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68" s="10" t="s">
         <v>84</v>
       </c>
@@ -6202,7 +6214,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69" s="1">
         <v>1908</v>
       </c>
@@ -6244,7 +6256,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70" s="1">
         <f t="shared" ref="A70:A76" si="39">A69+1</f>
         <v>1909</v>
@@ -6287,7 +6299,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71" s="1">
         <f t="shared" si="39"/>
         <v>1910</v>
@@ -6330,7 +6342,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72" s="1">
         <f t="shared" si="39"/>
         <v>1911</v>
@@ -6356,7 +6368,7 @@
       </c>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73" s="1">
         <f t="shared" si="39"/>
         <v>1912</v>
@@ -6399,7 +6411,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" s="1">
         <f t="shared" si="39"/>
         <v>1913</v>
@@ -6425,7 +6437,7 @@
       </c>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19">
       <c r="A75" s="1">
         <f t="shared" si="39"/>
         <v>1914</v>
@@ -6468,7 +6480,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19">
       <c r="A76" s="1">
         <f t="shared" si="39"/>
         <v>1915</v>
@@ -6520,7 +6532,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" s="1">
         <v>1916</v>
       </c>
@@ -6570,7 +6582,7 @@
         <v>1.1658168920416758</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19">
       <c r="A78" s="1">
         <v>1917</v>
       </c>
@@ -6600,12 +6612,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13">
       <c r="A82" s="10" t="s">
         <v>84</v>
       </c>
@@ -6646,7 +6658,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13">
       <c r="A83" s="1">
         <v>1908</v>
       </c>
@@ -6688,7 +6700,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13">
       <c r="A84" s="1">
         <f t="shared" ref="A84:A90" si="41">A83+1</f>
         <v>1909</v>
@@ -6731,7 +6743,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13">
       <c r="A85" s="1">
         <f t="shared" si="41"/>
         <v>1910</v>
@@ -6774,7 +6786,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13">
       <c r="A86" s="1">
         <f t="shared" si="41"/>
         <v>1911</v>
@@ -6800,7 +6812,7 @@
       </c>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13">
       <c r="A87" s="1">
         <f t="shared" si="41"/>
         <v>1912</v>
@@ -6843,7 +6855,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13">
       <c r="A88" s="1">
         <f t="shared" si="41"/>
         <v>1913</v>
@@ -6869,7 +6881,7 @@
       </c>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13">
       <c r="A89" s="1">
         <f t="shared" si="41"/>
         <v>1914</v>
@@ -6912,7 +6924,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13">
       <c r="A90" s="1">
         <f t="shared" si="41"/>
         <v>1915</v>
@@ -6955,7 +6967,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13">
       <c r="A91" s="1">
         <v>1916</v>
       </c>
@@ -6997,7 +7009,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13">
       <c r="A92" s="1">
         <v>1917</v>
       </c>
@@ -7022,12 +7034,12 @@
       </c>
       <c r="M92" s="4"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13">
       <c r="A94" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13">
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
@@ -7065,7 +7077,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13">
       <c r="A97" t="s">
         <v>143</v>
       </c>
@@ -7118,7 +7130,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13">
       <c r="A98" t="s">
         <v>144</v>
       </c>
@@ -7171,7 +7183,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13">
       <c r="A99" t="s">
         <v>145</v>
       </c>
@@ -7224,7 +7236,7 @@
         <v>54.280155642023345</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13">
       <c r="B100" s="26"/>
       <c r="C100" s="26"/>
       <c r="D100" s="26"/>
@@ -7238,7 +7250,7 @@
       <c r="L100" s="26"/>
       <c r="M100" s="26"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13">
       <c r="A101" t="s">
         <v>152</v>
       </c>
@@ -7255,7 +7267,7 @@
       <c r="L101" s="26"/>
       <c r="M101" s="26"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13">
       <c r="B102" s="26"/>
       <c r="C102" s="26"/>
       <c r="D102" s="26"/>
@@ -7269,7 +7281,7 @@
       <c r="L102" s="26"/>
       <c r="M102" s="26"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13">
       <c r="B103" s="10" t="s">
         <v>70</v>
       </c>
@@ -7307,7 +7319,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13">
       <c r="A104" t="s">
         <v>143</v>
       </c>
@@ -7360,7 +7372,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13">
       <c r="A105" t="s">
         <v>144</v>
       </c>
@@ -7413,7 +7425,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13">
       <c r="A106" t="s">
         <v>145</v>
       </c>
@@ -7466,7 +7478,7 @@
         <v>47.149894440534837</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13">
       <c r="B107" s="26"/>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
@@ -7480,7 +7492,7 @@
       <c r="L107" s="26"/>
       <c r="M107" s="26"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13">
       <c r="A108" t="s">
         <v>153</v>
       </c>
@@ -7497,7 +7509,7 @@
       <c r="L108" s="26"/>
       <c r="M108" s="26"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13">
       <c r="A109" t="s">
         <v>154</v>
       </c>
@@ -7514,7 +7526,7 @@
       <c r="L109" s="26"/>
       <c r="M109" s="26"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13">
       <c r="B110" s="26"/>
       <c r="C110" s="26"/>
       <c r="D110" s="26"/>
@@ -7528,7 +7540,7 @@
       <c r="L110" s="26"/>
       <c r="M110" s="26"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13">
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
@@ -7566,7 +7578,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13">
       <c r="B112" s="26">
         <f>B106</f>
         <v>6.9984447900466566</v>
@@ -7616,12 +7628,12 @@
         <v>50.715025041279091</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16">
       <c r="A114" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16">
       <c r="A116" s="10" t="s">
         <v>84</v>
       </c>
@@ -7668,7 +7680,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16">
       <c r="A117" s="1">
         <v>1896</v>
       </c>
@@ -7725,7 +7737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16">
       <c r="A118" s="1">
         <f>A117+1</f>
         <v>1897</v>
@@ -7783,7 +7795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16">
       <c r="A119" s="1">
         <f t="shared" ref="A119:A137" si="54">A118+1</f>
         <v>1898</v>
@@ -7841,7 +7853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16">
       <c r="A120" s="1">
         <f t="shared" si="54"/>
         <v>1899</v>
@@ -7899,7 +7911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16">
       <c r="A121" s="1">
         <f t="shared" si="54"/>
         <v>1900</v>
@@ -7957,7 +7969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16">
       <c r="A122" s="1">
         <f t="shared" si="54"/>
         <v>1901</v>
@@ -8015,7 +8027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16">
       <c r="A123" s="1">
         <f t="shared" si="54"/>
         <v>1902</v>
@@ -8073,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16">
       <c r="A124" s="1">
         <f t="shared" si="54"/>
         <v>1903</v>
@@ -8131,7 +8143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16">
       <c r="A125" s="1">
         <f t="shared" si="54"/>
         <v>1904</v>
@@ -8189,7 +8201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16">
       <c r="A126" s="1">
         <f t="shared" si="54"/>
         <v>1905</v>
@@ -8247,7 +8259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16">
       <c r="A127" s="1">
         <f t="shared" si="54"/>
         <v>1906</v>
@@ -8305,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16">
       <c r="A128" s="1">
         <f t="shared" si="54"/>
         <v>1907</v>
@@ -8363,7 +8375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16">
       <c r="A129" s="1">
         <f t="shared" si="54"/>
         <v>1908</v>
@@ -8410,7 +8422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16">
       <c r="A130" s="1">
         <f t="shared" si="54"/>
         <v>1909</v>
@@ -8457,7 +8469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16">
       <c r="A131" s="1">
         <f t="shared" si="54"/>
         <v>1910</v>
@@ -8504,7 +8516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16">
       <c r="A132" s="1">
         <f t="shared" si="54"/>
         <v>1911</v>
@@ -8562,7 +8574,7 @@
         <v>15723.438359773389</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16">
       <c r="A133" s="1">
         <f t="shared" si="54"/>
         <v>1912</v>
@@ -8609,7 +8621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16">
       <c r="A134" s="1">
         <f t="shared" si="54"/>
         <v>1913</v>
@@ -8667,7 +8679,7 @@
         <v>36173.276557684701</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16">
       <c r="A135" s="1">
         <f t="shared" si="54"/>
         <v>1914</v>
@@ -8714,7 +8726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16">
       <c r="A136" s="1">
         <f t="shared" si="54"/>
         <v>1915</v>
@@ -8761,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16">
       <c r="A137" s="1">
         <f t="shared" si="54"/>
         <v>1916</v>
@@ -8808,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16">
       <c r="A138" s="1">
         <v>1917</v>
       </c>
@@ -8865,7 +8877,7 @@
         <v>639.69124188047317</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16">
       <c r="A139" s="1"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -8880,7 +8892,7 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16">
       <c r="A140" s="30" t="s">
         <v>174</v>
       </c>
@@ -8897,7 +8909,7 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16">
       <c r="A141" s="1"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -8912,7 +8924,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16">
       <c r="A142" s="1">
         <v>1911</v>
       </c>
@@ -8953,7 +8965,7 @@
         <v>-11.876056132993654</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16">
       <c r="A143" s="1">
         <f>A142+1</f>
         <v>1912</v>
@@ -8971,7 +8983,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16">
       <c r="A144" s="1">
         <f t="shared" ref="A144:A148" si="74">A143+1</f>
         <v>1913</v>
@@ -9013,7 +9025,7 @@
         <v>116.94950349421394</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15">
       <c r="A145" s="1">
         <f t="shared" si="74"/>
         <v>1914</v>
@@ -9031,7 +9043,7 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15">
       <c r="A146" s="1">
         <f t="shared" si="74"/>
         <v>1915</v>
@@ -9049,7 +9061,7 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15">
       <c r="A147" s="1">
         <f t="shared" si="74"/>
         <v>1916</v>
@@ -9067,7 +9079,7 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15">
       <c r="A148" s="1">
         <f t="shared" si="74"/>
         <v>1917</v>
@@ -9109,7 +9121,7 @@
         <v>218.84913831012869</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15">
       <c r="A149" s="1"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -9124,7 +9136,7 @@
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15">
       <c r="A150" s="30" t="s">
         <v>172</v>
       </c>
@@ -9141,7 +9153,7 @@
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15">
       <c r="A151" s="1"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -9156,7 +9168,7 @@
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15">
       <c r="A152" s="10" t="str">
         <f t="shared" ref="A152:M152" si="76">A116</f>
         <v>фин. год</v>
@@ -9215,7 +9227,7 @@
         <v>разница</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15">
       <c r="A153" s="1">
         <f t="shared" ref="A153:M153" si="77">A117</f>
         <v>1896</v>
@@ -9274,7 +9286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15">
       <c r="A154" s="1">
         <f t="shared" ref="A154:M154" si="79">A118</f>
         <v>1897</v>
@@ -9333,7 +9345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15">
       <c r="A155" s="1">
         <f t="shared" ref="A155:M155" si="80">A119</f>
         <v>1898</v>
@@ -9392,7 +9404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15">
       <c r="A156" s="1">
         <f t="shared" ref="A156:M156" si="81">A120</f>
         <v>1899</v>
@@ -9451,7 +9463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15">
       <c r="A157" s="1">
         <f t="shared" ref="A157:M157" si="82">A121</f>
         <v>1900</v>
@@ -9510,7 +9522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15">
       <c r="A158" s="1">
         <f t="shared" ref="A158:M158" si="83">A122</f>
         <v>1901</v>
@@ -9569,7 +9581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15">
       <c r="A159" s="1">
         <f t="shared" ref="A159:M159" si="84">A123</f>
         <v>1902</v>
@@ -9628,7 +9640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15">
       <c r="A160" s="1">
         <f t="shared" ref="A160:M160" si="85">A124</f>
         <v>1903</v>
@@ -9687,7 +9699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15">
       <c r="A161" s="1">
         <f t="shared" ref="A161:M161" si="86">A125</f>
         <v>1904</v>
@@ -9746,7 +9758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15">
       <c r="A162" s="1">
         <f t="shared" ref="A162:M162" si="87">A126</f>
         <v>1905</v>
@@ -9805,7 +9817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15">
       <c r="A163" s="1">
         <f t="shared" ref="A163:M163" si="88">A127</f>
         <v>1906</v>
@@ -9864,7 +9876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15">
       <c r="A164" s="1">
         <f t="shared" ref="A164:M164" si="89">A128</f>
         <v>1907</v>
@@ -9923,7 +9935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15">
       <c r="A165" s="1">
         <f t="shared" ref="A165:M165" si="90">A129</f>
         <v>1908</v>
@@ -9982,7 +9994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15">
       <c r="A166" s="1">
         <f t="shared" ref="A166:M166" si="91">A130</f>
         <v>1909</v>
@@ -10041,7 +10053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15">
       <c r="A167" s="1">
         <f t="shared" ref="A167:M167" si="92">A131</f>
         <v>1910</v>
@@ -10100,7 +10112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15">
       <c r="A168" s="1">
         <f t="shared" ref="A168:A174" si="93">A132</f>
         <v>1911</v>
@@ -10159,7 +10171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15">
       <c r="A169" s="1">
         <f t="shared" si="93"/>
         <v>1912</v>
@@ -10218,7 +10230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15">
       <c r="A170" s="1">
         <f t="shared" si="93"/>
         <v>1913</v>
@@ -10277,7 +10289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15">
       <c r="A171" s="1">
         <f t="shared" si="93"/>
         <v>1914</v>
@@ -10336,7 +10348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15">
       <c r="A172" s="1">
         <f t="shared" si="93"/>
         <v>1915</v>
@@ -10395,7 +10407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15">
       <c r="A173" s="1">
         <f t="shared" si="93"/>
         <v>1916</v>
@@ -10454,7 +10466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15">
       <c r="A174" s="1">
         <f t="shared" si="93"/>
         <v>1917</v>
@@ -10513,12 +10525,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15">
       <c r="A176" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16">
       <c r="A178" s="10" t="s">
         <v>84</v>
       </c>
@@ -10562,7 +10574,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16">
       <c r="A179" s="1">
         <v>1896</v>
       </c>
@@ -10620,7 +10632,7 @@
       </c>
       <c r="P179" s="4"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16">
       <c r="A180" s="1">
         <f>A179+1</f>
         <v>1897</v>
@@ -10679,7 +10691,7 @@
       </c>
       <c r="P180" s="4"/>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16">
       <c r="A181" s="1">
         <f t="shared" ref="A181:A199" si="104">A180+1</f>
         <v>1898</v>
@@ -10738,7 +10750,7 @@
       </c>
       <c r="P181" s="4"/>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16">
       <c r="A182" s="1">
         <f t="shared" si="104"/>
         <v>1899</v>
@@ -10797,7 +10809,7 @@
       </c>
       <c r="P182" s="4"/>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16">
       <c r="A183" s="1">
         <f t="shared" si="104"/>
         <v>1900</v>
@@ -10856,7 +10868,7 @@
       </c>
       <c r="P183" s="4"/>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16">
       <c r="A184" s="1">
         <f t="shared" si="104"/>
         <v>1901</v>
@@ -10915,7 +10927,7 @@
       </c>
       <c r="P184" s="4"/>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16">
       <c r="A185" s="1">
         <f t="shared" si="104"/>
         <v>1902</v>
@@ -10974,7 +10986,7 @@
       </c>
       <c r="P185" s="4"/>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16">
       <c r="A186" s="1">
         <f t="shared" si="104"/>
         <v>1903</v>
@@ -11033,7 +11045,7 @@
       </c>
       <c r="P186" s="4"/>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16">
       <c r="A187" s="1">
         <f t="shared" si="104"/>
         <v>1904</v>
@@ -11092,7 +11104,7 @@
       </c>
       <c r="P187" s="4"/>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16">
       <c r="A188" s="1">
         <f t="shared" si="104"/>
         <v>1905</v>
@@ -11151,7 +11163,7 @@
       </c>
       <c r="P188" s="4"/>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16">
       <c r="A189" s="1">
         <f t="shared" si="104"/>
         <v>1906</v>
@@ -11210,7 +11222,7 @@
       </c>
       <c r="P189" s="4"/>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16">
       <c r="A190" s="1">
         <f t="shared" si="104"/>
         <v>1907</v>
@@ -11269,7 +11281,7 @@
       </c>
       <c r="P190" s="4"/>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16">
       <c r="A191" s="1">
         <f t="shared" si="104"/>
         <v>1908</v>
@@ -11327,7 +11339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16">
       <c r="A192" s="1">
         <f t="shared" si="104"/>
         <v>1909</v>
@@ -11385,7 +11397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15">
       <c r="A193" s="1">
         <f t="shared" si="104"/>
         <v>1910</v>
@@ -11443,7 +11455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15">
       <c r="A194" s="1">
         <f t="shared" si="104"/>
         <v>1911</v>
@@ -11501,7 +11513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15">
       <c r="A195" s="1">
         <f t="shared" si="104"/>
         <v>1912</v>
@@ -11559,7 +11571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15">
       <c r="A196" s="1">
         <f t="shared" si="104"/>
         <v>1913</v>
@@ -11617,7 +11629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15">
       <c r="A197" s="1">
         <f t="shared" si="104"/>
         <v>1914</v>
@@ -11675,7 +11687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15">
       <c r="A198" s="1">
         <f t="shared" si="104"/>
         <v>1915</v>
@@ -11733,7 +11745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15">
       <c r="A199" s="1">
         <f t="shared" si="104"/>
         <v>1916</v>
@@ -11791,7 +11803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15">
       <c r="A200" s="1">
         <v>1917</v>
       </c>
@@ -11848,12 +11860,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15">
       <c r="A202" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15">
       <c r="A204" s="10" t="s">
         <v>87</v>
       </c>
@@ -11897,7 +11909,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15">
       <c r="A205" s="1">
         <v>1896</v>
       </c>
@@ -11954,7 +11966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15">
       <c r="A206" s="1">
         <f>A205+1</f>
         <v>1897</v>
@@ -12012,7 +12024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15">
       <c r="A207" s="1">
         <f t="shared" ref="A207:A224" si="128">A206+1</f>
         <v>1898</v>
@@ -12070,7 +12082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15">
       <c r="A208" s="1">
         <f t="shared" si="128"/>
         <v>1899</v>
@@ -12128,7 +12140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15">
       <c r="A209" s="1">
         <f t="shared" si="128"/>
         <v>1900</v>
@@ -12186,7 +12198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15">
       <c r="A210" s="1">
         <f t="shared" si="128"/>
         <v>1901</v>
@@ -12244,7 +12256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15">
       <c r="A211" s="1">
         <f t="shared" si="128"/>
         <v>1902</v>
@@ -12302,7 +12314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15">
       <c r="A212" s="1">
         <f t="shared" si="128"/>
         <v>1903</v>
@@ -12360,7 +12372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15">
       <c r="A213" s="1">
         <f t="shared" si="128"/>
         <v>1904</v>
@@ -12418,7 +12430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15">
       <c r="A214" s="1">
         <f t="shared" si="128"/>
         <v>1905</v>
@@ -12476,7 +12488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15">
       <c r="A215" s="1">
         <f t="shared" si="128"/>
         <v>1906</v>
@@ -12534,7 +12546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15">
       <c r="A216" s="1">
         <f t="shared" si="128"/>
         <v>1907</v>
@@ -12592,7 +12604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15">
       <c r="A217" s="1">
         <f t="shared" si="128"/>
         <v>1908</v>
@@ -12650,7 +12662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15">
       <c r="A218" s="1">
         <f t="shared" si="128"/>
         <v>1909</v>
@@ -12708,7 +12720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15">
       <c r="A219" s="1">
         <f t="shared" si="128"/>
         <v>1910</v>
@@ -12766,7 +12778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15">
       <c r="A220" s="1">
         <f t="shared" si="128"/>
         <v>1911</v>
@@ -12824,7 +12836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15">
       <c r="A221" s="1">
         <f t="shared" si="128"/>
         <v>1912</v>
@@ -12882,7 +12894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15">
       <c r="A222" s="1">
         <f t="shared" si="128"/>
         <v>1913</v>
@@ -12940,7 +12952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15">
       <c r="A223" s="1">
         <f t="shared" si="128"/>
         <v>1914</v>
@@ -12998,7 +13010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15">
       <c r="A224" s="1">
         <f t="shared" si="128"/>
         <v>1915</v>
@@ -13056,7 +13068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15">
       <c r="A225" s="1">
         <v>1916</v>
       </c>
@@ -13113,7 +13125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15">
       <c r="A226" s="11" t="s">
         <v>49</v>
       </c>
@@ -13170,7 +13182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15">
       <c r="A227" s="11" t="s">
         <v>88</v>
       </c>
@@ -13223,15 +13235,15 @@
         <v>8.2845503895924058E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15">
       <c r="A229" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15">
       <c r="L230" s="4"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15">
       <c r="A231" t="s">
         <v>181</v>
       </c>
@@ -13240,10 +13252,10 @@
       </c>
       <c r="L231" s="4"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15">
       <c r="L232" s="4"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15">
       <c r="A233" s="10" t="s">
         <v>87</v>
       </c>
@@ -13287,7 +13299,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15">
       <c r="A234" s="1">
         <v>1896</v>
       </c>
@@ -13344,7 +13356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15">
       <c r="A235" s="1">
         <f>A234+1</f>
         <v>1897</v>
@@ -13402,7 +13414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15">
       <c r="A236" s="1">
         <f t="shared" ref="A236:A253" si="153">A235+1</f>
         <v>1898</v>
@@ -13460,7 +13472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15">
       <c r="A237" s="1">
         <f t="shared" si="153"/>
         <v>1899</v>
@@ -13518,7 +13530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15">
       <c r="A238" s="1">
         <f t="shared" si="153"/>
         <v>1900</v>
@@ -13576,7 +13588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15">
       <c r="A239" s="1">
         <f t="shared" si="153"/>
         <v>1901</v>
@@ -13634,7 +13646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15">
       <c r="A240" s="1">
         <f t="shared" si="153"/>
         <v>1902</v>
@@ -13692,7 +13704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15">
       <c r="A241" s="1">
         <f t="shared" si="153"/>
         <v>1903</v>
@@ -13750,7 +13762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15">
       <c r="A242" s="1">
         <f t="shared" si="153"/>
         <v>1904</v>
@@ -13808,7 +13820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15">
       <c r="A243" s="1">
         <f t="shared" si="153"/>
         <v>1905</v>
@@ -13866,7 +13878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15">
       <c r="A244" s="1">
         <f t="shared" si="153"/>
         <v>1906</v>
@@ -13924,7 +13936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15">
       <c r="A245" s="1">
         <f t="shared" si="153"/>
         <v>1907</v>
@@ -13982,7 +13994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15">
       <c r="A246" s="1">
         <f t="shared" si="153"/>
         <v>1908</v>
@@ -14040,7 +14052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15">
       <c r="A247" s="1">
         <f t="shared" si="153"/>
         <v>1909</v>
@@ -14098,7 +14110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15">
       <c r="A248" s="1">
         <f t="shared" si="153"/>
         <v>1910</v>
@@ -14156,7 +14168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15">
       <c r="A249" s="1">
         <f t="shared" si="153"/>
         <v>1911</v>
@@ -14214,7 +14226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15">
       <c r="A250" s="1">
         <f t="shared" si="153"/>
         <v>1912</v>
@@ -14272,7 +14284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15">
       <c r="A251" s="1">
         <f t="shared" si="153"/>
         <v>1913</v>
@@ -14330,7 +14342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15">
       <c r="A252" s="1">
         <f t="shared" si="153"/>
         <v>1914</v>
@@ -14388,7 +14400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15">
       <c r="A253" s="1">
         <f t="shared" si="153"/>
         <v>1915</v>
@@ -14446,7 +14458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15">
       <c r="A254" s="1">
         <v>1916</v>
       </c>
@@ -14503,7 +14515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15">
       <c r="A255" s="11" t="s">
         <v>49</v>
       </c>
@@ -14560,12 +14572,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17">
       <c r="A257" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17">
       <c r="A259" s="14" t="s">
         <v>182</v>
       </c>
@@ -14606,7 +14618,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17">
       <c r="B260">
         <v>0.55000000000000004</v>
       </c>
@@ -14641,7 +14653,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17">
       <c r="A262" s="10" t="s">
         <v>87</v>
       </c>
@@ -14685,7 +14697,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17">
       <c r="A263" s="1">
         <v>1896</v>
       </c>
@@ -14742,7 +14754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17">
       <c r="A264" s="1">
         <f>A263+1</f>
         <v>1897</v>
@@ -14800,7 +14812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17">
       <c r="A265" s="1">
         <f t="shared" ref="A265:A282" si="179">A264+1</f>
         <v>1898</v>
@@ -14858,7 +14870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17">
       <c r="A266" s="1">
         <f t="shared" si="179"/>
         <v>1899</v>
@@ -14916,7 +14928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17">
       <c r="A267" s="1">
         <f t="shared" si="179"/>
         <v>1900</v>
@@ -14974,7 +14986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17">
       <c r="A268" s="1">
         <f t="shared" si="179"/>
         <v>1901</v>
@@ -15033,7 +15045,7 @@
       </c>
       <c r="Q268" s="4"/>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17">
       <c r="A269" s="1">
         <f t="shared" si="179"/>
         <v>1902</v>
@@ -15091,7 +15103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17">
       <c r="A270" s="1">
         <f t="shared" si="179"/>
         <v>1903</v>
@@ -15149,7 +15161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17">
       <c r="A271" s="1">
         <f t="shared" si="179"/>
         <v>1904</v>
@@ -15207,7 +15219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17">
       <c r="A272" s="1">
         <f t="shared" si="179"/>
         <v>1905</v>
@@ -15265,7 +15277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15">
       <c r="A273" s="1">
         <f t="shared" si="179"/>
         <v>1906</v>
@@ -15323,7 +15335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15">
       <c r="A274" s="1">
         <f t="shared" si="179"/>
         <v>1907</v>
@@ -15381,7 +15393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15">
       <c r="A275" s="1">
         <f t="shared" si="179"/>
         <v>1908</v>
@@ -15439,7 +15451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15">
       <c r="A276" s="1">
         <f t="shared" si="179"/>
         <v>1909</v>
@@ -15497,7 +15509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15">
       <c r="A277" s="1">
         <f t="shared" si="179"/>
         <v>1910</v>
@@ -15555,7 +15567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15">
       <c r="A278" s="1">
         <f t="shared" si="179"/>
         <v>1911</v>
@@ -15613,7 +15625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15">
       <c r="A279" s="1">
         <f t="shared" si="179"/>
         <v>1912</v>
@@ -15671,7 +15683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15">
       <c r="A280" s="1">
         <f t="shared" si="179"/>
         <v>1913</v>
@@ -15729,7 +15741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15">
       <c r="A281" s="1">
         <f t="shared" si="179"/>
         <v>1914</v>
@@ -15787,7 +15799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15">
       <c r="A282" s="1">
         <f t="shared" si="179"/>
         <v>1915</v>
@@ -15845,7 +15857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15">
       <c r="A283" s="1">
         <v>1916</v>
       </c>
@@ -15902,7 +15914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15">
       <c r="A284" s="11" t="s">
         <v>49</v>
       </c>
@@ -15959,12 +15971,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15">
       <c r="A286" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15">
       <c r="A288" s="10" t="s">
         <v>87</v>
       </c>
@@ -16008,7 +16020,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15">
       <c r="A289" s="1">
         <v>1896</v>
       </c>
@@ -16065,7 +16077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15">
       <c r="A290" s="1">
         <f>A289+1</f>
         <v>1897</v>
@@ -16123,7 +16135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15">
       <c r="A291" s="1">
         <f t="shared" ref="A291:A308" si="203">A290+1</f>
         <v>1898</v>
@@ -16181,7 +16193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15">
       <c r="A292" s="1">
         <f t="shared" si="203"/>
         <v>1899</v>
@@ -16239,7 +16251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15">
       <c r="A293" s="1">
         <f t="shared" si="203"/>
         <v>1900</v>
@@ -16297,7 +16309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15">
       <c r="A294" s="1">
         <f t="shared" si="203"/>
         <v>1901</v>
@@ -16355,7 +16367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15">
       <c r="A295" s="1">
         <f t="shared" si="203"/>
         <v>1902</v>
@@ -16413,7 +16425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15">
       <c r="A296" s="1">
         <f t="shared" si="203"/>
         <v>1903</v>
@@ -16471,7 +16483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15">
       <c r="A297" s="1">
         <f t="shared" si="203"/>
         <v>1904</v>
@@ -16529,7 +16541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15">
       <c r="A298" s="1">
         <f t="shared" si="203"/>
         <v>1905</v>
@@ -16587,7 +16599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15">
       <c r="A299" s="1">
         <f t="shared" si="203"/>
         <v>1906</v>
@@ -16645,7 +16657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15">
       <c r="A300" s="1">
         <f t="shared" si="203"/>
         <v>1907</v>
@@ -16703,7 +16715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15">
       <c r="A301" s="1">
         <f t="shared" si="203"/>
         <v>1908</v>
@@ -16761,7 +16773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15">
       <c r="A302" s="1">
         <f t="shared" si="203"/>
         <v>1909</v>
@@ -16819,7 +16831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15">
       <c r="A303" s="1">
         <f t="shared" si="203"/>
         <v>1910</v>
@@ -16877,7 +16889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15">
       <c r="A304" s="1">
         <f t="shared" si="203"/>
         <v>1911</v>
@@ -16935,7 +16947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15">
       <c r="A305" s="1">
         <f t="shared" si="203"/>
         <v>1912</v>
@@ -16993,7 +17005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15">
       <c r="A306" s="1">
         <f t="shared" si="203"/>
         <v>1913</v>
@@ -17051,7 +17063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15">
       <c r="A307" s="1">
         <f t="shared" si="203"/>
         <v>1914</v>
@@ -17109,7 +17121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15">
       <c r="A308" s="1">
         <f t="shared" si="203"/>
         <v>1915</v>
@@ -17167,7 +17179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15">
       <c r="A309" s="1">
         <v>1916</v>
       </c>
@@ -17224,7 +17236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15">
       <c r="A310" s="11" t="s">
         <v>49</v>
       </c>
@@ -17293,30 +17305,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
   <dimension ref="A1:N213"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.41796875" customWidth="1"/>
+    <col min="2" max="2" width="17.41796875" customWidth="1"/>
+    <col min="3" max="3" width="10.68359375" customWidth="1"/>
+    <col min="4" max="4" width="14.26171875" customWidth="1"/>
+    <col min="5" max="5" width="11.83984375" customWidth="1"/>
+    <col min="6" max="6" width="13.26171875" customWidth="1"/>
+    <col min="7" max="7" width="10.26171875" customWidth="1"/>
+    <col min="9" max="9" width="12.26171875" customWidth="1"/>
+    <col min="10" max="10" width="11.578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="57.6">
       <c r="A4" s="2" t="s">
         <v>117</v>
       </c>
@@ -17351,7 +17363,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -17386,7 +17398,7 @@
         <v>30398</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -17421,7 +17433,7 @@
         <v>27525</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -17456,7 +17468,7 @@
         <v>64393</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>121</v>
       </c>
@@ -17491,7 +17503,7 @@
         <v>223248</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>122</v>
       </c>
@@ -17526,7 +17538,7 @@
         <v>279258</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -17561,7 +17573,7 @@
         <v>173914</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -17596,7 +17608,7 @@
         <v>340174</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -17631,7 +17643,7 @@
         <v>471971</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -17666,7 +17678,7 @@
         <v>409911</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" s="22" t="s">
         <v>129</v>
       </c>
@@ -17711,7 +17723,7 @@
         <v>2020792</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="22" t="s">
         <v>130</v>
       </c>
@@ -17756,7 +17768,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" s="17" t="s">
         <v>127</v>
       </c>
@@ -17801,7 +17813,7 @@
         <v>1395970</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14">
       <c r="A17" s="24" t="s">
         <v>128</v>
       </c>
@@ -17846,7 +17858,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14">
       <c r="A18" s="33" t="s">
         <v>185</v>
       </c>
@@ -17891,7 +17903,7 @@
         <v>566899</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14">
       <c r="A19" s="33" t="s">
         <v>186</v>
       </c>
@@ -17936,7 +17948,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>196</v>
       </c>
@@ -17951,7 +17963,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>194</v>
       </c>
@@ -17966,7 +17978,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -17978,7 +17990,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14">
       <c r="A25" s="36" t="s">
         <v>117</v>
       </c>
@@ -18009,7 +18021,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -18033,7 +18045,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>120</v>
       </c>
@@ -18059,7 +18071,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -18085,7 +18097,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>122</v>
       </c>
@@ -18111,7 +18123,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14">
       <c r="A30" s="21" t="s">
         <v>123</v>
       </c>
@@ -18140,7 +18152,7 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -18173,7 +18185,7 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -18204,7 +18216,7 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -18237,7 +18249,7 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14">
       <c r="A34" s="27" t="s">
         <v>127</v>
       </c>
@@ -18279,7 +18291,7 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14">
       <c r="A35" s="22" t="s">
         <v>88</v>
       </c>
@@ -18321,7 +18333,7 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14">
       <c r="A36" s="33" t="s">
         <v>185</v>
       </c>
@@ -18354,7 +18366,7 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14">
       <c r="A37" s="33" t="s">
         <v>88</v>
       </c>
@@ -18379,17 +18391,17 @@
         <v>99.993052867676965</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="72">
       <c r="A42" s="2" t="s">
         <v>117</v>
       </c>
@@ -18400,13 +18412,13 @@
         <v>109</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G42" s="39" t="s">
         <v>110</v>
@@ -18427,7 +18439,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -18460,7 +18472,7 @@
       </c>
       <c r="M43" s="4"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
         <v>120</v>
       </c>
@@ -18495,7 +18507,7 @@
       </c>
       <c r="M44" s="4"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
         <v>121</v>
       </c>
@@ -18530,7 +18542,7 @@
       </c>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
         <v>122</v>
       </c>
@@ -18565,7 +18577,7 @@
       </c>
       <c r="M46" s="4"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14">
       <c r="A47" s="21" t="s">
         <v>123</v>
       </c>
@@ -18600,7 +18612,7 @@
       </c>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
         <v>124</v>
       </c>
@@ -18637,7 +18649,7 @@
       </c>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -18672,7 +18684,7 @@
       </c>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -18709,7 +18721,7 @@
       </c>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13">
       <c r="A51" s="27" t="s">
         <v>127</v>
       </c>
@@ -18758,7 +18770,7 @@
         <v>2888132</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13">
       <c r="A52" s="22" t="s">
         <v>88</v>
       </c>
@@ -18770,27 +18782,27 @@
       <c r="D52" s="23"/>
       <c r="E52" s="23"/>
       <c r="F52" s="23">
-        <f>F51/$L51*100</f>
+        <f t="shared" ref="F52:K52" si="20">F51/$L51*100</f>
         <v>89.371296048795557</v>
       </c>
       <c r="G52" s="23">
-        <f>G51/$L51*100</f>
+        <f t="shared" si="20"/>
         <v>5.064069093794882</v>
       </c>
       <c r="H52" s="23">
-        <f>H51/$L51*100</f>
+        <f t="shared" si="20"/>
         <v>1.8785152479180314</v>
       </c>
       <c r="I52" s="23">
-        <f>I51/$L51*100</f>
+        <f t="shared" si="20"/>
         <v>9.3486031801870548E-4</v>
       </c>
       <c r="J52" s="23">
-        <f>J51/$L51*100</f>
+        <f t="shared" si="20"/>
         <v>0.29108780346604657</v>
       </c>
       <c r="K52" s="23">
-        <f>K51/$L51*100</f>
+        <f t="shared" si="20"/>
         <v>1.3988280314057668E-2</v>
       </c>
       <c r="L52" s="23">
@@ -18798,48 +18810,48 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13">
       <c r="A53" s="33" t="s">
         <v>185</v>
       </c>
       <c r="B53" s="34">
-        <f t="shared" ref="B53:K53" si="20">SUM(B44:B46)</f>
+        <f t="shared" ref="B53:K53" si="21">SUM(B44:B46)</f>
         <v>0</v>
       </c>
       <c r="C53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>447806</v>
       </c>
       <c r="D53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>70888</v>
       </c>
       <c r="E53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22287</v>
       </c>
       <c r="F53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>496407</v>
       </c>
       <c r="G53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15165</v>
       </c>
       <c r="H53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>40799</v>
       </c>
       <c r="I53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>35</v>
       </c>
       <c r="J53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L53" s="34">
@@ -18847,7 +18859,7 @@
         <v>552406</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13">
       <c r="A54" s="33" t="s">
         <v>88</v>
       </c>
@@ -18859,27 +18871,27 @@
       <c r="D54" s="35"/>
       <c r="E54" s="35"/>
       <c r="F54" s="35">
-        <f>F53/$L53*100</f>
+        <f t="shared" ref="F54:K54" si="22">F53/$L53*100</f>
         <v>89.862709673682033</v>
       </c>
       <c r="G54" s="35">
-        <f>G53/$L53*100</f>
+        <f t="shared" si="22"/>
         <v>2.7452634475367756</v>
       </c>
       <c r="H54" s="35">
-        <f>H53/$L53*100</f>
+        <f t="shared" si="22"/>
         <v>7.3856909591858155</v>
       </c>
       <c r="I54" s="35">
-        <f>I53/$L53*100</f>
+        <f t="shared" si="22"/>
         <v>6.3359195953700724E-3</v>
       </c>
       <c r="J54" s="35">
-        <f>J53/$L53*100</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K54" s="35">
-        <f>K53/$L53*100</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L54" s="35">
@@ -18887,12 +18899,12 @@
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13">
       <c r="A57" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13">
       <c r="A59" s="36" t="s">
         <v>19</v>
       </c>
@@ -18900,7 +18912,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
         <v>1896</v>
       </c>
@@ -18908,7 +18920,7 @@
         <v>35639</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
         <v>1897</v>
       </c>
@@ -18916,7 +18928,7 @@
         <v>28021</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13">
       <c r="A62" s="1">
         <v>1898</v>
       </c>
@@ -18924,7 +18936,7 @@
         <v>41907</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
         <v>1899</v>
       </c>
@@ -18932,7 +18944,7 @@
         <v>65559</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
         <v>1900</v>
       </c>
@@ -18940,7 +18952,7 @@
         <v>76085</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2">
       <c r="A65" s="1">
         <v>1901</v>
       </c>
@@ -18948,7 +18960,7 @@
         <v>83166</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66" s="1">
         <v>1902</v>
       </c>
@@ -18956,7 +18968,7 @@
         <v>103114</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2">
       <c r="A67" s="1">
         <v>1903</v>
       </c>
@@ -18964,7 +18976,7 @@
         <v>125022</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68" s="1">
         <v>1904</v>
       </c>
@@ -18972,7 +18984,7 @@
         <v>151739</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69" s="1">
         <v>1905</v>
       </c>
@@ -18980,7 +18992,7 @@
         <v>186157</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2">
       <c r="A70" s="1">
         <v>1906</v>
       </c>
@@ -18988,7 +19000,7 @@
         <v>221400</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2">
       <c r="A71" s="1">
         <v>1907</v>
       </c>
@@ -18996,7 +19008,7 @@
         <v>186071</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72" s="1">
         <v>1908</v>
       </c>
@@ -19004,7 +19016,7 @@
         <v>119541</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73" s="1">
         <v>1909</v>
       </c>
@@ -19012,7 +19024,7 @@
         <v>141698</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2">
       <c r="A74" s="1">
         <v>1910</v>
       </c>
@@ -19020,7 +19032,7 @@
         <v>162676</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2">
       <c r="A75" s="1">
         <v>1911</v>
       </c>
@@ -19028,7 +19040,7 @@
         <v>144660</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2">
       <c r="A76" s="1">
         <v>1912</v>
       </c>
@@ -19036,7 +19048,7 @@
         <v>217990</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2">
       <c r="A77" s="1">
         <v>1913</v>
       </c>
@@ -19044,7 +19056,7 @@
         <v>261265</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2">
       <c r="A78" s="1">
         <v>1914</v>
       </c>
@@ -19052,7 +19064,7 @@
         <v>119358</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2">
       <c r="A79" s="1">
         <v>1915</v>
       </c>
@@ -19060,7 +19072,7 @@
         <v>3880</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2">
       <c r="A80" s="1">
         <v>1916</v>
       </c>
@@ -19068,7 +19080,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" s="1" t="s">
         <v>49</v>
       </c>
@@ -19077,7 +19089,7 @@
         <v>2477253</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" s="1" t="s">
         <v>123</v>
       </c>
@@ -19086,7 +19098,7 @@
         <v>247211</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" s="1" t="s">
         <v>124</v>
       </c>
@@ -19095,7 +19107,7 @@
         <v>649198</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" s="1" t="s">
         <v>125</v>
       </c>
@@ -19104,7 +19116,7 @@
         <v>831386</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" s="1" t="s">
         <v>126</v>
       </c>
@@ -19113,7 +19125,7 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" s="36" t="s">
         <v>117</v>
       </c>
@@ -19131,16 +19143,16 @@
       </c>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B90" s="4">
-        <f t="shared" ref="B90:B97" si="21">K6</f>
+        <f t="shared" ref="B90:B97" si="23">K6</f>
         <v>27525</v>
       </c>
       <c r="C90" s="4">
-        <f>L43</f>
+        <f t="shared" ref="C90:C97" si="24">L43</f>
         <v>33658</v>
       </c>
       <c r="D90" s="26">
@@ -19149,16 +19161,16 @@
       </c>
       <c r="E90" s="14"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B91" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>64393</v>
       </c>
       <c r="C91" s="4">
-        <f>L44</f>
+        <f t="shared" si="24"/>
         <v>69982</v>
       </c>
       <c r="D91" s="26">
@@ -19166,54 +19178,54 @@
         <v>92.01366065559715</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B92" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>223248</v>
       </c>
       <c r="C92" s="4">
-        <f>L45</f>
+        <f t="shared" si="24"/>
         <v>189850</v>
       </c>
       <c r="D92" s="26">
-        <f t="shared" ref="D92:D97" si="22">B92/C92*100</f>
+        <f t="shared" ref="D92:D97" si="25">B92/C92*100</f>
         <v>117.59178298656833</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B93" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>279258</v>
       </c>
       <c r="C93" s="4">
-        <f>L46</f>
+        <f t="shared" si="24"/>
         <v>292574</v>
       </c>
       <c r="D93" s="26">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>95.448672814399089</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" s="43" t="s">
         <v>123</v>
       </c>
       <c r="B94" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>173914</v>
       </c>
       <c r="C94" s="4">
-        <f>L47</f>
+        <f t="shared" si="24"/>
         <v>246339</v>
       </c>
       <c r="D94" s="26">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>70.599458469832229</v>
       </c>
       <c r="E94" s="4">
@@ -19221,20 +19233,20 @@
         <v>247211</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B95" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>340174</v>
       </c>
       <c r="C95" s="4">
-        <f>L48</f>
+        <f t="shared" si="24"/>
         <v>644531</v>
       </c>
       <c r="D95" s="26">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>52.778531986824525</v>
       </c>
       <c r="E95" s="4">
@@ -19242,20 +19254,20 @@
         <v>649198</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B96" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>471971</v>
       </c>
       <c r="C96" s="4">
-        <f>L49</f>
+        <f t="shared" si="24"/>
         <v>986977</v>
       </c>
       <c r="D96" s="26">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>47.819858010875635</v>
       </c>
       <c r="E96" s="4">
@@ -19263,20 +19275,20 @@
         <v>831386</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B97" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>409911</v>
       </c>
       <c r="C97" s="4">
-        <f>L50</f>
+        <f t="shared" si="24"/>
         <v>1010285</v>
       </c>
       <c r="D97" s="26">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>40.573798482606392</v>
       </c>
       <c r="E97" s="4">
@@ -19284,18 +19296,18 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="B98" s="4"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="B99" s="4"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" s="14" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" s="36" t="s">
         <v>117</v>
       </c>
@@ -19303,97 +19315,97 @@
         <v>197</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" s="1" t="str">
         <f>A43</f>
         <v>1876-1880</v>
       </c>
       <c r="B102" s="4">
-        <f>L43</f>
+        <f t="shared" ref="B102:B110" si="26">L43</f>
         <v>33658</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" s="1" t="str">
-        <f t="shared" ref="A103:A110" si="23">A44</f>
+        <f t="shared" ref="A103:A110" si="27">A44</f>
         <v>1881-1885</v>
       </c>
       <c r="B103" s="4">
-        <f>L44</f>
+        <f t="shared" si="26"/>
         <v>69982</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1886-1890</v>
       </c>
       <c r="B104" s="4">
-        <f>L45</f>
+        <f t="shared" si="26"/>
         <v>189850</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1891-1895</v>
       </c>
       <c r="B105" s="4">
-        <f>L46</f>
+        <f t="shared" si="26"/>
         <v>292574</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
       <c r="A106" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1896-1900</v>
       </c>
       <c r="B106" s="4">
-        <f>L47</f>
+        <f t="shared" si="26"/>
         <v>246339</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1901-1905</v>
       </c>
       <c r="B107" s="4">
-        <f>L48</f>
+        <f t="shared" si="26"/>
         <v>644531</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
       <c r="A108" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1906-1910</v>
       </c>
       <c r="B108" s="4">
-        <f>L49</f>
+        <f t="shared" si="26"/>
         <v>986977</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5">
       <c r="A109" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1911-1915</v>
       </c>
       <c r="B109" s="4">
-        <f>L50</f>
+        <f t="shared" si="26"/>
         <v>1010285</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5">
       <c r="A110" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1896-1915</v>
       </c>
       <c r="B110" s="42">
-        <f>L51</f>
+        <f t="shared" si="26"/>
         <v>2888132</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111" s="10" t="s">
         <v>129</v>
       </c>
@@ -19402,12 +19414,12 @@
         <v>3474196</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" s="14" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" s="36" t="s">
         <v>117</v>
       </c>
@@ -19415,367 +19427,367 @@
         <v>197</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" s="1">
         <v>1876</v>
       </c>
-      <c r="B115" s="50">
+      <c r="B115" s="48">
         <v>5958.6872560000002</v>
       </c>
-      <c r="F115" s="50"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F115" s="48"/>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="1">
         <v>1877</v>
       </c>
-      <c r="B116" s="50">
+      <c r="B116" s="48">
         <v>6133.5817779999998</v>
       </c>
-      <c r="F116" s="50"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F116" s="48"/>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="1">
         <v>1878</v>
       </c>
-      <c r="B117" s="50">
+      <c r="B117" s="48">
         <v>6497.8953369999999</v>
       </c>
-      <c r="F117" s="50"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F117" s="48"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="1">
         <v>1879</v>
       </c>
-      <c r="B118" s="50">
+      <c r="B118" s="48">
         <v>7099.2952009999999</v>
       </c>
-      <c r="F118" s="50"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F118" s="48"/>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="1">
         <v>1880</v>
       </c>
-      <c r="B119" s="50">
+      <c r="B119" s="48">
         <v>7968.5404280000002</v>
       </c>
-      <c r="F119" s="50"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F119" s="48"/>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="1">
         <v>1881</v>
       </c>
-      <c r="B120" s="50">
+      <c r="B120" s="48">
         <v>9081.0078830000002</v>
       </c>
-      <c r="F120" s="50"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F120" s="48"/>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="1">
         <v>1882</v>
       </c>
-      <c r="B121" s="50">
+      <c r="B121" s="48">
         <v>10799.985825</v>
       </c>
-      <c r="F121" s="50"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F121" s="48"/>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="1">
         <v>1883</v>
       </c>
-      <c r="B122" s="50">
+      <c r="B122" s="48">
         <v>13180.685009000001</v>
       </c>
-      <c r="F122" s="50"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F122" s="48"/>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" s="1">
         <v>1884</v>
       </c>
-      <c r="B123" s="50">
+      <c r="B123" s="48">
         <v>16376.145667999999</v>
       </c>
-      <c r="F123" s="50"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F123" s="48"/>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="1">
         <v>1885</v>
       </c>
-      <c r="B124" s="50">
+      <c r="B124" s="48">
         <v>20544.175615</v>
       </c>
-      <c r="F124" s="50"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F124" s="48"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="1">
         <v>1886</v>
       </c>
-      <c r="B125" s="50">
+      <c r="B125" s="48">
         <v>26303.239323000002</v>
       </c>
-      <c r="F125" s="50"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F125" s="48"/>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="1">
         <v>1887</v>
       </c>
-      <c r="B126" s="50">
+      <c r="B126" s="48">
         <v>31933.797870999999</v>
       </c>
-      <c r="F126" s="50"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F126" s="48"/>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="1">
         <v>1888</v>
       </c>
-      <c r="B127" s="50">
+      <c r="B127" s="48">
         <v>37768.818612000003</v>
       </c>
-      <c r="F127" s="50"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F127" s="48"/>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="1">
         <v>1889</v>
       </c>
-      <c r="B128" s="50">
+      <c r="B128" s="48">
         <v>43815.890546000002</v>
       </c>
-      <c r="F128" s="50"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F128" s="48"/>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="1">
         <v>1890</v>
       </c>
-      <c r="B129" s="50">
+      <c r="B129" s="48">
         <v>50028.253647999998</v>
       </c>
-      <c r="F129" s="50"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F129" s="48"/>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="1">
         <v>1891</v>
       </c>
-      <c r="B130" s="50">
+      <c r="B130" s="48">
         <v>57244.128299000004</v>
       </c>
-      <c r="F130" s="50"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F130" s="48"/>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" s="1">
         <v>1892</v>
       </c>
-      <c r="B131" s="50">
+      <c r="B131" s="48">
         <v>60906.481652000002</v>
       </c>
-      <c r="F131" s="50"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F131" s="48"/>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="1">
         <v>1893</v>
       </c>
-      <c r="B132" s="50">
+      <c r="B132" s="48">
         <v>61556.958893000003</v>
       </c>
-      <c r="F132" s="50"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F132" s="48"/>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="1">
         <v>1894</v>
       </c>
-      <c r="B133" s="50">
+      <c r="B133" s="48">
         <v>59073.614796000002</v>
       </c>
-      <c r="F133" s="50"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F133" s="48"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="1">
         <v>1895</v>
       </c>
-      <c r="B134" s="50">
+      <c r="B134" s="48">
         <v>53792.816358999997</v>
       </c>
-      <c r="F134" s="50"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F134" s="48"/>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="1">
         <v>1896</v>
       </c>
-      <c r="B135" s="50">
+      <c r="B135" s="48">
         <v>44001.050108000003</v>
       </c>
-      <c r="F135" s="50"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F135" s="48"/>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="1">
         <v>1897</v>
       </c>
-      <c r="B136" s="50">
+      <c r="B136" s="48">
         <v>41555.827486000002</v>
       </c>
-      <c r="F136" s="50"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F136" s="48"/>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" s="1">
         <v>1898</v>
       </c>
-      <c r="B137" s="50">
+      <c r="B137" s="48">
         <v>43914.876993999998</v>
       </c>
-      <c r="F137" s="50"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F137" s="48"/>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" s="1">
         <v>1899</v>
       </c>
-      <c r="B138" s="50">
+      <c r="B138" s="48">
         <v>51608.617109999999</v>
       </c>
-      <c r="F138" s="50"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F138" s="48"/>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="1">
         <v>1900</v>
       </c>
-      <c r="B139" s="50">
+      <c r="B139" s="48">
         <v>65258.628300999997</v>
       </c>
-      <c r="F139" s="50"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F139" s="48"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="1">
         <v>1901</v>
       </c>
-      <c r="B140" s="50">
+      <c r="B140" s="48">
         <v>89374.285107000003</v>
       </c>
-      <c r="F140" s="50"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F140" s="48"/>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" s="1">
         <v>1902</v>
       </c>
-      <c r="B141" s="50">
+      <c r="B141" s="48">
         <v>110396.48513099999</v>
       </c>
-      <c r="F141" s="50"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F141" s="48"/>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" s="1">
         <v>1903</v>
       </c>
-      <c r="B142" s="50">
+      <c r="B142" s="48">
         <v>130369.29534500001</v>
       </c>
-      <c r="F142" s="50"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F142" s="48"/>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" s="1">
         <v>1904</v>
       </c>
-      <c r="B143" s="50">
+      <c r="B143" s="48">
         <v>148831.43620900001</v>
       </c>
-      <c r="F143" s="50"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F143" s="48"/>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="1">
         <v>1905</v>
       </c>
-      <c r="B144" s="50">
+      <c r="B144" s="48">
         <v>165559.498208</v>
       </c>
-      <c r="F144" s="50"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F144" s="48"/>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" s="1">
         <v>1906</v>
       </c>
-      <c r="B145" s="50">
+      <c r="B145" s="48">
         <v>180624.48191</v>
       </c>
-      <c r="F145" s="50"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F145" s="48"/>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" s="1">
         <v>1907</v>
       </c>
-      <c r="B146" s="50">
+      <c r="B146" s="48">
         <v>192365.54383800001</v>
       </c>
-      <c r="F146" s="50"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F146" s="48"/>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" s="1">
         <v>1908</v>
       </c>
-      <c r="B147" s="50">
+      <c r="B147" s="48">
         <v>200821.20595</v>
       </c>
-      <c r="F147" s="50"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F147" s="48"/>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" s="1">
         <v>1909</v>
       </c>
-      <c r="B148" s="50">
+      <c r="B148" s="48">
         <v>205811.42198099999</v>
       </c>
-      <c r="F148" s="50"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F148" s="48"/>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" s="1">
         <v>1910</v>
       </c>
-      <c r="B149" s="50">
+      <c r="B149" s="48">
         <v>207354.34632099999</v>
       </c>
-      <c r="F149" s="50"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F149" s="48"/>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" s="1">
         <v>1911</v>
       </c>
-      <c r="B150" s="50">
+      <c r="B150" s="48">
         <v>204407.818902</v>
       </c>
-      <c r="F150" s="50"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F150" s="48"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" s="1">
         <v>1912</v>
       </c>
-      <c r="B151" s="50">
+      <c r="B151" s="48">
         <v>202841.37030400001</v>
       </c>
-      <c r="F151" s="50"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F151" s="48"/>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" s="1">
         <v>1913</v>
       </c>
-      <c r="B152" s="50">
+      <c r="B152" s="48">
         <v>201633.03541400001</v>
       </c>
-      <c r="F152" s="50"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F152" s="48"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" s="1">
         <v>1914</v>
       </c>
-      <c r="B153" s="50">
+      <c r="B153" s="48">
         <v>200884.29531700001</v>
       </c>
-      <c r="F153" s="50"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F153" s="48"/>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" s="1">
         <v>1915</v>
       </c>
-      <c r="B154" s="50">
+      <c r="B154" s="48">
         <v>200518.480064</v>
       </c>
-      <c r="F154" s="50"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F154" s="48"/>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" s="10" t="s">
         <v>127</v>
       </c>
@@ -19784,7 +19796,7 @@
         <v>2888132</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6">
       <c r="A156" s="10" t="s">
         <v>129</v>
       </c>
@@ -19793,7 +19805,7 @@
         <v>3474195.9999989998</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6">
       <c r="A157" s="10" t="s">
         <v>185</v>
       </c>
@@ -19802,16 +19814,16 @@
         <v>552405.99999899999</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6">
       <c r="A158" s="10"/>
       <c r="B158" s="4"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6">
       <c r="A160" s="14" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2">
       <c r="A161" s="36" t="s">
         <v>117</v>
       </c>
@@ -19819,346 +19831,346 @@
         <v>197</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2">
       <c r="A162" s="1">
         <v>1881</v>
       </c>
       <c r="B162" s="4">
-        <f>(B120+B121) / 2</f>
+        <f t="shared" ref="B162:B195" si="28">(B120+B121) / 2</f>
         <v>9940.4968540000009</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2">
       <c r="A163" s="1">
         <f>A162+1</f>
         <v>1882</v>
       </c>
       <c r="B163" s="4">
-        <f>(B121+B122) / 2</f>
+        <f t="shared" si="28"/>
         <v>11990.335417</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2">
       <c r="A164" s="1">
-        <f t="shared" ref="A164:A195" si="24">A163+1</f>
+        <f t="shared" ref="A164:A195" si="29">A163+1</f>
         <v>1883</v>
       </c>
       <c r="B164" s="4">
-        <f>(B122+B123) / 2</f>
+        <f t="shared" si="28"/>
         <v>14778.415338499999</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2">
       <c r="A165" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1884</v>
       </c>
       <c r="B165" s="4">
-        <f>(B123+B124) / 2</f>
+        <f t="shared" si="28"/>
         <v>18460.160641499999</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2">
       <c r="A166" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1885</v>
       </c>
       <c r="B166" s="4">
-        <f>(B124+B125) / 2</f>
+        <f t="shared" si="28"/>
         <v>23423.707469000001</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2">
       <c r="A167" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1886</v>
       </c>
       <c r="B167" s="4">
-        <f>(B125+B126) / 2</f>
+        <f t="shared" si="28"/>
         <v>29118.518597000002</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2">
       <c r="A168" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1887</v>
       </c>
       <c r="B168" s="4">
-        <f>(B126+B127) / 2</f>
+        <f t="shared" si="28"/>
         <v>34851.308241500003</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2">
       <c r="A169" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1888</v>
       </c>
       <c r="B169" s="4">
-        <f>(B127+B128) / 2</f>
+        <f t="shared" si="28"/>
         <v>40792.354579000006</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2">
       <c r="A170" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1889</v>
       </c>
       <c r="B170" s="4">
-        <f>(B128+B129) / 2</f>
+        <f t="shared" si="28"/>
         <v>46922.072096999997</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2">
       <c r="A171" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1890</v>
       </c>
       <c r="B171" s="4">
-        <f>(B129+B130) / 2</f>
+        <f t="shared" si="28"/>
         <v>53636.190973500001</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2">
       <c r="A172" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1891</v>
       </c>
       <c r="B172" s="4">
-        <f>(B130+B131) / 2</f>
+        <f t="shared" si="28"/>
         <v>59075.304975500003</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2">
       <c r="A173" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1892</v>
       </c>
       <c r="B173" s="4">
-        <f>(B131+B132) / 2</f>
+        <f t="shared" si="28"/>
         <v>61231.720272500002</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2">
       <c r="A174" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1893</v>
       </c>
       <c r="B174" s="4">
-        <f>(B132+B133) / 2</f>
+        <f t="shared" si="28"/>
         <v>60315.286844500006</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2">
       <c r="A175" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1894</v>
       </c>
       <c r="B175" s="4">
-        <f>(B133+B134) / 2</f>
+        <f t="shared" si="28"/>
         <v>56433.215577499999</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2">
       <c r="A176" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1895</v>
       </c>
       <c r="B176" s="4">
-        <f>(B134+B135) / 2</f>
+        <f t="shared" si="28"/>
         <v>48896.9332335</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2">
       <c r="A177" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1896</v>
       </c>
       <c r="B177" s="4">
-        <f>(B135+B136) / 2</f>
+        <f t="shared" si="28"/>
         <v>42778.438797000003</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2">
       <c r="A178" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1897</v>
       </c>
       <c r="B178" s="4">
-        <f>(B136+B137) / 2</f>
+        <f t="shared" si="28"/>
         <v>42735.35224</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2">
       <c r="A179" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1898</v>
       </c>
       <c r="B179" s="4">
-        <f>(B137+B138) / 2</f>
+        <f t="shared" si="28"/>
         <v>47761.747051999999</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2">
       <c r="A180" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1899</v>
       </c>
       <c r="B180" s="4">
-        <f>(B138+B139) / 2</f>
+        <f t="shared" si="28"/>
         <v>58433.622705499998</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2">
       <c r="A181" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1900</v>
       </c>
       <c r="B181" s="4">
-        <f>(B139+B140) / 2</f>
+        <f t="shared" si="28"/>
         <v>77316.456703999997</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2">
       <c r="A182" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1901</v>
       </c>
       <c r="B182" s="4">
-        <f>(B140+B141) / 2</f>
+        <f t="shared" si="28"/>
         <v>99885.385118999999</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2">
       <c r="A183" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1902</v>
       </c>
       <c r="B183" s="4">
-        <f>(B141+B142) / 2</f>
+        <f t="shared" si="28"/>
         <v>120382.89023799999</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2">
       <c r="A184" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1903</v>
       </c>
       <c r="B184" s="4">
-        <f>(B142+B143) / 2</f>
+        <f t="shared" si="28"/>
         <v>139600.365777</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2">
       <c r="A185" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1904</v>
       </c>
       <c r="B185" s="4">
-        <f>(B143+B144) / 2</f>
+        <f t="shared" si="28"/>
         <v>157195.46720850002</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2">
       <c r="A186" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1905</v>
       </c>
       <c r="B186" s="4">
-        <f>(B144+B145) / 2</f>
+        <f t="shared" si="28"/>
         <v>173091.990059</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2">
       <c r="A187" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1906</v>
       </c>
       <c r="B187" s="4">
-        <f>(B145+B146) / 2</f>
+        <f t="shared" si="28"/>
         <v>186495.01287400001</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2">
       <c r="A188" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1907</v>
       </c>
       <c r="B188" s="4">
-        <f>(B146+B147) / 2</f>
+        <f t="shared" si="28"/>
         <v>196593.37489400001</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2">
       <c r="A189" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1908</v>
       </c>
       <c r="B189" s="4">
-        <f>(B147+B148) / 2</f>
+        <f t="shared" si="28"/>
         <v>203316.31396549998</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2">
       <c r="A190" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1909</v>
       </c>
       <c r="B190" s="4">
-        <f>(B148+B149) / 2</f>
+        <f t="shared" si="28"/>
         <v>206582.88415100001</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2">
       <c r="A191" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1910</v>
       </c>
       <c r="B191" s="4">
-        <f>(B149+B150) / 2</f>
+        <f t="shared" si="28"/>
         <v>205881.08261149999</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2">
       <c r="A192" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1911</v>
       </c>
       <c r="B192" s="4">
-        <f>(B150+B151) / 2</f>
+        <f t="shared" si="28"/>
         <v>203624.59460300001</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6">
       <c r="A193" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1912</v>
       </c>
       <c r="B193" s="4">
-        <f>(B151+B152) / 2</f>
+        <f t="shared" si="28"/>
         <v>202237.20285900001</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6">
       <c r="A194" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1913</v>
       </c>
       <c r="B194" s="4">
-        <f>(B152+B153) / 2</f>
+        <f t="shared" si="28"/>
         <v>201258.66536550003</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6">
       <c r="A195" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>1914</v>
       </c>
       <c r="B195" s="4">
-        <f>(B153+B154) / 2</f>
+        <f t="shared" si="28"/>
         <v>200701.38769050001</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6">
       <c r="A196" s="10" t="s">
         <v>123</v>
       </c>
@@ -20167,7 +20179,7 @@
         <v>269025.61749849998</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" ht="28.8">
       <c r="A197" s="45" t="s">
         <v>201</v>
       </c>
@@ -20176,9 +20188,9 @@
         <v>53805.123499699999</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6">
       <c r="A198" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B198" s="44"/>
       <c r="C198" s="41"/>
@@ -20186,7 +20198,7 @@
       <c r="E198" s="38"/>
       <c r="F198" s="38"/>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6">
       <c r="A199" s="1">
         <v>1881</v>
       </c>
@@ -20195,143 +20207,143 @@
         <v>18.475000534206423</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6">
       <c r="A200" s="1">
         <f>A199+1</f>
         <v>1882</v>
       </c>
       <c r="B200" s="26">
-        <f t="shared" ref="B200:B213" si="25">B163/B$197*100</f>
+        <f t="shared" ref="B200:B213" si="30">B163/B$197*100</f>
         <v>22.28474657634947</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6">
       <c r="A201" s="1">
-        <f t="shared" ref="A201:A213" si="26">A200+1</f>
+        <f t="shared" ref="A201:A213" si="31">A200+1</f>
         <v>1883</v>
       </c>
       <c r="B201" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>27.466557787163893</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6">
       <c r="A202" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1884</v>
       </c>
       <c r="B202" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>34.309298893446325</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6">
       <c r="A203" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1885</v>
       </c>
       <c r="B203" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>43.534343842051776</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6">
       <c r="A204" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1886</v>
       </c>
       <c r="B204" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>54.118486684938759</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6">
       <c r="A205" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1887</v>
       </c>
       <c r="B205" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>64.77321484392526</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6">
       <c r="A206" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1888</v>
       </c>
       <c r="B206" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>75.815000367441684</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6">
       <c r="A207" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1889</v>
       </c>
       <c r="B207" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>87.207442423697103</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6">
       <c r="A208" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1890</v>
       </c>
       <c r="B208" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>99.686028922132408</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2">
       <c r="A209" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1891</v>
       </c>
       <c r="B209" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>109.79494355371079</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2">
       <c r="A210" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1892</v>
       </c>
       <c r="B210" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>113.80276875090047</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2">
       <c r="A211" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1893</v>
       </c>
       <c r="B211" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>112.09952309622764</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2">
       <c r="A212" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1894</v>
       </c>
       <c r="B212" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>104.88446435368679</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2">
       <c r="A213" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1895</v>
       </c>
       <c r="B213" s="26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>90.877838490181389</v>
       </c>
     </row>
@@ -20344,42 +20356,42 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D506FF2-5C72-4314-9474-BB1C48673607}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.68359375" customWidth="1"/>
+    <col min="3" max="3" width="18.83984375" customWidth="1"/>
+    <col min="4" max="4" width="13.83984375" customWidth="1"/>
+    <col min="5" max="5" width="16.83984375" customWidth="1"/>
+    <col min="7" max="7" width="13.26171875" customWidth="1"/>
+    <col min="8" max="8" width="16.41796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>1</v>
       </c>
@@ -20387,7 +20399,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="B10" s="1">
         <v>1908</v>
       </c>
@@ -20395,7 +20407,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="B11" s="1">
         <v>1917</v>
       </c>
@@ -20403,7 +20415,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="B12" s="1">
         <v>1918</v>
       </c>
@@ -20411,7 +20423,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="B14" s="49" t="s">
         <v>163</v>
       </c>
@@ -20425,7 +20437,7 @@
       </c>
       <c r="H14" s="49"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="14" t="s">
         <v>19</v>
       </c>
@@ -20451,7 +20463,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="8">
         <v>1896</v>
       </c>
@@ -20481,7 +20493,7 @@
         <v>0.76905150314611981</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="8">
         <f>A16+1</f>
         <v>1897</v>
@@ -20512,7 +20524,7 @@
         <v>1.1447260834014719</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="8">
         <f t="shared" ref="A18:A36" si="3">A17+1</f>
         <v>1898</v>
@@ -20543,7 +20555,7 @@
         <v>3.4542314335060449E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="8">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -20574,7 +20586,7 @@
         <v>1.0711553175210407</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="8">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -20605,7 +20617,7 @@
         <v>2.3305537737866153</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="8">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -20636,7 +20648,7 @@
         <v>5.4061158328222199</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" s="8">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -20667,7 +20679,7 @@
         <v>7.1772055188530857</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="8">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -20698,7 +20710,7 @@
         <v>5.5701523909616393</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="8">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -20729,7 +20741,7 @@
         <v>7.0417936438833264</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="8">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -20760,7 +20772,7 @@
         <v>5.8077684314695697</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="8">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -20791,7 +20803,7 @@
         <v>5.8372604461200126</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="8">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -20822,7 +20834,7 @@
         <v>8.159514105330457</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="8">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -20853,7 +20865,7 @@
         <v>13.693419551160137</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="8">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -20884,7 +20896,7 @@
         <v>9.1432480191529386</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="8">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -20915,7 +20927,7 @@
         <v>11.441897961534032</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="8">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -20946,7 +20958,7 @@
         <v>13.023456612462224</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="8">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -20977,7 +20989,7 @@
         <v>13.15820198482195</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="8">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -21008,7 +21020,7 @@
         <v>9.6225471121240762</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" s="8">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -21039,7 +21051,7 @@
         <v>12.839879154078551</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="8">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -21070,7 +21082,7 @@
         <v>5.8097109177659272</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" s="8">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -21101,7 +21113,7 @@
         <v>5.6818181818181817</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="8" t="s">
         <v>80</v>
       </c>
@@ -21148,60 +21160,60 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
-    <col min="15" max="15" width="26.7109375" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.83984375" customWidth="1"/>
+    <col min="11" max="11" width="13.578125" customWidth="1"/>
+    <col min="15" max="15" width="26.68359375" customWidth="1"/>
+    <col min="16" max="16" width="19.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="41" t="s">
         <v>169</v>
       </c>
       <c r="P1" s="10"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1896</v>
       </c>
@@ -21247,7 +21259,7 @@
       <c r="P2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1897</v>
       </c>
@@ -21293,7 +21305,7 @@
       <c r="P3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>1898</v>
       </c>
@@ -21339,7 +21351,7 @@
       <c r="P4" s="4"/>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>1899</v>
       </c>
@@ -21385,7 +21397,7 @@
       <c r="P5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -21431,7 +21443,7 @@
       <c r="P6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>1901</v>
       </c>
@@ -21477,7 +21489,7 @@
       <c r="P7" s="4"/>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>1902</v>
       </c>
@@ -21523,7 +21535,7 @@
       <c r="P8" s="4"/>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>1903</v>
       </c>
@@ -21569,7 +21581,7 @@
       <c r="P9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>1904</v>
       </c>
@@ -21615,7 +21627,7 @@
       <c r="P10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>1905</v>
       </c>
@@ -21661,7 +21673,7 @@
       <c r="P11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>1906</v>
       </c>
@@ -21707,7 +21719,7 @@
       <c r="P12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>1907</v>
       </c>
@@ -21753,7 +21765,7 @@
       <c r="P13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>1908</v>
       </c>
@@ -21799,7 +21811,7 @@
       <c r="P14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>1909</v>
       </c>
@@ -21845,7 +21857,7 @@
       <c r="P15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>1910</v>
       </c>
@@ -21891,7 +21903,7 @@
       <c r="P16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>1911</v>
       </c>
@@ -21937,7 +21949,7 @@
       <c r="P17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>1912</v>
       </c>
@@ -21983,7 +21995,7 @@
       <c r="P18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>1913</v>
       </c>
@@ -22029,7 +22041,7 @@
       <c r="P19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>1914</v>
       </c>
@@ -22075,7 +22087,7 @@
       <c r="P20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>1915</v>
       </c>
@@ -22121,7 +22133,7 @@
       <c r="P21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>1916</v>
       </c>
@@ -22167,15 +22179,15 @@
       <c r="P22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18">
       <c r="R24" s="4"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18">
       <c r="A25" s="47" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18">
       <c r="A26" t="s">
         <v>203</v>
       </c>
@@ -22183,29 +22195,71 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18">
       <c r="A27" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
         <v>123</v>
       </c>
       <c r="B31" s="4">
-        <f>AVERAGE(B2:B6)</f>
+        <f t="shared" ref="B31:M31" si="0">AVERAGE(B2:B6)</f>
         <v>0.29029344824026204</v>
       </c>
       <c r="C31" s="4">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5861.5519938519883</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" ref="D31:M31" si="0">AVERAGE(D2:D6)</f>
+        <f t="shared" si="0"/>
         <v>4231.1951632577848</v>
       </c>
       <c r="E31" s="4">
@@ -22244,11 +22298,9 @@
         <f t="shared" si="0"/>
         <v>49.260590808123176</v>
       </c>
-      <c r="O31" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:18">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -22263,9 +22315,9 @@
       <c r="M32" s="4"/>
       <c r="O32" s="4"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -22281,37 +22333,155 @@
       <c r="M33" s="4"/>
       <c r="O33" s="4"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
+    <row r="34" spans="1:15">
+      <c r="A34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="O34" s="4"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="4">
+        <f>B31</f>
+        <v>0.29029344824026204</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4">
+        <f t="shared" ref="C35:M35" si="1">D31</f>
+        <v>4231.1951632577848</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" si="1"/>
+        <v>0.76053690733800128</v>
+      </c>
+      <c r="F35" s="4">
+        <f t="shared" si="1"/>
+        <v>25753.922387578099</v>
+      </c>
+      <c r="G35" s="4">
+        <f t="shared" si="1"/>
+        <v>5811.2768055236984</v>
+      </c>
+      <c r="H35" s="4">
+        <f t="shared" si="1"/>
+        <v>11833.25487288596</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="1"/>
+        <v>665.11834373800025</v>
+      </c>
+      <c r="J35" s="4">
+        <f t="shared" si="1"/>
+        <v>10.241153407602926</v>
+      </c>
+      <c r="K35" s="4">
+        <f t="shared" si="1"/>
+        <v>1011.3841073369298</v>
+      </c>
+      <c r="L35" s="4">
+        <f>SUM(B35:K35)+M35</f>
+        <v>49366.704254891782</v>
+      </c>
+      <c r="M35" s="4">
+        <f t="shared" si="1"/>
+        <v>49.260590808123176</v>
+      </c>
       <c r="O35" s="4"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="50">
+        <f>B35/$L35*100</f>
+        <v>5.8803489643831483E-4</v>
+      </c>
+      <c r="C36" s="50">
+        <f>C35/$L35*100</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="50">
+        <f>D35/$L35*100</f>
+        <v>8.5709492402230048</v>
+      </c>
+      <c r="E36" s="50">
+        <f>E35/$L35*100</f>
+        <v>1.5405867554195481E-3</v>
+      </c>
+      <c r="F36" s="50">
+        <f>F35/$L35*100</f>
+        <v>52.168607923681932</v>
+      </c>
+      <c r="G36" s="50">
+        <f>G35/$L35*100</f>
+        <v>11.771652358072608</v>
+      </c>
+      <c r="H36" s="50">
+        <f>H35/$L35*100</f>
+        <v>23.970113159242132</v>
+      </c>
+      <c r="I36" s="50">
+        <f>I35/$L35*100</f>
+        <v>1.3473014935407466</v>
+      </c>
+      <c r="J36" s="50">
+        <f>J35/$L35*100</f>
+        <v>2.0745062005203888E-2</v>
+      </c>
+      <c r="K36" s="50">
+        <f>K35/$L35*100</f>
+        <v>2.0487170910071661</v>
+      </c>
+      <c r="L36" s="50">
+        <f>L35/$L35*100</f>
+        <v>100</v>
+      </c>
+      <c r="M36" s="50">
+        <f>M35/$L35*100</f>
+        <v>9.9785050575341816E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -22333,64 +22503,68 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FEA9BB-FB24-45B6-A20A-F26B22290AE7}">
-  <dimension ref="A1:V25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="16" max="16" width="25.05078125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22">
       <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="T1" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R1" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="T1" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1">
         <v>1881</v>
       </c>
@@ -22398,65 +22572,67 @@
         <v>16.564583374629162</v>
       </c>
       <c r="C2" s="4">
-        <f>C$25*$B2/100</f>
+        <f>C$27*$B2/100</f>
         <v>4.8085900264844161E-2</v>
       </c>
       <c r="D2" s="4">
-        <f t="shared" ref="D2:N16" si="0">D$25*$B2/100</f>
+        <f>D$27*$B2/100</f>
         <v>0</v>
       </c>
       <c r="E2" s="4">
-        <f t="shared" si="0"/>
+        <f>E$27*$B2/100</f>
         <v>700.87985056111222</v>
       </c>
       <c r="F2" s="4">
-        <f t="shared" si="0"/>
+        <f>F$27*$B2/100</f>
         <v>0.12597977011082936</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" si="0"/>
+        <f>G$27*$B2/100</f>
         <v>4266.02994612766</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" si="0"/>
+        <f>H$27*$B2/100</f>
         <v>962.61379158145928</v>
       </c>
       <c r="I2" s="4">
-        <f t="shared" si="0"/>
+        <f>I$27*$B2/100</f>
         <v>1960.1293693515629</v>
       </c>
       <c r="J2" s="4">
-        <f t="shared" si="0"/>
+        <f>J$27*$B2/100</f>
         <v>110.17408258843363</v>
       </c>
       <c r="K2" s="4">
-        <f t="shared" si="0"/>
+        <f>K$27*$B2/100</f>
         <v>1.6964043947260623</v>
       </c>
       <c r="L2" s="4">
-        <f t="shared" si="0"/>
+        <f>L$27*$B2/100</f>
         <v>167.53156369757463</v>
       </c>
       <c r="M2" s="4">
-        <f t="shared" si="0"/>
-        <v>9148.3305526770018</v>
+        <f>M$27*$B2/100</f>
+        <v>8177.3888856081512</v>
       </c>
       <c r="N2" s="4">
-        <f t="shared" si="0"/>
+        <f>N$27*$B2/100</f>
         <v>8.1598116352464736</v>
       </c>
-      <c r="P2">
-        <v>0</v>
+      <c r="P2" s="29">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>9940.4968540000009</v>
       </c>
       <c r="T2" s="4">
-        <v>10028</v>
-      </c>
-      <c r="V2" s="4">
-        <f>T2-M2</f>
-        <v>879.66944732299817</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+        <f>M2/R2*100</f>
+        <v>82.263381858197718</v>
+      </c>
+      <c r="U2" s="53"/>
+      <c r="V2" s="54"/>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" s="1">
         <v>1882</v>
       </c>
@@ -22464,65 +22640,66 @@
         <v>19.924412112562521</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:C16" si="1">C$25*$B3/100</f>
+        <f>C$27*$B3/100</f>
         <v>5.7839262963158181E-2</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" si="0"/>
+        <f>D$27*$B3/100</f>
         <v>0</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" si="0"/>
+        <f>E$27*$B3/100</f>
         <v>843.04076161429361</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" si="0"/>
+        <f>F$27*$B3/100</f>
         <v>0.15153250768616114</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>G$27*$B3/100</f>
         <v>5131.3176316505615</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="0"/>
+        <f>H$27*$B3/100</f>
         <v>1157.8627397343</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" si="0"/>
+        <f>I$27*$B3/100</f>
         <v>2357.706467203685</v>
       </c>
       <c r="J3" s="4">
-        <f t="shared" si="0"/>
+        <f>J$27*$B3/100</f>
         <v>132.52091984260935</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" si="0"/>
+        <f>K$27*$B3/100</f>
         <v>2.040489610010547</v>
       </c>
       <c r="L3" s="4">
-        <f t="shared" si="0"/>
+        <f>L$27*$B3/100</f>
         <v>201.51233758677157</v>
       </c>
       <c r="M3" s="4">
-        <f t="shared" si="0"/>
-        <v>11003.905377581772</v>
+        <f>M$27*$B3/100</f>
+        <v>9836.0256021345758</v>
       </c>
       <c r="N3" s="4">
-        <f t="shared" si="0"/>
+        <f>N$27*$B3/100</f>
         <v>9.814883121693553</v>
       </c>
-      <c r="P3">
-        <v>0</v>
+      <c r="P3" s="29">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>11990.335417</v>
       </c>
       <c r="T3" s="4">
-        <v>12062</v>
-      </c>
-      <c r="V3" s="4">
-        <f t="shared" ref="V3:V16" si="2">T3-M3</f>
-        <v>1058.094622418228</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" ref="T3:T16" si="0">M3/R3*100</f>
+        <v>82.032947870573949</v>
+      </c>
+      <c r="V3" s="4"/>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" s="1">
         <v>1883</v>
       </c>
@@ -22530,65 +22707,66 @@
         <v>24.424831678196462</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B4/100</f>
         <v>7.0903686105516381E-2</v>
       </c>
       <c r="D4" s="4">
+        <f>D$27*$B4/100</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <f>E$27*$B4/100</f>
+        <v>1033.4622966017039</v>
+      </c>
+      <c r="F4" s="4">
+        <f>F$27*$B4/100</f>
+        <v>0.1857598594678678</v>
+      </c>
+      <c r="G4" s="4">
+        <f>G$27*$B4/100</f>
+        <v>6290.3521936993056</v>
+      </c>
+      <c r="H4" s="4">
+        <f>H$27*$B4/100</f>
+        <v>1419.3945781032357</v>
+      </c>
+      <c r="I4" s="4">
+        <f>I$27*$B4/100</f>
+        <v>2890.2525847543766</v>
+      </c>
+      <c r="J4" s="4">
+        <f>J$27*$B4/100</f>
+        <v>162.45403591881472</v>
+      </c>
+      <c r="K4" s="4">
+        <f>K$27*$B4/100</f>
+        <v>2.5013844817128956</v>
+      </c>
+      <c r="L4" s="4">
+        <f>L$27*$B4/100</f>
+        <v>247.02886583707493</v>
+      </c>
+      <c r="M4" s="4">
+        <f>M$27*$B4/100</f>
+        <v>12057.734419330367</v>
+      </c>
+      <c r="N4" s="4">
+        <f>N$27*$B4/100</f>
+        <v>12.031816388569204</v>
+      </c>
+      <c r="P4" s="29">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>14778.415338499999</v>
+      </c>
+      <c r="T4" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <f t="shared" si="0"/>
-        <v>1033.4622966017039</v>
-      </c>
-      <c r="F4" s="4">
-        <f t="shared" si="0"/>
-        <v>0.1857598594678678</v>
-      </c>
-      <c r="G4" s="4">
-        <f t="shared" si="0"/>
-        <v>6290.3521936993056</v>
-      </c>
-      <c r="H4" s="4">
-        <f t="shared" si="0"/>
-        <v>1419.3945781032357</v>
-      </c>
-      <c r="I4" s="4">
-        <f t="shared" si="0"/>
-        <v>2890.2525847543766</v>
-      </c>
-      <c r="J4" s="4">
-        <f t="shared" si="0"/>
-        <v>162.45403591881472</v>
-      </c>
-      <c r="K4" s="4">
-        <f t="shared" si="0"/>
-        <v>2.5013844817128956</v>
-      </c>
-      <c r="L4" s="4">
-        <f t="shared" si="0"/>
-        <v>247.02886583707493</v>
-      </c>
-      <c r="M4" s="4">
-        <f t="shared" si="0"/>
-        <v>13489.408627558685</v>
-      </c>
-      <c r="N4" s="4">
-        <f t="shared" si="0"/>
-        <v>12.031816388569204</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4">
-        <v>14786.5</v>
-      </c>
-      <c r="V4" s="4">
-        <f t="shared" si="2"/>
-        <v>1297.0913724413149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>81.590171497739348</v>
+      </c>
+      <c r="V4" s="4"/>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="1">
         <v>1884</v>
       </c>
@@ -22596,65 +22774,66 @@
         <v>30.304531969579841</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B5/100</f>
         <v>8.7972070827565918E-2</v>
       </c>
       <c r="D5" s="4">
+        <f>D$27*$B5/100</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f>E$27*$B5/100</f>
+        <v>1282.2438909447715</v>
+      </c>
+      <c r="F5" s="4">
+        <f>F$27*$B5/100</f>
+        <v>0.23047715022469842</v>
+      </c>
+      <c r="G5" s="4">
+        <f>G$27*$B5/100</f>
+        <v>7804.6056433643853</v>
+      </c>
+      <c r="H5" s="4">
+        <f>H$27*$B5/100</f>
+        <v>1761.0802373707074</v>
+      </c>
+      <c r="I5" s="4">
+        <f>I$27*$B5/100</f>
+        <v>3586.0125059955903</v>
+      </c>
+      <c r="J5" s="4">
+        <f>J$27*$B5/100</f>
+        <v>201.56100111362221</v>
+      </c>
+      <c r="K5" s="4">
+        <f>K$27*$B5/100</f>
+        <v>3.1035336084607441</v>
+      </c>
+      <c r="L5" s="4">
+        <f>L$27*$B5/100</f>
+        <v>306.49522014316955</v>
+      </c>
+      <c r="M5" s="4">
+        <f>M$27*$B5/100</f>
+        <v>14960.34867325161</v>
+      </c>
+      <c r="N5" s="4">
+        <f>N$27*$B5/100</f>
+        <v>14.928191489851597</v>
+      </c>
+      <c r="P5" s="29">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <v>18460.160641499999</v>
+      </c>
+      <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <f t="shared" si="0"/>
-        <v>1282.2438909447715</v>
-      </c>
-      <c r="F5" s="4">
-        <f t="shared" si="0"/>
-        <v>0.23047715022469842</v>
-      </c>
-      <c r="G5" s="4">
-        <f t="shared" si="0"/>
-        <v>7804.6056433643853</v>
-      </c>
-      <c r="H5" s="4">
-        <f t="shared" si="0"/>
-        <v>1761.0802373707074</v>
-      </c>
-      <c r="I5" s="4">
-        <f t="shared" si="0"/>
-        <v>3586.0125059955903</v>
-      </c>
-      <c r="J5" s="4">
-        <f t="shared" si="0"/>
-        <v>201.56100111362221</v>
-      </c>
-      <c r="K5" s="4">
-        <f t="shared" si="0"/>
-        <v>3.1035336084607441</v>
-      </c>
-      <c r="L5" s="4">
-        <f t="shared" si="0"/>
-        <v>306.49522014316955</v>
-      </c>
-      <c r="M5" s="4">
-        <f t="shared" si="0"/>
-        <v>16736.664571142035</v>
-      </c>
-      <c r="N5" s="4">
-        <f t="shared" si="0"/>
-        <v>14.928191489851597</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4">
-        <v>18346</v>
-      </c>
-      <c r="V5" s="4">
-        <f t="shared" si="2"/>
-        <v>1609.3354288579649</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>81.041270245609269</v>
+      </c>
+      <c r="V5" s="4"/>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1">
         <v>1885</v>
       </c>
@@ -22662,65 +22841,66 @@
         <v>38.098706944967525</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B6/100</f>
         <v>0.11059805012549843</v>
       </c>
       <c r="D6" s="4">
+        <f>D$27*$B6/100</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <f>E$27*$B6/100</f>
+        <v>1612.0306455192238</v>
+      </c>
+      <c r="F6" s="4">
+        <f>F$27*$B6/100</f>
+        <v>0.28975472753502435</v>
+      </c>
+      <c r="G6" s="4">
+        <f>G$27*$B6/100</f>
+        <v>9811.9114172777645</v>
+      </c>
+      <c r="H6" s="4">
+        <f>H$27*$B6/100</f>
+        <v>2214.0213198973443</v>
+      </c>
+      <c r="I6" s="4">
+        <f>I$27*$B6/100</f>
+        <v>4508.3170960719117</v>
+      </c>
+      <c r="J6" s="4">
+        <f>J$27*$B6/100</f>
+        <v>253.40148861796246</v>
+      </c>
+      <c r="K6" s="4">
+        <f>K$27*$B6/100</f>
+        <v>3.9017470245471939</v>
+      </c>
+      <c r="L6" s="4">
+        <f>L$27*$B6/100</f>
+        <v>385.32426714227267</v>
+      </c>
+      <c r="M6" s="4">
+        <f>M$27*$B6/100</f>
+        <v>18808.075982460032</v>
+      </c>
+      <c r="N6" s="4">
+        <f>N$27*$B6/100</f>
+        <v>18.767648131346458</v>
+      </c>
+      <c r="P6" s="29">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>23423.707469000001</v>
+      </c>
+      <c r="T6" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <f t="shared" si="0"/>
-        <v>1612.0306455192238</v>
-      </c>
-      <c r="F6" s="4">
-        <f t="shared" si="0"/>
-        <v>0.28975472753502435</v>
-      </c>
-      <c r="G6" s="4">
-        <f t="shared" si="0"/>
-        <v>9811.9114172777645</v>
-      </c>
-      <c r="H6" s="4">
-        <f t="shared" si="0"/>
-        <v>2214.0213198973443</v>
-      </c>
-      <c r="I6" s="4">
-        <f t="shared" si="0"/>
-        <v>4508.3170960719117</v>
-      </c>
-      <c r="J6" s="4">
-        <f t="shared" si="0"/>
-        <v>253.40148861796246</v>
-      </c>
-      <c r="K6" s="4">
-        <f t="shared" si="0"/>
-        <v>3.9017470245471939</v>
-      </c>
-      <c r="L6" s="4">
-        <f t="shared" si="0"/>
-        <v>385.32426714227267</v>
-      </c>
-      <c r="M6" s="4">
-        <f t="shared" si="0"/>
-        <v>21041.251499024605</v>
-      </c>
-      <c r="N6" s="4">
-        <f t="shared" si="0"/>
-        <v>18.767648131346458</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4">
-        <v>23064.5</v>
-      </c>
-      <c r="V6" s="4">
-        <f t="shared" si="2"/>
-        <v>2023.2485009753946</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>80.295042991599402</v>
+      </c>
+      <c r="V6" s="4"/>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1">
         <v>1886</v>
       </c>
@@ -22728,65 +22908,66 @@
         <v>47.195352402095843</v>
       </c>
       <c r="C7" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B7/100</f>
         <v>0.13700501589718736</v>
       </c>
       <c r="D7" s="4">
+        <f>D$27*$B7/100</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <f>E$27*$B7/100</f>
+        <v>1996.9274681199461</v>
+      </c>
+      <c r="F7" s="4">
+        <f>F$27*$B7/100</f>
+        <v>0.3589380735661708</v>
+      </c>
+      <c r="G7" s="4">
+        <f>G$27*$B7/100</f>
+        <v>12154.65442817974</v>
+      </c>
+      <c r="H7" s="4">
+        <f>H$27*$B7/100</f>
+        <v>2742.652567428167</v>
+      </c>
+      <c r="I7" s="4">
+        <f>I$27*$B7/100</f>
+        <v>5584.7463378967077</v>
+      </c>
+      <c r="J7" s="4">
+        <f>J$27*$B7/100</f>
+        <v>313.90494621813241</v>
+      </c>
+      <c r="K7" s="4">
+        <f>K$27*$B7/100</f>
+        <v>4.8333484407574483</v>
+      </c>
+      <c r="L7" s="4">
+        <f>L$27*$B7/100</f>
+        <v>477.32629359645529</v>
+      </c>
+      <c r="M7" s="4">
+        <f>M$27*$B7/100</f>
+        <v>23298.79004239662</v>
+      </c>
+      <c r="N7" s="4">
+        <f>N$27*$B7/100</f>
+        <v>23.248709427248162</v>
+      </c>
+      <c r="P7" s="29">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>29118.518597000002</v>
+      </c>
+      <c r="T7" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <f t="shared" si="0"/>
-        <v>1996.9274681199461</v>
-      </c>
-      <c r="F7" s="4">
-        <f t="shared" si="0"/>
-        <v>0.3589380735661708</v>
-      </c>
-      <c r="G7" s="4">
-        <f t="shared" si="0"/>
-        <v>12154.65442817974</v>
-      </c>
-      <c r="H7" s="4">
-        <f t="shared" si="0"/>
-        <v>2742.652567428167</v>
-      </c>
-      <c r="I7" s="4">
-        <f t="shared" si="0"/>
-        <v>5584.7463378967077</v>
-      </c>
-      <c r="J7" s="4">
-        <f t="shared" si="0"/>
-        <v>313.90494621813241</v>
-      </c>
-      <c r="K7" s="4">
-        <f t="shared" si="0"/>
-        <v>4.8333484407574483</v>
-      </c>
-      <c r="L7" s="4">
-        <f t="shared" si="0"/>
-        <v>477.32629359645529</v>
-      </c>
-      <c r="M7" s="4">
-        <f t="shared" si="0"/>
-        <v>26065.170162127142</v>
-      </c>
-      <c r="N7" s="4">
-        <f t="shared" si="0"/>
-        <v>23.248709427248162</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4">
-        <v>28571.5</v>
-      </c>
-      <c r="V7" s="4">
-        <f t="shared" si="2"/>
-        <v>2506.3298378728578</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>80.013651672503102</v>
+      </c>
+      <c r="V7" s="4"/>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1">
         <v>1887</v>
       </c>
@@ -22794,65 +22975,66 @@
         <v>56.825539984274542</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B8/100</f>
         <v>0.16496081950149943</v>
       </c>
       <c r="D8" s="4">
+        <f>D$27*$B8/100</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <f>E$27*$B8/100</f>
+        <v>2404.3994993097426</v>
+      </c>
+      <c r="F8" s="4">
+        <f>F$27*$B8/100</f>
+        <v>0.43217920437452095</v>
+      </c>
+      <c r="G8" s="4">
+        <f>G$27*$B8/100</f>
+        <v>14634.805463872226</v>
+      </c>
+      <c r="H8" s="4">
+        <f>H$27*$B8/100</f>
+        <v>3302.2894247197419</v>
+      </c>
+      <c r="I8" s="4">
+        <f>I$27*$B8/100</f>
+        <v>6724.3109792329269</v>
+      </c>
+      <c r="J8" s="4">
+        <f>J$27*$B8/100</f>
+        <v>377.95709036358198</v>
+      </c>
+      <c r="K8" s="4">
+        <f>K$27*$B8/100</f>
+        <v>5.8195907244882958</v>
+      </c>
+      <c r="L8" s="4">
+        <f>L$27*$B8/100</f>
+        <v>574.72448030934515</v>
+      </c>
+      <c r="M8" s="4">
+        <f>M$27*$B8/100</f>
+        <v>28052.896265282092</v>
+      </c>
+      <c r="N8" s="4">
+        <f>N$27*$B8/100</f>
+        <v>27.992596726159903</v>
+      </c>
+      <c r="P8" s="29">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>34851.308241500003</v>
+      </c>
+      <c r="T8" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
-        <f t="shared" si="0"/>
-        <v>2404.3994993097426</v>
-      </c>
-      <c r="F8" s="4">
-        <f t="shared" si="0"/>
-        <v>0.43217920437452095</v>
-      </c>
-      <c r="G8" s="4">
-        <f t="shared" si="0"/>
-        <v>14634.805463872226</v>
-      </c>
-      <c r="H8" s="4">
-        <f t="shared" si="0"/>
-        <v>3302.2894247197419</v>
-      </c>
-      <c r="I8" s="4">
-        <f t="shared" si="0"/>
-        <v>6724.3109792329269</v>
-      </c>
-      <c r="J8" s="4">
-        <f t="shared" si="0"/>
-        <v>377.95709036358198</v>
-      </c>
-      <c r="K8" s="4">
-        <f t="shared" si="0"/>
-        <v>5.8195907244882958</v>
-      </c>
-      <c r="L8" s="4">
-        <f t="shared" si="0"/>
-        <v>574.72448030934515</v>
-      </c>
-      <c r="M8" s="4">
-        <f t="shared" si="0"/>
-        <v>31383.754837247496</v>
-      </c>
-      <c r="N8" s="4">
-        <f t="shared" si="0"/>
-        <v>27.992596726159903</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4">
-        <v>34401.5</v>
-      </c>
-      <c r="V8" s="4">
-        <f t="shared" si="2"/>
-        <v>3017.7451627525043</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>80.493093891601617</v>
+      </c>
+      <c r="V8" s="4"/>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1">
         <v>1888</v>
       </c>
@@ -22860,65 +23042,66 @@
         <v>67.303943916959042</v>
       </c>
       <c r="C9" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B9/100</f>
         <v>0.19537893959823249</v>
       </c>
       <c r="D9" s="4">
+        <f>D$27*$B9/100</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <f>E$27*$B9/100</f>
+        <v>2847.7612196961027</v>
+      </c>
+      <c r="F9" s="4">
+        <f>F$27*$B9/100</f>
+        <v>0.51187133358254311</v>
+      </c>
+      <c r="G9" s="4">
+        <f>G$27*$B9/100</f>
+        <v>17333.405480152724</v>
+      </c>
+      <c r="H9" s="4">
+        <f>H$27*$B9/100</f>
+        <v>3911.2184820489188</v>
+      </c>
+      <c r="I9" s="4">
+        <f>I$27*$B9/100</f>
+        <v>7964.24722319799</v>
+      </c>
+      <c r="J9" s="4">
+        <f>J$27*$B9/100</f>
+        <v>447.65087705083056</v>
+      </c>
+      <c r="K9" s="4">
+        <f>K$27*$B9/100</f>
+        <v>6.892700145902813</v>
+      </c>
+      <c r="L9" s="4">
+        <f>L$27*$B9/100</f>
+        <v>680.70139238708407</v>
+      </c>
+      <c r="M9" s="4">
+        <f>M$27*$B9/100</f>
+        <v>33225.738945363395</v>
+      </c>
+      <c r="N9" s="4">
+        <f>N$27*$B9/100</f>
+        <v>33.154320410661903</v>
+      </c>
+      <c r="P9" s="29">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4">
+        <v>40792.354579000006</v>
+      </c>
+      <c r="T9" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <f t="shared" si="0"/>
-        <v>2847.7612196961027</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="0"/>
-        <v>0.51187133358254311</v>
-      </c>
-      <c r="G9" s="4">
-        <f t="shared" si="0"/>
-        <v>17333.405480152724</v>
-      </c>
-      <c r="H9" s="4">
-        <f t="shared" si="0"/>
-        <v>3911.2184820489188</v>
-      </c>
-      <c r="I9" s="4">
-        <f t="shared" si="0"/>
-        <v>7964.24722319799</v>
-      </c>
-      <c r="J9" s="4">
-        <f t="shared" si="0"/>
-        <v>447.65087705083056</v>
-      </c>
-      <c r="K9" s="4">
-        <f t="shared" si="0"/>
-        <v>6.892700145902813</v>
-      </c>
-      <c r="L9" s="4">
-        <f t="shared" si="0"/>
-        <v>680.70139238708407</v>
-      </c>
-      <c r="M9" s="4">
-        <f t="shared" si="0"/>
-        <v>37170.794611968937</v>
-      </c>
-      <c r="N9" s="4">
-        <f t="shared" si="0"/>
-        <v>33.154320410661903</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4">
-        <v>40745</v>
-      </c>
-      <c r="V9" s="4">
-        <f t="shared" si="2"/>
-        <v>3574.2053880310632</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>81.45089757203688</v>
+      </c>
+      <c r="V9" s="4"/>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="1">
         <v>1889</v>
       </c>
@@ -22926,65 +23109,66 @@
         <v>78.685900612499751</v>
       </c>
       <c r="C10" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B10/100</f>
         <v>0.228420014166931</v>
       </c>
       <c r="D10" s="4">
+        <f>D$27*$B10/100</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <f>E$27*$B10/100</f>
+        <v>3329.3540208819172</v>
+      </c>
+      <c r="F10" s="4">
+        <f>F$27*$B10/100</f>
+        <v>0.59843531502935898</v>
+      </c>
+      <c r="G10" s="4">
+        <f>G$27*$B10/100</f>
+        <v>20264.705773710026</v>
+      </c>
+      <c r="H10" s="4">
+        <f>H$27*$B10/100</f>
+        <v>4572.6554915116276</v>
+      </c>
+      <c r="I10" s="4">
+        <f>I$27*$B10/100</f>
+        <v>9311.1031685028302</v>
+      </c>
+      <c r="J10" s="4">
+        <f>J$27*$B10/100</f>
+        <v>523.35435890918734</v>
+      </c>
+      <c r="K10" s="4">
+        <f>K$27*$B10/100</f>
+        <v>8.0583437918800698</v>
+      </c>
+      <c r="L10" s="4">
+        <f>L$27*$B10/100</f>
+        <v>795.81669350975437</v>
+      </c>
+      <c r="M10" s="4">
+        <f>M$27*$B10/100</f>
+        <v>38844.635845670833</v>
+      </c>
+      <c r="N10" s="4">
+        <f>N$27*$B10/100</f>
+        <v>38.761139524409991</v>
+      </c>
+      <c r="P10" s="29">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4">
+        <v>46922.072096999997</v>
+      </c>
+      <c r="T10" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <f t="shared" si="0"/>
-        <v>3329.3540208819172</v>
-      </c>
-      <c r="F10" s="4">
-        <f t="shared" si="0"/>
-        <v>0.59843531502935898</v>
-      </c>
-      <c r="G10" s="4">
-        <f t="shared" si="0"/>
-        <v>20264.705773710026</v>
-      </c>
-      <c r="H10" s="4">
-        <f t="shared" si="0"/>
-        <v>4572.6554915116276</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" si="0"/>
-        <v>9311.1031685028302</v>
-      </c>
-      <c r="J10" s="4">
-        <f t="shared" si="0"/>
-        <v>523.35435890918734</v>
-      </c>
-      <c r="K10" s="4">
-        <f t="shared" si="0"/>
-        <v>8.0583437918800698</v>
-      </c>
-      <c r="L10" s="4">
-        <f t="shared" si="0"/>
-        <v>795.81669350975437</v>
-      </c>
-      <c r="M10" s="4">
-        <f t="shared" si="0"/>
-        <v>43456.850821903208</v>
-      </c>
-      <c r="N10" s="4">
-        <f t="shared" si="0"/>
-        <v>38.761139524409991</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4">
-        <v>47635.5</v>
-      </c>
-      <c r="V10" s="4">
-        <f t="shared" si="2"/>
-        <v>4178.6491780967917</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>82.785422956959309</v>
+      </c>
+      <c r="V10" s="4"/>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1">
         <v>1890</v>
       </c>
@@ -22992,65 +23176,66 @@
         <v>91.885699749582088</v>
       </c>
       <c r="C11" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B11/100</f>
         <v>0.26673816624275565</v>
       </c>
       <c r="D11" s="4">
+        <f>D$27*$B11/100</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <f>E$27*$B11/100</f>
+        <v>3887.8632835298877</v>
+      </c>
+      <c r="F11" s="4">
+        <f>F$27*$B11/100</f>
+        <v>0.69882465916135317</v>
+      </c>
+      <c r="G11" s="4">
+        <f>G$27*$B11/100</f>
+        <v>23664.171798790412</v>
+      </c>
+      <c r="H11" s="4">
+        <f>H$27*$B11/100</f>
+        <v>5339.7323571406105</v>
+      </c>
+      <c r="I11" s="4">
+        <f>I$27*$B11/100</f>
+        <v>10873.069043102785</v>
+      </c>
+      <c r="J11" s="4">
+        <f>J$27*$B11/100</f>
+        <v>611.1486443064922</v>
+      </c>
+      <c r="K11" s="4">
+        <f>K$27*$B11/100</f>
+        <v>9.4101554710041189</v>
+      </c>
+      <c r="L11" s="4">
+        <f>L$27*$B11/100</f>
+        <v>929.31736418260232</v>
+      </c>
+      <c r="M11" s="4">
+        <f>M$27*$B11/100</f>
+        <v>45360.941647914027</v>
+      </c>
+      <c r="N11" s="4">
+        <f>N$27*$B11/100</f>
+        <v>45.263438564822287</v>
+      </c>
+      <c r="P11" s="29">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4">
+        <v>53636.190973500001</v>
+      </c>
+      <c r="T11" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <f t="shared" si="0"/>
-        <v>3887.8632835298877</v>
-      </c>
-      <c r="F11" s="4">
-        <f t="shared" si="0"/>
-        <v>0.69882465916135317</v>
-      </c>
-      <c r="G11" s="4">
-        <f t="shared" si="0"/>
-        <v>23664.171798790412</v>
-      </c>
-      <c r="H11" s="4">
-        <f t="shared" si="0"/>
-        <v>5339.7323571406105</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="0"/>
-        <v>10873.069043102785</v>
-      </c>
-      <c r="J11" s="4">
-        <f t="shared" si="0"/>
-        <v>611.1486443064922</v>
-      </c>
-      <c r="K11" s="4">
-        <f t="shared" si="0"/>
-        <v>9.4101554710041189</v>
-      </c>
-      <c r="L11" s="4">
-        <f t="shared" si="0"/>
-        <v>929.31736418260232</v>
-      </c>
-      <c r="M11" s="4">
-        <f t="shared" si="0"/>
-        <v>50746.869713650514</v>
-      </c>
-      <c r="N11" s="4">
-        <f t="shared" si="0"/>
-        <v>45.263438564822287</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="T11" s="4">
-        <v>55626.5</v>
-      </c>
-      <c r="V11" s="4">
-        <f t="shared" si="2"/>
-        <v>4879.6302863494857</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v>84.571519387581944</v>
+      </c>
+      <c r="V11" s="4"/>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1">
         <v>1891</v>
       </c>
@@ -23058,65 +23243,66 @@
         <v>103.17019828605787</v>
       </c>
       <c r="C12" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B12/100</f>
         <v>0.2994963261609131</v>
       </c>
       <c r="D12" s="4">
+        <f>D$27*$B12/100</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <f>E$27*$B12/100</f>
+        <v>4365.3324398031464</v>
+      </c>
+      <c r="F12" s="4">
+        <f>F$27*$B12/100</f>
+        <v>0.78464743533926806</v>
+      </c>
+      <c r="G12" s="4">
+        <f>G$27*$B12/100</f>
+        <v>26570.372793701776</v>
+      </c>
+      <c r="H12" s="4">
+        <f>H$27*$B12/100</f>
+        <v>5995.5058032104889</v>
+      </c>
+      <c r="I12" s="4">
+        <f>I$27*$B12/100</f>
+        <v>12208.392516051048</v>
+      </c>
+      <c r="J12" s="4">
+        <f>J$27*$B12/100</f>
+        <v>686.20391407143882</v>
+      </c>
+      <c r="K12" s="4">
+        <f>K$27*$B12/100</f>
+        <v>10.565818277403311</v>
+      </c>
+      <c r="L12" s="4">
+        <f>L$27*$B12/100</f>
+        <v>1043.4469889731868</v>
+      </c>
+      <c r="M12" s="4">
+        <f>M$27*$B12/100</f>
+        <v>50931.726667063616</v>
+      </c>
+      <c r="N12" s="4">
+        <f>N$27*$B12/100</f>
+        <v>50.822249213624275</v>
+      </c>
+      <c r="P12" s="29">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4">
+        <v>59075.304975500003</v>
+      </c>
+      <c r="T12" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <f t="shared" si="0"/>
-        <v>4365.3324398031464</v>
-      </c>
-      <c r="F12" s="4">
-        <f t="shared" si="0"/>
-        <v>0.78464743533926806</v>
-      </c>
-      <c r="G12" s="4">
-        <f t="shared" si="0"/>
-        <v>26570.372793701776</v>
-      </c>
-      <c r="H12" s="4">
-        <f t="shared" si="0"/>
-        <v>5995.5058032104889</v>
-      </c>
-      <c r="I12" s="4">
-        <f t="shared" si="0"/>
-        <v>12208.392516051048</v>
-      </c>
-      <c r="J12" s="4">
-        <f t="shared" si="0"/>
-        <v>686.20391407143882</v>
-      </c>
-      <c r="K12" s="4">
-        <f t="shared" si="0"/>
-        <v>10.565818277403311</v>
-      </c>
-      <c r="L12" s="4">
-        <f t="shared" si="0"/>
-        <v>1043.4469889731868</v>
-      </c>
-      <c r="M12" s="4">
-        <f t="shared" si="0"/>
-        <v>56979.101481761092</v>
-      </c>
-      <c r="N12" s="4">
-        <f t="shared" si="0"/>
-        <v>50.822249213624275</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4">
-        <v>62458</v>
-      </c>
-      <c r="V12" s="4">
-        <f t="shared" si="2"/>
-        <v>5478.8985182389079</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v>86.214919564420825</v>
+      </c>
+      <c r="V12" s="4"/>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1">
         <v>1892</v>
       </c>
@@ -23124,65 +23310,66 @@
         <v>108.41724646012143</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B13/100</f>
         <v>0.31472816323622993</v>
       </c>
       <c r="D13" s="4">
+        <f>D$27*$B13/100</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>E$27*$B13/100</f>
+        <v>4587.3452883579293</v>
+      </c>
+      <c r="F13" s="4">
+        <f>F$27*$B13/100</f>
+        <v>0.82455317324882627</v>
+      </c>
+      <c r="G13" s="4">
+        <f>G$27*$B13/100</f>
+        <v>27921.693508088938</v>
+      </c>
+      <c r="H13" s="4">
+        <f>H$27*$B13/100</f>
+        <v>6300.4262967245004</v>
+      </c>
+      <c r="I13" s="4">
+        <f>I$27*$B13/100</f>
+        <v>12829.289099791102</v>
+      </c>
+      <c r="J13" s="4">
+        <f>J$27*$B13/100</f>
+        <v>721.10299398190534</v>
+      </c>
+      <c r="K13" s="4">
+        <f>K$27*$B13/100</f>
+        <v>11.103176530279988</v>
+      </c>
+      <c r="L13" s="4">
+        <f>L$27*$B13/100</f>
+        <v>1096.5148003099782</v>
+      </c>
+      <c r="M13" s="4">
+        <f>M$27*$B13/100</f>
+        <v>53522.021421265279</v>
+      </c>
+      <c r="N13" s="4">
+        <f>N$27*$B13/100</f>
+        <v>53.406976144154832</v>
+      </c>
+      <c r="P13" s="29">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
+        <v>61231.720272500002</v>
+      </c>
+      <c r="T13" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <f t="shared" si="0"/>
-        <v>4587.3452883579293</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="0"/>
-        <v>0.82455317324882627</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" si="0"/>
-        <v>27921.693508088938</v>
-      </c>
-      <c r="H13" s="4">
-        <f t="shared" si="0"/>
-        <v>6300.4262967245004</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" si="0"/>
-        <v>12829.289099791102</v>
-      </c>
-      <c r="J13" s="4">
-        <f t="shared" si="0"/>
-        <v>721.10299398190534</v>
-      </c>
-      <c r="K13" s="4">
-        <f t="shared" si="0"/>
-        <v>11.103176530279988</v>
-      </c>
-      <c r="L13" s="4">
-        <f t="shared" si="0"/>
-        <v>1096.5148003099782</v>
-      </c>
-      <c r="M13" s="4">
-        <f t="shared" si="0"/>
-        <v>59876.95469282796</v>
-      </c>
-      <c r="N13" s="4">
-        <f t="shared" si="0"/>
-        <v>53.406976144154832</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4">
-        <v>65634.5</v>
-      </c>
-      <c r="V13" s="4">
-        <f t="shared" si="2"/>
-        <v>5757.5453071720403</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+        <v>87.408978848015067</v>
+      </c>
+      <c r="V13" s="4"/>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="1">
         <v>1893</v>
       </c>
@@ -23190,65 +23377,66 @@
         <v>108.00098449258988</v>
       </c>
       <c r="C14" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B14/100</f>
         <v>0.31351978201696984</v>
       </c>
       <c r="D14" s="4">
+        <f>D$27*$B14/100</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>E$27*$B14/100</f>
+        <v>4569.7324321212536</v>
+      </c>
+      <c r="F14" s="4">
+        <f>F$27*$B14/100</f>
+        <v>0.82138734735453733</v>
+      </c>
+      <c r="G14" s="4">
+        <f>G$27*$B14/100</f>
+        <v>27814.489724041858</v>
+      </c>
+      <c r="H14" s="4">
+        <f>H$27*$B14/100</f>
+        <v>6276.2361615551217</v>
+      </c>
+      <c r="I14" s="4">
+        <f>I$27*$B14/100</f>
+        <v>12780.031760234202</v>
+      </c>
+      <c r="J14" s="4">
+        <f>J$27*$B14/100</f>
+        <v>718.33435927784831</v>
+      </c>
+      <c r="K14" s="4">
+        <f>K$27*$B14/100</f>
+        <v>11.060546503607577</v>
+      </c>
+      <c r="L14" s="4">
+        <f>L$27*$B14/100</f>
+        <v>1092.304792925476</v>
+      </c>
+      <c r="M14" s="4">
+        <f>M$27*$B14/100</f>
+        <v>53316.526606828382</v>
+      </c>
+      <c r="N14" s="4">
+        <f>N$27*$B14/100</f>
+        <v>53.201923039639269</v>
+      </c>
+      <c r="P14" s="29">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>60315.286844500006</v>
+      </c>
+      <c r="T14" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <f t="shared" si="0"/>
-        <v>4569.7324321212536</v>
-      </c>
-      <c r="F14" s="4">
-        <f t="shared" si="0"/>
-        <v>0.82138734735453733</v>
-      </c>
-      <c r="G14" s="4">
-        <f t="shared" si="0"/>
-        <v>27814.489724041858</v>
-      </c>
-      <c r="H14" s="4">
-        <f t="shared" si="0"/>
-        <v>6276.2361615551217</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="0"/>
-        <v>12780.031760234202</v>
-      </c>
-      <c r="J14" s="4">
-        <f t="shared" si="0"/>
-        <v>718.33435927784831</v>
-      </c>
-      <c r="K14" s="4">
-        <f t="shared" si="0"/>
-        <v>11.060546503607577</v>
-      </c>
-      <c r="L14" s="4">
-        <f t="shared" si="0"/>
-        <v>1092.304792925476</v>
-      </c>
-      <c r="M14" s="4">
-        <f t="shared" si="0"/>
-        <v>59647.060466733565</v>
-      </c>
-      <c r="N14" s="4">
-        <f t="shared" si="0"/>
-        <v>53.201923039639269</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="T14" s="4">
-        <v>65382.5</v>
-      </c>
-      <c r="V14" s="4">
-        <f t="shared" si="2"/>
-        <v>5735.4395332664353</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+        <v>88.39637411372135</v>
+      </c>
+      <c r="V14" s="4"/>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1">
         <v>1894</v>
       </c>
@@ -23256,65 +23444,66 @@
         <v>102.04777762360668</v>
       </c>
       <c r="C15" s="4">
-        <f t="shared" si="1"/>
+        <f>C$27*$B15/100</f>
         <v>0.29623801251612236</v>
       </c>
       <c r="D15" s="4">
+        <f>D$27*$B15/100</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <f>E$27*$B15/100</f>
+        <v>4317.8406310221062</v>
+      </c>
+      <c r="F15" s="4">
+        <f>F$27*$B15/100</f>
+        <v>0.77611101194573906</v>
+      </c>
+      <c r="G15" s="4">
+        <f>G$27*$B15/100</f>
+        <v>26281.305447431951</v>
+      </c>
+      <c r="H15" s="4">
+        <f>H$27*$B15/100</f>
+        <v>5930.2788315930575</v>
+      </c>
+      <c r="I15" s="4">
+        <f>I$27*$B15/100</f>
+        <v>12075.573618317265</v>
+      </c>
+      <c r="J15" s="4">
+        <f>J$27*$B15/100</f>
+        <v>678.73848835157037</v>
+      </c>
+      <c r="K15" s="4">
+        <f>K$27*$B15/100</f>
+        <v>10.450869455483053</v>
+      </c>
+      <c r="L15" s="4">
+        <f>L$27*$B15/100</f>
+        <v>1032.0950047756896</v>
+      </c>
+      <c r="M15" s="4">
+        <f>M$27*$B15/100</f>
+        <v>50377.624578135546</v>
+      </c>
+      <c r="N15" s="4">
+        <f>N$27*$B15/100</f>
+        <v>50.269338163948369</v>
+      </c>
+      <c r="P15" s="29">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>56433.215577499999</v>
+      </c>
+      <c r="T15" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <f t="shared" si="0"/>
-        <v>4317.8406310221062</v>
-      </c>
-      <c r="F15" s="4">
-        <f t="shared" si="0"/>
-        <v>0.77611101194573906</v>
-      </c>
-      <c r="G15" s="4">
-        <f t="shared" si="0"/>
-        <v>26281.305447431951</v>
-      </c>
-      <c r="H15" s="4">
-        <f t="shared" si="0"/>
-        <v>5930.2788315930575</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="0"/>
-        <v>12075.573618317265</v>
-      </c>
-      <c r="J15" s="4">
-        <f t="shared" si="0"/>
-        <v>678.73848835157037</v>
-      </c>
-      <c r="K15" s="4">
-        <f t="shared" si="0"/>
-        <v>10.450869455483053</v>
-      </c>
-      <c r="L15" s="4">
-        <f t="shared" si="0"/>
-        <v>1032.0950047756896</v>
-      </c>
-      <c r="M15" s="4">
-        <f t="shared" si="0"/>
-        <v>56359.208122113712</v>
-      </c>
-      <c r="N15" s="4">
-        <f t="shared" si="0"/>
-        <v>50.269338163948369</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="T15" s="4">
-        <v>61778.5</v>
-      </c>
-      <c r="V15" s="4">
-        <f t="shared" si="2"/>
-        <v>5419.2918778862877</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+        <v>89.269456051023212</v>
+      </c>
+      <c r="V15" s="4"/>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1">
         <v>1895</v>
       </c>
@@ -23322,122 +23511,237 @@
         <v>89.260110871044688</v>
       </c>
       <c r="C16" s="4">
+        <f>C$27*$B16/100</f>
+        <v>0.25911625375063663</v>
+      </c>
+      <c r="D16" s="4">
+        <f>D$27*$B16/100</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <f>E$27*$B16/100</f>
+        <v>3776.769493894179</v>
+      </c>
+      <c r="F16" s="4">
+        <f>F$27*$B16/100</f>
+        <v>0.67885608670511433</v>
+      </c>
+      <c r="G16" s="4">
+        <f>G$27*$B16/100</f>
+        <v>22987.97967679501</v>
+      </c>
+      <c r="H16" s="4">
+        <f>H$27*$B16/100</f>
+        <v>5187.1521196337571</v>
+      </c>
+      <c r="I16" s="4">
+        <f>I$27*$B16/100</f>
+        <v>10562.376419191307</v>
+      </c>
+      <c r="J16" s="4">
+        <f>J$27*$B16/100</f>
+        <v>593.68537104419511</v>
+      </c>
+      <c r="K16" s="4">
+        <f>K$27*$B16/100</f>
+        <v>9.141264886100144</v>
+      </c>
+      <c r="L16" s="4">
+        <f>L$27*$B16/100</f>
+        <v>902.76257554106905</v>
+      </c>
+      <c r="M16" s="4">
+        <f>M$27*$B16/100</f>
+        <v>44064.774951297135</v>
+      </c>
+      <c r="N16" s="4">
+        <f>N$27*$B16/100</f>
+        <v>43.970057971062396</v>
+      </c>
+      <c r="P16" s="29">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <v>48896.9332335</v>
+      </c>
+      <c r="T16" s="4">
+        <f t="shared" si="0"/>
+        <v>90.117665950280326</v>
+      </c>
+      <c r="V16" s="4"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="47" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="51"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="4">
+        <f>SUM(C2:C16)</f>
+        <v>2.8510004633740613</v>
+      </c>
+      <c r="D23" s="4">
+        <f t="shared" ref="D23:N23" si="1">SUM(D2:D16)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
         <f t="shared" si="1"/>
-        <v>0.25911625375063663</v>
-      </c>
-      <c r="D16" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <f t="shared" si="0"/>
-        <v>3776.769493894179</v>
-      </c>
-      <c r="F16" s="4">
-        <f t="shared" si="0"/>
-        <v>0.67885608670511433</v>
-      </c>
-      <c r="G16" s="4">
-        <f t="shared" si="0"/>
-        <v>22987.97967679501</v>
-      </c>
-      <c r="H16" s="4">
-        <f t="shared" si="0"/>
-        <v>5187.1521196337571</v>
-      </c>
-      <c r="I16" s="4">
-        <f t="shared" si="0"/>
-        <v>10562.376419191307</v>
-      </c>
-      <c r="J16" s="4">
-        <f t="shared" si="0"/>
-        <v>593.68537104419511</v>
-      </c>
-      <c r="K16" s="4">
-        <f t="shared" si="0"/>
-        <v>9.141264886100144</v>
-      </c>
-      <c r="L16" s="4">
-        <f t="shared" si="0"/>
-        <v>902.76257554106905</v>
-      </c>
-      <c r="M16" s="4">
-        <f t="shared" si="0"/>
-        <v>49296.80275977336</v>
-      </c>
-      <c r="N16" s="4">
-        <f t="shared" si="0"/>
-        <v>43.970057971062396</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="T16" s="4">
-        <v>54037</v>
-      </c>
-      <c r="V16" s="4">
-        <f t="shared" si="2"/>
-        <v>4740.1972402266401</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>41554.983221977316</v>
+      </c>
+      <c r="F23" s="4">
+        <f t="shared" si="1"/>
+        <v>7.4693076553320132</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="1"/>
+        <v>252931.80092688435</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" si="1"/>
+        <v>57073.120202253034</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="1"/>
+        <v>116215.55818889529</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="1"/>
+        <v>6532.1925716566257</v>
+      </c>
+      <c r="K23" s="4">
+        <f t="shared" si="1"/>
+        <v>100.57937334636426</v>
+      </c>
+      <c r="L23" s="4">
+        <f t="shared" si="1"/>
+        <v>9932.9026409175058</v>
+      </c>
+      <c r="M23" s="4">
+        <f t="shared" si="1"/>
+        <v>484835.25053400168</v>
+      </c>
+      <c r="N23" s="4">
+        <f t="shared" si="1"/>
+        <v>483.79309995243864</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="C26" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C27" s="4">
         <v>0.29029344824026204</v>
       </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
         <v>4231.1951632577848</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F27" s="4">
         <v>0.76053690733800128</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G27" s="4">
         <v>25753.922387578099</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H27" s="4">
         <v>5811.2768055236984</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I27" s="4">
         <v>11833.25487288596</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J27" s="4">
         <v>665.11834373800025</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K27" s="4">
         <v>10.241153407602926</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L27" s="4">
         <v>1011.3841073369298</v>
       </c>
-      <c r="M25" s="4">
-        <v>55228.256248743775</v>
-      </c>
-      <c r="N25" s="4">
+      <c r="M27" s="4">
+        <v>49366.704254891782</v>
+      </c>
+      <c r="N27" s="4">
         <v>49.260590808123176</v>
       </c>
-      <c r="P25" s="4">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" t="s">
+        <v>215</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="P29" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/emigration.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21740C73-4730-4EB9-9F14-C3677748D918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E078274-188C-4D37-AE00-10EACB0F6A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="217">
   <si>
     <t>Источник: ЦСК, "Ежегодник России" ("Статистический Ежегодник России")</t>
   </si>
@@ -630,9 +630,6 @@
     <t>Общая эмиграция из России по годам, с учётом реэмиграции, выдача EmigrationShowSum</t>
   </si>
   <si>
-    <t>с учётом реэмиграции</t>
-  </si>
-  <si>
     <t>NBER, "International Migrations", Volume I : Statistics, сост. W. Willcox, New York, 1929, стр. 241-248 (table 11)</t>
   </si>
   <si>
@@ -712,6 +709,10 @@
   </si>
   <si>
     <t>v%</t>
+  </si>
+  <si>
+    <t>с учётом
+реэмиграции</t>
   </si>
 </sst>
 </file>
@@ -797,7 +798,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -899,16 +900,16 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17304,14 +17305,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
-  <dimension ref="A1:N213"/>
+  <dimension ref="A1:N228"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.41796875" customWidth="1"/>
     <col min="2" max="2" width="17.41796875" customWidth="1"/>
     <col min="3" max="3" width="10.68359375" customWidth="1"/>
     <col min="4" max="4" width="14.26171875" customWidth="1"/>
-    <col min="5" max="5" width="11.83984375" customWidth="1"/>
+    <col min="5" max="5" width="12.62890625" customWidth="1"/>
     <col min="6" max="6" width="13.26171875" customWidth="1"/>
     <col min="7" max="7" width="10.26171875" customWidth="1"/>
     <col min="9" max="9" width="12.26171875" customWidth="1"/>
@@ -17320,12 +17321,12 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="57.6">
@@ -17950,7 +17951,7 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -17965,7 +17966,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -18393,12 +18394,12 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="72">
@@ -18412,13 +18413,13 @@
         <v>109</v>
       </c>
       <c r="D42" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="F42" s="40" t="s">
         <v>210</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="F42" s="40" t="s">
-        <v>211</v>
       </c>
       <c r="G42" s="39" t="s">
         <v>110</v>
@@ -18913,1437 +18914,1626 @@
       </c>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="1">
+      <c r="A60" s="52">
+        <f t="shared" ref="A60:A73" si="23">A61-1</f>
+        <v>1881</v>
+      </c>
+      <c r="B60" s="4">
+        <v>9121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" s="52">
+        <f t="shared" si="23"/>
+        <v>1882</v>
+      </c>
+      <c r="B61" s="4">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="A62" s="52">
+        <f t="shared" si="23"/>
+        <v>1883</v>
+      </c>
+      <c r="B62" s="4">
+        <v>13560</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" s="52">
+        <f t="shared" si="23"/>
+        <v>1884</v>
+      </c>
+      <c r="B63" s="4">
+        <v>16938</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64" s="52">
+        <f t="shared" si="23"/>
+        <v>1885</v>
+      </c>
+      <c r="B64" s="4">
+        <v>21491</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="52">
+        <f t="shared" si="23"/>
+        <v>1886</v>
+      </c>
+      <c r="B65" s="4">
+        <v>26717</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="52">
+        <f t="shared" si="23"/>
+        <v>1887</v>
+      </c>
+      <c r="B66" s="4">
+        <v>31977</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="52">
+        <f t="shared" si="23"/>
+        <v>1888</v>
+      </c>
+      <c r="B67" s="4">
+        <v>37427</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="52">
+        <f t="shared" si="23"/>
+        <v>1889</v>
+      </c>
+      <c r="B68" s="4">
+        <v>43051</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="52">
+        <f t="shared" si="23"/>
+        <v>1890</v>
+      </c>
+      <c r="B69" s="4">
+        <v>49211</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="52">
+        <f t="shared" si="23"/>
+        <v>1891</v>
+      </c>
+      <c r="B70" s="4">
+        <v>54201</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="52">
+        <f t="shared" si="23"/>
+        <v>1892</v>
+      </c>
+      <c r="B71" s="4">
+        <v>56181</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="52">
+        <f t="shared" si="23"/>
+        <v>1893</v>
+      </c>
+      <c r="B72" s="4">
+        <v>55339</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="52">
+        <f t="shared" si="23"/>
+        <v>1894</v>
+      </c>
+      <c r="B73" s="4">
+        <v>51779</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="52">
+        <f>A75-1</f>
+        <v>1895</v>
+      </c>
+      <c r="B74" s="4">
+        <v>44863</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="1">
         <v>1896</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B75" s="4">
         <v>35639</v>
       </c>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="1">
+      <c r="E75" s="4"/>
+      <c r="G75" s="4"/>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="1">
         <v>1897</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B76" s="4">
         <v>28021</v>
       </c>
-    </row>
-    <row r="62" spans="1:13">
-      <c r="A62" s="1">
+      <c r="E76" s="4"/>
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="1">
         <v>1898</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B77" s="4">
         <v>41907</v>
       </c>
-    </row>
-    <row r="63" spans="1:13">
-      <c r="A63" s="1">
+      <c r="E77" s="4"/>
+      <c r="G77" s="4"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="1">
         <v>1899</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B78" s="4">
         <v>65559</v>
       </c>
-    </row>
-    <row r="64" spans="1:13">
-      <c r="A64" s="1">
+      <c r="E78" s="4"/>
+      <c r="G78" s="4"/>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="1">
         <v>1900</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B79" s="4">
         <v>76085</v>
       </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="1">
+      <c r="E79" s="4"/>
+      <c r="G79" s="4"/>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="1">
         <v>1901</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B80" s="4">
         <v>83166</v>
       </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="1">
+      <c r="E80" s="4"/>
+      <c r="G80" s="4"/>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="1">
         <v>1902</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B81" s="4">
         <v>103114</v>
       </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="1">
+      <c r="E81" s="4"/>
+      <c r="G81" s="4"/>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="1">
         <v>1903</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B82" s="4">
         <v>125022</v>
       </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="1">
+      <c r="E82" s="4"/>
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="1">
         <v>1904</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B83" s="4">
         <v>151739</v>
       </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="1">
+      <c r="E83" s="4"/>
+      <c r="G83" s="4"/>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="1">
         <v>1905</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B84" s="4">
         <v>186157</v>
       </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="1">
+      <c r="E84" s="4"/>
+      <c r="G84" s="4"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="1">
         <v>1906</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B85" s="4">
         <v>221400</v>
       </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="1">
+      <c r="E85" s="4"/>
+      <c r="G85" s="4"/>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="1">
         <v>1907</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B86" s="4">
         <v>186071</v>
       </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="1">
+      <c r="E86" s="4"/>
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="1">
         <v>1908</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B87" s="4">
         <v>119541</v>
       </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="1">
+      <c r="E87" s="4"/>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="1">
         <v>1909</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B88" s="4">
         <v>141698</v>
       </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="1">
+      <c r="E88" s="4"/>
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="1">
         <v>1910</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B89" s="4">
         <v>162676</v>
       </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="1">
+      <c r="E89" s="4"/>
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="1">
         <v>1911</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B90" s="4">
         <v>144660</v>
       </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="1">
+      <c r="E90" s="4"/>
+      <c r="G90" s="4"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="1">
         <v>1912</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B91" s="4">
         <v>217990</v>
       </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="1">
+      <c r="E91" s="4"/>
+      <c r="G91" s="4"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="1">
         <v>1913</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B92" s="4">
         <v>261265</v>
       </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="1">
+      <c r="E92" s="4"/>
+      <c r="G92" s="4"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="1">
         <v>1914</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B93" s="4">
         <v>119358</v>
       </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="1">
+      <c r="E93" s="4"/>
+      <c r="G93" s="4"/>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="1">
         <v>1915</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B94" s="4">
         <v>3880</v>
       </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="1">
+      <c r="E94" s="4"/>
+      <c r="G94" s="4"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="1">
         <v>1916</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B95" s="4">
         <v>2305</v>
       </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="1" t="s">
+      <c r="E95" s="4"/>
+      <c r="G95" s="4"/>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B81" s="4">
-        <f>SUM(B60:B80)</f>
+      <c r="B96" s="4">
+        <f>SUM(B75:B95)</f>
         <v>2477253</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="A97" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B97" s="4">
+        <f>SUM(B75:B79)</f>
+        <v>247211</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B98" s="4">
+        <f>SUM(B80:B84)</f>
+        <v>649198</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B99" s="4">
+        <f>SUM(B85:B89)</f>
+        <v>831386</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B100" s="4">
+        <f>SUM(B90:B94)</f>
+        <v>747153</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="28.8">
+      <c r="A104" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F104" s="38"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B105" s="4">
+        <f>K6</f>
+        <v>27525</v>
+      </c>
+      <c r="C105" s="4">
+        <f>L43</f>
+        <v>33658</v>
+      </c>
+      <c r="D105" s="26">
+        <f>B105/C105*100</f>
+        <v>81.778477627904209</v>
+      </c>
+      <c r="E105" s="14"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B106" s="4">
+        <f>K7</f>
+        <v>64393</v>
+      </c>
+      <c r="C106" s="4">
+        <f>L44</f>
+        <v>69982</v>
+      </c>
+      <c r="D106" s="26">
+        <f>B106/C106*100</f>
+        <v>92.01366065559715</v>
+      </c>
+      <c r="E106" s="4">
         <f>SUM(B60:B64)</f>
+        <v>72110</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B107" s="4">
+        <f>K8</f>
+        <v>223248</v>
+      </c>
+      <c r="C107" s="4">
+        <f>L45</f>
+        <v>189850</v>
+      </c>
+      <c r="D107" s="26">
+        <f t="shared" ref="D107:D112" si="24">B107/C107*100</f>
+        <v>117.59178298656833</v>
+      </c>
+      <c r="E107" s="4">
+        <f>SUM(B65:B69)</f>
+        <v>188383</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B108" s="4">
+        <f>K9</f>
+        <v>279258</v>
+      </c>
+      <c r="C108" s="4">
+        <f>L46</f>
+        <v>292574</v>
+      </c>
+      <c r="D108" s="26">
+        <f t="shared" si="24"/>
+        <v>95.448672814399089</v>
+      </c>
+      <c r="E108" s="4">
+        <f>SUM(B70:B74)</f>
+        <v>262363</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B109" s="4">
+        <f>K10</f>
+        <v>173914</v>
+      </c>
+      <c r="C109" s="4">
+        <f>L47</f>
+        <v>246339</v>
+      </c>
+      <c r="D109" s="26">
+        <f t="shared" si="24"/>
+        <v>70.599458469832229</v>
+      </c>
+      <c r="E109" s="4">
+        <f>B97</f>
         <v>247211</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
-      <c r="A83" s="1" t="s">
+    <row r="110" spans="1:6">
+      <c r="A110" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B83" s="4">
-        <f>SUM(B65:B69)</f>
+      <c r="B110" s="4">
+        <f>K11</f>
+        <v>340174</v>
+      </c>
+      <c r="C110" s="4">
+        <f>L48</f>
+        <v>644531</v>
+      </c>
+      <c r="D110" s="26">
+        <f t="shared" si="24"/>
+        <v>52.778531986824525</v>
+      </c>
+      <c r="E110" s="4">
+        <f>B98</f>
         <v>649198</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84" s="1" t="s">
+    <row r="111" spans="1:6">
+      <c r="A111" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B84" s="4">
-        <f>SUM(B70:B74)</f>
+      <c r="B111" s="4">
+        <f>K12</f>
+        <v>471971</v>
+      </c>
+      <c r="C111" s="4">
+        <f>L49</f>
+        <v>986977</v>
+      </c>
+      <c r="D111" s="26">
+        <f t="shared" si="24"/>
+        <v>47.819858010875635</v>
+      </c>
+      <c r="E111" s="4">
+        <f>B99</f>
         <v>831386</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="1" t="s">
+    <row r="112" spans="1:6">
+      <c r="A112" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B85" s="4">
-        <f>SUM(B75:B79)</f>
+      <c r="B112" s="4">
+        <f>K13</f>
+        <v>409911</v>
+      </c>
+      <c r="C112" s="4">
+        <f>L50</f>
+        <v>1010285</v>
+      </c>
+      <c r="D112" s="26">
+        <f t="shared" si="24"/>
+        <v>40.573798482606392</v>
+      </c>
+      <c r="E112" s="4">
+        <f>B100</f>
         <v>747153</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="A89" s="36" t="s">
+    <row r="113" spans="1:2">
+      <c r="B113" s="4"/>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="B114" s="4"/>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B89" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="C89" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="D89" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="E89" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="F89" s="38"/>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B90" s="4">
-        <f t="shared" ref="B90:B97" si="23">K6</f>
-        <v>27525</v>
-      </c>
-      <c r="C90" s="4">
-        <f t="shared" ref="C90:C97" si="24">L43</f>
-        <v>33658</v>
-      </c>
-      <c r="D90" s="26">
-        <f>B90/C90*100</f>
-        <v>81.778477627904209</v>
-      </c>
-      <c r="E90" s="14"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B91" s="4">
-        <f t="shared" si="23"/>
-        <v>64393</v>
-      </c>
-      <c r="C91" s="4">
-        <f t="shared" si="24"/>
-        <v>69982</v>
-      </c>
-      <c r="D91" s="26">
-        <f>B91/C91*100</f>
-        <v>92.01366065559715</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B92" s="4">
-        <f t="shared" si="23"/>
-        <v>223248</v>
-      </c>
-      <c r="C92" s="4">
-        <f t="shared" si="24"/>
-        <v>189850</v>
-      </c>
-      <c r="D92" s="26">
-        <f t="shared" ref="D92:D97" si="25">B92/C92*100</f>
-        <v>117.59178298656833</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B93" s="4">
-        <f t="shared" si="23"/>
-        <v>279258</v>
-      </c>
-      <c r="C93" s="4">
-        <f t="shared" si="24"/>
-        <v>292574</v>
-      </c>
-      <c r="D93" s="26">
-        <f t="shared" si="25"/>
-        <v>95.448672814399089</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B94" s="4">
-        <f t="shared" si="23"/>
-        <v>173914</v>
-      </c>
-      <c r="C94" s="4">
-        <f t="shared" si="24"/>
-        <v>246339</v>
-      </c>
-      <c r="D94" s="26">
-        <f t="shared" si="25"/>
-        <v>70.599458469832229</v>
-      </c>
-      <c r="E94" s="4">
-        <f>B82</f>
-        <v>247211</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B95" s="4">
-        <f t="shared" si="23"/>
-        <v>340174</v>
-      </c>
-      <c r="C95" s="4">
-        <f t="shared" si="24"/>
-        <v>644531</v>
-      </c>
-      <c r="D95" s="26">
-        <f t="shared" si="25"/>
-        <v>52.778531986824525</v>
-      </c>
-      <c r="E95" s="4">
-        <f>B83</f>
-        <v>649198</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B96" s="4">
-        <f t="shared" si="23"/>
-        <v>471971</v>
-      </c>
-      <c r="C96" s="4">
-        <f t="shared" si="24"/>
-        <v>986977</v>
-      </c>
-      <c r="D96" s="26">
-        <f t="shared" si="25"/>
-        <v>47.819858010875635</v>
-      </c>
-      <c r="E96" s="4">
-        <f>B84</f>
-        <v>831386</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B97" s="4">
-        <f t="shared" si="23"/>
-        <v>409911</v>
-      </c>
-      <c r="C97" s="4">
-        <f t="shared" si="24"/>
-        <v>1010285</v>
-      </c>
-      <c r="D97" s="26">
-        <f t="shared" si="25"/>
-        <v>40.573798482606392</v>
-      </c>
-      <c r="E97" s="4">
-        <f>B85</f>
-        <v>747153</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="B98" s="4"/>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="B99" s="4"/>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="14" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="B101" s="36" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="1" t="str">
+      <c r="B116" s="36" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="1" t="str">
         <f>A43</f>
         <v>1876-1880</v>
       </c>
-      <c r="B102" s="4">
-        <f t="shared" ref="B102:B110" si="26">L43</f>
+      <c r="B117" s="4">
+        <f>L43</f>
         <v>33658</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="1" t="str">
-        <f t="shared" ref="A103:A110" si="27">A44</f>
+    <row r="118" spans="1:2">
+      <c r="A118" s="1" t="str">
+        <f>A44</f>
         <v>1881-1885</v>
       </c>
-      <c r="B103" s="4">
-        <f t="shared" si="26"/>
+      <c r="B118" s="4">
+        <f>L44</f>
         <v>69982</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="1" t="str">
-        <f t="shared" si="27"/>
+    <row r="119" spans="1:2">
+      <c r="A119" s="1" t="str">
+        <f>A45</f>
         <v>1886-1890</v>
       </c>
-      <c r="B104" s="4">
-        <f t="shared" si="26"/>
+      <c r="B119" s="4">
+        <f>L45</f>
         <v>189850</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="1" t="str">
-        <f t="shared" si="27"/>
+    <row r="120" spans="1:2">
+      <c r="A120" s="1" t="str">
+        <f>A46</f>
         <v>1891-1895</v>
       </c>
-      <c r="B105" s="4">
-        <f t="shared" si="26"/>
+      <c r="B120" s="4">
+        <f>L46</f>
         <v>292574</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="1" t="str">
-        <f t="shared" si="27"/>
+    <row r="121" spans="1:2">
+      <c r="A121" s="1" t="str">
+        <f>A47</f>
         <v>1896-1900</v>
       </c>
-      <c r="B106" s="4">
-        <f t="shared" si="26"/>
+      <c r="B121" s="4">
+        <f>L47</f>
         <v>246339</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="1" t="str">
-        <f t="shared" si="27"/>
+    <row r="122" spans="1:2">
+      <c r="A122" s="1" t="str">
+        <f>A48</f>
         <v>1901-1905</v>
       </c>
-      <c r="B107" s="4">
-        <f t="shared" si="26"/>
+      <c r="B122" s="4">
+        <f>L48</f>
         <v>644531</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="1" t="str">
-        <f t="shared" si="27"/>
+    <row r="123" spans="1:2">
+      <c r="A123" s="1" t="str">
+        <f>A49</f>
         <v>1906-1910</v>
       </c>
-      <c r="B108" s="4">
-        <f t="shared" si="26"/>
+      <c r="B123" s="4">
+        <f>L49</f>
         <v>986977</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="1" t="str">
-        <f t="shared" si="27"/>
+    <row r="124" spans="1:2">
+      <c r="A124" s="1" t="str">
+        <f>A50</f>
         <v>1911-1915</v>
       </c>
-      <c r="B109" s="4">
-        <f t="shared" si="26"/>
+      <c r="B124" s="4">
+        <f>L50</f>
         <v>1010285</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="10" t="str">
-        <f t="shared" si="27"/>
+    <row r="125" spans="1:2">
+      <c r="A125" s="10" t="str">
+        <f>A51</f>
         <v>1896-1915</v>
       </c>
-      <c r="B110" s="42">
-        <f t="shared" si="26"/>
+      <c r="B125" s="42">
+        <f>L51</f>
         <v>2888132</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="10" t="s">
+    <row r="126" spans="1:2">
+      <c r="A126" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B111" s="42">
-        <f>SUM(B102:B109)</f>
+      <c r="B126" s="42">
+        <f>SUM(B117:B124)</f>
         <v>3474196</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="A113" s="14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" s="36" t="s">
+    <row r="128" spans="1:2">
+      <c r="A128" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B114" s="36" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115" s="1">
-        <v>1876</v>
-      </c>
-      <c r="B115" s="48">
-        <v>5958.6872560000002</v>
-      </c>
-      <c r="F115" s="48"/>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116" s="1">
-        <v>1877</v>
-      </c>
-      <c r="B116" s="48">
-        <v>6133.5817779999998</v>
-      </c>
-      <c r="F116" s="48"/>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" s="1">
-        <v>1878</v>
-      </c>
-      <c r="B117" s="48">
-        <v>6497.8953369999999</v>
-      </c>
-      <c r="F117" s="48"/>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118" s="1">
-        <v>1879</v>
-      </c>
-      <c r="B118" s="48">
-        <v>7099.2952009999999</v>
-      </c>
-      <c r="F118" s="48"/>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119" s="1">
-        <v>1880</v>
-      </c>
-      <c r="B119" s="48">
-        <v>7968.5404280000002</v>
-      </c>
-      <c r="F119" s="48"/>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120" s="1">
-        <v>1881</v>
-      </c>
-      <c r="B120" s="48">
-        <v>9081.0078830000002</v>
-      </c>
-      <c r="F120" s="48"/>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121" s="1">
-        <v>1882</v>
-      </c>
-      <c r="B121" s="48">
-        <v>10799.985825</v>
-      </c>
-      <c r="F121" s="48"/>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" s="1">
-        <v>1883</v>
-      </c>
-      <c r="B122" s="48">
-        <v>13180.685009000001</v>
-      </c>
-      <c r="F122" s="48"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123" s="1">
-        <v>1884</v>
-      </c>
-      <c r="B123" s="48">
-        <v>16376.145667999999</v>
-      </c>
-      <c r="F123" s="48"/>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124" s="1">
-        <v>1885</v>
-      </c>
-      <c r="B124" s="48">
-        <v>20544.175615</v>
-      </c>
-      <c r="F124" s="48"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" s="1">
-        <v>1886</v>
-      </c>
-      <c r="B125" s="48">
-        <v>26303.239323000002</v>
-      </c>
-      <c r="F125" s="48"/>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126" s="1">
-        <v>1887</v>
-      </c>
-      <c r="B126" s="48">
-        <v>31933.797870999999</v>
-      </c>
-      <c r="F126" s="48"/>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" s="1">
-        <v>1888</v>
-      </c>
-      <c r="B127" s="48">
-        <v>37768.818612000003</v>
-      </c>
-      <c r="F127" s="48"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" s="1">
-        <v>1889</v>
-      </c>
-      <c r="B128" s="48">
-        <v>43815.890546000002</v>
-      </c>
-      <c r="F128" s="48"/>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" s="1">
-        <v>1890</v>
-      </c>
-      <c r="B129" s="48">
-        <v>50028.253647999998</v>
-      </c>
-      <c r="F129" s="48"/>
+      <c r="B129" s="36" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="1">
-        <v>1891</v>
+        <v>1876</v>
       </c>
       <c r="B130" s="48">
-        <v>57244.128299000004</v>
+        <v>5958.6872560000002</v>
       </c>
       <c r="F130" s="48"/>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="1">
-        <v>1892</v>
+        <v>1877</v>
       </c>
       <c r="B131" s="48">
-        <v>60906.481652000002</v>
+        <v>6133.5817779999998</v>
       </c>
       <c r="F131" s="48"/>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="1">
-        <v>1893</v>
+        <v>1878</v>
       </c>
       <c r="B132" s="48">
-        <v>61556.958893000003</v>
+        <v>6497.8953369999999</v>
       </c>
       <c r="F132" s="48"/>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="1">
-        <v>1894</v>
+        <v>1879</v>
       </c>
       <c r="B133" s="48">
-        <v>59073.614796000002</v>
+        <v>7099.2952009999999</v>
       </c>
       <c r="F133" s="48"/>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="1">
-        <v>1895</v>
+        <v>1880</v>
       </c>
       <c r="B134" s="48">
-        <v>53792.816358999997</v>
+        <v>7968.5404280000002</v>
       </c>
       <c r="F134" s="48"/>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="1">
-        <v>1896</v>
+        <v>1881</v>
       </c>
       <c r="B135" s="48">
-        <v>44001.050108000003</v>
+        <v>9081.0078830000002</v>
       </c>
       <c r="F135" s="48"/>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="1">
-        <v>1897</v>
+        <v>1882</v>
       </c>
       <c r="B136" s="48">
-        <v>41555.827486000002</v>
+        <v>10799.985825</v>
       </c>
       <c r="F136" s="48"/>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="1">
-        <v>1898</v>
+        <v>1883</v>
       </c>
       <c r="B137" s="48">
-        <v>43914.876993999998</v>
+        <v>13180.685009000001</v>
       </c>
       <c r="F137" s="48"/>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="1">
-        <v>1899</v>
+        <v>1884</v>
       </c>
       <c r="B138" s="48">
-        <v>51608.617109999999</v>
+        <v>16376.145667999999</v>
       </c>
       <c r="F138" s="48"/>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="1">
-        <v>1900</v>
+        <v>1885</v>
       </c>
       <c r="B139" s="48">
-        <v>65258.628300999997</v>
+        <v>20544.175615</v>
       </c>
       <c r="F139" s="48"/>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="1">
-        <v>1901</v>
+        <v>1886</v>
       </c>
       <c r="B140" s="48">
-        <v>89374.285107000003</v>
+        <v>26303.239323000002</v>
       </c>
       <c r="F140" s="48"/>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="1">
-        <v>1902</v>
+        <v>1887</v>
       </c>
       <c r="B141" s="48">
-        <v>110396.48513099999</v>
+        <v>31933.797870999999</v>
       </c>
       <c r="F141" s="48"/>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="1">
-        <v>1903</v>
+        <v>1888</v>
       </c>
       <c r="B142" s="48">
-        <v>130369.29534500001</v>
+        <v>37768.818612000003</v>
       </c>
       <c r="F142" s="48"/>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="1">
-        <v>1904</v>
+        <v>1889</v>
       </c>
       <c r="B143" s="48">
-        <v>148831.43620900001</v>
+        <v>43815.890546000002</v>
       </c>
       <c r="F143" s="48"/>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="1">
-        <v>1905</v>
+        <v>1890</v>
       </c>
       <c r="B144" s="48">
-        <v>165559.498208</v>
+        <v>50028.253647999998</v>
       </c>
       <c r="F144" s="48"/>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="1">
-        <v>1906</v>
+        <v>1891</v>
       </c>
       <c r="B145" s="48">
-        <v>180624.48191</v>
+        <v>57244.128299000004</v>
       </c>
       <c r="F145" s="48"/>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="1">
-        <v>1907</v>
+        <v>1892</v>
       </c>
       <c r="B146" s="48">
-        <v>192365.54383800001</v>
+        <v>60906.481652000002</v>
       </c>
       <c r="F146" s="48"/>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="1">
-        <v>1908</v>
+        <v>1893</v>
       </c>
       <c r="B147" s="48">
-        <v>200821.20595</v>
+        <v>61556.958893000003</v>
       </c>
       <c r="F147" s="48"/>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="1">
-        <v>1909</v>
+        <v>1894</v>
       </c>
       <c r="B148" s="48">
-        <v>205811.42198099999</v>
+        <v>59073.614796000002</v>
       </c>
       <c r="F148" s="48"/>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="1">
-        <v>1910</v>
+        <v>1895</v>
       </c>
       <c r="B149" s="48">
-        <v>207354.34632099999</v>
+        <v>53792.816358999997</v>
       </c>
       <c r="F149" s="48"/>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="1">
-        <v>1911</v>
+        <v>1896</v>
       </c>
       <c r="B150" s="48">
-        <v>204407.818902</v>
+        <v>44001.050108000003</v>
       </c>
       <c r="F150" s="48"/>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="1">
-        <v>1912</v>
+        <v>1897</v>
       </c>
       <c r="B151" s="48">
-        <v>202841.37030400001</v>
+        <v>41555.827486000002</v>
       </c>
       <c r="F151" s="48"/>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="1">
-        <v>1913</v>
+        <v>1898</v>
       </c>
       <c r="B152" s="48">
-        <v>201633.03541400001</v>
+        <v>43914.876993999998</v>
       </c>
       <c r="F152" s="48"/>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="1">
-        <v>1914</v>
+        <v>1899</v>
       </c>
       <c r="B153" s="48">
-        <v>200884.29531700001</v>
+        <v>51608.617109999999</v>
       </c>
       <c r="F153" s="48"/>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="1">
+        <v>1900</v>
+      </c>
+      <c r="B154" s="48">
+        <v>65258.628300999997</v>
+      </c>
+      <c r="F154" s="48"/>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="1">
+        <v>1901</v>
+      </c>
+      <c r="B155" s="48">
+        <v>89374.285107000003</v>
+      </c>
+      <c r="F155" s="48"/>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="1">
+        <v>1902</v>
+      </c>
+      <c r="B156" s="48">
+        <v>110396.48513099999</v>
+      </c>
+      <c r="F156" s="48"/>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="1">
+        <v>1903</v>
+      </c>
+      <c r="B157" s="48">
+        <v>130369.29534500001</v>
+      </c>
+      <c r="F157" s="48"/>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="1">
+        <v>1904</v>
+      </c>
+      <c r="B158" s="48">
+        <v>148831.43620900001</v>
+      </c>
+      <c r="F158" s="48"/>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="1">
+        <v>1905</v>
+      </c>
+      <c r="B159" s="48">
+        <v>165559.498208</v>
+      </c>
+      <c r="F159" s="48"/>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="1">
+        <v>1906</v>
+      </c>
+      <c r="B160" s="48">
+        <v>180624.48191</v>
+      </c>
+      <c r="F160" s="48"/>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="1">
+        <v>1907</v>
+      </c>
+      <c r="B161" s="48">
+        <v>192365.54383800001</v>
+      </c>
+      <c r="F161" s="48"/>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="1">
+        <v>1908</v>
+      </c>
+      <c r="B162" s="48">
+        <v>200821.20595</v>
+      </c>
+      <c r="F162" s="48"/>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="1">
+        <v>1909</v>
+      </c>
+      <c r="B163" s="48">
+        <v>205811.42198099999</v>
+      </c>
+      <c r="F163" s="48"/>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="1">
+        <v>1910</v>
+      </c>
+      <c r="B164" s="48">
+        <v>207354.34632099999</v>
+      </c>
+      <c r="F164" s="48"/>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="1">
+        <v>1911</v>
+      </c>
+      <c r="B165" s="48">
+        <v>204407.818902</v>
+      </c>
+      <c r="F165" s="48"/>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" s="1">
+        <v>1912</v>
+      </c>
+      <c r="B166" s="48">
+        <v>202841.37030400001</v>
+      </c>
+      <c r="F166" s="48"/>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="1">
+        <v>1913</v>
+      </c>
+      <c r="B167" s="48">
+        <v>201633.03541400001</v>
+      </c>
+      <c r="F167" s="48"/>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="1">
+        <v>1914</v>
+      </c>
+      <c r="B168" s="48">
+        <v>200884.29531700001</v>
+      </c>
+      <c r="F168" s="48"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="1">
         <v>1915</v>
       </c>
-      <c r="B154" s="48">
+      <c r="B169" s="48">
         <v>200518.480064</v>
       </c>
-      <c r="F154" s="48"/>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" s="10" t="s">
+      <c r="F169" s="48"/>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B155" s="4">
-        <f>SUM(B135:B154)</f>
+      <c r="B170" s="4">
+        <f>SUM(B150:B169)</f>
         <v>2888132</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
-      <c r="A156" s="10" t="s">
+    <row r="171" spans="1:6">
+      <c r="A171" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B156" s="4">
-        <f>SUM(B115:B154)</f>
+      <c r="B171" s="4">
+        <f>SUM(B130:B169)</f>
         <v>3474195.9999989998</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
-      <c r="A157" s="10" t="s">
+    <row r="172" spans="1:6">
+      <c r="A172" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B157" s="4">
-        <f>SUM(B120:B134)</f>
+      <c r="B172" s="4">
+        <f>SUM(B135:B149)</f>
         <v>552405.99999899999</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
-      <c r="A158" s="10"/>
-      <c r="B158" s="4"/>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160" s="14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="36" t="s">
+    <row r="173" spans="1:6">
+      <c r="A173" s="10"/>
+      <c r="B173" s="4"/>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B161" s="36" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="1">
-        <v>1881</v>
-      </c>
-      <c r="B162" s="4">
-        <f t="shared" ref="B162:B195" si="28">(B120+B121) / 2</f>
-        <v>9940.4968540000009</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="1">
-        <f>A162+1</f>
-        <v>1882</v>
-      </c>
-      <c r="B163" s="4">
-        <f t="shared" si="28"/>
-        <v>11990.335417</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="1">
-        <f t="shared" ref="A164:A195" si="29">A163+1</f>
-        <v>1883</v>
-      </c>
-      <c r="B164" s="4">
-        <f t="shared" si="28"/>
-        <v>14778.415338499999</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="1">
-        <f t="shared" si="29"/>
-        <v>1884</v>
-      </c>
-      <c r="B165" s="4">
-        <f t="shared" si="28"/>
-        <v>18460.160641499999</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="1">
-        <f t="shared" si="29"/>
-        <v>1885</v>
-      </c>
-      <c r="B166" s="4">
-        <f t="shared" si="28"/>
-        <v>23423.707469000001</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="1">
-        <f t="shared" si="29"/>
-        <v>1886</v>
-      </c>
-      <c r="B167" s="4">
-        <f t="shared" si="28"/>
-        <v>29118.518597000002</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="1">
-        <f t="shared" si="29"/>
-        <v>1887</v>
-      </c>
-      <c r="B168" s="4">
-        <f t="shared" si="28"/>
-        <v>34851.308241500003</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="1">
-        <f t="shared" si="29"/>
-        <v>1888</v>
-      </c>
-      <c r="B169" s="4">
-        <f t="shared" si="28"/>
-        <v>40792.354579000006</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="1">
-        <f t="shared" si="29"/>
-        <v>1889</v>
-      </c>
-      <c r="B170" s="4">
-        <f t="shared" si="28"/>
-        <v>46922.072096999997</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="1">
-        <f t="shared" si="29"/>
-        <v>1890</v>
-      </c>
-      <c r="B171" s="4">
-        <f t="shared" si="28"/>
-        <v>53636.190973500001</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="1">
-        <f t="shared" si="29"/>
-        <v>1891</v>
-      </c>
-      <c r="B172" s="4">
-        <f t="shared" si="28"/>
-        <v>59075.304975500003</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="1">
-        <f t="shared" si="29"/>
-        <v>1892</v>
-      </c>
-      <c r="B173" s="4">
-        <f t="shared" si="28"/>
-        <v>61231.720272500002</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="1">
-        <f t="shared" si="29"/>
-        <v>1893</v>
-      </c>
-      <c r="B174" s="4">
-        <f t="shared" si="28"/>
-        <v>60315.286844500006</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="1">
-        <f t="shared" si="29"/>
-        <v>1894</v>
-      </c>
-      <c r="B175" s="4">
-        <f t="shared" si="28"/>
-        <v>56433.215577499999</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="1">
-        <f t="shared" si="29"/>
-        <v>1895</v>
-      </c>
-      <c r="B176" s="4">
-        <f t="shared" si="28"/>
-        <v>48896.9332335</v>
+      <c r="B176" s="36" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="1">
-        <f t="shared" si="29"/>
-        <v>1896</v>
+        <v>1881</v>
       </c>
       <c r="B177" s="4">
-        <f t="shared" si="28"/>
-        <v>42778.438797000003</v>
+        <f t="shared" ref="B177:B210" si="25">(B135+B136) / 2</f>
+        <v>9940.4968540000009</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="1">
-        <f t="shared" si="29"/>
-        <v>1897</v>
+        <f>A177+1</f>
+        <v>1882</v>
       </c>
       <c r="B178" s="4">
-        <f t="shared" si="28"/>
-        <v>42735.35224</v>
+        <f t="shared" si="25"/>
+        <v>11990.335417</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="1">
-        <f t="shared" si="29"/>
-        <v>1898</v>
+        <f t="shared" ref="A179:A210" si="26">A178+1</f>
+        <v>1883</v>
       </c>
       <c r="B179" s="4">
-        <f t="shared" si="28"/>
-        <v>47761.747051999999</v>
+        <f t="shared" si="25"/>
+        <v>14778.415338499999</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="1">
-        <f t="shared" si="29"/>
-        <v>1899</v>
+        <f t="shared" si="26"/>
+        <v>1884</v>
       </c>
       <c r="B180" s="4">
-        <f t="shared" si="28"/>
-        <v>58433.622705499998</v>
+        <f t="shared" si="25"/>
+        <v>18460.160641499999</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="1">
-        <f t="shared" si="29"/>
-        <v>1900</v>
+        <f t="shared" si="26"/>
+        <v>1885</v>
       </c>
       <c r="B181" s="4">
-        <f t="shared" si="28"/>
-        <v>77316.456703999997</v>
+        <f t="shared" si="25"/>
+        <v>23423.707469000001</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="1">
-        <f t="shared" si="29"/>
-        <v>1901</v>
+        <f t="shared" si="26"/>
+        <v>1886</v>
       </c>
       <c r="B182" s="4">
-        <f t="shared" si="28"/>
-        <v>99885.385118999999</v>
+        <f t="shared" si="25"/>
+        <v>29118.518597000002</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="1">
-        <f t="shared" si="29"/>
-        <v>1902</v>
+        <f t="shared" si="26"/>
+        <v>1887</v>
       </c>
       <c r="B183" s="4">
-        <f t="shared" si="28"/>
-        <v>120382.89023799999</v>
+        <f t="shared" si="25"/>
+        <v>34851.308241500003</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="1">
-        <f t="shared" si="29"/>
-        <v>1903</v>
+        <f t="shared" si="26"/>
+        <v>1888</v>
       </c>
       <c r="B184" s="4">
-        <f t="shared" si="28"/>
-        <v>139600.365777</v>
+        <f t="shared" si="25"/>
+        <v>40792.354579000006</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="1">
-        <f t="shared" si="29"/>
-        <v>1904</v>
+        <f t="shared" si="26"/>
+        <v>1889</v>
       </c>
       <c r="B185" s="4">
-        <f t="shared" si="28"/>
-        <v>157195.46720850002</v>
+        <f t="shared" si="25"/>
+        <v>46922.072096999997</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="1">
-        <f t="shared" si="29"/>
-        <v>1905</v>
+        <f t="shared" si="26"/>
+        <v>1890</v>
       </c>
       <c r="B186" s="4">
-        <f t="shared" si="28"/>
-        <v>173091.990059</v>
+        <f t="shared" si="25"/>
+        <v>53636.190973500001</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="1">
-        <f t="shared" si="29"/>
-        <v>1906</v>
+        <f t="shared" si="26"/>
+        <v>1891</v>
       </c>
       <c r="B187" s="4">
-        <f t="shared" si="28"/>
-        <v>186495.01287400001</v>
+        <f t="shared" si="25"/>
+        <v>59075.304975500003</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="1">
-        <f t="shared" si="29"/>
-        <v>1907</v>
+        <f t="shared" si="26"/>
+        <v>1892</v>
       </c>
       <c r="B188" s="4">
-        <f t="shared" si="28"/>
-        <v>196593.37489400001</v>
+        <f t="shared" si="25"/>
+        <v>61231.720272500002</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="1">
-        <f t="shared" si="29"/>
-        <v>1908</v>
+        <f t="shared" si="26"/>
+        <v>1893</v>
       </c>
       <c r="B189" s="4">
-        <f t="shared" si="28"/>
-        <v>203316.31396549998</v>
+        <f t="shared" si="25"/>
+        <v>60315.286844500006</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="1">
-        <f t="shared" si="29"/>
-        <v>1909</v>
+        <f t="shared" si="26"/>
+        <v>1894</v>
       </c>
       <c r="B190" s="4">
-        <f t="shared" si="28"/>
-        <v>206582.88415100001</v>
+        <f t="shared" si="25"/>
+        <v>56433.215577499999</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="1">
-        <f t="shared" si="29"/>
-        <v>1910</v>
+        <f t="shared" si="26"/>
+        <v>1895</v>
       </c>
       <c r="B191" s="4">
-        <f t="shared" si="28"/>
-        <v>205881.08261149999</v>
+        <f t="shared" si="25"/>
+        <v>48896.9332335</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
+        <v>1896</v>
+      </c>
+      <c r="B192" s="4">
+        <f t="shared" si="25"/>
+        <v>42778.438797000003</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="1">
+        <f t="shared" si="26"/>
+        <v>1897</v>
+      </c>
+      <c r="B193" s="4">
+        <f t="shared" si="25"/>
+        <v>42735.35224</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="1">
+        <f t="shared" si="26"/>
+        <v>1898</v>
+      </c>
+      <c r="B194" s="4">
+        <f t="shared" si="25"/>
+        <v>47761.747051999999</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="1">
+        <f t="shared" si="26"/>
+        <v>1899</v>
+      </c>
+      <c r="B195" s="4">
+        <f t="shared" si="25"/>
+        <v>58433.622705499998</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="1">
+        <f t="shared" si="26"/>
+        <v>1900</v>
+      </c>
+      <c r="B196" s="4">
+        <f t="shared" si="25"/>
+        <v>77316.456703999997</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="1">
+        <f t="shared" si="26"/>
+        <v>1901</v>
+      </c>
+      <c r="B197" s="4">
+        <f t="shared" si="25"/>
+        <v>99885.385118999999</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="1">
+        <f t="shared" si="26"/>
+        <v>1902</v>
+      </c>
+      <c r="B198" s="4">
+        <f t="shared" si="25"/>
+        <v>120382.89023799999</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="1">
+        <f t="shared" si="26"/>
+        <v>1903</v>
+      </c>
+      <c r="B199" s="4">
+        <f t="shared" si="25"/>
+        <v>139600.365777</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="1">
+        <f t="shared" si="26"/>
+        <v>1904</v>
+      </c>
+      <c r="B200" s="4">
+        <f t="shared" si="25"/>
+        <v>157195.46720850002</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="1">
+        <f t="shared" si="26"/>
+        <v>1905</v>
+      </c>
+      <c r="B201" s="4">
+        <f t="shared" si="25"/>
+        <v>173091.990059</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="1">
+        <f t="shared" si="26"/>
+        <v>1906</v>
+      </c>
+      <c r="B202" s="4">
+        <f t="shared" si="25"/>
+        <v>186495.01287400001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="1">
+        <f t="shared" si="26"/>
+        <v>1907</v>
+      </c>
+      <c r="B203" s="4">
+        <f t="shared" si="25"/>
+        <v>196593.37489400001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="1">
+        <f t="shared" si="26"/>
+        <v>1908</v>
+      </c>
+      <c r="B204" s="4">
+        <f t="shared" si="25"/>
+        <v>203316.31396549998</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="1">
+        <f t="shared" si="26"/>
+        <v>1909</v>
+      </c>
+      <c r="B205" s="4">
+        <f t="shared" si="25"/>
+        <v>206582.88415100001</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="1">
+        <f t="shared" si="26"/>
+        <v>1910</v>
+      </c>
+      <c r="B206" s="4">
+        <f t="shared" si="25"/>
+        <v>205881.08261149999</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="1">
+        <f t="shared" si="26"/>
         <v>1911</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B207" s="4">
+        <f t="shared" si="25"/>
+        <v>203624.59460300001</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="1">
+        <f t="shared" si="26"/>
+        <v>1912</v>
+      </c>
+      <c r="B208" s="4">
+        <f t="shared" si="25"/>
+        <v>202237.20285900001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="1">
+        <f t="shared" si="26"/>
+        <v>1913</v>
+      </c>
+      <c r="B209" s="4">
+        <f t="shared" si="25"/>
+        <v>201258.66536550003</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="1">
+        <f t="shared" si="26"/>
+        <v>1914</v>
+      </c>
+      <c r="B210" s="4">
+        <f t="shared" si="25"/>
+        <v>200701.38769050001</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B211" s="42">
+        <f>SUM(B192:B196)</f>
+        <v>269025.61749849998</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="28.8">
+      <c r="A212" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="B212" s="46">
+        <f>B211/5</f>
+        <v>53805.123499699999</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="B213" s="44"/>
+      <c r="C213" s="41"/>
+      <c r="D213" s="38"/>
+      <c r="E213" s="38"/>
+      <c r="F213" s="38"/>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="1">
+        <v>1881</v>
+      </c>
+      <c r="B214" s="26">
+        <f>B177/B$212*100</f>
+        <v>18.475000534206423</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="1">
+        <f>A214+1</f>
+        <v>1882</v>
+      </c>
+      <c r="B215" s="26">
+        <f t="shared" ref="B215:B228" si="27">B178/B$212*100</f>
+        <v>22.28474657634947</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="1">
+        <f t="shared" ref="A216:A228" si="28">A215+1</f>
+        <v>1883</v>
+      </c>
+      <c r="B216" s="26">
+        <f t="shared" si="27"/>
+        <v>27.466557787163893</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="1">
         <f t="shared" si="28"/>
-        <v>203624.59460300001</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193" s="1">
-        <f t="shared" si="29"/>
-        <v>1912</v>
-      </c>
-      <c r="B193" s="4">
+        <v>1884</v>
+      </c>
+      <c r="B217" s="26">
+        <f t="shared" si="27"/>
+        <v>34.309298893446325</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="1">
         <f t="shared" si="28"/>
-        <v>202237.20285900001</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" s="1">
-        <f t="shared" si="29"/>
-        <v>1913</v>
-      </c>
-      <c r="B194" s="4">
+        <v>1885</v>
+      </c>
+      <c r="B218" s="26">
+        <f t="shared" si="27"/>
+        <v>43.534343842051776</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="1">
         <f t="shared" si="28"/>
-        <v>201258.66536550003</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195" s="1">
-        <f t="shared" si="29"/>
-        <v>1914</v>
-      </c>
-      <c r="B195" s="4">
+        <v>1886</v>
+      </c>
+      <c r="B219" s="26">
+        <f t="shared" si="27"/>
+        <v>54.118486684938759</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="1">
         <f t="shared" si="28"/>
-        <v>200701.38769050001</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B196" s="42">
-        <f>SUM(B177:B181)</f>
-        <v>269025.61749849998</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" ht="28.8">
-      <c r="A197" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="B197" s="46">
-        <f>B196/5</f>
-        <v>53805.123499699999</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="B198" s="44"/>
-      <c r="C198" s="41"/>
-      <c r="D198" s="38"/>
-      <c r="E198" s="38"/>
-      <c r="F198" s="38"/>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199" s="1">
-        <v>1881</v>
-      </c>
-      <c r="B199" s="26">
-        <f>B162/B$197*100</f>
-        <v>18.475000534206423</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200" s="1">
-        <f>A199+1</f>
-        <v>1882</v>
-      </c>
-      <c r="B200" s="26">
-        <f t="shared" ref="B200:B213" si="30">B163/B$197*100</f>
-        <v>22.28474657634947</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201" s="1">
-        <f t="shared" ref="A201:A213" si="31">A200+1</f>
-        <v>1883</v>
-      </c>
-      <c r="B201" s="26">
-        <f t="shared" si="30"/>
-        <v>27.466557787163893</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202" s="1">
-        <f t="shared" si="31"/>
-        <v>1884</v>
-      </c>
-      <c r="B202" s="26">
-        <f t="shared" si="30"/>
-        <v>34.309298893446325</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203" s="1">
-        <f t="shared" si="31"/>
-        <v>1885</v>
-      </c>
-      <c r="B203" s="26">
-        <f t="shared" si="30"/>
-        <v>43.534343842051776</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204" s="1">
-        <f t="shared" si="31"/>
-        <v>1886</v>
-      </c>
-      <c r="B204" s="26">
-        <f t="shared" si="30"/>
-        <v>54.118486684938759</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205" s="1">
-        <f t="shared" si="31"/>
         <v>1887</v>
       </c>
-      <c r="B205" s="26">
-        <f t="shared" si="30"/>
+      <c r="B220" s="26">
+        <f t="shared" si="27"/>
         <v>64.77321484392526</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
-      <c r="A206" s="1">
-        <f t="shared" si="31"/>
+    <row r="221" spans="1:6">
+      <c r="A221" s="1">
+        <f t="shared" si="28"/>
         <v>1888</v>
       </c>
-      <c r="B206" s="26">
-        <f t="shared" si="30"/>
+      <c r="B221" s="26">
+        <f t="shared" si="27"/>
         <v>75.815000367441684</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
-      <c r="A207" s="1">
-        <f t="shared" si="31"/>
+    <row r="222" spans="1:6">
+      <c r="A222" s="1">
+        <f t="shared" si="28"/>
         <v>1889</v>
       </c>
-      <c r="B207" s="26">
-        <f t="shared" si="30"/>
+      <c r="B222" s="26">
+        <f t="shared" si="27"/>
         <v>87.207442423697103</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
-      <c r="A208" s="1">
-        <f t="shared" si="31"/>
+    <row r="223" spans="1:6">
+      <c r="A223" s="1">
+        <f t="shared" si="28"/>
         <v>1890</v>
       </c>
-      <c r="B208" s="26">
-        <f t="shared" si="30"/>
+      <c r="B223" s="26">
+        <f t="shared" si="27"/>
         <v>99.686028922132408</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
-      <c r="A209" s="1">
-        <f t="shared" si="31"/>
+    <row r="224" spans="1:6">
+      <c r="A224" s="1">
+        <f t="shared" si="28"/>
         <v>1891</v>
       </c>
-      <c r="B209" s="26">
-        <f t="shared" si="30"/>
+      <c r="B224" s="26">
+        <f t="shared" si="27"/>
         <v>109.79494355371079</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
-      <c r="A210" s="1">
-        <f t="shared" si="31"/>
+    <row r="225" spans="1:2">
+      <c r="A225" s="1">
+        <f t="shared" si="28"/>
         <v>1892</v>
       </c>
-      <c r="B210" s="26">
-        <f t="shared" si="30"/>
+      <c r="B225" s="26">
+        <f t="shared" si="27"/>
         <v>113.80276875090047</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="1">
-        <f t="shared" si="31"/>
+    <row r="226" spans="1:2">
+      <c r="A226" s="1">
+        <f t="shared" si="28"/>
         <v>1893</v>
       </c>
-      <c r="B211" s="26">
-        <f t="shared" si="30"/>
+      <c r="B226" s="26">
+        <f t="shared" si="27"/>
         <v>112.09952309622764</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
-      <c r="A212" s="1">
-        <f t="shared" si="31"/>
+    <row r="227" spans="1:2">
+      <c r="A227" s="1">
+        <f t="shared" si="28"/>
         <v>1894</v>
       </c>
-      <c r="B212" s="26">
-        <f t="shared" si="30"/>
+      <c r="B227" s="26">
+        <f t="shared" si="27"/>
         <v>104.88446435368679</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
-      <c r="A213" s="1">
-        <f t="shared" si="31"/>
+    <row r="228" spans="1:2">
+      <c r="A228" s="1">
+        <f t="shared" si="28"/>
         <v>1895</v>
       </c>
-      <c r="B213" s="26">
-        <f t="shared" si="30"/>
+      <c r="B228" s="26">
+        <f t="shared" si="27"/>
         <v>90.877838490181389</v>
       </c>
     </row>
@@ -20424,18 +20614,18 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49" t="s">
+      <c r="C14" s="51"/>
+      <c r="D14" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="G14" s="49" t="s">
+      <c r="E14" s="51"/>
+      <c r="G14" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="H14" s="49"/>
+      <c r="H14" s="51"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="14" t="s">
@@ -21159,7 +21349,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.83984375" customWidth="1"/>
@@ -22184,12 +22374,12 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F26" s="4"/>
       <c r="L26" s="4"/>
@@ -22197,12 +22387,12 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -22317,7 +22507,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -22387,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" ref="C35:M35" si="1">D31</f>
+        <f t="shared" ref="D35:M35" si="1">D31</f>
         <v>4231.1951632577848</v>
       </c>
       <c r="E35" s="4">
@@ -22432,52 +22622,52 @@
       <c r="A36" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="50">
-        <f>B35/$L35*100</f>
+      <c r="B36" s="49">
+        <f t="shared" ref="B36:M36" si="2">B35/$L35*100</f>
         <v>5.8803489643831483E-4</v>
       </c>
-      <c r="C36" s="50">
-        <f>C35/$L35*100</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="50">
-        <f>D35/$L35*100</f>
+      <c r="C36" s="49">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="49">
+        <f t="shared" si="2"/>
         <v>8.5709492402230048</v>
       </c>
-      <c r="E36" s="50">
-        <f>E35/$L35*100</f>
+      <c r="E36" s="49">
+        <f t="shared" si="2"/>
         <v>1.5405867554195481E-3</v>
       </c>
-      <c r="F36" s="50">
-        <f>F35/$L35*100</f>
+      <c r="F36" s="49">
+        <f t="shared" si="2"/>
         <v>52.168607923681932</v>
       </c>
-      <c r="G36" s="50">
-        <f>G35/$L35*100</f>
+      <c r="G36" s="49">
+        <f t="shared" si="2"/>
         <v>11.771652358072608</v>
       </c>
-      <c r="H36" s="50">
-        <f>H35/$L35*100</f>
+      <c r="H36" s="49">
+        <f t="shared" si="2"/>
         <v>23.970113159242132</v>
       </c>
-      <c r="I36" s="50">
-        <f>I35/$L35*100</f>
+      <c r="I36" s="49">
+        <f t="shared" si="2"/>
         <v>1.3473014935407466</v>
       </c>
-      <c r="J36" s="50">
-        <f>J35/$L35*100</f>
+      <c r="J36" s="49">
+        <f t="shared" si="2"/>
         <v>2.0745062005203888E-2</v>
       </c>
-      <c r="K36" s="50">
-        <f>K35/$L35*100</f>
+      <c r="K36" s="49">
+        <f t="shared" si="2"/>
         <v>2.0487170910071661</v>
       </c>
-      <c r="L36" s="50">
-        <f>L35/$L35*100</f>
+      <c r="L36" s="49">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="M36" s="50">
-        <f>M35/$L35*100</f>
+      <c r="M36" s="49">
+        <f t="shared" si="2"/>
         <v>9.9785050575341816E-2</v>
       </c>
     </row>
@@ -22496,6 +22686,50 @@
       <c r="M37" s="4"/>
       <c r="O37" s="4"/>
     </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="4">
+        <f>SUM(L2:L6)</f>
+        <v>276141.28124371887</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" s="4">
+        <f>SUM(L7:L11)</f>
+        <v>705906.12273697765</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="4">
+        <f>SUM(L12:L16)</f>
+        <v>878080.04671502998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="4">
+        <f>SUM(L17:L22)</f>
+        <v>777781.94085353415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22503,7 +22737,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FEA9BB-FB24-45B6-A20A-F26B22290AE7}">
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="16" max="16" width="25.05078125" customWidth="1"/>
@@ -22555,69 +22789,69 @@
       <c r="P1" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="R1" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="T1" s="52" t="s">
-        <v>216</v>
-      </c>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
+      <c r="R1" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="T1" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="1">
         <v>1881</v>
       </c>
       <c r="B2" s="26">
-        <v>16.564583374629162</v>
+        <v>18.475000534206423</v>
       </c>
       <c r="C2" s="4">
-        <f>C$27*$B2/100</f>
-        <v>4.8085900264844161E-2</v>
+        <f t="shared" ref="C2:N16" si="0">C$27*$B2/100</f>
+        <v>5.3631716113154662E-2</v>
       </c>
       <c r="D2" s="4">
-        <f>D$27*$B2/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E2" s="4">
-        <f>E$27*$B2/100</f>
-        <v>700.87985056111222</v>
+        <f t="shared" si="0"/>
+        <v>781.71332901519202</v>
       </c>
       <c r="F2" s="4">
-        <f>F$27*$B2/100</f>
-        <v>0.12597977011082936</v>
+        <f t="shared" si="0"/>
+        <v>0.14050919769353276</v>
       </c>
       <c r="G2" s="4">
-        <f>G$27*$B2/100</f>
-        <v>4266.02994612766</v>
+        <f t="shared" si="0"/>
+        <v>4758.0372986841612</v>
       </c>
       <c r="H2" s="4">
-        <f>H$27*$B2/100</f>
-        <v>962.61379158145928</v>
+        <f t="shared" si="0"/>
+        <v>1073.6334208647172</v>
       </c>
       <c r="I2" s="4">
-        <f>I$27*$B2/100</f>
-        <v>1960.1293693515629</v>
+        <f t="shared" si="0"/>
+        <v>2186.1939009796888</v>
       </c>
       <c r="J2" s="4">
-        <f>J$27*$B2/100</f>
-        <v>110.17408258843363</v>
+        <f t="shared" si="0"/>
+        <v>122.88061755870045</v>
       </c>
       <c r="K2" s="4">
-        <f>K$27*$B2/100</f>
-        <v>1.6964043947260623</v>
+        <f t="shared" si="0"/>
+        <v>1.89205314676354</v>
       </c>
       <c r="L2" s="4">
-        <f>L$27*$B2/100</f>
-        <v>167.53156369757463</v>
+        <f t="shared" si="0"/>
+        <v>186.85321923337662</v>
       </c>
       <c r="M2" s="4">
-        <f>M$27*$B2/100</f>
-        <v>8177.3888856081512</v>
+        <f t="shared" si="0"/>
+        <v>9120.498874811361</v>
       </c>
       <c r="N2" s="4">
-        <f>N$27*$B2/100</f>
-        <v>8.1598116352464736</v>
+        <f t="shared" si="0"/>
+        <v>9.1008944149539968</v>
       </c>
       <c r="P2" s="29">
         <v>0</v>
@@ -22627,65 +22861,64 @@
       </c>
       <c r="T2" s="4">
         <f>M2/R2*100</f>
-        <v>82.263381858197718</v>
-      </c>
-      <c r="U2" s="53"/>
-      <c r="V2" s="54"/>
+        <v>91.750935680255481</v>
+      </c>
+      <c r="V2" s="4"/>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
         <v>1882</v>
       </c>
       <c r="B3" s="26">
-        <v>19.924412112562521</v>
+        <v>22.28474657634947</v>
       </c>
       <c r="C3" s="4">
-        <f>C$27*$B3/100</f>
-        <v>5.7839262963158181E-2</v>
+        <f t="shared" si="0"/>
+        <v>6.4691159268088605E-2</v>
       </c>
       <c r="D3" s="4">
-        <f>D$27*$B3/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E3" s="4">
-        <f>E$27*$B3/100</f>
-        <v>843.04076161429361</v>
+        <f t="shared" si="0"/>
+        <v>942.91111928275348</v>
       </c>
       <c r="F3" s="4">
-        <f>F$27*$B3/100</f>
-        <v>0.15153250768616114</v>
+        <f t="shared" si="0"/>
+        <v>0.16948372241987936</v>
       </c>
       <c r="G3" s="4">
-        <f>G$27*$B3/100</f>
-        <v>5131.3176316505615</v>
+        <f t="shared" si="0"/>
+        <v>5739.1963375415107</v>
       </c>
       <c r="H3" s="4">
-        <f>H$27*$B3/100</f>
-        <v>1157.8627397343</v>
+        <f t="shared" si="0"/>
+        <v>1295.0283089611332</v>
       </c>
       <c r="I3" s="4">
-        <f>I$27*$B3/100</f>
-        <v>2357.706467203685</v>
+        <f t="shared" si="0"/>
+        <v>2637.0108601561606</v>
       </c>
       <c r="J3" s="4">
-        <f>J$27*$B3/100</f>
-        <v>132.52091984260935</v>
+        <f t="shared" si="0"/>
+        <v>148.21993733482631</v>
       </c>
       <c r="K3" s="4">
-        <f>K$27*$B3/100</f>
-        <v>2.040489610010547</v>
+        <f t="shared" si="0"/>
+        <v>2.2822150833794903</v>
       </c>
       <c r="L3" s="4">
-        <f>L$27*$B3/100</f>
-        <v>201.51233758677157</v>
+        <f t="shared" si="0"/>
+        <v>225.38438523350908</v>
       </c>
       <c r="M3" s="4">
-        <f>M$27*$B3/100</f>
-        <v>9836.0256021345758</v>
+        <f t="shared" si="0"/>
+        <v>11001.244936298564</v>
       </c>
       <c r="N3" s="4">
-        <f>N$27*$B3/100</f>
-        <v>9.814883121693553</v>
+        <f t="shared" si="0"/>
+        <v>10.97759782360275</v>
       </c>
       <c r="P3" s="29">
         <v>0</v>
@@ -22694,8 +22927,8 @@
         <v>11990.335417</v>
       </c>
       <c r="T3" s="4">
-        <f t="shared" ref="T3:T16" si="0">M3/R3*100</f>
-        <v>82.032947870573949</v>
+        <f t="shared" ref="T3:T16" si="1">M3/R3*100</f>
+        <v>91.750935680255495</v>
       </c>
       <c r="V3" s="4"/>
     </row>
@@ -22704,55 +22937,55 @@
         <v>1883</v>
       </c>
       <c r="B4" s="26">
-        <v>24.424831678196462</v>
+        <v>27.466557787163893</v>
       </c>
       <c r="C4" s="4">
-        <f>C$27*$B4/100</f>
-        <v>7.0903686105516381E-2</v>
+        <f t="shared" si="0"/>
+        <v>7.9733617713262275E-2</v>
       </c>
       <c r="D4" s="4">
-        <f>D$27*$B4/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <f>E$27*$B4/100</f>
-        <v>1033.4622966017039</v>
+        <f t="shared" si="0"/>
+        <v>1162.163664603883</v>
       </c>
       <c r="F4" s="4">
-        <f>F$27*$B4/100</f>
-        <v>0.1857598594678678</v>
+        <f t="shared" si="0"/>
+        <v>0.20889330914670123</v>
       </c>
       <c r="G4" s="4">
-        <f>G$27*$B4/100</f>
-        <v>6290.3521936993056</v>
+        <f t="shared" si="0"/>
+        <v>7073.7159750454775</v>
       </c>
       <c r="H4" s="4">
-        <f>H$27*$B4/100</f>
-        <v>1419.3945781032357</v>
+        <f t="shared" si="0"/>
+        <v>1596.1577019612187</v>
       </c>
       <c r="I4" s="4">
-        <f>I$27*$B4/100</f>
-        <v>2890.2525847543766</v>
+        <f t="shared" si="0"/>
+        <v>3250.1877877636098</v>
       </c>
       <c r="J4" s="4">
-        <f>J$27*$B4/100</f>
-        <v>162.45403591881472</v>
+        <f t="shared" si="0"/>
+        <v>182.68511423582521</v>
       </c>
       <c r="K4" s="4">
-        <f>K$27*$B4/100</f>
-        <v>2.5013844817128956</v>
+        <f t="shared" si="0"/>
+        <v>2.8128923187713624</v>
       </c>
       <c r="L4" s="4">
-        <f>L$27*$B4/100</f>
-        <v>247.02886583707493</v>
+        <f t="shared" si="0"/>
+        <v>277.79240029188952</v>
       </c>
       <c r="M4" s="4">
-        <f>M$27*$B4/100</f>
-        <v>12057.734419330367</v>
+        <f t="shared" si="0"/>
+        <v>13559.334351788148</v>
       </c>
       <c r="N4" s="4">
-        <f>N$27*$B4/100</f>
-        <v>12.031816388569204</v>
+        <f t="shared" si="0"/>
+        <v>13.530188640611497</v>
       </c>
       <c r="P4" s="29">
         <v>0</v>
@@ -22761,8 +22994,8 @@
         <v>14778.415338499999</v>
       </c>
       <c r="T4" s="4">
-        <f t="shared" si="0"/>
-        <v>81.590171497739348</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255509</v>
       </c>
       <c r="V4" s="4"/>
     </row>
@@ -22771,55 +23004,55 @@
         <v>1884</v>
       </c>
       <c r="B5" s="26">
-        <v>30.304531969579841</v>
+        <v>34.309298893446325</v>
       </c>
       <c r="C5" s="4">
-        <f>C$27*$B5/100</f>
-        <v>8.7972070827565918E-2</v>
+        <f t="shared" si="0"/>
+        <v>9.9597646824843414E-2</v>
       </c>
       <c r="D5" s="4">
-        <f>D$27*$B5/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <f>E$27*$B5/100</f>
-        <v>1282.2438909447715</v>
+        <f t="shared" si="0"/>
+        <v>1451.6933953271575</v>
       </c>
       <c r="F5" s="4">
-        <f>F$27*$B5/100</f>
-        <v>0.23047715022469842</v>
+        <f t="shared" si="0"/>
+        <v>0.2609348807335678</v>
       </c>
       <c r="G5" s="4">
-        <f>G$27*$B5/100</f>
-        <v>7804.6056433643853</v>
+        <f t="shared" si="0"/>
+        <v>8835.990208740357</v>
       </c>
       <c r="H5" s="4">
-        <f>H$27*$B5/100</f>
-        <v>1761.0802373707074</v>
+        <f t="shared" si="0"/>
+        <v>1993.8083287326454</v>
       </c>
       <c r="I5" s="4">
-        <f>I$27*$B5/100</f>
-        <v>3586.0125059955903</v>
+        <f t="shared" si="0"/>
+        <v>4059.9067831617458</v>
       </c>
       <c r="J5" s="4">
-        <f>J$27*$B5/100</f>
-        <v>201.56100111362221</v>
+        <f t="shared" si="0"/>
+        <v>228.19744054821024</v>
       </c>
       <c r="K5" s="4">
-        <f>K$27*$B5/100</f>
-        <v>3.1035336084607441</v>
+        <f t="shared" si="0"/>
+        <v>3.5136679327508511</v>
       </c>
       <c r="L5" s="4">
-        <f>L$27*$B5/100</f>
-        <v>306.49522014316955</v>
+        <f t="shared" si="0"/>
+        <v>346.99879634704126</v>
       </c>
       <c r="M5" s="4">
-        <f>M$27*$B5/100</f>
-        <v>14960.34867325161</v>
+        <f t="shared" si="0"/>
+        <v>16937.370116654507</v>
       </c>
       <c r="N5" s="4">
-        <f>N$27*$B5/100</f>
-        <v>14.928191489851597</v>
+        <f t="shared" si="0"/>
+        <v>16.900963337036526</v>
       </c>
       <c r="P5" s="29">
         <v>0</v>
@@ -22828,8 +23061,8 @@
         <v>18460.160641499999</v>
       </c>
       <c r="T5" s="4">
-        <f t="shared" si="0"/>
-        <v>81.041270245609269</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255509</v>
       </c>
       <c r="V5" s="4"/>
     </row>
@@ -22838,55 +23071,55 @@
         <v>1885</v>
       </c>
       <c r="B6" s="26">
-        <v>38.098706944967525</v>
+        <v>43.534343842051776</v>
       </c>
       <c r="C6" s="4">
-        <f>C$27*$B6/100</f>
-        <v>0.11059805012549843</v>
+        <f t="shared" si="0"/>
+        <v>0.12637734790786428</v>
       </c>
       <c r="D6" s="4">
-        <f>D$27*$B6/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f>E$27*$B6/100</f>
-        <v>1612.0306455192238</v>
+        <f t="shared" si="0"/>
+        <v>1842.023051000908</v>
       </c>
       <c r="F6" s="4">
-        <f>F$27*$B6/100</f>
-        <v>0.28975472753502435</v>
+        <f t="shared" si="0"/>
+        <v>0.3310947522862322</v>
       </c>
       <c r="G6" s="4">
-        <f>G$27*$B6/100</f>
-        <v>9811.9114172777645</v>
+        <f t="shared" si="0"/>
+        <v>11211.801125023399</v>
       </c>
       <c r="H6" s="4">
-        <f>H$27*$B6/100</f>
-        <v>2214.0213198973443</v>
+        <f t="shared" si="0"/>
+        <v>2529.9012261300891</v>
       </c>
       <c r="I6" s="4">
-        <f>I$27*$B6/100</f>
-        <v>4508.3170960719117</v>
+        <f t="shared" si="0"/>
+        <v>5151.5298640685205</v>
       </c>
       <c r="J6" s="4">
-        <f>J$27*$B6/100</f>
-        <v>253.40148861796246</v>
+        <f t="shared" si="0"/>
+        <v>289.55490671946086</v>
       </c>
       <c r="K6" s="4">
-        <f>K$27*$B6/100</f>
-        <v>3.9017470245471939</v>
+        <f t="shared" si="0"/>
+        <v>4.4584189378578598</v>
       </c>
       <c r="L6" s="4">
-        <f>L$27*$B6/100</f>
-        <v>385.32426714227267</v>
+        <f t="shared" si="0"/>
+        <v>440.29943485192501</v>
       </c>
       <c r="M6" s="4">
-        <f>M$27*$B6/100</f>
-        <v>18808.075982460032</v>
+        <f t="shared" si="0"/>
+        <v>21491.470773813395</v>
       </c>
       <c r="N6" s="4">
-        <f>N$27*$B6/100</f>
-        <v>18.767648131346458</v>
+        <f t="shared" si="0"/>
+        <v>21.445274981034494</v>
       </c>
       <c r="P6" s="29">
         <v>0</v>
@@ -22895,8 +23128,8 @@
         <v>23423.707469000001</v>
       </c>
       <c r="T6" s="4">
-        <f t="shared" si="0"/>
-        <v>80.295042991599402</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255495</v>
       </c>
       <c r="V6" s="4"/>
     </row>
@@ -22905,55 +23138,55 @@
         <v>1886</v>
       </c>
       <c r="B7" s="26">
-        <v>47.195352402095843</v>
+        <v>54.118486684938759</v>
       </c>
       <c r="C7" s="4">
-        <f>C$27*$B7/100</f>
-        <v>0.13700501589718736</v>
+        <f t="shared" si="0"/>
+        <v>0.15710242113315581</v>
       </c>
       <c r="D7" s="4">
-        <f>D$27*$B7/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f>E$27*$B7/100</f>
-        <v>1996.9274681199461</v>
+        <f t="shared" si="0"/>
+        <v>2289.8587910414371</v>
       </c>
       <c r="F7" s="4">
-        <f>F$27*$B7/100</f>
-        <v>0.3589380735661708</v>
+        <f t="shared" si="0"/>
+        <v>0.41159106493176123</v>
       </c>
       <c r="G7" s="4">
-        <f>G$27*$B7/100</f>
-        <v>12154.65442817974</v>
+        <f t="shared" si="0"/>
+        <v>13937.633058170915</v>
       </c>
       <c r="H7" s="4">
-        <f>H$27*$B7/100</f>
-        <v>2742.652567428167</v>
+        <f t="shared" si="0"/>
+        <v>3144.9750642222771</v>
       </c>
       <c r="I7" s="4">
-        <f>I$27*$B7/100</f>
-        <v>5584.7463378967077</v>
+        <f t="shared" si="0"/>
+        <v>6403.9784627776544</v>
       </c>
       <c r="J7" s="4">
-        <f>J$27*$B7/100</f>
-        <v>313.90494621813241</v>
+        <f t="shared" si="0"/>
+        <v>359.95198229493485</v>
       </c>
       <c r="K7" s="4">
-        <f>K$27*$B7/100</f>
-        <v>4.8333484407574483</v>
+        <f t="shared" si="0"/>
+        <v>5.5423572432777419</v>
       </c>
       <c r="L7" s="4">
-        <f>L$27*$B7/100</f>
-        <v>477.32629359645529</v>
+        <f t="shared" si="0"/>
+        <v>547.34577346272306</v>
       </c>
       <c r="M7" s="4">
-        <f>M$27*$B7/100</f>
-        <v>23298.79004239662</v>
+        <f t="shared" si="0"/>
+        <v>26716.513268976705</v>
       </c>
       <c r="N7" s="4">
-        <f>N$27*$B7/100</f>
-        <v>23.248709427248162</v>
+        <f t="shared" si="0"/>
+        <v>26.659086277416307</v>
       </c>
       <c r="P7" s="29">
         <v>0</v>
@@ -22962,8 +23195,8 @@
         <v>29118.518597000002</v>
       </c>
       <c r="T7" s="4">
-        <f t="shared" si="0"/>
-        <v>80.013651672503102</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255481</v>
       </c>
       <c r="V7" s="4"/>
     </row>
@@ -22972,55 +23205,55 @@
         <v>1887</v>
       </c>
       <c r="B8" s="26">
-        <v>56.825539984274542</v>
+        <v>64.77321484392526</v>
       </c>
       <c r="C8" s="4">
-        <f>C$27*$B8/100</f>
-        <v>0.16496081950149943</v>
+        <f t="shared" si="0"/>
+        <v>0.18803239890650392</v>
       </c>
       <c r="D8" s="4">
-        <f>D$27*$B8/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f>E$27*$B8/100</f>
-        <v>2404.3994993097426</v>
+        <f t="shared" si="0"/>
+        <v>2740.681133562739</v>
       </c>
       <c r="F8" s="4">
-        <f>F$27*$B8/100</f>
-        <v>0.43217920437452095</v>
+        <f t="shared" si="0"/>
+        <v>0.49262420495738835</v>
       </c>
       <c r="G8" s="4">
-        <f>G$27*$B8/100</f>
-        <v>14634.805463872226</v>
+        <f t="shared" si="0"/>
+        <v>16681.643478843729</v>
       </c>
       <c r="H8" s="4">
-        <f>H$27*$B8/100</f>
-        <v>3302.2894247197419</v>
+        <f t="shared" si="0"/>
+        <v>3764.1508104170621</v>
       </c>
       <c r="I8" s="4">
-        <f>I$27*$B8/100</f>
-        <v>6724.3109792329269</v>
+        <f t="shared" si="0"/>
+        <v>7664.7796018436784</v>
       </c>
       <c r="J8" s="4">
-        <f>J$27*$B8/100</f>
-        <v>377.95709036358198</v>
+        <f t="shared" si="0"/>
+        <v>430.81853375577225</v>
       </c>
       <c r="K8" s="4">
-        <f>K$27*$B8/100</f>
-        <v>5.8195907244882958</v>
+        <f t="shared" si="0"/>
+        <v>6.6335242992026169</v>
       </c>
       <c r="L8" s="4">
-        <f>L$27*$B8/100</f>
-        <v>574.72448030934515</v>
+        <f t="shared" si="0"/>
+        <v>655.10600074266517</v>
       </c>
       <c r="M8" s="4">
-        <f>M$27*$B8/100</f>
-        <v>28052.896265282092</v>
+        <f t="shared" si="0"/>
+        <v>31976.401408386246</v>
       </c>
       <c r="N8" s="4">
-        <f>N$27*$B8/100</f>
-        <v>27.992596726159903</v>
+        <f t="shared" si="0"/>
+        <v>31.907668317532526</v>
       </c>
       <c r="P8" s="29">
         <v>0</v>
@@ -23029,8 +23262,8 @@
         <v>34851.308241500003</v>
       </c>
       <c r="T8" s="4">
-        <f t="shared" si="0"/>
-        <v>80.493093891601617</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255481</v>
       </c>
       <c r="V8" s="4"/>
     </row>
@@ -23039,55 +23272,55 @@
         <v>1888</v>
       </c>
       <c r="B9" s="26">
-        <v>67.303943916959042</v>
+        <v>75.815000367441684</v>
       </c>
       <c r="C9" s="4">
-        <f>C$27*$B9/100</f>
-        <v>0.19537893959823249</v>
+        <f t="shared" si="0"/>
+        <v>0.2200859788500138</v>
       </c>
       <c r="D9" s="4">
-        <f>D$27*$B9/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f>E$27*$B9/100</f>
-        <v>2847.7612196961027</v>
+        <f t="shared" si="0"/>
+        <v>3207.8806285710643</v>
       </c>
       <c r="F9" s="4">
-        <f>F$27*$B9/100</f>
-        <v>0.51187133358254311</v>
+        <f t="shared" si="0"/>
+        <v>0.57660105909283532</v>
       </c>
       <c r="G9" s="4">
-        <f>G$27*$B9/100</f>
-        <v>17333.405480152724</v>
+        <f t="shared" si="0"/>
+        <v>19525.336352772982</v>
       </c>
       <c r="H9" s="4">
-        <f>H$27*$B9/100</f>
-        <v>3911.2184820489188</v>
+        <f t="shared" si="0"/>
+        <v>4405.8195314608447</v>
       </c>
       <c r="I9" s="4">
-        <f>I$27*$B9/100</f>
-        <v>7964.24722319799</v>
+        <f t="shared" si="0"/>
+        <v>8971.3822253588023</v>
       </c>
       <c r="J9" s="4">
-        <f>J$27*$B9/100</f>
-        <v>447.65087705083056</v>
+        <f t="shared" si="0"/>
+        <v>504.25947474888693</v>
       </c>
       <c r="K9" s="4">
-        <f>K$27*$B9/100</f>
-        <v>6.892700145902813</v>
+        <f t="shared" si="0"/>
+        <v>7.7643304936044251</v>
       </c>
       <c r="L9" s="4">
-        <f>L$27*$B9/100</f>
-        <v>680.70139238708407</v>
+        <f t="shared" si="0"/>
+        <v>766.78086469374011</v>
       </c>
       <c r="M9" s="4">
-        <f>M$27*$B9/100</f>
-        <v>33225.738945363395</v>
+        <f t="shared" si="0"/>
+        <v>37427.367012240051</v>
       </c>
       <c r="N9" s="4">
-        <f>N$27*$B9/100</f>
-        <v>33.154320410661903</v>
+        <f t="shared" si="0"/>
+        <v>37.34691710218253</v>
       </c>
       <c r="P9" s="29">
         <v>0</v>
@@ -23096,8 +23329,8 @@
         <v>40792.354579000006</v>
       </c>
       <c r="T9" s="4">
-        <f t="shared" si="0"/>
-        <v>81.45089757203688</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255481</v>
       </c>
       <c r="V9" s="4"/>
     </row>
@@ -23106,55 +23339,55 @@
         <v>1889</v>
       </c>
       <c r="B10" s="26">
-        <v>78.685900612499751</v>
+        <v>87.207442423697103</v>
       </c>
       <c r="C10" s="4">
-        <f>C$27*$B10/100</f>
-        <v>0.228420014166931</v>
+        <f t="shared" si="0"/>
+        <v>0.25315749173389146</v>
       </c>
       <c r="D10" s="4">
-        <f>D$27*$B10/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f>E$27*$B10/100</f>
-        <v>3329.3540208819172</v>
+        <f t="shared" si="0"/>
+        <v>3689.9170858322891</v>
       </c>
       <c r="F10" s="4">
-        <f>F$27*$B10/100</f>
-        <v>0.59843531502935898</v>
+        <f t="shared" si="0"/>
+        <v>0.66324478557775413</v>
       </c>
       <c r="G10" s="4">
-        <f>G$27*$B10/100</f>
-        <v>20264.705773710026</v>
+        <f t="shared" si="0"/>
+        <v>22459.337037990812</v>
       </c>
       <c r="H10" s="4">
-        <f>H$27*$B10/100</f>
-        <v>4572.6554915116276</v>
+        <f t="shared" si="0"/>
+        <v>5067.865874258744</v>
       </c>
       <c r="I10" s="4">
-        <f>I$27*$B10/100</f>
-        <v>9311.1031685028302</v>
+        <f t="shared" si="0"/>
+        <v>10319.478930121355</v>
       </c>
       <c r="J10" s="4">
-        <f>J$27*$B10/100</f>
-        <v>523.35435890918734</v>
+        <f t="shared" si="0"/>
+        <v>580.03269666476433</v>
       </c>
       <c r="K10" s="4">
-        <f>K$27*$B10/100</f>
-        <v>8.0583437918800698</v>
+        <f t="shared" si="0"/>
+        <v>8.931047961457816</v>
       </c>
       <c r="L10" s="4">
-        <f>L$27*$B10/100</f>
-        <v>795.81669350975437</v>
+        <f t="shared" si="0"/>
+        <v>882.00221308827588</v>
       </c>
       <c r="M10" s="4">
-        <f>M$27*$B10/100</f>
-        <v>38844.635845670833</v>
+        <f t="shared" si="0"/>
+        <v>43051.440189561574</v>
       </c>
       <c r="N10" s="4">
-        <f>N$27*$B10/100</f>
-        <v>38.761139524409991</v>
+        <f t="shared" si="0"/>
+        <v>42.958901366567041</v>
       </c>
       <c r="P10" s="29">
         <v>0</v>
@@ -23163,8 +23396,8 @@
         <v>46922.072096999997</v>
       </c>
       <c r="T10" s="4">
-        <f t="shared" si="0"/>
-        <v>82.785422956959309</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255481</v>
       </c>
       <c r="V10" s="4"/>
     </row>
@@ -23173,55 +23406,55 @@
         <v>1890</v>
       </c>
       <c r="B11" s="26">
-        <v>91.885699749582088</v>
+        <v>99.686028922132408</v>
       </c>
       <c r="C11" s="4">
-        <f>C$27*$B11/100</f>
-        <v>0.26673816624275565</v>
+        <f t="shared" si="0"/>
+        <v>0.28938201077184311</v>
       </c>
       <c r="D11" s="4">
-        <f>D$27*$B11/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f>E$27*$B11/100</f>
-        <v>3887.8632835298877</v>
+        <f t="shared" si="0"/>
+        <v>4217.9104341970224</v>
       </c>
       <c r="F11" s="4">
-        <f>F$27*$B11/100</f>
-        <v>0.69882465916135317</v>
+        <f t="shared" si="0"/>
+        <v>0.75814904141245132</v>
       </c>
       <c r="G11" s="4">
-        <f>G$27*$B11/100</f>
-        <v>23664.171798790412</v>
+        <f t="shared" si="0"/>
+        <v>25673.062519864634</v>
       </c>
       <c r="H11" s="4">
-        <f>H$27*$B11/100</f>
-        <v>5339.7323571406105</v>
+        <f t="shared" si="0"/>
+        <v>5793.0310770995266</v>
       </c>
       <c r="I11" s="4">
-        <f>I$27*$B11/100</f>
-        <v>10873.069043102785</v>
+        <f t="shared" si="0"/>
+        <v>11796.101875014741</v>
       </c>
       <c r="J11" s="4">
-        <f>J$27*$B11/100</f>
-        <v>611.1486443064922</v>
+        <f t="shared" si="0"/>
+        <v>663.03006450507087</v>
       </c>
       <c r="K11" s="4">
-        <f>K$27*$B11/100</f>
-        <v>9.4101554710041189</v>
+        <f t="shared" si="0"/>
+        <v>10.208999147863002</v>
       </c>
       <c r="L11" s="4">
-        <f>L$27*$B11/100</f>
-        <v>929.31736418260232</v>
+        <f t="shared" si="0"/>
+        <v>1008.2086537537425</v>
       </c>
       <c r="M11" s="4">
-        <f>M$27*$B11/100</f>
-        <v>45360.941647914027</v>
+        <f t="shared" si="0"/>
+        <v>49211.707081434986</v>
       </c>
       <c r="N11" s="4">
-        <f>N$27*$B11/100</f>
-        <v>45.263438564822287</v>
+        <f t="shared" si="0"/>
+        <v>49.105926800198965</v>
       </c>
       <c r="P11" s="29">
         <v>0</v>
@@ -23230,8 +23463,8 @@
         <v>53636.190973500001</v>
       </c>
       <c r="T11" s="4">
-        <f t="shared" si="0"/>
-        <v>84.571519387581944</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255481</v>
       </c>
       <c r="V11" s="4"/>
     </row>
@@ -23240,55 +23473,55 @@
         <v>1891</v>
       </c>
       <c r="B12" s="26">
-        <v>103.17019828605787</v>
+        <v>109.79494355371079</v>
       </c>
       <c r="C12" s="4">
-        <f>C$27*$B12/100</f>
-        <v>0.2994963261609131</v>
+        <f t="shared" si="0"/>
+        <v>0.31872752763551637</v>
       </c>
       <c r="D12" s="4">
-        <f>D$27*$B12/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>E$27*$B12/100</f>
-        <v>4365.3324398031464</v>
+        <f t="shared" si="0"/>
+        <v>4645.6383411462266</v>
       </c>
       <c r="F12" s="4">
-        <f>F$27*$B12/100</f>
-        <v>0.78464743533926806</v>
+        <f t="shared" si="0"/>
+        <v>0.83503106811689631</v>
       </c>
       <c r="G12" s="4">
-        <f>G$27*$B12/100</f>
-        <v>26570.372793701776</v>
+        <f t="shared" si="0"/>
+        <v>28276.504548307861</v>
       </c>
       <c r="H12" s="4">
-        <f>H$27*$B12/100</f>
-        <v>5995.5058032104889</v>
+        <f t="shared" si="0"/>
+        <v>6380.4880883746328</v>
       </c>
       <c r="I12" s="4">
-        <f>I$27*$B12/100</f>
-        <v>12208.392516051048</v>
+        <f t="shared" si="0"/>
+        <v>12992.315508251872</v>
       </c>
       <c r="J12" s="4">
-        <f>J$27*$B12/100</f>
-        <v>686.20391407143882</v>
+        <f t="shared" si="0"/>
+        <v>730.26631007251342</v>
       </c>
       <c r="K12" s="4">
-        <f>K$27*$B12/100</f>
-        <v>10.565818277403311</v>
+        <f t="shared" si="0"/>
+        <v>11.244268603126564</v>
       </c>
       <c r="L12" s="4">
-        <f>L$27*$B12/100</f>
-        <v>1043.4469889731868</v>
+        <f t="shared" si="0"/>
+        <v>1110.4486097617839</v>
       </c>
       <c r="M12" s="4">
-        <f>M$27*$B12/100</f>
-        <v>50931.726667063616</v>
+        <f t="shared" si="0"/>
+        <v>54202.145070985782</v>
       </c>
       <c r="N12" s="4">
-        <f>N$27*$B12/100</f>
-        <v>50.822249213624275</v>
+        <f t="shared" si="0"/>
+        <v>54.085637872003289</v>
       </c>
       <c r="P12" s="29">
         <v>0</v>
@@ -23297,8 +23530,8 @@
         <v>59075.304975500003</v>
       </c>
       <c r="T12" s="4">
-        <f t="shared" si="0"/>
-        <v>86.214919564420825</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255495</v>
       </c>
       <c r="V12" s="4"/>
     </row>
@@ -23307,55 +23540,55 @@
         <v>1892</v>
       </c>
       <c r="B13" s="26">
-        <v>108.41724646012143</v>
+        <v>113.80276875090047</v>
       </c>
       <c r="C13" s="4">
-        <f>C$27*$B13/100</f>
-        <v>0.31472816323622993</v>
+        <f t="shared" si="0"/>
+        <v>0.33036198159988039</v>
       </c>
       <c r="D13" s="4">
-        <f>D$27*$B13/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E13" s="4">
-        <f>E$27*$B13/100</f>
-        <v>4587.3452883579293</v>
+        <f t="shared" si="0"/>
+        <v>4815.2172470415426</v>
       </c>
       <c r="F13" s="4">
-        <f>F$27*$B13/100</f>
-        <v>0.82455317324882627</v>
+        <f t="shared" si="0"/>
+        <v>0.86551205792311581</v>
       </c>
       <c r="G13" s="4">
-        <f>G$27*$B13/100</f>
-        <v>27921.693508088938</v>
+        <f t="shared" si="0"/>
+        <v>29308.676739021888</v>
       </c>
       <c r="H13" s="4">
-        <f>H$27*$B13/100</f>
-        <v>6300.4262967245004</v>
+        <f t="shared" si="0"/>
+        <v>6613.3939044648505</v>
       </c>
       <c r="I13" s="4">
-        <f>I$27*$B13/100</f>
-        <v>12829.289099791102</v>
+        <f t="shared" si="0"/>
+        <v>13466.571678695071</v>
       </c>
       <c r="J13" s="4">
-        <f>J$27*$B13/100</f>
-        <v>721.10299398190534</v>
+        <f t="shared" si="0"/>
+        <v>756.92309064397568</v>
       </c>
       <c r="K13" s="4">
-        <f>K$27*$B13/100</f>
-        <v>11.103176530279988</v>
+        <f t="shared" si="0"/>
+        <v>11.65471612987932</v>
       </c>
       <c r="L13" s="4">
-        <f>L$27*$B13/100</f>
-        <v>1096.5148003099782</v>
+        <f t="shared" si="0"/>
+        <v>1150.9831168560052</v>
       </c>
       <c r="M13" s="4">
-        <f>M$27*$B13/100</f>
-        <v>53522.021421265279</v>
+        <f t="shared" si="0"/>
+        <v>56180.676283135435</v>
       </c>
       <c r="N13" s="4">
-        <f>N$27*$B13/100</f>
-        <v>53.406976144154832</v>
+        <f t="shared" si="0"/>
+        <v>56.059916242695756</v>
       </c>
       <c r="P13" s="29">
         <v>0</v>
@@ -23364,8 +23597,8 @@
         <v>61231.720272500002</v>
       </c>
       <c r="T13" s="4">
-        <f t="shared" si="0"/>
-        <v>87.408978848015067</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255481</v>
       </c>
       <c r="V13" s="4"/>
     </row>
@@ -23374,55 +23607,55 @@
         <v>1893</v>
       </c>
       <c r="B14" s="26">
-        <v>108.00098449258988</v>
+        <v>112.09952309622764</v>
       </c>
       <c r="C14" s="4">
-        <f>C$27*$B14/100</f>
-        <v>0.31351978201696984</v>
+        <f t="shared" si="0"/>
+        <v>0.32541757105692815</v>
       </c>
       <c r="D14" s="4">
-        <f>D$27*$B14/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14" s="4">
-        <f>E$27*$B14/100</f>
-        <v>4569.7324321212536</v>
+        <f t="shared" si="0"/>
+        <v>4743.1495992826276</v>
       </c>
       <c r="F14" s="4">
-        <f>F$27*$B14/100</f>
-        <v>0.82138734735453733</v>
+        <f t="shared" si="0"/>
+        <v>0.85255824609669817</v>
       </c>
       <c r="G14" s="4">
-        <f>G$27*$B14/100</f>
-        <v>27814.489724041858</v>
+        <f t="shared" si="0"/>
+        <v>28870.024175047653</v>
       </c>
       <c r="H14" s="4">
-        <f>H$27*$B14/100</f>
-        <v>6276.2361615551217</v>
+        <f t="shared" si="0"/>
+        <v>6514.4135847937587</v>
       </c>
       <c r="I14" s="4">
-        <f>I$27*$B14/100</f>
-        <v>12780.031760234202</v>
+        <f t="shared" si="0"/>
+        <v>13265.022279266279</v>
       </c>
       <c r="J14" s="4">
-        <f>J$27*$B14/100</f>
-        <v>718.33435927784831</v>
+        <f t="shared" si="0"/>
+        <v>745.59449135582634</v>
       </c>
       <c r="K14" s="4">
-        <f>K$27*$B14/100</f>
-        <v>11.060546503607577</v>
+        <f t="shared" si="0"/>
+        <v>11.480284129475947</v>
       </c>
       <c r="L14" s="4">
-        <f>L$27*$B14/100</f>
-        <v>1092.304792925476</v>
+        <f t="shared" si="0"/>
+        <v>1133.7567609957375</v>
       </c>
       <c r="M14" s="4">
-        <f>M$27*$B14/100</f>
-        <v>53316.526606828382</v>
+        <f t="shared" si="0"/>
+        <v>55339.840038058806</v>
       </c>
       <c r="N14" s="4">
-        <f>N$27*$B14/100</f>
-        <v>53.201923039639269</v>
+        <f t="shared" si="0"/>
+        <v>55.220887370290228</v>
       </c>
       <c r="P14" s="29">
         <v>0</v>
@@ -23431,8 +23664,8 @@
         <v>60315.286844500006</v>
       </c>
       <c r="T14" s="4">
-        <f t="shared" si="0"/>
-        <v>88.39637411372135</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255495</v>
       </c>
       <c r="V14" s="4"/>
     </row>
@@ -23441,55 +23674,55 @@
         <v>1894</v>
       </c>
       <c r="B15" s="26">
-        <v>102.04777762360668</v>
+        <v>104.88446435368679</v>
       </c>
       <c r="C15" s="4">
-        <f>C$27*$B15/100</f>
-        <v>0.29623801251612236</v>
+        <f t="shared" si="0"/>
+        <v>0.30447272824064586</v>
       </c>
       <c r="D15" s="4">
-        <f>D$27*$B15/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <f>E$27*$B15/100</f>
-        <v>4317.8406310221062</v>
+        <f t="shared" si="0"/>
+        <v>4437.8663827420314</v>
       </c>
       <c r="F15" s="4">
-        <f>F$27*$B15/100</f>
-        <v>0.77611101194573906</v>
+        <f t="shared" si="0"/>
+        <v>0.79768506147355789</v>
       </c>
       <c r="G15" s="4">
-        <f>G$27*$B15/100</f>
-        <v>26281.305447431951</v>
+        <f t="shared" si="0"/>
+        <v>27011.863546275516</v>
       </c>
       <c r="H15" s="4">
-        <f>H$27*$B15/100</f>
-        <v>5930.2788315930575</v>
+        <f t="shared" si="0"/>
+        <v>6095.1265495835723</v>
       </c>
       <c r="I15" s="4">
-        <f>I$27*$B15/100</f>
-        <v>12075.573618317265</v>
+        <f t="shared" si="0"/>
+        <v>12411.245989032981</v>
       </c>
       <c r="J15" s="4">
-        <f>J$27*$B15/100</f>
-        <v>678.73848835157037</v>
+        <f t="shared" si="0"/>
+        <v>697.60581214771491</v>
       </c>
       <c r="K15" s="4">
-        <f>K$27*$B15/100</f>
-        <v>10.450869455483053</v>
+        <f t="shared" si="0"/>
+        <v>10.741378895203672</v>
       </c>
       <c r="L15" s="4">
-        <f>L$27*$B15/100</f>
-        <v>1032.0950047756896</v>
+        <f t="shared" si="0"/>
+        <v>1060.7848035386555</v>
       </c>
       <c r="M15" s="4">
-        <f>M$27*$B15/100</f>
-        <v>50377.624578135546</v>
+        <f t="shared" si="0"/>
+        <v>51778.003326811951</v>
       </c>
       <c r="N15" s="4">
-        <f>N$27*$B15/100</f>
-        <v>50.269338163948369</v>
+        <f t="shared" si="0"/>
+        <v>51.666706806561471</v>
       </c>
       <c r="P15" s="29">
         <v>0</v>
@@ -23498,8 +23731,8 @@
         <v>56433.215577499999</v>
       </c>
       <c r="T15" s="4">
-        <f t="shared" si="0"/>
-        <v>89.269456051023212</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255495</v>
       </c>
       <c r="V15" s="4"/>
     </row>
@@ -23508,55 +23741,55 @@
         <v>1895</v>
       </c>
       <c r="B16" s="26">
-        <v>89.260110871044688</v>
+        <v>90.877838490181389</v>
       </c>
       <c r="C16" s="4">
-        <f>C$27*$B16/100</f>
-        <v>0.25911625375063663</v>
+        <f t="shared" si="0"/>
+        <v>0.26381241103936365</v>
       </c>
       <c r="D16" s="4">
-        <f>D$27*$B16/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="4">
-        <f>E$27*$B16/100</f>
-        <v>3776.769493894179</v>
+        <f t="shared" si="0"/>
+        <v>3845.2187066697766</v>
       </c>
       <c r="F16" s="4">
-        <f>F$27*$B16/100</f>
-        <v>0.67885608670511433</v>
+        <f t="shared" si="0"/>
+        <v>0.69115950230884937</v>
       </c>
       <c r="G16" s="4">
-        <f>G$27*$B16/100</f>
-        <v>22987.97967679501</v>
+        <f t="shared" si="0"/>
+        <v>23404.607992269892</v>
       </c>
       <c r="H16" s="4">
-        <f>H$27*$B16/100</f>
-        <v>5187.1521196337571</v>
+        <f t="shared" si="0"/>
+        <v>5281.1627495411994</v>
       </c>
       <c r="I16" s="4">
-        <f>I$27*$B16/100</f>
-        <v>10562.376419191307</v>
+        <f t="shared" si="0"/>
+        <v>10753.806251512822</v>
       </c>
       <c r="J16" s="4">
-        <f>J$27*$B16/100</f>
-        <v>593.68537104419511</v>
+        <f t="shared" si="0"/>
+        <v>604.44517419078932</v>
       </c>
       <c r="K16" s="4">
-        <f>K$27*$B16/100</f>
-        <v>9.141264886100144</v>
+        <f t="shared" si="0"/>
+        <v>9.3069388532930954</v>
       </c>
       <c r="L16" s="4">
-        <f>L$27*$B16/100</f>
-        <v>902.76257554106905</v>
+        <f t="shared" si="0"/>
+        <v>919.12401558101783</v>
       </c>
       <c r="M16" s="4">
-        <f>M$27*$B16/100</f>
-        <v>44064.774951297135</v>
+        <f t="shared" si="0"/>
+        <v>44863.393760686064</v>
       </c>
       <c r="N16" s="4">
-        <f>N$27*$B16/100</f>
-        <v>43.970057971062396</v>
+        <f t="shared" si="0"/>
+        <v>44.766960153915313</v>
       </c>
       <c r="P16" s="29">
         <v>0</v>
@@ -23565,28 +23798,28 @@
         <v>48896.9332335</v>
       </c>
       <c r="T16" s="4">
-        <f t="shared" si="0"/>
-        <v>90.117665950280326</v>
+        <f t="shared" si="1"/>
+        <v>91.750935680255509</v>
       </c>
       <c r="V16" s="4"/>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="51"/>
+      <c r="A21" s="14"/>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
@@ -23594,56 +23827,56 @@
       </c>
       <c r="C23" s="4">
         <f>SUM(C2:C16)</f>
-        <v>2.8510004633740613</v>
+        <v>3.0745840087949561</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" ref="D23:N23" si="1">SUM(D2:D16)</f>
+        <f t="shared" ref="D23:N23" si="2">SUM(D2:D16)</f>
         <v>0</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="1"/>
-        <v>41554.983221977316</v>
+        <f t="shared" si="2"/>
+        <v>44813.842909316649</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" si="1"/>
-        <v>7.4693076553320132</v>
+        <f t="shared" si="2"/>
+        <v>8.0550719541712201</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="1"/>
-        <v>252931.80092688435</v>
+        <f t="shared" si="2"/>
+        <v>272767.43039360078</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>57073.120202253034</v>
+        <f t="shared" si="2"/>
+        <v>61548.956220866268</v>
       </c>
       <c r="I23" s="4">
-        <f t="shared" si="1"/>
-        <v>116215.55818889529</v>
+        <f t="shared" si="2"/>
+        <v>125329.51199800498</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" si="1"/>
-        <v>6532.1925716566257</v>
+        <f t="shared" si="2"/>
+        <v>7044.465646777272</v>
       </c>
       <c r="K23" s="4">
-        <f t="shared" si="1"/>
-        <v>100.57937334636426</v>
+        <f t="shared" si="2"/>
+        <v>108.46709317590728</v>
       </c>
       <c r="L23" s="4">
-        <f t="shared" si="1"/>
-        <v>9932.9026409175058</v>
+        <f t="shared" si="2"/>
+        <v>10711.869048432089</v>
       </c>
       <c r="M23" s="4">
-        <f t="shared" si="1"/>
-        <v>484835.25053400168</v>
+        <f t="shared" si="2"/>
+        <v>522857.40649364353</v>
       </c>
       <c r="N23" s="4">
-        <f t="shared" si="1"/>
-        <v>483.79309995243864</v>
+        <f t="shared" si="2"/>
+        <v>521.73352750660274</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -23727,7 +23960,7 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -23743,6 +23976,41 @@
       <c r="N29" s="4"/>
       <c r="P29" s="4"/>
     </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" s="4">
+        <f>SUM(M2:M4)</f>
+        <v>33681.078162898077</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="4">
+        <f>SUM(M7:M11)</f>
+        <v>188383.42896059956</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="4">
+        <f>SUM(M12:M16)</f>
+        <v>262364.058479678</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/rtss-pre1917/src/main/resources/emigration.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E078274-188C-4D37-AE00-10EACB0F6A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F18C200-0DFF-4DEB-8469-8F5FF1CE9944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="218">
   <si>
     <t>Источник: ЦСК, "Ежегодник России" ("Статистический Ежегодник России")</t>
   </si>
@@ -627,9 +627,6 @@
     <t>эмигрантов</t>
   </si>
   <si>
-    <t>Общая эмиграция из России по годам, с учётом реэмиграции, выдача EmigrationShowSum</t>
-  </si>
-  <si>
     <t>NBER, "International Migrations", Volume I : Statistics, сост. W. Willcox, New York, 1929, стр. 241-248 (table 11)</t>
   </si>
   <si>
@@ -713,6 +710,12 @@
   <si>
     <t>с учётом
 реэмиграции</t>
+  </si>
+  <si>
+    <t>v2</t>
+  </si>
+  <si>
+    <t>Общая эмиграция из России по годам, с учётом реэмиграции, выдача модуля RTSS EmigrationShowSum</t>
   </si>
 </sst>
 </file>
@@ -798,7 +801,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -905,9 +908,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1225,11 +1225,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E018E8-FFD2-476D-8A98-BDF34A70858D}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.578125" customWidth="1"/>
-    <col min="3" max="3" width="20.83984375" customWidth="1"/>
-    <col min="4" max="4" width="24.578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8">
+    <row r="5" spans="1:5" ht="30">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1801,14 +1801,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7496F63D-12C4-4F78-B39E-C61E39C373AD}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="10.41796875" customWidth="1"/>
-    <col min="5" max="5" width="12.41796875" customWidth="1"/>
-    <col min="6" max="6" width="27.15625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="43.2">
+    <row r="1" spans="1:20" ht="45">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -2445,35 +2445,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54424CF4-C226-4A4F-8C1B-D8A2CB8D4757}">
   <dimension ref="A1:AI310"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.578125" customWidth="1"/>
-    <col min="2" max="2" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.15625" customWidth="1"/>
-    <col min="4" max="4" width="7.578125" customWidth="1"/>
-    <col min="5" max="5" width="5.68359375" customWidth="1"/>
-    <col min="6" max="6" width="9.578125" customWidth="1"/>
-    <col min="7" max="7" width="8.15625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.68359375" customWidth="1"/>
-    <col min="9" max="9" width="7.578125" customWidth="1"/>
-    <col min="10" max="10" width="7.15625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.15625" customWidth="1"/>
-    <col min="13" max="13" width="6.83984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.41796875" customWidth="1"/>
-    <col min="17" max="17" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -17306,30 +17306,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
   <dimension ref="A1:N228"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.41796875" customWidth="1"/>
-    <col min="2" max="2" width="17.41796875" customWidth="1"/>
-    <col min="3" max="3" width="10.68359375" customWidth="1"/>
-    <col min="4" max="4" width="14.26171875" customWidth="1"/>
-    <col min="5" max="5" width="12.62890625" customWidth="1"/>
-    <col min="6" max="6" width="13.26171875" customWidth="1"/>
-    <col min="7" max="7" width="10.26171875" customWidth="1"/>
-    <col min="9" max="9" width="12.26171875" customWidth="1"/>
-    <col min="10" max="10" width="11.578125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="57.6">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60">
       <c r="A4" s="2" t="s">
         <v>117</v>
       </c>
@@ -17951,7 +17951,7 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -17966,7 +17966,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -18394,15 +18394,15 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="72">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="75">
       <c r="A42" s="2" t="s">
         <v>117</v>
       </c>
@@ -18413,13 +18413,13 @@
         <v>109</v>
       </c>
       <c r="D42" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="40" t="s">
         <v>209</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="F42" s="40" t="s">
-        <v>210</v>
       </c>
       <c r="G42" s="39" t="s">
         <v>110</v>
@@ -18902,7 +18902,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -18914,7 +18914,7 @@
       </c>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="52">
+      <c r="A60" s="1">
         <f t="shared" ref="A60:A73" si="23">A61-1</f>
         <v>1881</v>
       </c>
@@ -18923,7 +18923,7 @@
       </c>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="52">
+      <c r="A61" s="1">
         <f t="shared" si="23"/>
         <v>1882</v>
       </c>
@@ -18932,7 +18932,7 @@
       </c>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="52">
+      <c r="A62" s="1">
         <f t="shared" si="23"/>
         <v>1883</v>
       </c>
@@ -18941,7 +18941,7 @@
       </c>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="52">
+      <c r="A63" s="1">
         <f t="shared" si="23"/>
         <v>1884</v>
       </c>
@@ -18950,7 +18950,7 @@
       </c>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="52">
+      <c r="A64" s="1">
         <f t="shared" si="23"/>
         <v>1885</v>
       </c>
@@ -18959,7 +18959,7 @@
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="52">
+      <c r="A65" s="1">
         <f t="shared" si="23"/>
         <v>1886</v>
       </c>
@@ -18968,7 +18968,7 @@
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="52">
+      <c r="A66" s="1">
         <f t="shared" si="23"/>
         <v>1887</v>
       </c>
@@ -18977,7 +18977,7 @@
       </c>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="52">
+      <c r="A67" s="1">
         <f t="shared" si="23"/>
         <v>1888</v>
       </c>
@@ -18986,7 +18986,7 @@
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="52">
+      <c r="A68" s="1">
         <f t="shared" si="23"/>
         <v>1889</v>
       </c>
@@ -18995,7 +18995,7 @@
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="52">
+      <c r="A69" s="1">
         <f t="shared" si="23"/>
         <v>1890</v>
       </c>
@@ -19004,7 +19004,7 @@
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="52">
+      <c r="A70" s="1">
         <f t="shared" si="23"/>
         <v>1891</v>
       </c>
@@ -19013,7 +19013,7 @@
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="52">
+      <c r="A71" s="1">
         <f t="shared" si="23"/>
         <v>1892</v>
       </c>
@@ -19022,7 +19022,7 @@
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="52">
+      <c r="A72" s="1">
         <f t="shared" si="23"/>
         <v>1893</v>
       </c>
@@ -19031,7 +19031,7 @@
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="52">
+      <c r="A73" s="1">
         <f t="shared" si="23"/>
         <v>1894</v>
       </c>
@@ -19040,7 +19040,7 @@
       </c>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="52">
+      <c r="A74" s="1">
         <f>A75-1</f>
         <v>1895</v>
       </c>
@@ -19303,7 +19303,7 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="28.8">
+    <row r="104" spans="1:6" ht="45">
       <c r="A104" s="2" t="s">
         <v>117</v>
       </c>
@@ -19317,7 +19317,7 @@
         <v>189</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F104" s="38"/>
     </row>
@@ -19326,11 +19326,11 @@
         <v>119</v>
       </c>
       <c r="B105" s="4">
-        <f>K6</f>
+        <f t="shared" ref="B105:B112" si="24">K6</f>
         <v>27525</v>
       </c>
       <c r="C105" s="4">
-        <f>L43</f>
+        <f t="shared" ref="C105:C112" si="25">L43</f>
         <v>33658</v>
       </c>
       <c r="D105" s="26">
@@ -19344,11 +19344,11 @@
         <v>120</v>
       </c>
       <c r="B106" s="4">
-        <f>K7</f>
+        <f t="shared" si="24"/>
         <v>64393</v>
       </c>
       <c r="C106" s="4">
-        <f>L44</f>
+        <f t="shared" si="25"/>
         <v>69982</v>
       </c>
       <c r="D106" s="26">
@@ -19365,15 +19365,15 @@
         <v>121</v>
       </c>
       <c r="B107" s="4">
-        <f>K8</f>
+        <f t="shared" si="24"/>
         <v>223248</v>
       </c>
       <c r="C107" s="4">
-        <f>L45</f>
+        <f t="shared" si="25"/>
         <v>189850</v>
       </c>
       <c r="D107" s="26">
-        <f t="shared" ref="D107:D112" si="24">B107/C107*100</f>
+        <f t="shared" ref="D107:D112" si="26">B107/C107*100</f>
         <v>117.59178298656833</v>
       </c>
       <c r="E107" s="4">
@@ -19386,15 +19386,15 @@
         <v>122</v>
       </c>
       <c r="B108" s="4">
-        <f>K9</f>
+        <f t="shared" si="24"/>
         <v>279258</v>
       </c>
       <c r="C108" s="4">
-        <f>L46</f>
+        <f t="shared" si="25"/>
         <v>292574</v>
       </c>
       <c r="D108" s="26">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>95.448672814399089</v>
       </c>
       <c r="E108" s="4">
@@ -19407,15 +19407,15 @@
         <v>123</v>
       </c>
       <c r="B109" s="4">
-        <f>K10</f>
+        <f t="shared" si="24"/>
         <v>173914</v>
       </c>
       <c r="C109" s="4">
-        <f>L47</f>
+        <f t="shared" si="25"/>
         <v>246339</v>
       </c>
       <c r="D109" s="26">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>70.599458469832229</v>
       </c>
       <c r="E109" s="4">
@@ -19428,15 +19428,15 @@
         <v>124</v>
       </c>
       <c r="B110" s="4">
-        <f>K11</f>
+        <f t="shared" si="24"/>
         <v>340174</v>
       </c>
       <c r="C110" s="4">
-        <f>L48</f>
+        <f t="shared" si="25"/>
         <v>644531</v>
       </c>
       <c r="D110" s="26">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>52.778531986824525</v>
       </c>
       <c r="E110" s="4">
@@ -19449,15 +19449,15 @@
         <v>125</v>
       </c>
       <c r="B111" s="4">
-        <f>K12</f>
+        <f t="shared" si="24"/>
         <v>471971</v>
       </c>
       <c r="C111" s="4">
-        <f>L49</f>
+        <f t="shared" si="25"/>
         <v>986977</v>
       </c>
       <c r="D111" s="26">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>47.819858010875635</v>
       </c>
       <c r="E111" s="4">
@@ -19470,15 +19470,15 @@
         <v>126</v>
       </c>
       <c r="B112" s="4">
-        <f>K13</f>
+        <f t="shared" si="24"/>
         <v>409911</v>
       </c>
       <c r="C112" s="4">
-        <f>L50</f>
+        <f t="shared" si="25"/>
         <v>1010285</v>
       </c>
       <c r="D112" s="26">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>40.573798482606392</v>
       </c>
       <c r="E112" s="4">
@@ -19494,7 +19494,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -19502,96 +19502,96 @@
         <v>117</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="1" t="str">
-        <f>A43</f>
+        <f t="shared" ref="A117:A125" si="27">A43</f>
         <v>1876-1880</v>
       </c>
       <c r="B117" s="4">
-        <f>L43</f>
+        <f t="shared" ref="B117:B125" si="28">L43</f>
         <v>33658</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="1" t="str">
-        <f>A44</f>
+        <f t="shared" si="27"/>
         <v>1881-1885</v>
       </c>
       <c r="B118" s="4">
-        <f>L44</f>
+        <f t="shared" si="28"/>
         <v>69982</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="1" t="str">
-        <f>A45</f>
+        <f t="shared" si="27"/>
         <v>1886-1890</v>
       </c>
       <c r="B119" s="4">
-        <f>L45</f>
+        <f t="shared" si="28"/>
         <v>189850</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1" t="str">
-        <f>A46</f>
+        <f t="shared" si="27"/>
         <v>1891-1895</v>
       </c>
       <c r="B120" s="4">
-        <f>L46</f>
+        <f t="shared" si="28"/>
         <v>292574</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="1" t="str">
-        <f>A47</f>
+        <f t="shared" si="27"/>
         <v>1896-1900</v>
       </c>
       <c r="B121" s="4">
-        <f>L47</f>
+        <f t="shared" si="28"/>
         <v>246339</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1" t="str">
-        <f>A48</f>
+        <f t="shared" si="27"/>
         <v>1901-1905</v>
       </c>
       <c r="B122" s="4">
-        <f>L48</f>
+        <f t="shared" si="28"/>
         <v>644531</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="1" t="str">
-        <f>A49</f>
+        <f t="shared" si="27"/>
         <v>1906-1910</v>
       </c>
       <c r="B123" s="4">
-        <f>L49</f>
+        <f t="shared" si="28"/>
         <v>986977</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1" t="str">
-        <f>A50</f>
+        <f t="shared" si="27"/>
         <v>1911-1915</v>
       </c>
       <c r="B124" s="4">
-        <f>L50</f>
+        <f t="shared" si="28"/>
         <v>1010285</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="10" t="str">
-        <f>A51</f>
+        <f t="shared" si="27"/>
         <v>1896-1915</v>
       </c>
       <c r="B125" s="42">
-        <f>L51</f>
+        <f t="shared" si="28"/>
         <v>2888132</v>
       </c>
     </row>
@@ -19606,7 +19606,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -19614,7 +19614,7 @@
         <v>117</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -20010,7 +20010,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -20018,7 +20018,7 @@
         <v>117</v>
       </c>
       <c r="B176" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -20026,7 +20026,7 @@
         <v>1881</v>
       </c>
       <c r="B177" s="4">
-        <f t="shared" ref="B177:B210" si="25">(B135+B136) / 2</f>
+        <f t="shared" ref="B177:B210" si="29">(B135+B136) / 2</f>
         <v>9940.4968540000009</v>
       </c>
     </row>
@@ -20036,327 +20036,327 @@
         <v>1882</v>
       </c>
       <c r="B178" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>11990.335417</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="1">
-        <f t="shared" ref="A179:A210" si="26">A178+1</f>
+        <f t="shared" ref="A179:A210" si="30">A178+1</f>
         <v>1883</v>
       </c>
       <c r="B179" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>14778.415338499999</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1884</v>
       </c>
       <c r="B180" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>18460.160641499999</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1885</v>
       </c>
       <c r="B181" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>23423.707469000001</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1886</v>
       </c>
       <c r="B182" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>29118.518597000002</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1887</v>
       </c>
       <c r="B183" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>34851.308241500003</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1888</v>
       </c>
       <c r="B184" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>40792.354579000006</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1889</v>
       </c>
       <c r="B185" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>46922.072096999997</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1890</v>
       </c>
       <c r="B186" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>53636.190973500001</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1891</v>
       </c>
       <c r="B187" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>59075.304975500003</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1892</v>
       </c>
       <c r="B188" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>61231.720272500002</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1893</v>
       </c>
       <c r="B189" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>60315.286844500006</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1894</v>
       </c>
       <c r="B190" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>56433.215577499999</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1895</v>
       </c>
       <c r="B191" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>48896.9332335</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1896</v>
       </c>
       <c r="B192" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>42778.438797000003</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1897</v>
       </c>
       <c r="B193" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>42735.35224</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1898</v>
       </c>
       <c r="B194" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>47761.747051999999</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1899</v>
       </c>
       <c r="B195" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>58433.622705499998</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1900</v>
       </c>
       <c r="B196" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>77316.456703999997</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1901</v>
       </c>
       <c r="B197" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>99885.385118999999</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1902</v>
       </c>
       <c r="B198" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>120382.89023799999</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1903</v>
       </c>
       <c r="B199" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>139600.365777</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1904</v>
       </c>
       <c r="B200" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>157195.46720850002</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1905</v>
       </c>
       <c r="B201" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>173091.990059</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1906</v>
       </c>
       <c r="B202" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>186495.01287400001</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1907</v>
       </c>
       <c r="B203" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>196593.37489400001</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1908</v>
       </c>
       <c r="B204" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>203316.31396549998</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1909</v>
       </c>
       <c r="B205" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>206582.88415100001</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1910</v>
       </c>
       <c r="B206" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>205881.08261149999</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1911</v>
       </c>
       <c r="B207" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>203624.59460300001</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1912</v>
       </c>
       <c r="B208" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>202237.20285900001</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1913</v>
       </c>
       <c r="B209" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>201258.66536550003</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>1914</v>
       </c>
       <c r="B210" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>200701.38769050001</v>
       </c>
     </row>
@@ -20369,9 +20369,9 @@
         <v>269025.61749849998</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="28.8">
+    <row r="212" spans="1:6" ht="30">
       <c r="A212" s="45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B212" s="46">
         <f>B211/5</f>
@@ -20380,7 +20380,7 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B213" s="44"/>
       <c r="C213" s="41"/>
@@ -20403,137 +20403,137 @@
         <v>1882</v>
       </c>
       <c r="B215" s="26">
-        <f t="shared" ref="B215:B228" si="27">B178/B$212*100</f>
+        <f t="shared" ref="B215:B228" si="31">B178/B$212*100</f>
         <v>22.28474657634947</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="1">
-        <f t="shared" ref="A216:A228" si="28">A215+1</f>
+        <f t="shared" ref="A216:A228" si="32">A215+1</f>
         <v>1883</v>
       </c>
       <c r="B216" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>27.466557787163893</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1884</v>
       </c>
       <c r="B217" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>34.309298893446325</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1885</v>
       </c>
       <c r="B218" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>43.534343842051776</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1886</v>
       </c>
       <c r="B219" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>54.118486684938759</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1887</v>
       </c>
       <c r="B220" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>64.77321484392526</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1888</v>
       </c>
       <c r="B221" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>75.815000367441684</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1889</v>
       </c>
       <c r="B222" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>87.207442423697103</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1890</v>
       </c>
       <c r="B223" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>99.686028922132408</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1891</v>
       </c>
       <c r="B224" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>109.79494355371079</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1892</v>
       </c>
       <c r="B225" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>113.80276875090047</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1893</v>
       </c>
       <c r="B226" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>112.09952309622764</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1894</v>
       </c>
       <c r="B227" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>104.88446435368679</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>1895</v>
       </c>
       <c r="B228" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>90.877838490181389</v>
       </c>
     </row>
@@ -20546,14 +20546,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D506FF2-5C72-4314-9474-BB1C48673607}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.68359375" customWidth="1"/>
-    <col min="3" max="3" width="18.83984375" customWidth="1"/>
-    <col min="4" max="4" width="13.83984375" customWidth="1"/>
-    <col min="5" max="5" width="16.83984375" customWidth="1"/>
-    <col min="7" max="7" width="13.26171875" customWidth="1"/>
-    <col min="8" max="8" width="16.41796875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -21350,12 +21350,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.83984375" customWidth="1"/>
-    <col min="11" max="11" width="13.578125" customWidth="1"/>
-    <col min="15" max="15" width="26.68359375" customWidth="1"/>
-    <col min="16" max="16" width="19.83984375" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -22374,12 +22374,12 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="47" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F26" s="4"/>
       <c r="L26" s="4"/>
@@ -22387,12 +22387,12 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -22507,7 +22507,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -22737,13 +22737,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FEA9BB-FB24-45B6-A20A-F26B22290AE7}">
-  <dimension ref="A1:V34"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:W34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="16" max="16" width="25.05078125" customWidth="1"/>
+    <col min="16" max="16" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
@@ -22790,15 +22790,17 @@
         <v>169</v>
       </c>
       <c r="R1" s="50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T1" s="50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="V1" s="50" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="1">
         <v>1881</v>
       </c>
@@ -22863,9 +22865,13 @@
         <f>M2/R2*100</f>
         <v>91.750935680255481</v>
       </c>
-      <c r="V2" s="4"/>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="V2" s="4">
+        <f>SUM(C2:L2)+N2-M2</f>
+        <v>0</v>
+      </c>
+      <c r="W2" s="4"/>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" s="1">
         <v>1882</v>
       </c>
@@ -22930,9 +22936,12 @@
         <f t="shared" ref="T3:T16" si="1">M3/R3*100</f>
         <v>91.750935680255495</v>
       </c>
-      <c r="V3" s="4"/>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4"/>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" s="1">
         <v>1883</v>
       </c>
@@ -22997,9 +23006,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255509</v>
       </c>
-      <c r="V4" s="4"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4"/>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" s="1">
         <v>1884</v>
       </c>
@@ -23064,9 +23076,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255509</v>
       </c>
-      <c r="V5" s="4"/>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="V5" s="4">
+        <v>0</v>
+      </c>
+      <c r="W5" s="4"/>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" s="1">
         <v>1885</v>
       </c>
@@ -23131,9 +23146,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255495</v>
       </c>
-      <c r="V6" s="4"/>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" s="1">
         <v>1886</v>
       </c>
@@ -23198,9 +23216,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255481</v>
       </c>
-      <c r="V7" s="4"/>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" s="1">
         <v>1887</v>
       </c>
@@ -23265,9 +23286,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255481</v>
       </c>
-      <c r="V8" s="4"/>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9" s="1">
         <v>1888</v>
       </c>
@@ -23332,9 +23356,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255481</v>
       </c>
-      <c r="V9" s="4"/>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="V9" s="4">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" s="1">
         <v>1889</v>
       </c>
@@ -23399,9 +23426,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255481</v>
       </c>
-      <c r="V10" s="4"/>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="V10" s="4">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" s="1">
         <v>1890</v>
       </c>
@@ -23466,9 +23496,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255481</v>
       </c>
-      <c r="V11" s="4"/>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="V11" s="4">
+        <v>0</v>
+      </c>
+      <c r="W11" s="4"/>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" s="1">
         <v>1891</v>
       </c>
@@ -23533,9 +23566,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255495</v>
       </c>
-      <c r="V12" s="4"/>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="V12" s="4">
+        <v>0</v>
+      </c>
+      <c r="W12" s="4"/>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" s="1">
         <v>1892</v>
       </c>
@@ -23600,9 +23636,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255481</v>
       </c>
-      <c r="V13" s="4"/>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="V13" s="4">
+        <v>0</v>
+      </c>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" s="1">
         <v>1893</v>
       </c>
@@ -23667,9 +23706,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255495</v>
       </c>
-      <c r="V14" s="4"/>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="V14" s="4">
+        <v>0</v>
+      </c>
+      <c r="W14" s="4"/>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="1">
         <v>1894</v>
       </c>
@@ -23734,9 +23776,12 @@
         <f t="shared" si="1"/>
         <v>91.750935680255495</v>
       </c>
-      <c r="V15" s="4"/>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="1">
         <v>1895</v>
       </c>
@@ -23801,21 +23846,24 @@
         <f t="shared" si="1"/>
         <v>91.750935680255509</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4"/>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="47" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -23876,7 +23924,7 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -23960,7 +24008,7 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>

--- a/rtss-pre1917/src/main/resources/emigration.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F18C200-0DFF-4DEB-8469-8F5FF1CE9944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7ED293A-9297-42E9-8CB3-E337FE69082E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="64470" yWindow="3165" windowWidth="38700" windowHeight="17415" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -1225,11 +1225,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E018E8-FFD2-476D-8A98-BDF34A70858D}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.578125" customWidth="1"/>
+    <col min="3" max="3" width="20.83984375" customWidth="1"/>
+    <col min="4" max="4" width="24.578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5" ht="28.8">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1801,14 +1801,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7496F63D-12C4-4F78-B39E-C61E39C373AD}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.41796875" customWidth="1"/>
+    <col min="5" max="5" width="12.41796875" customWidth="1"/>
+    <col min="6" max="6" width="27.15625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45">
+    <row r="1" spans="1:20" ht="43.2">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -2445,35 +2445,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54424CF4-C226-4A4F-8C1B-D8A2CB8D4757}">
   <dimension ref="A1:AI310"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.578125" customWidth="1"/>
+    <col min="2" max="2" width="7.26171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.15625" customWidth="1"/>
+    <col min="4" max="4" width="7.578125" customWidth="1"/>
+    <col min="5" max="5" width="5.68359375" customWidth="1"/>
+    <col min="6" max="6" width="9.578125" customWidth="1"/>
+    <col min="7" max="7" width="8.15625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.68359375" customWidth="1"/>
+    <col min="9" max="9" width="7.578125" customWidth="1"/>
+    <col min="10" max="10" width="7.15625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.42578125" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.15625" customWidth="1"/>
+    <col min="13" max="13" width="6.83984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.41796875" customWidth="1"/>
+    <col min="17" max="17" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -17306,17 +17306,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
   <dimension ref="A1:N228"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.41796875" customWidth="1"/>
+    <col min="2" max="2" width="17.41796875" customWidth="1"/>
+    <col min="3" max="3" width="10.68359375" customWidth="1"/>
+    <col min="4" max="4" width="14.26171875" customWidth="1"/>
+    <col min="5" max="5" width="12.578125" customWidth="1"/>
+    <col min="6" max="6" width="13.26171875" customWidth="1"/>
+    <col min="7" max="7" width="10.26171875" customWidth="1"/>
+    <col min="9" max="9" width="12.26171875" customWidth="1"/>
+    <col min="10" max="10" width="11.578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -17329,7 +17329,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="60">
+    <row r="4" spans="1:11" ht="57.6">
       <c r="A4" s="2" t="s">
         <v>117</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="75">
+    <row r="42" spans="1:14" ht="72">
       <c r="A42" s="2" t="s">
         <v>117</v>
       </c>
@@ -18921,6 +18921,8 @@
       <c r="B60" s="4">
         <v>9121</v>
       </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
@@ -18930,6 +18932,8 @@
       <c r="B61" s="4">
         <v>11000</v>
       </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
@@ -18939,6 +18943,8 @@
       <c r="B62" s="4">
         <v>13560</v>
       </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
@@ -18948,6 +18954,8 @@
       <c r="B63" s="4">
         <v>16938</v>
       </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
@@ -18957,6 +18965,8 @@
       <c r="B64" s="4">
         <v>21491</v>
       </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="1">
@@ -18966,6 +18976,8 @@
       <c r="B65" s="4">
         <v>26717</v>
       </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="1">
@@ -18975,6 +18987,8 @@
       <c r="B66" s="4">
         <v>31977</v>
       </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1">
@@ -18984,6 +18998,8 @@
       <c r="B67" s="4">
         <v>37427</v>
       </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1">
@@ -18993,6 +19009,8 @@
       <c r="B68" s="4">
         <v>43051</v>
       </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1">
@@ -19002,6 +19020,8 @@
       <c r="B69" s="4">
         <v>49211</v>
       </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1">
@@ -19011,6 +19031,8 @@
       <c r="B70" s="4">
         <v>54201</v>
       </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="1">
@@ -19020,6 +19042,8 @@
       <c r="B71" s="4">
         <v>56181</v>
       </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1">
@@ -19029,6 +19053,8 @@
       <c r="B72" s="4">
         <v>55339</v>
       </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1">
@@ -19038,6 +19064,8 @@
       <c r="B73" s="4">
         <v>51779</v>
       </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1">
@@ -19047,6 +19075,8 @@
       <c r="B74" s="4">
         <v>44863</v>
       </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1">
@@ -19056,6 +19086,7 @@
         <v>35639</v>
       </c>
       <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
       <c r="G75" s="4"/>
     </row>
     <row r="76" spans="1:7">
@@ -19066,6 +19097,7 @@
         <v>28021</v>
       </c>
       <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
       <c r="G76" s="4"/>
     </row>
     <row r="77" spans="1:7">
@@ -19076,6 +19108,7 @@
         <v>41907</v>
       </c>
       <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
       <c r="G77" s="4"/>
     </row>
     <row r="78" spans="1:7">
@@ -19086,6 +19119,7 @@
         <v>65559</v>
       </c>
       <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
       <c r="G78" s="4"/>
     </row>
     <row r="79" spans="1:7">
@@ -19096,6 +19130,7 @@
         <v>76085</v>
       </c>
       <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
       <c r="G79" s="4"/>
     </row>
     <row r="80" spans="1:7">
@@ -19106,6 +19141,7 @@
         <v>83166</v>
       </c>
       <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
       <c r="G80" s="4"/>
     </row>
     <row r="81" spans="1:7">
@@ -19116,6 +19152,7 @@
         <v>103114</v>
       </c>
       <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
       <c r="G81" s="4"/>
     </row>
     <row r="82" spans="1:7">
@@ -19126,6 +19163,7 @@
         <v>125022</v>
       </c>
       <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
       <c r="G82" s="4"/>
     </row>
     <row r="83" spans="1:7">
@@ -19136,6 +19174,7 @@
         <v>151739</v>
       </c>
       <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
       <c r="G83" s="4"/>
     </row>
     <row r="84" spans="1:7">
@@ -19146,6 +19185,7 @@
         <v>186157</v>
       </c>
       <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
       <c r="G84" s="4"/>
     </row>
     <row r="85" spans="1:7">
@@ -19156,6 +19196,7 @@
         <v>221400</v>
       </c>
       <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
       <c r="G85" s="4"/>
     </row>
     <row r="86" spans="1:7">
@@ -19166,6 +19207,7 @@
         <v>186071</v>
       </c>
       <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
       <c r="G86" s="4"/>
     </row>
     <row r="87" spans="1:7">
@@ -19176,6 +19218,7 @@
         <v>119541</v>
       </c>
       <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
       <c r="G87" s="4"/>
     </row>
     <row r="88" spans="1:7">
@@ -19186,6 +19229,7 @@
         <v>141698</v>
       </c>
       <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
       <c r="G88" s="4"/>
     </row>
     <row r="89" spans="1:7">
@@ -19196,6 +19240,7 @@
         <v>162676</v>
       </c>
       <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
       <c r="G89" s="4"/>
     </row>
     <row r="90" spans="1:7">
@@ -19206,6 +19251,7 @@
         <v>144660</v>
       </c>
       <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
       <c r="G90" s="4"/>
     </row>
     <row r="91" spans="1:7">
@@ -19216,6 +19262,7 @@
         <v>217990</v>
       </c>
       <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
       <c r="G91" s="4"/>
     </row>
     <row r="92" spans="1:7">
@@ -19226,6 +19273,7 @@
         <v>261265</v>
       </c>
       <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
       <c r="G92" s="4"/>
     </row>
     <row r="93" spans="1:7">
@@ -19236,6 +19284,7 @@
         <v>119358</v>
       </c>
       <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
       <c r="G93" s="4"/>
     </row>
     <row r="94" spans="1:7">
@@ -19246,6 +19295,7 @@
         <v>3880</v>
       </c>
       <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
       <c r="G94" s="4"/>
     </row>
     <row r="95" spans="1:7">
@@ -19256,6 +19306,7 @@
         <v>2305</v>
       </c>
       <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
       <c r="G95" s="4"/>
     </row>
     <row r="96" spans="1:7">
@@ -19303,7 +19354,7 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="45">
+    <row r="104" spans="1:6" ht="28.8">
       <c r="A104" s="2" t="s">
         <v>117</v>
       </c>
@@ -20369,7 +20420,7 @@
         <v>269025.61749849998</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="30">
+    <row r="212" spans="1:6" ht="28.8">
       <c r="A212" s="45" t="s">
         <v>199</v>
       </c>
@@ -20546,14 +20597,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D506FF2-5C72-4314-9474-BB1C48673607}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.68359375" customWidth="1"/>
+    <col min="3" max="3" width="18.83984375" customWidth="1"/>
+    <col min="4" max="4" width="13.83984375" customWidth="1"/>
+    <col min="5" max="5" width="16.83984375" customWidth="1"/>
+    <col min="7" max="7" width="13.26171875" customWidth="1"/>
+    <col min="8" max="8" width="16.41796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -21350,12 +21401,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
-    <col min="15" max="15" width="26.7109375" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.83984375" customWidth="1"/>
+    <col min="11" max="11" width="13.578125" customWidth="1"/>
+    <col min="15" max="15" width="26.68359375" customWidth="1"/>
+    <col min="16" max="16" width="19.83984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -22738,7 +22789,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FEA9BB-FB24-45B6-A20A-F26B22290AE7}">
   <dimension ref="A1:W34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="16" max="16" width="25" customWidth="1"/>
   </cols>

--- a/rtss-pre1917/src/main/resources/emigration.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7ED293A-9297-42E9-8CB3-E337FE69082E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005BBD72-976C-43A0-B25D-B91E90D99726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="64470" yWindow="3165" windowWidth="38700" windowHeight="17415" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -325,9 +325,6 @@
   </si>
   <si>
     <t>Разбивка по народностям иммигрантов из Россси в США в финансовый год заканчивающийся 30 июня YYYY.</t>
-  </si>
-  <si>
-    <t>Для 1896-1899 гг. разбивка расчитана исходя из общего числа иммигрантов из России в США в данный год, в предположении,</t>
   </si>
   <si>
     <t>-нет-</t>
@@ -716,6 +713,9 @@
   </si>
   <si>
     <t>Общая эмиграция из России по годам, с учётом реэмиграции, выдача модуля RTSS EmigrationShowSum</t>
+  </si>
+  <si>
+    <t>Для 1896-1898 гг. разбивка расчитана исходя из общего числа иммигрантов из России в США в данный год, в предположении,</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="2:2">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="2:2">
@@ -1468,7 +1468,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1499,7 +1499,7 @@
         <v>1896</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1508,7 +1508,7 @@
         <v>1897</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1517,7 +1517,7 @@
         <v>1898</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1692,17 +1692,17 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1710,7 +1710,7 @@
         <v>1908</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1719,7 +1719,7 @@
         <v>1909</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1728,7 +1728,7 @@
         <v>1910</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1737,7 +1737,7 @@
         <v>1911</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1746,7 +1746,7 @@
         <v>1912</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1755,7 +1755,7 @@
         <v>1913</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1764,7 +1764,7 @@
         <v>1914</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1773,7 +1773,7 @@
         <v>1915</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1782,7 +1782,7 @@
         <v>1916</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="97" spans="2:3">
@@ -1790,7 +1790,7 @@
         <v>1917</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1834,19 +1834,19 @@
         <v>51</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q1" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="S1" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="R1" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="S1" s="20" t="s">
+      <c r="T1" s="20" t="s">
         <v>104</v>
-      </c>
-      <c r="T1" s="20" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -1873,7 +1873,7 @@
         <v>48240</v>
       </c>
       <c r="J2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P2" s="1">
         <v>1896</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="5" spans="1:35">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -2501,7 +2501,7 @@
         <v>83</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2578,46 +2578,46 @@
         <v>81</v>
       </c>
       <c r="P10" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="Q10" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="S10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="T10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="T10" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="V10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="W10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="W10" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="Y10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="Z10" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="AB10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AC10" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="AE10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AF10" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="AH10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI10" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="AI10" s="10" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -4840,7 +4840,7 @@
         <v>81</v>
       </c>
       <c r="O40" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -6171,7 +6171,7 @@
     </row>
     <row r="66" spans="1:19">
       <c r="A66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -6524,13 +6524,13 @@
         <v>78</v>
       </c>
       <c r="P76" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q76" t="s">
         <v>175</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="R76" t="s">
         <v>176</v>
-      </c>
-      <c r="R76" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -6610,12 +6610,12 @@
         <v>8961.6344491243617</v>
       </c>
       <c r="S78" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:19">
       <c r="A80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -7037,7 +7037,7 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7080,7 +7080,7 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B97" s="4">
         <f t="shared" ref="B97:M97" si="43">SUM(B83:B92)</f>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B98" s="4">
         <f t="shared" ref="B98:M98" si="44">SUM(B69:B78)</f>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B99" s="26">
         <f>100*B98/B97</f>
@@ -7253,7 +7253,7 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B101" s="26"/>
       <c r="C101" s="26"/>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B104" s="4">
         <f>SUM(B83:B89)</f>
@@ -7375,7 +7375,7 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B105" s="4">
         <f>SUM(B69:B75)</f>
@@ -7428,7 +7428,7 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B106" s="26">
         <f>100*B105/B104</f>
@@ -7495,7 +7495,7 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B108" s="26"/>
       <c r="C108" s="26"/>
@@ -7512,7 +7512,7 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B109" s="26"/>
       <c r="C109" s="26"/>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="114" spans="1:16">
       <c r="A114" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7675,10 +7675,10 @@
         <v>81</v>
       </c>
       <c r="O116" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P116" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8895,7 +8895,7 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -9139,7 +9139,7 @@
     </row>
     <row r="150" spans="1:15">
       <c r="A150" s="30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -10528,7 +10528,7 @@
     </row>
     <row r="176" spans="1:15">
       <c r="A176" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10572,7 +10572,7 @@
         <v>81</v>
       </c>
       <c r="O178" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11863,7 +11863,7 @@
     </row>
     <row r="202" spans="1:15">
       <c r="A202" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="204" spans="1:15">
@@ -11907,7 +11907,7 @@
         <v>81</v>
       </c>
       <c r="O204" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="205" spans="1:15">
@@ -13238,7 +13238,7 @@
     </row>
     <row r="229" spans="1:15">
       <c r="A229" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="230" spans="1:15">
@@ -13246,7 +13246,7 @@
     </row>
     <row r="231" spans="1:15">
       <c r="A231" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G231">
         <v>89</v>
@@ -13297,7 +13297,7 @@
         <v>81</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="234" spans="1:15">
@@ -14575,12 +14575,12 @@
     </row>
     <row r="257" spans="1:17">
       <c r="A257" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="259" spans="1:17">
       <c r="A259" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B259" s="10" t="s">
         <v>70</v>
@@ -14695,7 +14695,7 @@
         <v>81</v>
       </c>
       <c r="O262" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="263" spans="1:17">
@@ -15974,7 +15974,7 @@
     </row>
     <row r="286" spans="1:15">
       <c r="A286" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="288" spans="1:15">
@@ -16018,7 +16018,7 @@
         <v>81</v>
       </c>
       <c r="O288" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="289" spans="1:15">
@@ -17321,44 +17321,44 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="57.6">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>80</v>
@@ -17366,7 +17366,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4">
         <v>4339</v>
@@ -17401,7 +17401,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B6" s="4">
         <v>20056</v>
@@ -17436,7 +17436,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4">
         <v>184</v>
@@ -17471,7 +17471,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" s="4">
         <v>1951</v>
@@ -17506,7 +17506,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B9" s="4">
         <v>7227</v>
@@ -17541,7 +17541,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B10" s="4">
         <v>1594</v>
@@ -17576,7 +17576,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" s="4">
         <v>2787</v>
@@ -17611,7 +17611,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12" s="4">
         <v>3292</v>
@@ -17646,7 +17646,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4">
         <v>24693</v>
@@ -17681,7 +17681,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" s="12">
         <f t="shared" ref="B14:K14" si="0">SUM(B5:B13)</f>
@@ -17726,7 +17726,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" s="23">
         <f t="shared" ref="B15" si="1">100*B14/$K14</f>
@@ -17771,7 +17771,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B16" s="17">
         <f t="shared" ref="B16:K16" si="11">SUM(B10:B13)</f>
@@ -17816,7 +17816,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B17" s="25">
         <f>100*B16/$K16</f>
@@ -17861,7 +17861,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B18" s="34">
         <f t="shared" ref="B18:K18" si="12">SUM(B7:B9)</f>
@@ -17906,7 +17906,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" s="35">
         <f t="shared" ref="B19:K19" si="13">B18/$K18*100</f>
@@ -17951,7 +17951,7 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -17966,7 +17966,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -17993,28 +17993,28 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B25" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="C25" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="37" t="s">
+      <c r="G25" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="G25" s="37" t="s">
+      <c r="H25" s="37" t="s">
         <v>150</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>151</v>
       </c>
       <c r="I25" s="37" t="s">
         <v>80</v>
@@ -18024,7 +18024,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
@@ -18048,7 +18048,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4">
@@ -18074,7 +18074,7 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
@@ -18100,7 +18100,7 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
@@ -18126,7 +18126,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
@@ -18155,7 +18155,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="4">
         <v>12995</v>
@@ -18188,7 +18188,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B32" s="4">
         <v>26337</v>
@@ -18219,7 +18219,7 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="4">
         <v>58290</v>
@@ -18252,7 +18252,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B34" s="12">
         <f>SUM(B30:B33)</f>
@@ -18336,7 +18336,7 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" s="34"/>
       <c r="C36" s="34">
@@ -18394,47 +18394,47 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="72">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B42" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H42" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="I42" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="C42" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="F42" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="G42" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="H42" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="I42" s="39" t="s">
+      <c r="J42" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="J42" s="39" t="s">
+      <c r="K42" s="39" t="s">
         <v>150</v>
-      </c>
-      <c r="K42" s="39" t="s">
-        <v>151</v>
       </c>
       <c r="L42" s="39" t="s">
         <v>80</v>
@@ -18442,7 +18442,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
@@ -18475,7 +18475,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
@@ -18510,7 +18510,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
@@ -18545,7 +18545,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
@@ -18580,7 +18580,7 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
@@ -18615,7 +18615,7 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B48" s="4">
         <v>12995</v>
@@ -18652,7 +18652,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B49" s="4">
         <v>26337</v>
@@ -18687,7 +18687,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B50" s="4">
         <v>58290</v>
@@ -18724,7 +18724,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B51" s="12">
         <f>SUM(B47:B50)</f>
@@ -18813,7 +18813,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B53" s="34">
         <f t="shared" ref="B53:K53" si="21">SUM(B44:B46)</f>
@@ -18902,7 +18902,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -18910,7 +18910,7 @@
         <v>19</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -19320,7 +19320,7 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B97" s="4">
         <f>SUM(B75:B79)</f>
@@ -19329,7 +19329,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B98" s="4">
         <f>SUM(B80:B84)</f>
@@ -19338,7 +19338,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B99" s="4">
         <f>SUM(B85:B89)</f>
@@ -19347,7 +19347,7 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B100" s="4">
         <f>SUM(B90:B94)</f>
@@ -19356,25 +19356,25 @@
     </row>
     <row r="104" spans="1:6" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="E104" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F104" s="38"/>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B105" s="4">
         <f t="shared" ref="B105:B112" si="24">K6</f>
@@ -19392,7 +19392,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B106" s="4">
         <f t="shared" si="24"/>
@@ -19413,7 +19413,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B107" s="4">
         <f t="shared" si="24"/>
@@ -19434,7 +19434,7 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B108" s="4">
         <f t="shared" si="24"/>
@@ -19455,7 +19455,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B109" s="4">
         <f t="shared" si="24"/>
@@ -19476,7 +19476,7 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B110" s="4">
         <f t="shared" si="24"/>
@@ -19497,7 +19497,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B111" s="4">
         <f t="shared" si="24"/>
@@ -19518,7 +19518,7 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B112" s="4">
         <f t="shared" si="24"/>
@@ -19545,15 +19545,15 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B116" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -19648,7 +19648,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B126" s="42">
         <f>SUM(B117:B124)</f>
@@ -19657,15 +19657,15 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -20030,7 +20030,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B170" s="4">
         <f>SUM(B150:B169)</f>
@@ -20039,7 +20039,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B171" s="4">
         <f>SUM(B130:B169)</f>
@@ -20048,7 +20048,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B172" s="4">
         <f>SUM(B135:B149)</f>
@@ -20061,15 +20061,15 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B176" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -20413,7 +20413,7 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B211" s="42">
         <f>SUM(B192:B196)</f>
@@ -20422,7 +20422,7 @@
     </row>
     <row r="212" spans="1:6" ht="28.8">
       <c r="A212" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B212" s="46">
         <f>B211/5</f>
@@ -20431,7 +20431,7 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="41" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B213" s="44"/>
       <c r="C213" s="41"/>
@@ -20609,27 +20609,27 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="B5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -20637,7 +20637,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -20645,7 +20645,7 @@
         <v>1908</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20653,7 +20653,7 @@
         <v>1917</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -20666,15 +20666,15 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="51" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" s="51"/>
       <c r="D14" s="51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E14" s="51"/>
       <c r="G14" s="51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H14" s="51"/>
     </row>
@@ -20683,25 +20683,25 @@
         <v>19</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>165</v>
-      </c>
       <c r="D15" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E15" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>165</v>
-      </c>
       <c r="G15" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H15" s="14" t="s">
-        <v>165</v>
-      </c>
       <c r="J15" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -21450,7 +21450,7 @@
         <v>81</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P1" s="10"/>
     </row>
@@ -22425,12 +22425,12 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F26" s="4"/>
       <c r="L26" s="4"/>
@@ -22438,12 +22438,12 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -22489,7 +22489,7 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" ref="B31:M31" si="0">AVERAGE(B2:B6)</f>
@@ -22558,7 +22558,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -22618,7 +22618,7 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B35" s="4">
         <f>B31</f>
@@ -22739,7 +22739,7 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>80</v>
@@ -22747,7 +22747,7 @@
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B40" s="4">
         <f>SUM(L2:L6)</f>
@@ -22756,7 +22756,7 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B41" s="4">
         <f>SUM(L7:L11)</f>
@@ -22765,7 +22765,7 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="4">
         <f>SUM(L12:L16)</f>
@@ -22774,7 +22774,7 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43" s="4">
         <f>SUM(L17:L22)</f>
@@ -22838,17 +22838,17 @@
         <v>81</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R1" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="T1" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U1" s="10"/>
       <c r="V1" s="50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -23904,17 +23904,17 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -23922,7 +23922,7 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="4">
         <f>SUM(C2:C16)</f>
@@ -23975,7 +23975,7 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -24018,7 +24018,7 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C27" s="4">
         <v>0.29029344824026204</v>
@@ -24059,7 +24059,7 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -24077,7 +24077,7 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>80</v>
@@ -24085,7 +24085,7 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B32" s="4">
         <f>SUM(M2:M4)</f>
@@ -24094,7 +24094,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" s="4">
         <f>SUM(M7:M11)</f>
@@ -24103,7 +24103,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B34" s="4">
         <f>SUM(M12:M16)</f>

--- a/rtss-pre1917/src/main/resources/emigration.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005BBD72-976C-43A0-B25D-B91E90D99726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADABBDF4-79E4-4BD0-86D1-92ECE85C572A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="165" yWindow="1530" windowWidth="29775" windowHeight="21255" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="data-1896-1916" sheetId="4" r:id="rId6"/>
     <sheet name="data-1881-1895" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,12 +29,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -727,7 +722,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -928,9 +923,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -968,7 +963,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1074,7 +1069,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1216,7 +1211,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1225,24 +1220,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E018E8-FFD2-476D-8A98-BDF34A70858D}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.578125" customWidth="1"/>
-    <col min="3" max="3" width="20.83984375" customWidth="1"/>
-    <col min="4" max="4" width="24.578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1254,7 +1249,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>1904</v>
       </c>
@@ -1265,7 +1260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>1906</v>
       </c>
@@ -1276,7 +1271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>1909</v>
       </c>
@@ -1287,7 +1282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>1910</v>
       </c>
@@ -1298,7 +1293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>1911</v>
       </c>
@@ -1309,7 +1304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>1912</v>
       </c>
@@ -1320,7 +1315,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>1913</v>
       </c>
@@ -1331,162 +1326,162 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>53</v>
       </c>
@@ -1494,7 +1489,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B60" s="1">
         <v>1896</v>
       </c>
@@ -1502,7 +1497,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B61" s="1">
         <f>B60+1</f>
         <v>1897</v>
@@ -1511,7 +1506,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B62" s="1">
         <f t="shared" ref="B62:B80" si="0">B61+1</f>
         <v>1898</v>
@@ -1520,7 +1515,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B63" s="1">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -1529,7 +1524,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B64" s="1">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -1538,7 +1533,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="2:3">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -1547,7 +1542,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="2:3">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -1556,7 +1551,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="2:3">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="1">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -1565,7 +1560,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="2:3">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="1">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -1574,7 +1569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="2:3">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="1">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -1583,7 +1578,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="2:3">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="1">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -1592,7 +1587,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="2:3">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="1">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -1601,7 +1596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="2:3">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="1">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -1610,7 +1605,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="2:3">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="1">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -1619,7 +1614,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="2:3">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="1">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -1628,7 +1623,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="2:3">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="1">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -1637,7 +1632,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="2:3">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="1">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -1646,7 +1641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="2:3">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="1">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -1655,7 +1650,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="78" spans="2:3">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="1">
         <f t="shared" si="0"/>
         <v>1914</v>
@@ -1664,7 +1659,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="79" spans="2:3">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="1">
         <f t="shared" si="0"/>
         <v>1915</v>
@@ -1673,7 +1668,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="2:3">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="1">
         <f t="shared" si="0"/>
         <v>1916</v>
@@ -1682,7 +1677,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B81" s="1">
         <v>1917</v>
       </c>
@@ -1690,22 +1685,22 @@
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B88" s="1">
         <v>1908</v>
       </c>
@@ -1713,7 +1708,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B89" s="1">
         <f t="shared" ref="B89:B96" si="1">B88+1</f>
         <v>1909</v>
@@ -1722,7 +1717,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B90" s="1">
         <f t="shared" si="1"/>
         <v>1910</v>
@@ -1731,7 +1726,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B91" s="1">
         <f t="shared" si="1"/>
         <v>1911</v>
@@ -1740,7 +1735,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B92" s="1">
         <f t="shared" si="1"/>
         <v>1912</v>
@@ -1749,7 +1744,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B93" s="1">
         <f t="shared" si="1"/>
         <v>1913</v>
@@ -1758,7 +1753,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B94" s="1">
         <f t="shared" si="1"/>
         <v>1914</v>
@@ -1767,7 +1762,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B95" s="1">
         <f t="shared" si="1"/>
         <v>1915</v>
@@ -1776,7 +1771,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B96" s="1">
         <f t="shared" si="1"/>
         <v>1916</v>
@@ -1785,7 +1780,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="97" spans="2:3">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="1">
         <v>1917</v>
       </c>
@@ -1801,14 +1796,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7496F63D-12C4-4F78-B39E-C61E39C373AD}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.41796875" customWidth="1"/>
-    <col min="5" max="5" width="12.41796875" customWidth="1"/>
-    <col min="6" max="6" width="27.15625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="43.2">
+    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -1849,7 +1844,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1896</v>
       </c>
@@ -1892,7 +1887,7 @@
         <v>52136</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>1897</v>
@@ -1934,7 +1929,7 @@
         <v>29981</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A22" si="3">A3+1</f>
         <v>1898</v>
@@ -1976,7 +1971,7 @@
         <v>34554</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -2000,7 +1995,7 @@
         <v>57773.68421052632</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -2024,7 +2019,7 @@
         <v>82289.473684210534</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -2048,7 +2043,7 @@
         <v>79218.947368421053</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -2072,7 +2067,7 @@
         <v>98398.947368421053</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -2096,7 +2091,7 @@
         <v>123398.94736842105</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -2120,7 +2115,7 @@
         <v>142088.42105263157</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -2144,7 +2139,7 @@
         <v>176721.05263157896</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -2168,7 +2163,7 @@
         <v>212135.78947368421</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -2192,7 +2187,7 @@
         <v>256929.47368421053</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -2216,7 +2211,7 @@
         <v>157857.89473684211</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -2240,7 +2235,7 @@
         <v>114497.89473684211</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -2264,7 +2259,7 @@
         <v>180058.94736842107</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -2288,7 +2283,7 @@
         <v>156781.05263157896</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -2312,7 +2307,7 @@
         <v>163951.57894736843</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -2336,7 +2331,7 @@
         <v>292930.5263157895</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -2360,7 +2355,7 @@
         <v>255636.84210526317</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -2384,7 +2379,7 @@
         <v>23910.526315789473</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -2408,7 +2403,7 @@
         <v>2308.4210526315792</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2433,7 +2428,7 @@
         <v>2687088.4210526319</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
@@ -2445,58 +2440,58 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54424CF4-C226-4A4F-8C1B-D8A2CB8D4757}">
   <dimension ref="A1:AI310"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.578125" customWidth="1"/>
-    <col min="2" max="2" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.15625" customWidth="1"/>
-    <col min="4" max="4" width="7.578125" customWidth="1"/>
-    <col min="5" max="5" width="5.68359375" customWidth="1"/>
-    <col min="6" max="6" width="9.578125" customWidth="1"/>
-    <col min="7" max="7" width="8.15625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.68359375" customWidth="1"/>
-    <col min="9" max="9" width="7.578125" customWidth="1"/>
-    <col min="10" max="10" width="7.15625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.15625" customWidth="1"/>
-    <col min="13" max="13" width="6.83984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.41796875" customWidth="1"/>
-    <col min="17" max="17" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -2504,7 +2499,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="P9" s="14" t="s">
         <v>71</v>
       </c>
@@ -2537,7 +2532,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>84</v>
       </c>
@@ -2620,7 +2615,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1896</v>
       </c>
@@ -2674,7 +2669,7 @@
       </c>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f>A11+1</f>
         <v>1897</v>
@@ -2729,7 +2724,7 @@
       </c>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" ref="A13:A31" si="2">A12+1</f>
         <v>1898</v>
@@ -2784,7 +2779,7 @@
       </c>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>1899</v>
@@ -2882,7 +2877,7 @@
         <v>4.3528753924899997</v>
       </c>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>1900</v>
@@ -2980,7 +2975,7 @@
         <v>5.6415392085457636</v>
       </c>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>1901</v>
@@ -3078,7 +3073,7 @@
         <v>2.5448767286540708</v>
       </c>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1902</v>
@@ -3176,7 +3171,7 @@
         <v>3.0960917891717461</v>
       </c>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1903</v>
@@ -3274,7 +3269,7 @@
         <v>1.9799110237312059</v>
       </c>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1904</v>
@@ -3372,7 +3367,7 @@
         <v>1.427190352127677</v>
       </c>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>1905</v>
@@ -3470,7 +3465,7 @@
         <v>1.1078286558345642</v>
       </c>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>1906</v>
@@ -3568,7 +3563,7 @@
         <v>1.61159938769543</v>
       </c>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>1907</v>
@@ -3666,7 +3661,7 @@
         <v>2.650444548432382</v>
       </c>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>1908</v>
@@ -3764,7 +3759,7 @@
         <v>1.6072463326115465</v>
       </c>
     </row>
-    <row r="24" spans="1:35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>1909</v>
@@ -3862,7 +3857,7 @@
         <v>1.6887644302205966</v>
       </c>
     </row>
-    <row r="25" spans="1:35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>1910</v>
@@ -3960,7 +3955,7 @@
         <v>2.6865499548398257</v>
       </c>
     </row>
-    <row r="26" spans="1:35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>1911</v>
@@ -4058,7 +4053,7 @@
         <v>1.5918358446542664</v>
       </c>
     </row>
-    <row r="27" spans="1:35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>1912</v>
@@ -4156,7 +4151,7 @@
         <v>1.3100851238884845</v>
       </c>
     </row>
-    <row r="28" spans="1:35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>1913</v>
@@ -4254,7 +4249,7 @@
         <v>2.3027080052662829</v>
       </c>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>1914</v>
@@ -4352,7 +4347,7 @@
         <v>2.0608548525781489</v>
       </c>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>1915</v>
@@ -4450,7 +4445,7 @@
         <v>0.49870172690928577</v>
       </c>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>1916</v>
@@ -4548,7 +4543,7 @@
         <v>1.3926559566033798</v>
       </c>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>1917</v>
       </c>
@@ -4645,7 +4640,7 @@
         <v>5.8184812868690303E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="P33" s="17">
         <f>SUM(P14:P31)-P32</f>
         <v>0</v>
@@ -4688,7 +4683,7 @@
       </c>
       <c r="AI33" s="4"/>
     </row>
-    <row r="34" spans="1:35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4741,7 +4736,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -4794,12 +4789,12 @@
         <v>0.1375376540970189</v>
       </c>
     </row>
-    <row r="38" spans="1:35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>87</v>
       </c>
@@ -4843,7 +4838,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="41" spans="1:35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>1896</v>
       </c>
@@ -4900,7 +4895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <f>A41+1</f>
         <v>1897</v>
@@ -4958,7 +4953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <f t="shared" ref="A43:A60" si="17">A42+1</f>
         <v>1898</v>
@@ -5016,7 +5011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <f t="shared" si="17"/>
         <v>1899</v>
@@ -5074,7 +5069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <f t="shared" si="17"/>
         <v>1900</v>
@@ -5132,7 +5127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="17"/>
         <v>1901</v>
@@ -5190,7 +5185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="17"/>
         <v>1902</v>
@@ -5248,7 +5243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <f t="shared" si="17"/>
         <v>1903</v>
@@ -5306,7 +5301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <f t="shared" si="17"/>
         <v>1904</v>
@@ -5364,7 +5359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <f t="shared" si="17"/>
         <v>1905</v>
@@ -5422,7 +5417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <f t="shared" si="17"/>
         <v>1906</v>
@@ -5480,7 +5475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <f t="shared" si="17"/>
         <v>1907</v>
@@ -5538,7 +5533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <f t="shared" si="17"/>
         <v>1908</v>
@@ -5596,7 +5591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <f t="shared" si="17"/>
         <v>1909</v>
@@ -5654,7 +5649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <f t="shared" si="17"/>
         <v>1910</v>
@@ -5712,7 +5707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <f t="shared" si="17"/>
         <v>1911</v>
@@ -5770,7 +5765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <f t="shared" si="17"/>
         <v>1912</v>
@@ -5828,7 +5823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <f t="shared" si="17"/>
         <v>1913</v>
@@ -5886,7 +5881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <f t="shared" si="17"/>
         <v>1914</v>
@@ -5944,7 +5939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <f t="shared" si="17"/>
         <v>1915</v>
@@ -6002,7 +5997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>1916</v>
       </c>
@@ -6059,7 +6054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>49</v>
       </c>
@@ -6116,7 +6111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>88</v>
       </c>
@@ -6169,12 +6164,12 @@
         <v>0.12899442300236147</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>84</v>
       </c>
@@ -6215,7 +6210,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>1908</v>
       </c>
@@ -6257,7 +6252,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <f t="shared" ref="A70:A76" si="39">A69+1</f>
         <v>1909</v>
@@ -6300,7 +6295,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <f t="shared" si="39"/>
         <v>1910</v>
@@ -6343,7 +6338,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <f t="shared" si="39"/>
         <v>1911</v>
@@ -6369,7 +6364,7 @@
       </c>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <f t="shared" si="39"/>
         <v>1912</v>
@@ -6412,7 +6407,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <f t="shared" si="39"/>
         <v>1913</v>
@@ -6438,7 +6433,7 @@
       </c>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <f t="shared" si="39"/>
         <v>1914</v>
@@ -6481,7 +6476,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <f t="shared" si="39"/>
         <v>1915</v>
@@ -6533,7 +6528,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>1916</v>
       </c>
@@ -6583,7 +6578,7 @@
         <v>1.1658168920416758</v>
       </c>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>1917</v>
       </c>
@@ -6613,12 +6608,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>84</v>
       </c>
@@ -6659,7 +6654,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>1908</v>
       </c>
@@ -6701,7 +6696,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <f t="shared" ref="A84:A90" si="41">A83+1</f>
         <v>1909</v>
@@ -6744,7 +6739,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <f t="shared" si="41"/>
         <v>1910</v>
@@ -6787,7 +6782,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <f t="shared" si="41"/>
         <v>1911</v>
@@ -6813,7 +6808,7 @@
       </c>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <f t="shared" si="41"/>
         <v>1912</v>
@@ -6856,7 +6851,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <f t="shared" si="41"/>
         <v>1913</v>
@@ -6882,7 +6877,7 @@
       </c>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <f t="shared" si="41"/>
         <v>1914</v>
@@ -6925,7 +6920,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <f t="shared" si="41"/>
         <v>1915</v>
@@ -6968,7 +6963,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>1916</v>
       </c>
@@ -7010,7 +7005,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>1917</v>
       </c>
@@ -7035,12 +7030,12 @@
       </c>
       <c r="M92" s="4"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
@@ -7078,7 +7073,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>142</v>
       </c>
@@ -7131,7 +7126,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>143</v>
       </c>
@@ -7184,7 +7179,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>144</v>
       </c>
@@ -7237,7 +7232,7 @@
         <v>54.280155642023345</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B100" s="26"/>
       <c r="C100" s="26"/>
       <c r="D100" s="26"/>
@@ -7251,7 +7246,7 @@
       <c r="L100" s="26"/>
       <c r="M100" s="26"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>151</v>
       </c>
@@ -7268,7 +7263,7 @@
       <c r="L101" s="26"/>
       <c r="M101" s="26"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B102" s="26"/>
       <c r="C102" s="26"/>
       <c r="D102" s="26"/>
@@ -7282,7 +7277,7 @@
       <c r="L102" s="26"/>
       <c r="M102" s="26"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B103" s="10" t="s">
         <v>70</v>
       </c>
@@ -7320,7 +7315,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>142</v>
       </c>
@@ -7373,7 +7368,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>143</v>
       </c>
@@ -7426,7 +7421,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>144</v>
       </c>
@@ -7479,7 +7474,7 @@
         <v>47.149894440534837</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B107" s="26"/>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
@@ -7493,7 +7488,7 @@
       <c r="L107" s="26"/>
       <c r="M107" s="26"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>152</v>
       </c>
@@ -7510,7 +7505,7 @@
       <c r="L108" s="26"/>
       <c r="M108" s="26"/>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -7527,7 +7522,7 @@
       <c r="L109" s="26"/>
       <c r="M109" s="26"/>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B110" s="26"/>
       <c r="C110" s="26"/>
       <c r="D110" s="26"/>
@@ -7541,7 +7536,7 @@
       <c r="L110" s="26"/>
       <c r="M110" s="26"/>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
@@ -7579,7 +7574,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B112" s="26">
         <f>B106</f>
         <v>6.9984447900466566</v>
@@ -7629,12 +7624,12 @@
         <v>50.715025041279091</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>84</v>
       </c>
@@ -7681,7 +7676,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>1896</v>
       </c>
@@ -7738,7 +7733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <f>A117+1</f>
         <v>1897</v>
@@ -7796,7 +7791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <f t="shared" ref="A119:A137" si="54">A118+1</f>
         <v>1898</v>
@@ -7854,7 +7849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <f t="shared" si="54"/>
         <v>1899</v>
@@ -7912,7 +7907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <f t="shared" si="54"/>
         <v>1900</v>
@@ -7970,7 +7965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <f t="shared" si="54"/>
         <v>1901</v>
@@ -8028,7 +8023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <f t="shared" si="54"/>
         <v>1902</v>
@@ -8086,7 +8081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <f t="shared" si="54"/>
         <v>1903</v>
@@ -8144,7 +8139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <f t="shared" si="54"/>
         <v>1904</v>
@@ -8202,7 +8197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <f t="shared" si="54"/>
         <v>1905</v>
@@ -8260,7 +8255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <f t="shared" si="54"/>
         <v>1906</v>
@@ -8318,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <f t="shared" si="54"/>
         <v>1907</v>
@@ -8376,7 +8371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <f t="shared" si="54"/>
         <v>1908</v>
@@ -8423,7 +8418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <f t="shared" si="54"/>
         <v>1909</v>
@@ -8470,7 +8465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <f t="shared" si="54"/>
         <v>1910</v>
@@ -8517,7 +8512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <f t="shared" si="54"/>
         <v>1911</v>
@@ -8575,7 +8570,7 @@
         <v>15723.438359773389</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <f t="shared" si="54"/>
         <v>1912</v>
@@ -8622,7 +8617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <f t="shared" si="54"/>
         <v>1913</v>
@@ -8680,7 +8675,7 @@
         <v>36173.276557684701</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <f t="shared" si="54"/>
         <v>1914</v>
@@ -8727,7 +8722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <f t="shared" si="54"/>
         <v>1915</v>
@@ -8774,7 +8769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <f t="shared" si="54"/>
         <v>1916</v>
@@ -8821,7 +8816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>1917</v>
       </c>
@@ -8878,7 +8873,7 @@
         <v>639.69124188047317</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -8893,7 +8888,7 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="30" t="s">
         <v>173</v>
       </c>
@@ -8910,7 +8905,7 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -8925,7 +8920,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>1911</v>
       </c>
@@ -8966,7 +8961,7 @@
         <v>-11.876056132993654</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <f>A142+1</f>
         <v>1912</v>
@@ -8984,7 +8979,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <f t="shared" ref="A144:A148" si="74">A143+1</f>
         <v>1913</v>
@@ -9026,7 +9021,7 @@
         <v>116.94950349421394</v>
       </c>
     </row>
-    <row r="145" spans="1:15">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <f t="shared" si="74"/>
         <v>1914</v>
@@ -9044,7 +9039,7 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
     </row>
-    <row r="146" spans="1:15">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <f t="shared" si="74"/>
         <v>1915</v>
@@ -9062,7 +9057,7 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
     </row>
-    <row r="147" spans="1:15">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <f t="shared" si="74"/>
         <v>1916</v>
@@ -9080,7 +9075,7 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
     </row>
-    <row r="148" spans="1:15">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <f t="shared" si="74"/>
         <v>1917</v>
@@ -9122,7 +9117,7 @@
         <v>218.84913831012869</v>
       </c>
     </row>
-    <row r="149" spans="1:15">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -9137,7 +9132,7 @@
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
     </row>
-    <row r="150" spans="1:15">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="30" t="s">
         <v>171</v>
       </c>
@@ -9154,7 +9149,7 @@
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
     </row>
-    <row r="151" spans="1:15">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -9169,7 +9164,7 @@
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
     </row>
-    <row r="152" spans="1:15">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="str">
         <f t="shared" ref="A152:M152" si="76">A116</f>
         <v>фин. год</v>
@@ -9228,7 +9223,7 @@
         <v>разница</v>
       </c>
     </row>
-    <row r="153" spans="1:15">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <f t="shared" ref="A153:M153" si="77">A117</f>
         <v>1896</v>
@@ -9287,7 +9282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:15">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <f t="shared" ref="A154:M154" si="79">A118</f>
         <v>1897</v>
@@ -9346,7 +9341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <f t="shared" ref="A155:M155" si="80">A119</f>
         <v>1898</v>
@@ -9405,7 +9400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <f t="shared" ref="A156:M156" si="81">A120</f>
         <v>1899</v>
@@ -9464,7 +9459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <f t="shared" ref="A157:M157" si="82">A121</f>
         <v>1900</v>
@@ -9523,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <f t="shared" ref="A158:M158" si="83">A122</f>
         <v>1901</v>
@@ -9582,7 +9577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:15">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <f t="shared" ref="A159:M159" si="84">A123</f>
         <v>1902</v>
@@ -9641,7 +9636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <f t="shared" ref="A160:M160" si="85">A124</f>
         <v>1903</v>
@@ -9700,7 +9695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <f t="shared" ref="A161:M161" si="86">A125</f>
         <v>1904</v>
@@ -9759,7 +9754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <f t="shared" ref="A162:M162" si="87">A126</f>
         <v>1905</v>
@@ -9818,7 +9813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <f t="shared" ref="A163:M163" si="88">A127</f>
         <v>1906</v>
@@ -9877,7 +9872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <f t="shared" ref="A164:M164" si="89">A128</f>
         <v>1907</v>
@@ -9936,7 +9931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <f t="shared" ref="A165:M165" si="90">A129</f>
         <v>1908</v>
@@ -9995,7 +9990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <f t="shared" ref="A166:M166" si="91">A130</f>
         <v>1909</v>
@@ -10054,7 +10049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <f t="shared" ref="A167:M167" si="92">A131</f>
         <v>1910</v>
@@ -10113,7 +10108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:15">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <f t="shared" ref="A168:A174" si="93">A132</f>
         <v>1911</v>
@@ -10172,7 +10167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:15">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <f t="shared" si="93"/>
         <v>1912</v>
@@ -10231,7 +10226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <f t="shared" si="93"/>
         <v>1913</v>
@@ -10290,7 +10285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <f t="shared" si="93"/>
         <v>1914</v>
@@ -10349,7 +10344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <f t="shared" si="93"/>
         <v>1915</v>
@@ -10408,7 +10403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <f t="shared" si="93"/>
         <v>1916</v>
@@ -10467,7 +10462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <f t="shared" si="93"/>
         <v>1917</v>
@@ -10526,12 +10521,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
         <v>84</v>
       </c>
@@ -10575,7 +10570,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>1896</v>
       </c>
@@ -10633,7 +10628,7 @@
       </c>
       <c r="P179" s="4"/>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <f>A179+1</f>
         <v>1897</v>
@@ -10692,7 +10687,7 @@
       </c>
       <c r="P180" s="4"/>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <f t="shared" ref="A181:A199" si="104">A180+1</f>
         <v>1898</v>
@@ -10751,7 +10746,7 @@
       </c>
       <c r="P181" s="4"/>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <f t="shared" si="104"/>
         <v>1899</v>
@@ -10810,7 +10805,7 @@
       </c>
       <c r="P182" s="4"/>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <f t="shared" si="104"/>
         <v>1900</v>
@@ -10869,7 +10864,7 @@
       </c>
       <c r="P183" s="4"/>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <f t="shared" si="104"/>
         <v>1901</v>
@@ -10928,7 +10923,7 @@
       </c>
       <c r="P184" s="4"/>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <f t="shared" si="104"/>
         <v>1902</v>
@@ -10987,7 +10982,7 @@
       </c>
       <c r="P185" s="4"/>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <f t="shared" si="104"/>
         <v>1903</v>
@@ -11046,7 +11041,7 @@
       </c>
       <c r="P186" s="4"/>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <f t="shared" si="104"/>
         <v>1904</v>
@@ -11105,7 +11100,7 @@
       </c>
       <c r="P187" s="4"/>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <f t="shared" si="104"/>
         <v>1905</v>
@@ -11164,7 +11159,7 @@
       </c>
       <c r="P188" s="4"/>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <f t="shared" si="104"/>
         <v>1906</v>
@@ -11223,7 +11218,7 @@
       </c>
       <c r="P189" s="4"/>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <f t="shared" si="104"/>
         <v>1907</v>
@@ -11282,7 +11277,7 @@
       </c>
       <c r="P190" s="4"/>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <f t="shared" si="104"/>
         <v>1908</v>
@@ -11340,7 +11335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <f t="shared" si="104"/>
         <v>1909</v>
@@ -11398,7 +11393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <f t="shared" si="104"/>
         <v>1910</v>
@@ -11456,7 +11451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <f t="shared" si="104"/>
         <v>1911</v>
@@ -11514,7 +11509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <f t="shared" si="104"/>
         <v>1912</v>
@@ -11572,7 +11567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:15">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <f t="shared" si="104"/>
         <v>1913</v>
@@ -11630,7 +11625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:15">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <f t="shared" si="104"/>
         <v>1914</v>
@@ -11688,7 +11683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <f t="shared" si="104"/>
         <v>1915</v>
@@ -11746,7 +11741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <f t="shared" si="104"/>
         <v>1916</v>
@@ -11804,7 +11799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:15">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>1917</v>
       </c>
@@ -11861,12 +11856,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="204" spans="1:15">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
         <v>87</v>
       </c>
@@ -11910,7 +11905,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="205" spans="1:15">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>1896</v>
       </c>
@@ -11967,7 +11962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:15">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <f>A205+1</f>
         <v>1897</v>
@@ -12025,7 +12020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:15">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <f t="shared" ref="A207:A224" si="128">A206+1</f>
         <v>1898</v>
@@ -12083,7 +12078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <f t="shared" si="128"/>
         <v>1899</v>
@@ -12141,7 +12136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <f t="shared" si="128"/>
         <v>1900</v>
@@ -12199,7 +12194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:15">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <f t="shared" si="128"/>
         <v>1901</v>
@@ -12257,7 +12252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:15">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <f t="shared" si="128"/>
         <v>1902</v>
@@ -12315,7 +12310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <f t="shared" si="128"/>
         <v>1903</v>
@@ -12373,7 +12368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:15">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <f t="shared" si="128"/>
         <v>1904</v>
@@ -12431,7 +12426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <f t="shared" si="128"/>
         <v>1905</v>
@@ -12489,7 +12484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:15">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <f t="shared" si="128"/>
         <v>1906</v>
@@ -12547,7 +12542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <f t="shared" si="128"/>
         <v>1907</v>
@@ -12605,7 +12600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <f t="shared" si="128"/>
         <v>1908</v>
@@ -12663,7 +12658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <f t="shared" si="128"/>
         <v>1909</v>
@@ -12721,7 +12716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:15">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <f t="shared" si="128"/>
         <v>1910</v>
@@ -12779,7 +12774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:15">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <f t="shared" si="128"/>
         <v>1911</v>
@@ -12837,7 +12832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <f t="shared" si="128"/>
         <v>1912</v>
@@ -12895,7 +12890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <f t="shared" si="128"/>
         <v>1913</v>
@@ -12953,7 +12948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <f t="shared" si="128"/>
         <v>1914</v>
@@ -13011,7 +13006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <f t="shared" si="128"/>
         <v>1915</v>
@@ -13069,7 +13064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>1916</v>
       </c>
@@ -13126,7 +13121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:15">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>49</v>
       </c>
@@ -13183,7 +13178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:15">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>88</v>
       </c>
@@ -13236,15 +13231,15 @@
         <v>8.2845503895924058E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:15">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="230" spans="1:15">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L230" s="4"/>
     </row>
-    <row r="231" spans="1:15">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>180</v>
       </c>
@@ -13253,10 +13248,10 @@
       </c>
       <c r="L231" s="4"/>
     </row>
-    <row r="232" spans="1:15">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L232" s="4"/>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
         <v>87</v>
       </c>
@@ -13300,7 +13295,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="234" spans="1:15">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>1896</v>
       </c>
@@ -13357,7 +13352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <f>A234+1</f>
         <v>1897</v>
@@ -13415,7 +13410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <f t="shared" ref="A236:A253" si="153">A235+1</f>
         <v>1898</v>
@@ -13473,7 +13468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:15">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <f t="shared" si="153"/>
         <v>1899</v>
@@ -13531,7 +13526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:15">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <f t="shared" si="153"/>
         <v>1900</v>
@@ -13589,7 +13584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <f t="shared" si="153"/>
         <v>1901</v>
@@ -13647,7 +13642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:15">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <f t="shared" si="153"/>
         <v>1902</v>
@@ -13705,7 +13700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <f t="shared" si="153"/>
         <v>1903</v>
@@ -13763,7 +13758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <f t="shared" si="153"/>
         <v>1904</v>
@@ -13821,7 +13816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <f t="shared" si="153"/>
         <v>1905</v>
@@ -13879,7 +13874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:15">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <f t="shared" si="153"/>
         <v>1906</v>
@@ -13937,7 +13932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:15">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <f t="shared" si="153"/>
         <v>1907</v>
@@ -13995,7 +13990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:15">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <f t="shared" si="153"/>
         <v>1908</v>
@@ -14053,7 +14048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <f t="shared" si="153"/>
         <v>1909</v>
@@ -14111,7 +14106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:15">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <f t="shared" si="153"/>
         <v>1910</v>
@@ -14169,7 +14164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <f t="shared" si="153"/>
         <v>1911</v>
@@ -14227,7 +14222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <f t="shared" si="153"/>
         <v>1912</v>
@@ -14285,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:15">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <f t="shared" si="153"/>
         <v>1913</v>
@@ -14343,7 +14338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <f t="shared" si="153"/>
         <v>1914</v>
@@ -14401,7 +14396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <f t="shared" si="153"/>
         <v>1915</v>
@@ -14459,7 +14454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>1916</v>
       </c>
@@ -14516,7 +14511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>49</v>
       </c>
@@ -14573,12 +14568,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:17">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="259" spans="1:17">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A259" s="14" t="s">
         <v>181</v>
       </c>
@@ -14619,7 +14614,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="260" spans="1:17">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B260">
         <v>0.55000000000000004</v>
       </c>
@@ -14654,7 +14649,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="262" spans="1:17">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
         <v>87</v>
       </c>
@@ -14698,7 +14693,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="263" spans="1:17">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>1896</v>
       </c>
@@ -14755,7 +14750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <f>A263+1</f>
         <v>1897</v>
@@ -14813,7 +14808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:17">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <f t="shared" ref="A265:A282" si="179">A264+1</f>
         <v>1898</v>
@@ -14871,7 +14866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <f t="shared" si="179"/>
         <v>1899</v>
@@ -14929,7 +14924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:17">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <f t="shared" si="179"/>
         <v>1900</v>
@@ -14987,7 +14982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <f t="shared" si="179"/>
         <v>1901</v>
@@ -15046,7 +15041,7 @@
       </c>
       <c r="Q268" s="4"/>
     </row>
-    <row r="269" spans="1:17">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <f t="shared" si="179"/>
         <v>1902</v>
@@ -15104,7 +15099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:17">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <f t="shared" si="179"/>
         <v>1903</v>
@@ -15162,7 +15157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:17">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <f t="shared" si="179"/>
         <v>1904</v>
@@ -15220,7 +15215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:17">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <f t="shared" si="179"/>
         <v>1905</v>
@@ -15278,7 +15273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:15">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <f t="shared" si="179"/>
         <v>1906</v>
@@ -15336,7 +15331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:15">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <f t="shared" si="179"/>
         <v>1907</v>
@@ -15394,7 +15389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:15">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <f t="shared" si="179"/>
         <v>1908</v>
@@ -15452,7 +15447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <f t="shared" si="179"/>
         <v>1909</v>
@@ -15510,7 +15505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:15">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <f t="shared" si="179"/>
         <v>1910</v>
@@ -15568,7 +15563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:15">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <f t="shared" si="179"/>
         <v>1911</v>
@@ -15626,7 +15621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <f t="shared" si="179"/>
         <v>1912</v>
@@ -15684,7 +15679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <f t="shared" si="179"/>
         <v>1913</v>
@@ -15742,7 +15737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <f t="shared" si="179"/>
         <v>1914</v>
@@ -15800,7 +15795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <f t="shared" si="179"/>
         <v>1915</v>
@@ -15858,7 +15853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>1916</v>
       </c>
@@ -15915,7 +15910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:15">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
         <v>49</v>
       </c>
@@ -15972,12 +15967,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:15">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="288" spans="1:15">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
         <v>87</v>
       </c>
@@ -16021,7 +16016,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="289" spans="1:15">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>1896</v>
       </c>
@@ -16078,7 +16073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:15">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <f>A289+1</f>
         <v>1897</v>
@@ -16136,7 +16131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:15">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <f t="shared" ref="A291:A308" si="203">A290+1</f>
         <v>1898</v>
@@ -16194,7 +16189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:15">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <f t="shared" si="203"/>
         <v>1899</v>
@@ -16252,7 +16247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:15">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <f t="shared" si="203"/>
         <v>1900</v>
@@ -16310,7 +16305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <f t="shared" si="203"/>
         <v>1901</v>
@@ -16368,7 +16363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:15">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <f t="shared" si="203"/>
         <v>1902</v>
@@ -16426,7 +16421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:15">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <f t="shared" si="203"/>
         <v>1903</v>
@@ -16484,7 +16479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:15">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <f t="shared" si="203"/>
         <v>1904</v>
@@ -16542,7 +16537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:15">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <f t="shared" si="203"/>
         <v>1905</v>
@@ -16600,7 +16595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:15">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <f t="shared" si="203"/>
         <v>1906</v>
@@ -16658,7 +16653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <f t="shared" si="203"/>
         <v>1907</v>
@@ -16716,7 +16711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <f t="shared" si="203"/>
         <v>1908</v>
@@ -16774,7 +16769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:15">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <f t="shared" si="203"/>
         <v>1909</v>
@@ -16832,7 +16827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:15">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <f t="shared" si="203"/>
         <v>1910</v>
@@ -16890,7 +16885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:15">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <f t="shared" si="203"/>
         <v>1911</v>
@@ -16948,7 +16943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <f t="shared" si="203"/>
         <v>1912</v>
@@ -17006,7 +17001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:15">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <f t="shared" si="203"/>
         <v>1913</v>
@@ -17064,7 +17059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:15">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <f t="shared" si="203"/>
         <v>1914</v>
@@ -17122,7 +17117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <f t="shared" si="203"/>
         <v>1915</v>
@@ -17180,7 +17175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>1916</v>
       </c>
@@ -17237,7 +17232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
         <v>49</v>
       </c>
@@ -17306,30 +17301,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
   <dimension ref="A1:N228"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.41796875" customWidth="1"/>
-    <col min="2" max="2" width="17.41796875" customWidth="1"/>
-    <col min="3" max="3" width="10.68359375" customWidth="1"/>
-    <col min="4" max="4" width="14.26171875" customWidth="1"/>
-    <col min="5" max="5" width="12.578125" customWidth="1"/>
-    <col min="6" max="6" width="13.26171875" customWidth="1"/>
-    <col min="7" max="7" width="10.26171875" customWidth="1"/>
-    <col min="9" max="9" width="12.26171875" customWidth="1"/>
-    <col min="10" max="10" width="11.578125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="57.6">
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>116</v>
       </c>
@@ -17364,7 +17359,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>117</v>
       </c>
@@ -17399,7 +17394,7 @@
         <v>30398</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -17434,7 +17429,7 @@
         <v>27525</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -17469,7 +17464,7 @@
         <v>64393</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -17504,7 +17499,7 @@
         <v>223248</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -17539,7 +17534,7 @@
         <v>279258</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -17574,7 +17569,7 @@
         <v>173914</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>123</v>
       </c>
@@ -17609,7 +17604,7 @@
         <v>340174</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
@@ -17644,7 +17639,7 @@
         <v>471971</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -17679,7 +17674,7 @@
         <v>409911</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>128</v>
       </c>
@@ -17724,7 +17719,7 @@
         <v>2020792</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>129</v>
       </c>
@@ -17769,7 +17764,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>126</v>
       </c>
@@ -17814,7 +17809,7 @@
         <v>1395970</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>127</v>
       </c>
@@ -17859,7 +17854,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>184</v>
       </c>
@@ -17904,7 +17899,7 @@
         <v>566899</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
         <v>185</v>
       </c>
@@ -17949,7 +17944,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>193</v>
       </c>
@@ -17964,7 +17959,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>191</v>
       </c>
@@ -17979,7 +17974,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -17991,7 +17986,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
         <v>116</v>
       </c>
@@ -18022,7 +18017,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -18046,7 +18041,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>119</v>
       </c>
@@ -18072,7 +18067,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>120</v>
       </c>
@@ -18098,7 +18093,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -18124,7 +18119,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
         <v>122</v>
       </c>
@@ -18153,7 +18148,7 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -18186,7 +18181,7 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -18217,7 +18212,7 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>125</v>
       </c>
@@ -18250,7 +18245,7 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
         <v>126</v>
       </c>
@@ -18292,7 +18287,7 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
         <v>88</v>
       </c>
@@ -18334,7 +18329,7 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
         <v>184</v>
       </c>
@@ -18367,7 +18362,7 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="33" t="s">
         <v>88</v>
       </c>
@@ -18392,17 +18387,17 @@
         <v>99.993052867676965</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="72">
+    <row r="42" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>116</v>
       </c>
@@ -18440,7 +18435,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>118</v>
       </c>
@@ -18473,7 +18468,7 @@
       </c>
       <c r="M43" s="4"/>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>119</v>
       </c>
@@ -18508,7 +18503,7 @@
       </c>
       <c r="M44" s="4"/>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>120</v>
       </c>
@@ -18543,7 +18538,7 @@
       </c>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>121</v>
       </c>
@@ -18578,7 +18573,7 @@
       </c>
       <c r="M46" s="4"/>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>122</v>
       </c>
@@ -18613,7 +18608,7 @@
       </c>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>123</v>
       </c>
@@ -18650,7 +18645,7 @@
       </c>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>124</v>
       </c>
@@ -18685,7 +18680,7 @@
       </c>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>125</v>
       </c>
@@ -18722,7 +18717,7 @@
       </c>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
         <v>126</v>
       </c>
@@ -18771,7 +18766,7 @@
         <v>2888132</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
         <v>88</v>
       </c>
@@ -18811,7 +18806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
         <v>184</v>
       </c>
@@ -18860,7 +18855,7 @@
         <v>552406</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
         <v>88</v>
       </c>
@@ -18900,12 +18895,12 @@
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="36" t="s">
         <v>19</v>
       </c>
@@ -18913,7 +18908,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <f t="shared" ref="A60:A73" si="23">A61-1</f>
         <v>1881</v>
@@ -18923,8 +18918,9 @@
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-    </row>
-    <row r="61" spans="1:13">
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <f t="shared" si="23"/>
         <v>1882</v>
@@ -18934,8 +18930,9 @@
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-    </row>
-    <row r="62" spans="1:13">
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <f t="shared" si="23"/>
         <v>1883</v>
@@ -18945,8 +18942,9 @@
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
-    </row>
-    <row r="63" spans="1:13">
+      <c r="G62" s="4"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <f t="shared" si="23"/>
         <v>1884</v>
@@ -18956,8 +18954,9 @@
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
-    </row>
-    <row r="64" spans="1:13">
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <f t="shared" si="23"/>
         <v>1885</v>
@@ -18967,8 +18966,9 @@
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <f t="shared" si="23"/>
         <v>1886</v>
@@ -18978,8 +18978,9 @@
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <f t="shared" si="23"/>
         <v>1887</v>
@@ -18989,8 +18990,9 @@
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <f t="shared" si="23"/>
         <v>1888</v>
@@ -19000,8 +19002,9 @@
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <f t="shared" si="23"/>
         <v>1889</v>
@@ -19011,8 +19014,9 @@
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <f t="shared" si="23"/>
         <v>1890</v>
@@ -19022,8 +19026,9 @@
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="G69" s="4"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <f t="shared" si="23"/>
         <v>1891</v>
@@ -19033,8 +19038,9 @@
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <f t="shared" si="23"/>
         <v>1892</v>
@@ -19044,8 +19050,9 @@
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="G71" s="4"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <f t="shared" si="23"/>
         <v>1893</v>
@@ -19055,8 +19062,9 @@
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="G72" s="4"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <f t="shared" si="23"/>
         <v>1894</v>
@@ -19066,8 +19074,9 @@
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="G73" s="4"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <f>A75-1</f>
         <v>1895</v>
@@ -19077,8 +19086,9 @@
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="G74" s="4"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>1896</v>
       </c>
@@ -19089,7 +19099,7 @@
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>1897</v>
       </c>
@@ -19100,7 +19110,7 @@
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>1898</v>
       </c>
@@ -19111,7 +19121,7 @@
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>1899</v>
       </c>
@@ -19122,7 +19132,7 @@
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>1900</v>
       </c>
@@ -19133,7 +19143,7 @@
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>1901</v>
       </c>
@@ -19144,7 +19154,7 @@
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>1902</v>
       </c>
@@ -19155,7 +19165,7 @@
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>1903</v>
       </c>
@@ -19166,7 +19176,7 @@
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>1904</v>
       </c>
@@ -19177,7 +19187,7 @@
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>1905</v>
       </c>
@@ -19188,7 +19198,7 @@
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>1906</v>
       </c>
@@ -19199,7 +19209,7 @@
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>1907</v>
       </c>
@@ -19210,7 +19220,7 @@
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>1908</v>
       </c>
@@ -19221,7 +19231,7 @@
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>1909</v>
       </c>
@@ -19232,7 +19242,7 @@
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>1910</v>
       </c>
@@ -19243,7 +19253,7 @@
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>1911</v>
       </c>
@@ -19254,7 +19264,7 @@
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>1912</v>
       </c>
@@ -19265,7 +19275,7 @@
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>1913</v>
       </c>
@@ -19276,7 +19286,7 @@
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>1914</v>
       </c>
@@ -19287,7 +19297,7 @@
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>1915</v>
       </c>
@@ -19298,7 +19308,7 @@
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>1916</v>
       </c>
@@ -19309,7 +19319,7 @@
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>49</v>
       </c>
@@ -19318,7 +19328,7 @@
         <v>2477253</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>122</v>
       </c>
@@ -19327,7 +19337,7 @@
         <v>247211</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>123</v>
       </c>
@@ -19336,7 +19346,7 @@
         <v>649198</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>124</v>
       </c>
@@ -19345,7 +19355,7 @@
         <v>831386</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>125</v>
       </c>
@@ -19354,7 +19364,7 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="28.8">
+    <row r="104" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>116</v>
       </c>
@@ -19372,7 +19382,7 @@
       </c>
       <c r="F104" s="38"/>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>118</v>
       </c>
@@ -19390,7 +19400,7 @@
       </c>
       <c r="E105" s="14"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>119</v>
       </c>
@@ -19411,7 +19421,7 @@
         <v>72110</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>120</v>
       </c>
@@ -19432,7 +19442,7 @@
         <v>188383</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>121</v>
       </c>
@@ -19453,7 +19463,7 @@
         <v>262363</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="43" t="s">
         <v>122</v>
       </c>
@@ -19474,7 +19484,7 @@
         <v>247211</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
@@ -19495,7 +19505,7 @@
         <v>649198</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>124</v>
       </c>
@@ -19516,7 +19526,7 @@
         <v>831386</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>125</v>
       </c>
@@ -19537,18 +19547,18 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B113" s="4"/>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B114" s="4"/>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="36" t="s">
         <v>116</v>
       </c>
@@ -19556,7 +19566,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="str">
         <f t="shared" ref="A117:A125" si="27">A43</f>
         <v>1876-1880</v>
@@ -19566,7 +19576,7 @@
         <v>33658</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="str">
         <f t="shared" si="27"/>
         <v>1881-1885</v>
@@ -19576,7 +19586,7 @@
         <v>69982</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="str">
         <f t="shared" si="27"/>
         <v>1886-1890</v>
@@ -19586,7 +19596,7 @@
         <v>189850</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
         <f t="shared" si="27"/>
         <v>1891-1895</v>
@@ -19596,7 +19606,7 @@
         <v>292574</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
         <f t="shared" si="27"/>
         <v>1896-1900</v>
@@ -19606,7 +19616,7 @@
         <v>246339</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="str">
         <f t="shared" si="27"/>
         <v>1901-1905</v>
@@ -19616,7 +19626,7 @@
         <v>644531</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="str">
         <f t="shared" si="27"/>
         <v>1906-1910</v>
@@ -19626,7 +19636,7 @@
         <v>986977</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="str">
         <f t="shared" si="27"/>
         <v>1911-1915</v>
@@ -19636,7 +19646,7 @@
         <v>1010285</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="str">
         <f t="shared" si="27"/>
         <v>1896-1915</v>
@@ -19646,7 +19656,7 @@
         <v>2888132</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
         <v>128</v>
       </c>
@@ -19655,12 +19665,12 @@
         <v>3474196</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="14" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="36" t="s">
         <v>116</v>
       </c>
@@ -19668,7 +19678,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>1876</v>
       </c>
@@ -19677,7 +19687,7 @@
       </c>
       <c r="F130" s="48"/>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>1877</v>
       </c>
@@ -19686,7 +19696,7 @@
       </c>
       <c r="F131" s="48"/>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>1878</v>
       </c>
@@ -19695,7 +19705,7 @@
       </c>
       <c r="F132" s="48"/>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>1879</v>
       </c>
@@ -19704,7 +19714,7 @@
       </c>
       <c r="F133" s="48"/>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>1880</v>
       </c>
@@ -19713,7 +19723,7 @@
       </c>
       <c r="F134" s="48"/>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>1881</v>
       </c>
@@ -19722,7 +19732,7 @@
       </c>
       <c r="F135" s="48"/>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>1882</v>
       </c>
@@ -19731,7 +19741,7 @@
       </c>
       <c r="F136" s="48"/>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>1883</v>
       </c>
@@ -19740,7 +19750,7 @@
       </c>
       <c r="F137" s="48"/>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>1884</v>
       </c>
@@ -19749,7 +19759,7 @@
       </c>
       <c r="F138" s="48"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>1885</v>
       </c>
@@ -19758,7 +19768,7 @@
       </c>
       <c r="F139" s="48"/>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>1886</v>
       </c>
@@ -19767,7 +19777,7 @@
       </c>
       <c r="F140" s="48"/>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>1887</v>
       </c>
@@ -19776,7 +19786,7 @@
       </c>
       <c r="F141" s="48"/>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>1888</v>
       </c>
@@ -19785,7 +19795,7 @@
       </c>
       <c r="F142" s="48"/>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>1889</v>
       </c>
@@ -19794,7 +19804,7 @@
       </c>
       <c r="F143" s="48"/>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>1890</v>
       </c>
@@ -19803,7 +19813,7 @@
       </c>
       <c r="F144" s="48"/>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>1891</v>
       </c>
@@ -19812,7 +19822,7 @@
       </c>
       <c r="F145" s="48"/>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>1892</v>
       </c>
@@ -19821,7 +19831,7 @@
       </c>
       <c r="F146" s="48"/>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>1893</v>
       </c>
@@ -19830,7 +19840,7 @@
       </c>
       <c r="F147" s="48"/>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>1894</v>
       </c>
@@ -19839,7 +19849,7 @@
       </c>
       <c r="F148" s="48"/>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>1895</v>
       </c>
@@ -19848,7 +19858,7 @@
       </c>
       <c r="F149" s="48"/>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>1896</v>
       </c>
@@ -19857,7 +19867,7 @@
       </c>
       <c r="F150" s="48"/>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>1897</v>
       </c>
@@ -19866,7 +19876,7 @@
       </c>
       <c r="F151" s="48"/>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>1898</v>
       </c>
@@ -19875,7 +19885,7 @@
       </c>
       <c r="F152" s="48"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>1899</v>
       </c>
@@ -19884,7 +19894,7 @@
       </c>
       <c r="F153" s="48"/>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>1900</v>
       </c>
@@ -19893,7 +19903,7 @@
       </c>
       <c r="F154" s="48"/>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>1901</v>
       </c>
@@ -19902,7 +19912,7 @@
       </c>
       <c r="F155" s="48"/>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>1902</v>
       </c>
@@ -19911,7 +19921,7 @@
       </c>
       <c r="F156" s="48"/>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>1903</v>
       </c>
@@ -19920,7 +19930,7 @@
       </c>
       <c r="F157" s="48"/>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>1904</v>
       </c>
@@ -19929,7 +19939,7 @@
       </c>
       <c r="F158" s="48"/>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>1905</v>
       </c>
@@ -19938,7 +19948,7 @@
       </c>
       <c r="F159" s="48"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>1906</v>
       </c>
@@ -19947,7 +19957,7 @@
       </c>
       <c r="F160" s="48"/>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>1907</v>
       </c>
@@ -19956,7 +19966,7 @@
       </c>
       <c r="F161" s="48"/>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>1908</v>
       </c>
@@ -19965,7 +19975,7 @@
       </c>
       <c r="F162" s="48"/>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>1909</v>
       </c>
@@ -19974,7 +19984,7 @@
       </c>
       <c r="F163" s="48"/>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>1910</v>
       </c>
@@ -19983,7 +19993,7 @@
       </c>
       <c r="F164" s="48"/>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>1911</v>
       </c>
@@ -19992,7 +20002,7 @@
       </c>
       <c r="F165" s="48"/>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>1912</v>
       </c>
@@ -20001,7 +20011,7 @@
       </c>
       <c r="F166" s="48"/>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>1913</v>
       </c>
@@ -20010,7 +20020,7 @@
       </c>
       <c r="F167" s="48"/>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>1914</v>
       </c>
@@ -20019,7 +20029,7 @@
       </c>
       <c r="F168" s="48"/>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>1915</v>
       </c>
@@ -20028,7 +20038,7 @@
       </c>
       <c r="F169" s="48"/>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
         <v>126</v>
       </c>
@@ -20037,7 +20047,7 @@
         <v>2888132</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="10" t="s">
         <v>128</v>
       </c>
@@ -20046,7 +20056,7 @@
         <v>3474195.9999989998</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
         <v>184</v>
       </c>
@@ -20055,16 +20065,16 @@
         <v>552405.99999899999</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="10"/>
       <c r="B173" s="4"/>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="14" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="36" t="s">
         <v>116</v>
       </c>
@@ -20072,7 +20082,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>1881</v>
       </c>
@@ -20081,7 +20091,7 @@
         <v>9940.4968540000009</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <f>A177+1</f>
         <v>1882</v>
@@ -20091,7 +20101,7 @@
         <v>11990.335417</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <f t="shared" ref="A179:A210" si="30">A178+1</f>
         <v>1883</v>
@@ -20101,7 +20111,7 @@
         <v>14778.415338499999</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <f t="shared" si="30"/>
         <v>1884</v>
@@ -20111,7 +20121,7 @@
         <v>18460.160641499999</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <f t="shared" si="30"/>
         <v>1885</v>
@@ -20121,7 +20131,7 @@
         <v>23423.707469000001</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <f t="shared" si="30"/>
         <v>1886</v>
@@ -20131,7 +20141,7 @@
         <v>29118.518597000002</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <f t="shared" si="30"/>
         <v>1887</v>
@@ -20141,7 +20151,7 @@
         <v>34851.308241500003</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <f t="shared" si="30"/>
         <v>1888</v>
@@ -20151,7 +20161,7 @@
         <v>40792.354579000006</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <f t="shared" si="30"/>
         <v>1889</v>
@@ -20161,7 +20171,7 @@
         <v>46922.072096999997</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <f t="shared" si="30"/>
         <v>1890</v>
@@ -20171,7 +20181,7 @@
         <v>53636.190973500001</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <f t="shared" si="30"/>
         <v>1891</v>
@@ -20181,7 +20191,7 @@
         <v>59075.304975500003</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <f t="shared" si="30"/>
         <v>1892</v>
@@ -20191,7 +20201,7 @@
         <v>61231.720272500002</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <f t="shared" si="30"/>
         <v>1893</v>
@@ -20201,7 +20211,7 @@
         <v>60315.286844500006</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <f t="shared" si="30"/>
         <v>1894</v>
@@ -20211,7 +20221,7 @@
         <v>56433.215577499999</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <f t="shared" si="30"/>
         <v>1895</v>
@@ -20221,7 +20231,7 @@
         <v>48896.9332335</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <f t="shared" si="30"/>
         <v>1896</v>
@@ -20231,7 +20241,7 @@
         <v>42778.438797000003</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <f t="shared" si="30"/>
         <v>1897</v>
@@ -20241,7 +20251,7 @@
         <v>42735.35224</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <f t="shared" si="30"/>
         <v>1898</v>
@@ -20251,7 +20261,7 @@
         <v>47761.747051999999</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <f t="shared" si="30"/>
         <v>1899</v>
@@ -20261,7 +20271,7 @@
         <v>58433.622705499998</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <f t="shared" si="30"/>
         <v>1900</v>
@@ -20271,7 +20281,7 @@
         <v>77316.456703999997</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <f t="shared" si="30"/>
         <v>1901</v>
@@ -20281,7 +20291,7 @@
         <v>99885.385118999999</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <f t="shared" si="30"/>
         <v>1902</v>
@@ -20291,7 +20301,7 @@
         <v>120382.89023799999</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <f t="shared" si="30"/>
         <v>1903</v>
@@ -20301,7 +20311,7 @@
         <v>139600.365777</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <f t="shared" si="30"/>
         <v>1904</v>
@@ -20311,7 +20321,7 @@
         <v>157195.46720850002</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <f t="shared" si="30"/>
         <v>1905</v>
@@ -20321,7 +20331,7 @@
         <v>173091.990059</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <f t="shared" si="30"/>
         <v>1906</v>
@@ -20331,7 +20341,7 @@
         <v>186495.01287400001</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <f t="shared" si="30"/>
         <v>1907</v>
@@ -20341,7 +20351,7 @@
         <v>196593.37489400001</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <f t="shared" si="30"/>
         <v>1908</v>
@@ -20351,7 +20361,7 @@
         <v>203316.31396549998</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <f t="shared" si="30"/>
         <v>1909</v>
@@ -20361,7 +20371,7 @@
         <v>206582.88415100001</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <f t="shared" si="30"/>
         <v>1910</v>
@@ -20371,7 +20381,7 @@
         <v>205881.08261149999</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <f t="shared" si="30"/>
         <v>1911</v>
@@ -20381,7 +20391,7 @@
         <v>203624.59460300001</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <f t="shared" si="30"/>
         <v>1912</v>
@@ -20391,7 +20401,7 @@
         <v>202237.20285900001</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <f t="shared" si="30"/>
         <v>1913</v>
@@ -20401,7 +20411,7 @@
         <v>201258.66536550003</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <f t="shared" si="30"/>
         <v>1914</v>
@@ -20411,7 +20421,7 @@
         <v>200701.38769050001</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
         <v>122</v>
       </c>
@@ -20420,7 +20430,7 @@
         <v>269025.61749849998</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="28.8">
+    <row r="212" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A212" s="45" t="s">
         <v>198</v>
       </c>
@@ -20429,7 +20439,7 @@
         <v>53805.123499699999</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="41" t="s">
         <v>202</v>
       </c>
@@ -20439,7 +20449,7 @@
       <c r="E213" s="38"/>
       <c r="F213" s="38"/>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>1881</v>
       </c>
@@ -20448,7 +20458,7 @@
         <v>18.475000534206423</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <f>A214+1</f>
         <v>1882</v>
@@ -20458,7 +20468,7 @@
         <v>22.28474657634947</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <f t="shared" ref="A216:A228" si="32">A215+1</f>
         <v>1883</v>
@@ -20468,7 +20478,7 @@
         <v>27.466557787163893</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <f t="shared" si="32"/>
         <v>1884</v>
@@ -20478,7 +20488,7 @@
         <v>34.309298893446325</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <f t="shared" si="32"/>
         <v>1885</v>
@@ -20488,7 +20498,7 @@
         <v>43.534343842051776</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <f t="shared" si="32"/>
         <v>1886</v>
@@ -20498,7 +20508,7 @@
         <v>54.118486684938759</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <f t="shared" si="32"/>
         <v>1887</v>
@@ -20508,7 +20518,7 @@
         <v>64.77321484392526</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <f t="shared" si="32"/>
         <v>1888</v>
@@ -20518,7 +20528,7 @@
         <v>75.815000367441684</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <f t="shared" si="32"/>
         <v>1889</v>
@@ -20528,7 +20538,7 @@
         <v>87.207442423697103</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <f t="shared" si="32"/>
         <v>1890</v>
@@ -20538,7 +20548,7 @@
         <v>99.686028922132408</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <f t="shared" si="32"/>
         <v>1891</v>
@@ -20548,7 +20558,7 @@
         <v>109.79494355371079</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <f t="shared" si="32"/>
         <v>1892</v>
@@ -20558,7 +20568,7 @@
         <v>113.80276875090047</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <f t="shared" si="32"/>
         <v>1893</v>
@@ -20568,7 +20578,7 @@
         <v>112.09952309622764</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <f t="shared" si="32"/>
         <v>1894</v>
@@ -20578,7 +20588,7 @@
         <v>104.88446435368679</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <f t="shared" si="32"/>
         <v>1895</v>
@@ -20597,42 +20607,42 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D506FF2-5C72-4314-9474-BB1C48673607}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.68359375" customWidth="1"/>
-    <col min="3" max="3" width="18.83984375" customWidth="1"/>
-    <col min="4" max="4" width="13.83984375" customWidth="1"/>
-    <col min="5" max="5" width="16.83984375" customWidth="1"/>
-    <col min="7" max="7" width="13.26171875" customWidth="1"/>
-    <col min="8" max="8" width="16.41796875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>1</v>
       </c>
@@ -20640,7 +20650,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>1908</v>
       </c>
@@ -20648,7 +20658,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>1917</v>
       </c>
@@ -20656,7 +20666,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>1918</v>
       </c>
@@ -20664,7 +20674,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="51" t="s">
         <v>162</v>
       </c>
@@ -20678,7 +20688,7 @@
       </c>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>19</v>
       </c>
@@ -20704,7 +20714,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1896</v>
       </c>
@@ -20734,7 +20744,7 @@
         <v>0.76905150314611981</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f>A16+1</f>
         <v>1897</v>
@@ -20765,7 +20775,7 @@
         <v>1.1447260834014719</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" ref="A18:A36" si="3">A17+1</f>
         <v>1898</v>
@@ -20796,7 +20806,7 @@
         <v>3.4542314335060449E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -20827,7 +20837,7 @@
         <v>1.0711553175210407</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -20858,7 +20868,7 @@
         <v>2.3305537737866153</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -20889,7 +20899,7 @@
         <v>5.4061158328222199</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -20920,7 +20930,7 @@
         <v>7.1772055188530857</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -20951,7 +20961,7 @@
         <v>5.5701523909616393</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -20982,7 +20992,7 @@
         <v>7.0417936438833264</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -21013,7 +21023,7 @@
         <v>5.8077684314695697</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -21044,7 +21054,7 @@
         <v>5.8372604461200126</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -21075,7 +21085,7 @@
         <v>8.159514105330457</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -21106,7 +21116,7 @@
         <v>13.693419551160137</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -21137,7 +21147,7 @@
         <v>9.1432480191529386</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -21168,7 +21178,7 @@
         <v>11.441897961534032</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -21199,7 +21209,7 @@
         <v>13.023456612462224</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -21230,7 +21240,7 @@
         <v>13.15820198482195</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -21261,7 +21271,7 @@
         <v>9.6225471121240762</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -21292,7 +21302,7 @@
         <v>12.839879154078551</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -21323,7 +21333,7 @@
         <v>5.8097109177659272</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -21354,7 +21364,7 @@
         <v>5.6818181818181817</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>80</v>
       </c>
@@ -21401,15 +21411,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.83984375" customWidth="1"/>
-    <col min="11" max="11" width="13.578125" customWidth="1"/>
-    <col min="15" max="15" width="26.68359375" customWidth="1"/>
-    <col min="16" max="16" width="19.83984375" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
@@ -21454,7 +21464,7 @@
       </c>
       <c r="P1" s="10"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1896</v>
       </c>
@@ -21500,7 +21510,7 @@
       <c r="P2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1897</v>
       </c>
@@ -21546,7 +21556,7 @@
       <c r="P3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1898</v>
       </c>
@@ -21592,7 +21602,7 @@
       <c r="P4" s="4"/>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1899</v>
       </c>
@@ -21638,7 +21648,7 @@
       <c r="P5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -21684,7 +21694,7 @@
       <c r="P6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1901</v>
       </c>
@@ -21730,7 +21740,7 @@
       <c r="P7" s="4"/>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1902</v>
       </c>
@@ -21776,7 +21786,7 @@
       <c r="P8" s="4"/>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1903</v>
       </c>
@@ -21822,7 +21832,7 @@
       <c r="P9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1904</v>
       </c>
@@ -21868,7 +21878,7 @@
       <c r="P10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1905</v>
       </c>
@@ -21914,7 +21924,7 @@
       <c r="P11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1906</v>
       </c>
@@ -21960,7 +21970,7 @@
       <c r="P12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1907</v>
       </c>
@@ -22006,7 +22016,7 @@
       <c r="P13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1908</v>
       </c>
@@ -22052,7 +22062,7 @@
       <c r="P14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1909</v>
       </c>
@@ -22098,7 +22108,7 @@
       <c r="P15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1910</v>
       </c>
@@ -22144,7 +22154,7 @@
       <c r="P16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1911</v>
       </c>
@@ -22190,7 +22200,7 @@
       <c r="P17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1912</v>
       </c>
@@ -22236,7 +22246,7 @@
       <c r="P18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1913</v>
       </c>
@@ -22282,7 +22292,7 @@
       <c r="P19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1914</v>
       </c>
@@ -22328,7 +22338,7 @@
       <c r="P20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1915</v>
       </c>
@@ -22374,7 +22384,7 @@
       <c r="P21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1916</v>
       </c>
@@ -22420,15 +22430,15 @@
       <c r="P22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="R24" s="4"/>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="47" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>200</v>
       </c>
@@ -22436,17 +22446,17 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>19</v>
       </c>
@@ -22487,7 +22497,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>122</v>
       </c>
@@ -22541,7 +22551,7 @@
       </c>
       <c r="O31" s="4"/>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -22556,7 +22566,7 @@
       <c r="M32" s="4"/>
       <c r="O32" s="4"/>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>211</v>
       </c>
@@ -22574,7 +22584,7 @@
       <c r="M33" s="4"/>
       <c r="O33" s="4"/>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>19</v>
       </c>
@@ -22616,7 +22626,7 @@
       </c>
       <c r="O34" s="4"/>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>122</v>
       </c>
@@ -22669,7 +22679,7 @@
       </c>
       <c r="O35" s="4"/>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -22722,7 +22732,7 @@
         <v>9.9785050575341816E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -22737,7 +22747,7 @@
       <c r="M37" s="4"/>
       <c r="O37" s="4"/>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>116</v>
       </c>
@@ -22745,7 +22755,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
         <v>122</v>
       </c>
@@ -22754,7 +22764,7 @@
         <v>276141.28124371887</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>123</v>
       </c>
@@ -22763,7 +22773,7 @@
         <v>705906.12273697765</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -22772,7 +22782,7 @@
         <v>878080.04671502998</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>125</v>
       </c>
@@ -22789,12 +22799,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FEA9BB-FB24-45B6-A20A-F26B22290AE7}">
   <dimension ref="A1:W34"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="16" max="16" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
@@ -22851,7 +22861,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1881</v>
       </c>
@@ -22922,7 +22932,7 @@
       </c>
       <c r="W2" s="4"/>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1882</v>
       </c>
@@ -22992,7 +23002,7 @@
       </c>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1883</v>
       </c>
@@ -23062,7 +23072,7 @@
       </c>
       <c r="W4" s="4"/>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1884</v>
       </c>
@@ -23132,7 +23142,7 @@
       </c>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1885</v>
       </c>
@@ -23202,7 +23212,7 @@
       </c>
       <c r="W6" s="4"/>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1886</v>
       </c>
@@ -23272,7 +23282,7 @@
       </c>
       <c r="W7" s="4"/>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1887</v>
       </c>
@@ -23342,7 +23352,7 @@
       </c>
       <c r="W8" s="4"/>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1888</v>
       </c>
@@ -23412,7 +23422,7 @@
       </c>
       <c r="W9" s="4"/>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1889</v>
       </c>
@@ -23482,7 +23492,7 @@
       </c>
       <c r="W10" s="4"/>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1890</v>
       </c>
@@ -23552,7 +23562,7 @@
       </c>
       <c r="W11" s="4"/>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1891</v>
       </c>
@@ -23622,7 +23632,7 @@
       </c>
       <c r="W12" s="4"/>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>1892</v>
       </c>
@@ -23692,7 +23702,7 @@
       </c>
       <c r="W13" s="4"/>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>1893</v>
       </c>
@@ -23762,7 +23772,7 @@
       </c>
       <c r="W14" s="4"/>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>1894</v>
       </c>
@@ -23832,7 +23842,7 @@
       </c>
       <c r="W15" s="4"/>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1895</v>
       </c>
@@ -23902,25 +23912,25 @@
       </c>
       <c r="W16" s="4"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>184</v>
       </c>
@@ -23973,12 +23983,12 @@
         <v>521.73352750660274</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C26" s="10" t="s">
         <v>70</v>
       </c>
@@ -24016,7 +24026,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>122</v>
       </c>
@@ -24057,7 +24067,7 @@
         <v>49.260590808123176</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>212</v>
       </c>
@@ -24075,7 +24085,7 @@
       <c r="N29" s="4"/>
       <c r="P29" s="4"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>116</v>
       </c>
@@ -24083,7 +24093,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>119</v>
       </c>
@@ -24092,7 +24102,7 @@
         <v>33681.078162898077</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>120</v>
       </c>
@@ -24101,7 +24111,7 @@
         <v>188383.42896059956</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>121</v>
       </c>
